--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S173"/>
+  <dimension ref="A1:S178"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -466,19 +466,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>阴影色NS12</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B2" t="str">
         <v>妹妹</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1788534744815-pzs6jqs2pm.jpg</v>
+        <v>assets/1789654858942-ws3mqfv0zf.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>否</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -525,19 +525,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B3" t="str">
         <v>弟弟</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1788534522775-my4ggv0pwo.jpg</v>
+        <v>assets/1789654723483-fyl8c7wdqg.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>否</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -584,13 +584,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>红虎斑</v>
+        <v>银虎班补丁</v>
       </c>
       <c r="B4" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1788442386268-ilpasqz91m.jpg</v>
+        <v>assets/1789654675792-6d4kyyncmf.jpg</v>
       </c>
       <c r="D4" t="str">
         <v>否</v>
@@ -643,19 +643,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>浅银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B5" t="str">
         <v>弟弟</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1788442356842-bbleakpy85.jpg</v>
+        <v>assets/1789654628929-2wok5d7b71.jpg</v>
       </c>
       <c r="D5" t="str">
         <v>否</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -702,19 +702,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B6" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1788442221802-et3crh0tww.jpg</v>
+        <v>assets/1789654549268-68uab4pdoy.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>否</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -761,22 +761,22 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>凯米尔</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B7" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1788014088852-oqkg79cki9.jpg</v>
+        <v>assets/1788534744815-pzs6jqs2pm.jpg</v>
       </c>
       <c r="D7" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-06-26</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F7" t="str">
-        <v>湖北襄阳</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -823,16 +823,16 @@
         <v>棕虎斑</v>
       </c>
       <c r="B8" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1788014050978-9a2sguuo1u.jpg</v>
+        <v>assets/1788534522775-my4ggv0pwo.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>否</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -879,22 +879,22 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B9" t="str">
         <v>弟弟</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1788013924404-gmlh0hfjae.jpg</v>
+        <v>assets/1788442386268-ilpasqz91m.jpg</v>
       </c>
       <c r="D9" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F9" t="str">
-        <v>浙江嘉兴</v>
+        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -938,22 +938,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>凯米尔色</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B10" t="str">
         <v>弟弟</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1788013889955-wpykaycfde.jpg</v>
+        <v>assets/1788442356842-bbleakpy85.jpg</v>
       </c>
       <c r="D10" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F10" t="str">
-        <v>湖北襄阳</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -997,19 +997,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B11" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1788013810551-b90h1mwfiq.jpg</v>
+        <v>assets/1788442221802-et3crh0tww.jpg</v>
       </c>
       <c r="D11" t="str">
         <v>否</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-06-26</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1056,22 +1056,22 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B12" t="str">
         <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1787837910484-r7urrsuib0.jpg</v>
+        <v>assets/1788014088852-oqkg79cki9.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>是</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F12" t="str">
-        <v>香港</v>
+        <v>湖北襄阳</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1115,19 +1115,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B13" t="str">
         <v>妹妹</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1787837846581-6q9nxgad35.jpg</v>
+        <v>assets/1788014050978-9a2sguuo1u.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>否</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -1174,22 +1174,22 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>凯米尔</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B14" t="str">
         <v>弟弟</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1787837779354-hkuyvt39iz.jpg</v>
+        <v>assets/1788013924404-gmlh0hfjae.jpg</v>
       </c>
       <c r="D14" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>浙江嘉兴</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1233,22 +1233,22 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B15" t="str">
         <v>弟弟</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
+        <v>assets/1788013889955-wpykaycfde.jpg</v>
       </c>
       <c r="D15" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>湖北襄阳</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1292,22 +1292,22 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B16" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1787837648423-9riberz3tq.jpg</v>
+        <v>assets/1788013810551-b90h1mwfiq.jpg</v>
       </c>
       <c r="D16" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F16" t="str">
-        <v>北京</v>
+        <v/>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1351,22 +1351,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B17" t="str">
         <v>弟弟</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
+        <v>assets/1787837910484-r7urrsuib0.jpg</v>
       </c>
       <c r="D17" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-06-10</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>香港</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1410,13 +1410,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B18" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1787479268842-7en9nzy302.jpg</v>
+        <v>assets/1787837846581-6q9nxgad35.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>否</v>
@@ -1437,7 +1437,7 @@
         <v/>
       </c>
       <c r="J18" t="str">
-        <v>2026-06-10</v>
+        <v/>
       </c>
       <c r="K18" t="str">
         <v/>
@@ -1469,19 +1469,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>纯黑色</v>
+        <v>凯米尔</v>
       </c>
       <c r="B19" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1787479242639-32zuh5lham.jpg</v>
+        <v>assets/1787837779354-hkuyvt39iz.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>否</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -1528,22 +1528,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B20" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1787466121255-21jto2cugv.jpg</v>
+        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
       </c>
       <c r="D20" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F20" t="str">
-        <v>四川广安</v>
+        <v/>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B21" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
+        <v>assets/1787837648423-9riberz3tq.jpg</v>
       </c>
       <c r="D21" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E21" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1649,16 +1649,16 @@
         <v>棕虎斑</v>
       </c>
       <c r="B22" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1787388277490-e6u506cx0r.jpg</v>
+        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>否</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -1705,22 +1705,22 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B23" t="str">
         <v>弟弟</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1787328436957-x30od0gw28.jpg</v>
+        <v>assets/1787479268842-7en9nzy302.jpg</v>
       </c>
       <c r="D23" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E23" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F23" t="str">
-        <v>江苏苏州</v>
+        <v/>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1732,7 +1732,7 @@
         <v/>
       </c>
       <c r="J23" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="K23" t="str">
         <v/>
@@ -1764,22 +1764,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>蓝虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B24" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
+        <v>assets/1787479242639-32zuh5lham.jpg</v>
       </c>
       <c r="D24" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E24" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F24" t="str">
-        <v>辽宁东港</v>
+        <v/>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1826,10 +1826,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B25" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1787327967245-m62ohievcl.jpg</v>
+        <v>assets/1787466121255-21jto2cugv.jpg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
@@ -1838,7 +1838,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>福建福州</v>
+        <v>四川广安</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1882,22 +1882,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B26" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
+        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
       </c>
       <c r="D26" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E26" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F26" t="str">
-        <v>上海</v>
+        <v/>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1941,22 +1941,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>纯蓝色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B27" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1787327793837-znk2knoo6p.jpg</v>
+        <v>assets/1787388277490-e6u506cx0r.jpg</v>
       </c>
       <c r="D27" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E27" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F27" t="str">
-        <v>河南鹤壁</v>
+        <v/>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -2006,7 +2006,7 @@
         <v>弟弟</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1787327752832-kkpmp21os3.jpg</v>
+        <v>assets/1787328436957-x30od0gw28.jpg</v>
       </c>
       <c r="D28" t="str">
         <v>是</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>陕西西安</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B29" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
+        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>是</v>
@@ -2074,7 +2074,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>陕西西安</v>
+        <v>辽宁东港</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2118,13 +2118,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B30" t="str">
         <v>弟弟</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1787327573762-h23cux94p2.jpg</v>
+        <v>assets/1787327967245-m62ohievcl.jpg</v>
       </c>
       <c r="D30" t="str">
         <v>是</v>
@@ -2133,7 +2133,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>北京</v>
+        <v>福建福州</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2177,13 +2177,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B31" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1787327496557-9daggljg4g.jpg</v>
+        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
@@ -2192,7 +2192,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>黑龙江哈尔滨</v>
+        <v>上海</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2236,13 +2236,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>烟灰色</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B32" t="str">
         <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
+        <v>assets/1787327793837-znk2knoo6p.jpg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
@@ -2251,7 +2251,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>甘肃嘉峪关</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2295,13 +2295,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B33" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
+        <v>assets/1787327752832-kkpmp21os3.jpg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
@@ -2310,7 +2310,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>安徽合肥</v>
+        <v>陕西西安</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2357,10 +2357,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B34" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1787327337811-u5u2pdew3.jpg</v>
+        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
@@ -2369,7 +2369,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>安徽合肥</v>
+        <v>陕西西安</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2413,13 +2413,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B35" t="str">
         <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1787327309143-6c1dan1sev.jpg</v>
+        <v>assets/1787327573762-h23cux94p2.jpg</v>
       </c>
       <c r="D35" t="str">
         <v>是</v>
@@ -2428,7 +2428,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>四川成都</v>
+        <v>北京</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2475,10 +2475,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B36" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1787327277453-w89ujg69fm.jpg</v>
+        <v>assets/1787327496557-9daggljg4g.jpg</v>
       </c>
       <c r="D36" t="str">
         <v>是</v>
@@ -2487,7 +2487,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>四川成都</v>
+        <v>黑龙江哈尔滨</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>蓝银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B37" t="str">
         <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1787327232159-lkrcl588a5.jpg</v>
+        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
@@ -2546,7 +2546,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>四川成都</v>
+        <v>甘肃嘉峪关</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2590,13 +2590,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>玳瑁色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B38" t="str">
         <v>妹妹</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1787327182347-3az0z7sys2.jpg</v>
+        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>四川内江</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B39" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
+        <v>assets/1787327337811-u5u2pdew3.jpg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2664,7 +2664,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>贵州贵阳</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2708,13 +2708,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>黑烟色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B40" t="str">
         <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1787327101790-tqjlseog5y.jpg</v>
+        <v>assets/1787327309143-6c1dan1sev.jpg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2723,7 +2723,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>浙江杭州</v>
+        <v>四川成都</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2767,13 +2767,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B41" t="str">
         <v>弟弟</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1787327019632-l1780lu2hj.jpg</v>
+        <v>assets/1787327277453-w89ujg69fm.jpg</v>
       </c>
       <c r="D41" t="str">
         <v>是</v>
@@ -2782,7 +2782,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>山东威海</v>
+        <v>四川成都</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2826,13 +2826,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>棕虎补丁</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B42" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1787326905275-plz3fpgo97.jpg</v>
+        <v>assets/1787327232159-lkrcl588a5.jpg</v>
       </c>
       <c r="D42" t="str">
         <v>是</v>
@@ -2841,7 +2841,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>浙江杭州</v>
+        <v>四川成都</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2885,13 +2885,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>蓝虎斑</v>
+        <v>玳瑁色</v>
       </c>
       <c r="B43" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
+        <v>assets/1787327182347-3az0z7sys2.jpg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
@@ -2900,7 +2900,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>四川成都</v>
+        <v>四川内江</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B44" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
+        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>四川成都</v>
+        <v>贵州贵阳</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3003,13 +3003,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>凯米尔</v>
+        <v>黑烟色</v>
       </c>
       <c r="B45" t="str">
         <v>弟弟</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1787326814713-p5oavnlulg.jpg</v>
+        <v>assets/1787327101790-tqjlseog5y.jpg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
@@ -3018,7 +3018,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B46" t="str">
         <v>弟弟</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1787326773577-13q5out2d0.jpg</v>
+        <v>assets/1787327019632-l1780lu2hj.jpg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>四川宜宾</v>
+        <v>山东威海</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3121,13 +3121,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>金棕虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B47" t="str">
         <v>妹妹</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1787326548993-89s929m2hg.jpg</v>
+        <v>assets/1787326905275-plz3fpgo97.jpg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>上海</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3180,13 +3180,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>凯米尔色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B48" t="str">
         <v>弟弟</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1787326449218-09s9ucram4.jpg</v>
+        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>德国</v>
+        <v>四川成都</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>棕虎补丁</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B49" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1787326277374-8ti107m5ki.jpg</v>
+        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -3254,7 +3254,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>广东深圳</v>
+        <v>四川成都</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -3298,13 +3298,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔</v>
       </c>
       <c r="B50" t="str">
         <v>弟弟</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1787326236952-2pmwche4t3.jpg</v>
+        <v>assets/1787326814713-p5oavnlulg.jpg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
@@ -3313,7 +3313,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>福建泉州</v>
+        <v>四川成都</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3357,13 +3357,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B51" t="str">
         <v>弟弟</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1787326184557-90v6clkwen.jpg</v>
+        <v>assets/1787326773577-13q5out2d0.jpg</v>
       </c>
       <c r="D51" t="str">
         <v>是</v>
@@ -3372,7 +3372,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>福建福州</v>
+        <v>四川宜宾</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,13 +3416,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>棕虎斑</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B52" t="str">
         <v>妹妹</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
+        <v>assets/1787326548993-89s929m2hg.jpg</v>
       </c>
       <c r="D52" t="str">
         <v>是</v>
@@ -3431,7 +3431,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>广西贵港</v>
+        <v>上海</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3481,7 +3481,7 @@
         <v>弟弟</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1787325862706-wq18k3ej56.jpg</v>
+        <v>assets/1787326449218-09s9ucram4.jpg</v>
       </c>
       <c r="D53" t="str">
         <v>是</v>
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>江苏苏州</v>
+        <v>德国</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3534,13 +3534,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B54" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
+        <v>assets/1787326277374-8ti107m5ki.jpg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
@@ -3549,7 +3549,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>江苏苏州</v>
+        <v>广东深圳</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3593,13 +3593,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B55" t="str">
         <v>弟弟</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1787325706797-kgk81ghccy.jpg</v>
+        <v>assets/1787326236952-2pmwche4t3.jpg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
@@ -3608,7 +3608,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>北京</v>
+        <v>福建泉州</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B56" t="str">
         <v>弟弟</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
+        <v>assets/1787326184557-90v6clkwen.jpg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
@@ -3667,7 +3667,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>上海</v>
+        <v>福建福州</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3717,7 +3717,7 @@
         <v>妹妹</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1787325554341-608thexrne.jpg</v>
+        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
       </c>
       <c r="D57" t="str">
         <v>是</v>
@@ -3726,7 +3726,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>江苏苏州</v>
+        <v>广西贵港</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3770,13 +3770,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>浅色银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B58" t="str">
         <v>弟弟</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1787325480828-q90pskoiw3.jpg</v>
+        <v>assets/1787325862706-wq18k3ej56.jpg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
@@ -3785,7 +3785,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>四川成都</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>浅色银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B59" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1787325448999-a2pg8176fu.jpg</v>
+        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
       </c>
       <c r="D59" t="str">
         <v>是</v>
@@ -3844,7 +3844,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>中国台湾</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3888,13 +3888,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B60" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
+        <v>assets/1787325706797-kgk81ghccy.jpg</v>
       </c>
       <c r="D60" t="str">
         <v>是</v>
@@ -3903,7 +3903,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>浙江杭州</v>
+        <v>北京</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3947,13 +3947,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B61" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1787325237876-t19isaq5gu.jpg</v>
+        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
       </c>
       <c r="D61" t="str">
         <v>是</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>辽宁沈阳</v>
+        <v>上海</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4006,13 +4006,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>金棕虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B62" t="str">
         <v>妹妹</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1787325199931-e7wms9qtya.jpg</v>
+        <v>assets/1787325554341-608thexrne.jpg</v>
       </c>
       <c r="D62" t="str">
         <v>是</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>四川成都</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4065,13 +4065,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>蓝虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B63" t="str">
         <v>弟弟</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
+        <v>assets/1787325480828-q90pskoiw3.jpg</v>
       </c>
       <c r="D63" t="str">
         <v>是</v>
@@ -4080,7 +4080,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>中国香港</v>
+        <v>四川成都</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -4124,13 +4124,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>烟灰色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B64" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C64" t="str">
-        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
+        <v>assets/1787325448999-a2pg8176fu.jpg</v>
       </c>
       <c r="D64" t="str">
         <v>是</v>
@@ -4139,7 +4139,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>中国澳门</v>
+        <v>中国台湾</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -4183,13 +4183,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B65" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C65" t="str">
-        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
+        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
       </c>
       <c r="D65" t="str">
         <v>是</v>
@@ -4198,7 +4198,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>山东青岛</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -4245,10 +4245,10 @@
         <v>烟灰色</v>
       </c>
       <c r="B66" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C66" t="str">
-        <v>assets/1787324954998-w5m5jox439.jpg</v>
+        <v>assets/1787325237876-t19isaq5gu.jpg</v>
       </c>
       <c r="D66" t="str">
         <v>是</v>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>海南海口</v>
+        <v>辽宁沈阳</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -4301,13 +4301,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>棕虎斑</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B67" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C67" t="str">
-        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
+        <v>assets/1787325199931-e7wms9qtya.jpg</v>
       </c>
       <c r="D67" t="str">
         <v>是</v>
@@ -4316,7 +4316,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>内蒙古</v>
+        <v>四川成都</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4360,13 +4360,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B68" t="str">
         <v>弟弟</v>
       </c>
       <c r="C68" t="str">
-        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
+        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
       </c>
       <c r="D68" t="str">
         <v>是</v>
@@ -4425,7 +4425,7 @@
         <v>弟弟</v>
       </c>
       <c r="C69" t="str">
-        <v>assets/1787324806613-31yyz14tsf.jpg</v>
+        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
       </c>
       <c r="D69" t="str">
         <v>是</v>
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>四川成都</v>
+        <v>中国澳门</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4478,13 +4478,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B70" t="str">
         <v>弟弟</v>
       </c>
       <c r="C70" t="str">
-        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
+        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
       </c>
       <c r="D70" t="str">
         <v>是</v>
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>湖北武汉</v>
+        <v>山东青岛</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -4543,7 +4543,7 @@
         <v>弟弟</v>
       </c>
       <c r="C71" t="str">
-        <v>assets/1787324522658-smn44crast.jpg</v>
+        <v>assets/1787324954998-w5m5jox439.jpg</v>
       </c>
       <c r="D71" t="str">
         <v>是</v>
@@ -4552,7 +4552,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>湖北武汉</v>
+        <v>海南海口</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -4602,7 +4602,7 @@
         <v>弟弟</v>
       </c>
       <c r="C72" t="str">
-        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
+        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
       </c>
       <c r="D72" t="str">
         <v>是</v>
@@ -4611,7 +4611,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>新疆</v>
+        <v>内蒙古</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -4655,13 +4655,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>浅凯米尔</v>
+        <v>烟灰色</v>
       </c>
       <c r="B73" t="str">
         <v>弟弟</v>
       </c>
       <c r="C73" t="str">
-        <v>assets/1787324331029-d74lcuycf6.jpg</v>
+        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
       </c>
       <c r="D73" t="str">
         <v>是</v>
@@ -4670,7 +4670,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>四川成都</v>
+        <v>中国香港</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4714,13 +4714,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B74" t="str">
         <v>弟弟</v>
       </c>
       <c r="C74" t="str">
-        <v>assets/1787324297469-ans1lse2l5.jpg</v>
+        <v>assets/1787324806613-31yyz14tsf.jpg</v>
       </c>
       <c r="D74" t="str">
         <v>是</v>
@@ -4729,7 +4729,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>四川乐山</v>
+        <v>四川成都</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4779,7 +4779,7 @@
         <v>弟弟</v>
       </c>
       <c r="C75" t="str">
-        <v>assets/1787324256827-7w383z4bg1.jpg</v>
+        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
       </c>
       <c r="D75" t="str">
         <v>是</v>
@@ -4788,7 +4788,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>中国台湾</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -4832,13 +4832,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B76" t="str">
         <v>弟弟</v>
       </c>
       <c r="C76" t="str">
-        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
+        <v>assets/1787324522658-smn44crast.jpg</v>
       </c>
       <c r="D76" t="str">
         <v>是</v>
@@ -4847,7 +4847,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>四川成都</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4891,13 +4891,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B77" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C77" t="str">
-        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
+        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
       </c>
       <c r="D77" t="str">
         <v>是</v>
@@ -4906,7 +4906,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>江苏南京</v>
+        <v>新疆</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4950,13 +4950,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>棕虎斑</v>
+        <v>浅凯米尔</v>
       </c>
       <c r="B78" t="str">
         <v>弟弟</v>
       </c>
       <c r="C78" t="str">
-        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
+        <v>assets/1787324331029-d74lcuycf6.jpg</v>
       </c>
       <c r="D78" t="str">
         <v>是</v>
@@ -4965,7 +4965,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>江苏南京</v>
+        <v>四川成都</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -5009,13 +5009,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B79" t="str">
         <v>弟弟</v>
       </c>
       <c r="C79" t="str">
-        <v>assets/1787323318612-soge38hpsf.jpg</v>
+        <v>assets/1787324297469-ans1lse2l5.jpg</v>
       </c>
       <c r="D79" t="str">
         <v>是</v>
@@ -5024,7 +5024,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>上海</v>
+        <v>四川乐山</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -5068,13 +5068,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B80" t="str">
         <v>弟弟</v>
       </c>
       <c r="C80" t="str">
-        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
+        <v>assets/1787324256827-7w383z4bg1.jpg</v>
       </c>
       <c r="D80" t="str">
         <v>是</v>
@@ -5083,7 +5083,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>四川成都</v>
+        <v>中国台湾</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -5130,10 +5130,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B81" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C81" t="str">
-        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
+        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
       </c>
       <c r="D81" t="str">
         <v>是</v>
@@ -5142,7 +5142,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>浙江宁波</v>
+        <v>四川成都</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -5186,13 +5186,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>银虎斑补丁</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B82" t="str">
         <v>妹妹</v>
       </c>
       <c r="C82" t="str">
-        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
+        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
       </c>
       <c r="D82" t="str">
         <v>是</v>
@@ -5201,7 +5201,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>马来西亚</v>
+        <v>江苏南京</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -5245,13 +5245,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B83" t="str">
         <v>弟弟</v>
       </c>
       <c r="C83" t="str">
-        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
+        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
       </c>
       <c r="D83" t="str">
         <v>是</v>
@@ -5260,7 +5260,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>陕西西安</v>
+        <v>江苏南京</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -5304,13 +5304,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B84" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C84" t="str">
-        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
+        <v>assets/1787323318612-soge38hpsf.jpg</v>
       </c>
       <c r="D84" t="str">
         <v>是</v>
@@ -5319,7 +5319,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>广西南宁</v>
+        <v>上海</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -5369,7 +5369,7 @@
         <v>弟弟</v>
       </c>
       <c r="C85" t="str">
-        <v>assets/1787322760950-gn3qgego4s.jpg</v>
+        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
       </c>
       <c r="D85" t="str">
         <v>是</v>
@@ -5378,7 +5378,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>广西南宁</v>
+        <v>四川成都</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -5422,13 +5422,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B86" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C86" t="str">
-        <v>assets/1787322605982-04n50xegt2.jpg</v>
+        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
       </c>
       <c r="D86" t="str">
         <v>是</v>
@@ -5437,7 +5437,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>上海</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -5481,13 +5481,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B87" t="str">
         <v>妹妹</v>
       </c>
       <c r="C87" t="str">
-        <v>assets/1787322490045-kog3ru43dy.jpg</v>
+        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
       </c>
       <c r="D87" t="str">
         <v>是</v>
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>上海</v>
+        <v>马来西亚</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -5540,13 +5540,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B88" t="str">
         <v>弟弟</v>
       </c>
       <c r="C88" t="str">
-        <v>assets/1787322419996-0m33yx89nm.jpg</v>
+        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
       </c>
       <c r="D88" t="str">
         <v>是</v>
@@ -5555,7 +5555,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>广东广州</v>
+        <v>陕西西安</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -5599,13 +5599,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>浅色银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B89" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C89" t="str">
-        <v>assets/1787322377730-vj5csj2mll.jpg</v>
+        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
       </c>
       <c r="D89" t="str">
         <v>是</v>
@@ -5614,7 +5614,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>柬埔寨</v>
+        <v>广西南宁</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -5658,13 +5658,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B90" t="str">
         <v>弟弟</v>
       </c>
       <c r="C90" t="str">
-        <v>assets/1787322269611-53yaj5ideu.jpg</v>
+        <v>assets/1787322760950-gn3qgego4s.jpg</v>
       </c>
       <c r="D90" t="str">
         <v>是</v>
@@ -5673,7 +5673,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>山东枣庄</v>
+        <v>广西南宁</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -5717,13 +5717,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B91" t="str">
         <v>弟弟</v>
       </c>
       <c r="C91" t="str">
-        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
+        <v>assets/1787322605982-04n50xegt2.jpg</v>
       </c>
       <c r="D91" t="str">
         <v>是</v>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>陕西西安</v>
+        <v>上海</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -5776,13 +5776,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B92" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C92" t="str">
-        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
+        <v>assets/1787322490045-kog3ru43dy.jpg</v>
       </c>
       <c r="D92" t="str">
         <v>是</v>
@@ -5791,7 +5791,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>山东东营</v>
+        <v>上海</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -5835,13 +5835,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>凯米尔色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B93" t="str">
         <v>弟弟</v>
       </c>
       <c r="C93" t="str">
-        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
+        <v>assets/1787322419996-0m33yx89nm.jpg</v>
       </c>
       <c r="D93" t="str">
         <v>是</v>
@@ -5850,7 +5850,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>中国台湾</v>
+        <v>广东广州</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -5894,13 +5894,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>烟灰色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B94" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C94" t="str">
-        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
+        <v>assets/1787322377730-vj5csj2mll.jpg</v>
       </c>
       <c r="D94" t="str">
         <v>是</v>
@@ -5909,7 +5909,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>中国台湾</v>
+        <v>柬埔寨</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -5953,13 +5953,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B95" t="str">
         <v>弟弟</v>
       </c>
       <c r="C95" t="str">
-        <v>assets/1787321834306-efgnyhujon.jpg</v>
+        <v>assets/1787322269611-53yaj5ideu.jpg</v>
       </c>
       <c r="D95" t="str">
         <v>是</v>
@@ -5968,7 +5968,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>北京</v>
+        <v>山东枣庄</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -6018,7 +6018,7 @@
         <v>弟弟</v>
       </c>
       <c r="C96" t="str">
-        <v>assets/1787321439916-uttgpbkogb.jpg</v>
+        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
       </c>
       <c r="D96" t="str">
         <v>是</v>
@@ -6027,7 +6027,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>安徽合肥</v>
+        <v>陕西西安</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -6077,7 +6077,7 @@
         <v>弟弟</v>
       </c>
       <c r="C97" t="str">
-        <v>assets/1787321419210-51hhgurygq.jpg</v>
+        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
       </c>
       <c r="D97" t="str">
         <v>是</v>
@@ -6086,7 +6086,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>上海</v>
+        <v>山东东营</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -6133,10 +6133,10 @@
         <v>凯米尔色</v>
       </c>
       <c r="B98" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C98" t="str">
-        <v>assets/1787321363369-bzjn51j5il.jpg</v>
+        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
       </c>
       <c r="D98" t="str">
         <v>是</v>
@@ -6189,13 +6189,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B99" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C99" t="str">
-        <v>assets/1787321332559-87p6spuch3.jpg</v>
+        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
       </c>
       <c r="D99" t="str">
         <v>是</v>
@@ -6248,13 +6248,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B100" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C100" t="str">
-        <v>assets/1787321232531-59lnzv8y98.jpg</v>
+        <v>assets/1787321834306-efgnyhujon.jpg</v>
       </c>
       <c r="D100" t="str">
         <v>是</v>
@@ -6310,10 +6310,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B101" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C101" t="str">
-        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
+        <v>assets/1787321439916-uttgpbkogb.jpg</v>
       </c>
       <c r="D101" t="str">
         <v>是</v>
@@ -6322,7 +6322,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>浙江宁波</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -6369,10 +6369,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B102" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C102" t="str">
-        <v>assets/1787319800704-v3qeu062ak.jpg</v>
+        <v>assets/1787321419210-51hhgurygq.jpg</v>
       </c>
       <c r="D102" t="str">
         <v>是</v>
@@ -6381,7 +6381,7 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>河北唐山</v>
+        <v>上海</v>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -6425,13 +6425,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B103" t="str">
         <v>妹妹</v>
       </c>
       <c r="C103" t="str">
-        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
+        <v>assets/1787321363369-bzjn51j5il.jpg</v>
       </c>
       <c r="D103" t="str">
         <v>是</v>
@@ -6440,7 +6440,7 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>河北石家庄</v>
+        <v>中国台湾</v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -6484,13 +6484,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>棕虎补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B104" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C104" t="str">
-        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
+        <v>assets/1787321332559-87p6spuch3.jpg</v>
       </c>
       <c r="D104" t="str">
         <v>是</v>
@@ -6499,7 +6499,7 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>韩国</v>
+        <v>中国台湾</v>
       </c>
       <c r="G104" t="str">
         <v/>
@@ -6543,13 +6543,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>蓝银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B105" t="str">
         <v>妹妹</v>
       </c>
       <c r="C105" t="str">
-        <v>assets/1787319501376-xscwljnu1j.jpg</v>
+        <v>assets/1787321232531-59lnzv8y98.jpg</v>
       </c>
       <c r="D105" t="str">
         <v>是</v>
@@ -6558,7 +6558,7 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>美国</v>
+        <v>北京</v>
       </c>
       <c r="G105" t="str">
         <v/>
@@ -6602,13 +6602,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B106" t="str">
         <v>妹妹</v>
       </c>
       <c r="C106" t="str">
-        <v>assets/1787319443529-4a0zqikufx.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D106" t="str">
         <v>是</v>
@@ -6617,7 +6617,7 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>中国台湾</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G106" t="str">
         <v/>
@@ -6661,13 +6661,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B107" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C107" t="str">
-        <v>assets/1787319356194-lr2d5680i9.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D107" t="str">
         <v>是</v>
@@ -6676,7 +6676,7 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>中国台湾</v>
+        <v>河北唐山</v>
       </c>
       <c r="G107" t="str">
         <v/>
@@ -6720,13 +6720,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B108" t="str">
         <v>妹妹</v>
       </c>
       <c r="C108" t="str">
-        <v>assets/1787319208828-aizqo4blcv.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D108" t="str">
         <v>是</v>
@@ -6735,7 +6735,7 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>山东淄博</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G108" t="str">
         <v/>
@@ -6779,13 +6779,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B109" t="str">
         <v>妹妹</v>
       </c>
       <c r="C109" t="str">
-        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D109" t="str">
         <v>是</v>
@@ -6838,13 +6838,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>棕虎补丁</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B110" t="str">
         <v>妹妹</v>
       </c>
       <c r="C110" t="str">
-        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D110" t="str">
         <v>是</v>
@@ -6853,7 +6853,7 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>四川成都</v>
+        <v>美国</v>
       </c>
       <c r="G110" t="str">
         <v/>
@@ -6897,13 +6897,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B111" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C111" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D111" t="str">
         <v>是</v>
@@ -6912,7 +6912,7 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>广东广州</v>
+        <v>中国台湾</v>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -6956,13 +6956,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B112" t="str">
         <v>弟弟</v>
       </c>
       <c r="C112" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D112" t="str">
         <v>是</v>
@@ -6971,7 +6971,7 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>中国台湾</v>
       </c>
       <c r="G112" t="str">
         <v/>
@@ -7015,13 +7015,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B113" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C113" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D113" t="str">
         <v>是</v>
@@ -7030,7 +7030,7 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>天津</v>
+        <v>山东淄博</v>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -7077,10 +7077,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B114" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C114" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D114" t="str">
         <v>是</v>
@@ -7089,7 +7089,7 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>山西朔州</v>
+        <v>韩国</v>
       </c>
       <c r="G114" t="str">
         <v/>
@@ -7119,7 +7119,7 @@
         <v/>
       </c>
       <c r="P114" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q114" t="str">
         <v/>
@@ -7133,13 +7133,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B115" t="str">
         <v>妹妹</v>
       </c>
       <c r="C115" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D115" t="str">
         <v>是</v>
@@ -7148,7 +7148,7 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>贵州</v>
+        <v>四川成都</v>
       </c>
       <c r="G115" t="str">
         <v/>
@@ -7192,22 +7192,22 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B116" t="str">
         <v>弟弟</v>
       </c>
       <c r="C116" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D116" t="str">
         <v>是</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F116" t="str">
-        <v>北京</v>
+        <v>广东广州</v>
       </c>
       <c r="G116" t="str">
         <v/>
@@ -7246,27 +7246,27 @@
         <v/>
       </c>
       <c r="S116" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B117" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C117" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D117" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-02-20</v>
+        <v/>
       </c>
       <c r="F117" t="str">
-        <v/>
+        <v>黑龙江鹤岗</v>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -7305,27 +7305,27 @@
         <v/>
       </c>
       <c r="S117" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>阴影色NS12</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B118" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C118" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D118" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-05-28</v>
+        <v/>
       </c>
       <c r="F118" t="str">
-        <v/>
+        <v>天津</v>
       </c>
       <c r="G118" t="str">
         <v/>
@@ -7364,27 +7364,27 @@
         <v/>
       </c>
       <c r="S118" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>阴影色NS11</v>
+        <v>银虎斑</v>
       </c>
       <c r="B119" t="str">
         <v>弟弟</v>
       </c>
       <c r="C119" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D119" t="str">
         <v>是</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-06-15</v>
+        <v/>
       </c>
       <c r="F119" t="str">
-        <v>重庆</v>
+        <v>山西朔州</v>
       </c>
       <c r="G119" t="str">
         <v/>
@@ -7414,7 +7414,7 @@
         <v/>
       </c>
       <c r="P119" t="str">
-        <v/>
+        <v>已接猫</v>
       </c>
       <c r="Q119" t="str">
         <v/>
@@ -7423,27 +7423,27 @@
         <v/>
       </c>
       <c r="S119" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>浅烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B120" t="str">
         <v>妹妹</v>
       </c>
       <c r="C120" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D120" t="str">
         <v>是</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-03-21</v>
+        <v/>
       </c>
       <c r="F120" t="str">
-        <v>中国澳门</v>
+        <v>贵州</v>
       </c>
       <c r="G120" t="str">
         <v/>
@@ -7482,7 +7482,7 @@
         <v/>
       </c>
       <c r="S120" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="121">
@@ -7490,19 +7490,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B121" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C121" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D121" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E121" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F121" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G121" t="str">
         <v/>
@@ -7546,19 +7546,19 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B122" t="str">
         <v>妹妹</v>
       </c>
       <c r="C122" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D122" t="str">
         <v>否</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-06-06</v>
+        <v>2026-02-20</v>
       </c>
       <c r="F122" t="str">
         <v/>
@@ -7605,19 +7605,19 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B123" t="str">
         <v>妹妹</v>
       </c>
       <c r="C123" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D123" t="str">
         <v>否</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F123" t="str">
         <v/>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B124" t="str">
         <v>弟弟</v>
       </c>
       <c r="C124" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D124" t="str">
         <v>是</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F124" t="str">
-        <v>北京</v>
+        <v>重庆</v>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B125" t="str">
         <v>妹妹</v>
       </c>
       <c r="C125" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D125" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F125" t="str">
-        <v/>
+        <v>中国澳门</v>
       </c>
       <c r="G125" t="str">
         <v/>
@@ -7782,13 +7782,13 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B126" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C126" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D126" t="str">
         <v>否</v>
@@ -7841,13 +7841,13 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B127" t="str">
         <v>妹妹</v>
       </c>
       <c r="C127" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D127" t="str">
         <v>否</v>
@@ -7900,19 +7900,19 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B128" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C128" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D128" t="str">
         <v>否</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F128" t="str">
         <v/>
@@ -7959,22 +7959,22 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B129" t="str">
         <v>弟弟</v>
       </c>
       <c r="C129" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D129" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F129" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G129" t="str">
         <v/>
@@ -8018,19 +8018,19 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B130" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C130" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D130" t="str">
         <v>否</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F130" t="str">
         <v/>
@@ -8077,19 +8077,19 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>阴影色NS11</v>
+        <v>烟灰色</v>
       </c>
       <c r="B131" t="str">
         <v>弟弟</v>
       </c>
       <c r="C131" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D131" t="str">
         <v>否</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F131" t="str">
         <v/>
@@ -8136,19 +8136,19 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>浅色银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B132" t="str">
         <v>妹妹</v>
       </c>
       <c r="C132" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D132" t="str">
         <v>否</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F132" t="str">
         <v/>
@@ -8195,22 +8195,22 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>浅烟灰色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B133" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C133" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D133" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F133" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G133" t="str">
         <v/>
@@ -8254,22 +8254,22 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>凯米尔色</v>
+        <v>纯黑色</v>
       </c>
       <c r="B134" t="str">
         <v>弟弟</v>
       </c>
       <c r="C134" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D134" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-02-14</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F134" t="str">
-        <v>上海浦东</v>
+        <v/>
       </c>
       <c r="G134" t="str">
         <v/>
@@ -8313,19 +8313,19 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>银虎斑补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B135" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C135" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D135" t="str">
         <v>否</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F135" t="str">
         <v/>
@@ -8372,19 +8372,19 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>烟灰色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B136" t="str">
         <v>弟弟</v>
       </c>
       <c r="C136" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D136" t="str">
         <v>否</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F136" t="str">
         <v/>
@@ -8431,19 +8431,19 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B137" t="str">
         <v>妹妹</v>
       </c>
       <c r="C137" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D137" t="str">
         <v>否</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F137" t="str">
         <v/>
@@ -8490,22 +8490,22 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B138" t="str">
         <v>妹妹</v>
       </c>
       <c r="C138" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D138" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-05-24</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F138" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G138" t="str">
         <v/>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B139" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C139" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D139" t="str">
         <v>是</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F139" t="str">
-        <v>湖北恩施</v>
+        <v>上海浦东</v>
       </c>
       <c r="G139" t="str">
         <v/>
@@ -8608,22 +8608,22 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B140" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C140" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D140" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F140" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G140" t="str">
         <v/>
@@ -8667,22 +8667,22 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B141" t="str">
         <v>弟弟</v>
       </c>
       <c r="C141" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D141" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E141" t="str">
-        <v>2025-11-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F141" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -8726,19 +8726,19 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B142" t="str">
         <v>妹妹</v>
       </c>
       <c r="C142" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D142" t="str">
         <v>否</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-05-18</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F142" t="str">
         <v/>
@@ -8785,22 +8785,22 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B143" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C143" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D143" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F143" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G143" t="str">
         <v/>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B144" t="str">
         <v>妹妹</v>
       </c>
       <c r="C144" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D144" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F144" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G144" t="str">
         <v/>
@@ -8903,22 +8903,22 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B145" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C145" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D145" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F145" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G145" t="str">
         <v/>
@@ -8965,16 +8965,16 @@
         <v>银虎斑</v>
       </c>
       <c r="B146" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C146" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D146" t="str">
         <v>是</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-03-05</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F146" t="str">
         <v>韩国</v>
@@ -9021,22 +9021,22 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B147" t="str">
         <v>妹妹</v>
       </c>
       <c r="C147" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D147" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F147" t="str">
-        <v>河北邢台</v>
+        <v/>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -9086,13 +9086,13 @@
         <v>弟弟</v>
       </c>
       <c r="C148" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D148" t="str">
         <v>是</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F148" t="str">
         <v>四川自贡</v>
@@ -9139,19 +9139,19 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B149" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C149" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D149" t="str">
         <v>否</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F149" t="str">
         <v/>
@@ -9198,13 +9198,13 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>棕虎斑补丁</v>
+        <v>纯黑色</v>
       </c>
       <c r="B150" t="str">
         <v>妹妹</v>
       </c>
       <c r="C150" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D150" t="str">
         <v>否</v>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B151" t="str">
         <v>妹妹</v>
       </c>
       <c r="C151" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D151" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F151" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G151" t="str">
         <v/>
@@ -9316,22 +9316,22 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B152" t="str">
         <v>妹妹</v>
       </c>
       <c r="C152" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D152" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F152" t="str">
-        <v/>
+        <v>河北邢台</v>
       </c>
       <c r="G152" t="str">
         <v/>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B153" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C153" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D153" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F153" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G153" t="str">
         <v/>
@@ -9437,49 +9437,49 @@
         <v>蓝虎斑</v>
       </c>
       <c r="B154" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C154" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D154" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-02-20</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F154" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G154" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H154" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I154" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J154" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K154" t="str">
         <v/>
       </c>
       <c r="L154" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M154" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N154" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O154" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P154" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q154" t="str">
         <v/>
@@ -9488,27 +9488,27 @@
         <v/>
       </c>
       <c r="S154" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B155" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C155" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D155" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E155" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F155" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G155" t="str">
         <v/>
@@ -9552,22 +9552,22 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B156" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C156" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D156" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E156" t="str">
-        <v/>
+        <v>2026-04-05</v>
       </c>
       <c r="F156" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G156" t="str">
         <v/>
@@ -9614,19 +9614,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B157" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C157" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D157" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E157" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F157" t="str">
-        <v>山西朔州</v>
+        <v/>
       </c>
       <c r="G157" t="str">
         <v/>
@@ -9676,16 +9676,16 @@
         <v>妹妹</v>
       </c>
       <c r="C158" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D158" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E158" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F158" t="str">
-        <v>浙江宁波</v>
+        <v/>
       </c>
       <c r="G158" t="str">
         <v/>
@@ -9729,52 +9729,52 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B159" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C159" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D159" t="str">
         <v>是</v>
       </c>
       <c r="E159" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F159" t="str">
-        <v>陕西西安</v>
+        <v>荷兰</v>
       </c>
       <c r="G159" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H159" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I159" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J159" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K159" t="str">
         <v/>
       </c>
       <c r="L159" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M159" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N159" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O159" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P159" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q159" t="str">
         <v/>
@@ -9783,18 +9783,18 @@
         <v/>
       </c>
       <c r="S159" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B160" t="str">
         <v>弟弟</v>
       </c>
       <c r="C160" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D160" t="str">
         <v>是</v>
@@ -9803,7 +9803,7 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>黑龙江漠河</v>
+        <v>广东广州</v>
       </c>
       <c r="G160" t="str">
         <v/>
@@ -9847,13 +9847,13 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B161" t="str">
         <v>弟弟</v>
       </c>
       <c r="C161" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D161" t="str">
         <v>是</v>
@@ -9862,7 +9862,7 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>日本</v>
+        <v>广东广州</v>
       </c>
       <c r="G161" t="str">
         <v/>
@@ -9909,10 +9909,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B162" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C162" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D162" t="str">
         <v>是</v>
@@ -9921,7 +9921,7 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>浙江杭州</v>
+        <v>山西朔州</v>
       </c>
       <c r="G162" t="str">
         <v/>
@@ -9971,7 +9971,7 @@
         <v>妹妹</v>
       </c>
       <c r="C163" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D163" t="str">
         <v>是</v>
@@ -9980,7 +9980,7 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>贵州安顺</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G163" t="str">
         <v/>
@@ -10027,10 +10027,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B164" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C164" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D164" t="str">
         <v>是</v>
@@ -10039,7 +10039,7 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>山东青岛</v>
+        <v>陕西西安</v>
       </c>
       <c r="G164" t="str">
         <v/>
@@ -10089,7 +10089,7 @@
         <v>弟弟</v>
       </c>
       <c r="C165" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D165" t="str">
         <v>是</v>
@@ -10142,13 +10142,13 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>纯蓝色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B166" t="str">
         <v>弟弟</v>
       </c>
       <c r="C166" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D166" t="str">
         <v>是</v>
@@ -10157,7 +10157,7 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>河南鹤壁</v>
+        <v>日本</v>
       </c>
       <c r="G166" t="str">
         <v/>
@@ -10204,10 +10204,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B167" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C167" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D167" t="str">
         <v>是</v>
@@ -10216,7 +10216,7 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>陕西西安</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G167" t="str">
         <v/>
@@ -10260,13 +10260,13 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B168" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C168" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D168" t="str">
         <v>是</v>
@@ -10275,7 +10275,7 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>四川成都</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G168" t="str">
         <v/>
@@ -10319,22 +10319,22 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B169" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C169" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D169" t="str">
         <v>是</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F169" t="str">
-        <v>四川成都</v>
+        <v>山东青岛</v>
       </c>
       <c r="G169" t="str">
         <v/>
@@ -10384,7 +10384,7 @@
         <v>弟弟</v>
       </c>
       <c r="C170" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D170" t="str">
         <v>是</v>
@@ -10393,7 +10393,7 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>新加坡</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G170" t="str">
         <v/>
@@ -10437,13 +10437,13 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>凯米尔色</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B171" t="str">
         <v>弟弟</v>
       </c>
       <c r="C171" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D171" t="str">
         <v>是</v>
@@ -10452,7 +10452,7 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>上海浦东</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G171" t="str">
         <v/>
@@ -10496,22 +10496,22 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B172" t="str">
         <v>弟弟</v>
       </c>
       <c r="C172" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D172" t="str">
         <v>是</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F172" t="str">
-        <v>浙江温州</v>
+        <v>陕西西安</v>
       </c>
       <c r="G172" t="str">
         <v/>
@@ -10558,63 +10558,358 @@
         <v>棕虎斑</v>
       </c>
       <c r="B173" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C173" t="str">
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+      </c>
+      <c r="D173" t="str">
+        <v>是</v>
+      </c>
+      <c r="E173" t="str">
+        <v/>
+      </c>
+      <c r="F173" t="str">
+        <v>四川成都</v>
+      </c>
+      <c r="G173" t="str">
+        <v/>
+      </c>
+      <c r="H173" t="str">
+        <v/>
+      </c>
+      <c r="I173" t="str">
+        <v/>
+      </c>
+      <c r="J173" t="str">
+        <v/>
+      </c>
+      <c r="K173" t="str">
+        <v/>
+      </c>
+      <c r="L173" t="str">
+        <v/>
+      </c>
+      <c r="M173" t="str">
+        <v/>
+      </c>
+      <c r="N173" t="str">
+        <v/>
+      </c>
+      <c r="O173" t="str">
+        <v/>
+      </c>
+      <c r="P173" t="str">
+        <v/>
+      </c>
+      <c r="Q173" t="str">
+        <v/>
+      </c>
+      <c r="R173" t="str">
+        <v/>
+      </c>
+      <c r="S173" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>烟灰色</v>
+      </c>
+      <c r="B174" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C174" t="str">
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+      </c>
+      <c r="D174" t="str">
+        <v>是</v>
+      </c>
+      <c r="E174" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="F174" t="str">
+        <v>四川成都</v>
+      </c>
+      <c r="G174" t="str">
+        <v/>
+      </c>
+      <c r="H174" t="str">
+        <v/>
+      </c>
+      <c r="I174" t="str">
+        <v/>
+      </c>
+      <c r="J174" t="str">
+        <v/>
+      </c>
+      <c r="K174" t="str">
+        <v/>
+      </c>
+      <c r="L174" t="str">
+        <v/>
+      </c>
+      <c r="M174" t="str">
+        <v/>
+      </c>
+      <c r="N174" t="str">
+        <v/>
+      </c>
+      <c r="O174" t="str">
+        <v/>
+      </c>
+      <c r="P174" t="str">
+        <v/>
+      </c>
+      <c r="Q174" t="str">
+        <v/>
+      </c>
+      <c r="R174" t="str">
+        <v/>
+      </c>
+      <c r="S174" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B175" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C175" t="str">
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+      </c>
+      <c r="D175" t="str">
+        <v>是</v>
+      </c>
+      <c r="E175" t="str">
+        <v/>
+      </c>
+      <c r="F175" t="str">
+        <v>新加坡</v>
+      </c>
+      <c r="G175" t="str">
+        <v/>
+      </c>
+      <c r="H175" t="str">
+        <v/>
+      </c>
+      <c r="I175" t="str">
+        <v/>
+      </c>
+      <c r="J175" t="str">
+        <v/>
+      </c>
+      <c r="K175" t="str">
+        <v/>
+      </c>
+      <c r="L175" t="str">
+        <v/>
+      </c>
+      <c r="M175" t="str">
+        <v/>
+      </c>
+      <c r="N175" t="str">
+        <v/>
+      </c>
+      <c r="O175" t="str">
+        <v/>
+      </c>
+      <c r="P175" t="str">
+        <v/>
+      </c>
+      <c r="Q175" t="str">
+        <v/>
+      </c>
+      <c r="R175" t="str">
+        <v/>
+      </c>
+      <c r="S175" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B176" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C176" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D176" t="str">
+        <v>是</v>
+      </c>
+      <c r="E176" t="str">
+        <v/>
+      </c>
+      <c r="F176" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G176" t="str">
+        <v/>
+      </c>
+      <c r="H176" t="str">
+        <v/>
+      </c>
+      <c r="I176" t="str">
+        <v/>
+      </c>
+      <c r="J176" t="str">
+        <v/>
+      </c>
+      <c r="K176" t="str">
+        <v/>
+      </c>
+      <c r="L176" t="str">
+        <v/>
+      </c>
+      <c r="M176" t="str">
+        <v/>
+      </c>
+      <c r="N176" t="str">
+        <v/>
+      </c>
+      <c r="O176" t="str">
+        <v/>
+      </c>
+      <c r="P176" t="str">
+        <v/>
+      </c>
+      <c r="Q176" t="str">
+        <v/>
+      </c>
+      <c r="R176" t="str">
+        <v/>
+      </c>
+      <c r="S176" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B177" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C177" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D177" t="str">
+        <v>是</v>
+      </c>
+      <c r="E177" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F177" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G177" t="str">
+        <v/>
+      </c>
+      <c r="H177" t="str">
+        <v/>
+      </c>
+      <c r="I177" t="str">
+        <v/>
+      </c>
+      <c r="J177" t="str">
+        <v/>
+      </c>
+      <c r="K177" t="str">
+        <v/>
+      </c>
+      <c r="L177" t="str">
+        <v/>
+      </c>
+      <c r="M177" t="str">
+        <v/>
+      </c>
+      <c r="N177" t="str">
+        <v/>
+      </c>
+      <c r="O177" t="str">
+        <v/>
+      </c>
+      <c r="P177" t="str">
+        <v/>
+      </c>
+      <c r="Q177" t="str">
+        <v/>
+      </c>
+      <c r="R177" t="str">
+        <v/>
+      </c>
+      <c r="S177" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B178" t="str">
         <v>妹妹</v>
       </c>
-      <c r="C173" t="str">
+      <c r="C178" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D173" t="str">
-        <v>否</v>
-      </c>
-      <c r="E173" t="str">
+      <c r="D178" t="str">
+        <v>否</v>
+      </c>
+      <c r="E178" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F173" t="str">
-        <v/>
-      </c>
-      <c r="G173" t="str">
-        <v/>
-      </c>
-      <c r="H173" t="str">
-        <v/>
-      </c>
-      <c r="I173" t="str">
-        <v/>
-      </c>
-      <c r="J173" t="str">
-        <v/>
-      </c>
-      <c r="K173" t="str">
-        <v/>
-      </c>
-      <c r="L173" t="str">
-        <v/>
-      </c>
-      <c r="M173" t="str">
-        <v/>
-      </c>
-      <c r="N173" t="str">
-        <v/>
-      </c>
-      <c r="O173" t="str">
-        <v/>
-      </c>
-      <c r="P173" t="str">
-        <v/>
-      </c>
-      <c r="Q173" t="str">
-        <v/>
-      </c>
-      <c r="R173" t="str">
-        <v/>
-      </c>
-      <c r="S173" t="str">
+      <c r="F178" t="str">
+        <v/>
+      </c>
+      <c r="G178" t="str">
+        <v/>
+      </c>
+      <c r="H178" t="str">
+        <v/>
+      </c>
+      <c r="I178" t="str">
+        <v/>
+      </c>
+      <c r="J178" t="str">
+        <v/>
+      </c>
+      <c r="K178" t="str">
+        <v/>
+      </c>
+      <c r="L178" t="str">
+        <v/>
+      </c>
+      <c r="M178" t="str">
+        <v/>
+      </c>
+      <c r="N178" t="str">
+        <v/>
+      </c>
+      <c r="O178" t="str">
+        <v/>
+      </c>
+      <c r="P178" t="str">
+        <v/>
+      </c>
+      <c r="Q178" t="str">
+        <v/>
+      </c>
+      <c r="R178" t="str">
+        <v/>
+      </c>
+      <c r="S178" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S173"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S178"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S178"/>
+  <dimension ref="A1:S179"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>浅银虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B2" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1789654858942-ws3mqfv0zf.jpg</v>
+        <v>assets/1789655131156-6ywyod2pgz.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>否</v>
@@ -525,19 +525,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>红虎斑</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B3" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1789654723483-fyl8c7wdqg.jpg</v>
+        <v>assets/1789654858942-ws3mqfv0zf.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>否</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -584,13 +584,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>银虎班补丁</v>
+        <v>红虎斑</v>
       </c>
       <c r="B4" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1789654675792-6d4kyyncmf.jpg</v>
+        <v>assets/1789654723483-fyl8c7wdqg.jpg</v>
       </c>
       <c r="D4" t="str">
         <v>否</v>
@@ -643,19 +643,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>烟灰色</v>
+        <v>银虎班补丁</v>
       </c>
       <c r="B5" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1789654628929-2wok5d7b71.jpg</v>
+        <v>assets/1789654675792-6d4kyyncmf.jpg</v>
       </c>
       <c r="D5" t="str">
         <v>否</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -702,19 +702,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>阴影色NS11</v>
+        <v>烟灰色</v>
       </c>
       <c r="B6" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1789654549268-68uab4pdoy.jpg</v>
+        <v>assets/1789654628929-2wok5d7b71.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>否</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -761,19 +761,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>阴影色NS12</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B7" t="str">
         <v>妹妹</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1788534744815-pzs6jqs2pm.jpg</v>
+        <v>assets/1789654549268-68uab4pdoy.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>否</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -820,19 +820,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B8" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1788534522775-my4ggv0pwo.jpg</v>
+        <v>assets/1788534744815-pzs6jqs2pm.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>否</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -879,19 +879,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B9" t="str">
         <v>弟弟</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1788442386268-ilpasqz91m.jpg</v>
+        <v>assets/1788534522775-my4ggv0pwo.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>否</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -938,19 +938,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>浅银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B10" t="str">
         <v>弟弟</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1788442356842-bbleakpy85.jpg</v>
+        <v>assets/1788442386268-ilpasqz91m.jpg</v>
       </c>
       <c r="D10" t="str">
         <v>否</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -997,19 +997,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>浅烟灰色</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B11" t="str">
         <v>弟弟</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1788442221802-et3crh0tww.jpg</v>
+        <v>assets/1788442356842-bbleakpy85.jpg</v>
       </c>
       <c r="D11" t="str">
         <v>否</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1056,22 +1056,22 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>凯米尔</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B12" t="str">
         <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1788014088852-oqkg79cki9.jpg</v>
+        <v>assets/1788442221802-et3crh0tww.jpg</v>
       </c>
       <c r="D12" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-06-26</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F12" t="str">
-        <v>湖北襄阳</v>
+        <v/>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1115,22 +1115,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B13" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1788014050978-9a2sguuo1u.jpg</v>
+        <v>assets/1788014088852-oqkg79cki9.jpg</v>
       </c>
       <c r="D13" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>湖北襄阳</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1177,19 +1177,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B14" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1788013924404-gmlh0hfjae.jpg</v>
+        <v>assets/1788014050978-9a2sguuo1u.jpg</v>
       </c>
       <c r="D14" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F14" t="str">
-        <v>浙江嘉兴</v>
+        <v/>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1233,22 +1233,22 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B15" t="str">
         <v>弟弟</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1788013889955-wpykaycfde.jpg</v>
+        <v>assets/1788013924404-gmlh0hfjae.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>是</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F15" t="str">
-        <v>湖北襄阳</v>
+        <v>浙江嘉兴</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1292,22 +1292,22 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>银虎斑补丁</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B16" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1788013810551-b90h1mwfiq.jpg</v>
+        <v>assets/1788013889955-wpykaycfde.jpg</v>
       </c>
       <c r="D16" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E16" t="str">
         <v>2026-06-26</v>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>湖北襄阳</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1351,22 +1351,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B17" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1787837910484-r7urrsuib0.jpg</v>
+        <v>assets/1788013810551-b90h1mwfiq.jpg</v>
       </c>
       <c r="D17" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F17" t="str">
-        <v>香港</v>
+        <v/>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1410,22 +1410,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B18" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1787837846581-6q9nxgad35.jpg</v>
+        <v>assets/1787837910484-r7urrsuib0.jpg</v>
       </c>
       <c r="D18" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-06-10</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>香港</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1469,19 +1469,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>凯米尔</v>
+        <v>纯黑色</v>
       </c>
       <c r="B19" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1787837779354-hkuyvt39iz.jpg</v>
+        <v>assets/1787837846581-6q9nxgad35.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>否</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -1528,19 +1528,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔</v>
       </c>
       <c r="B20" t="str">
         <v>弟弟</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
+        <v>assets/1787837779354-hkuyvt39iz.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>否</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B21" t="str">
         <v>弟弟</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1787837648423-9riberz3tq.jpg</v>
+        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
       </c>
       <c r="D21" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E21" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F21" t="str">
-        <v>北京</v>
+        <v/>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1652,16 +1652,16 @@
         <v>弟弟</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
+        <v>assets/1787837648423-9riberz3tq.jpg</v>
       </c>
       <c r="D22" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F22" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1711,7 +1711,7 @@
         <v>弟弟</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1787479268842-7en9nzy302.jpg</v>
+        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
       </c>
       <c r="D23" t="str">
         <v>否</v>
@@ -1732,7 +1732,7 @@
         <v/>
       </c>
       <c r="J23" t="str">
-        <v>2026-06-10</v>
+        <v/>
       </c>
       <c r="K23" t="str">
         <v/>
@@ -1764,13 +1764,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B24" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1787479242639-32zuh5lham.jpg</v>
+        <v>assets/1787479268842-7en9nzy302.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>否</v>
@@ -1791,7 +1791,7 @@
         <v/>
       </c>
       <c r="J24" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="K24" t="str">
         <v/>
@@ -1823,22 +1823,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B25" t="str">
         <v>妹妹</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1787466121255-21jto2cugv.jpg</v>
+        <v>assets/1787479242639-32zuh5lham.jpg</v>
       </c>
       <c r="D25" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E25" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F25" t="str">
-        <v>四川广安</v>
+        <v/>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1882,22 +1882,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B26" t="str">
         <v>妹妹</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
+        <v>assets/1787466121255-21jto2cugv.jpg</v>
       </c>
       <c r="D26" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F26" t="str">
-        <v/>
+        <v>四川广安</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1941,13 +1941,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B27" t="str">
         <v>妹妹</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1787388277490-e6u506cx0r.jpg</v>
+        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
       </c>
       <c r="D27" t="str">
         <v>否</v>
@@ -2000,22 +2000,22 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B28" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1787328436957-x30od0gw28.jpg</v>
+        <v>assets/1787388277490-e6u506cx0r.jpg</v>
       </c>
       <c r="D28" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F28" t="str">
-        <v>江苏苏州</v>
+        <v/>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B29" t="str">
         <v>弟弟</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
+        <v>assets/1787328436957-x30od0gw28.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>是</v>
@@ -2074,7 +2074,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>辽宁东港</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2118,13 +2118,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B30" t="str">
         <v>弟弟</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1787327967245-m62ohievcl.jpg</v>
+        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
       </c>
       <c r="D30" t="str">
         <v>是</v>
@@ -2133,7 +2133,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>福建福州</v>
+        <v>辽宁东港</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2177,13 +2177,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B31" t="str">
         <v>弟弟</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
+        <v>assets/1787327967245-m62ohievcl.jpg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
@@ -2192,7 +2192,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>上海</v>
+        <v>福建福州</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2236,13 +2236,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>纯蓝色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B32" t="str">
         <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1787327793837-znk2knoo6p.jpg</v>
+        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
@@ -2251,7 +2251,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>河南鹤壁</v>
+        <v>上海</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2295,13 +2295,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>银虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B33" t="str">
         <v>弟弟</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1787327752832-kkpmp21os3.jpg</v>
+        <v>assets/1787327793837-znk2knoo6p.jpg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
@@ -2310,7 +2310,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>陕西西安</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2357,10 +2357,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B34" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
+        <v>assets/1787327752832-kkpmp21os3.jpg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
@@ -2416,10 +2416,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B35" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1787327573762-h23cux94p2.jpg</v>
+        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
       </c>
       <c r="D35" t="str">
         <v>是</v>
@@ -2428,7 +2428,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>北京</v>
+        <v>陕西西安</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2475,10 +2475,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B36" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1787327496557-9daggljg4g.jpg</v>
+        <v>assets/1787327573762-h23cux94p2.jpg</v>
       </c>
       <c r="D36" t="str">
         <v>是</v>
@@ -2487,7 +2487,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>黑龙江哈尔滨</v>
+        <v>北京</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B37" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
+        <v>assets/1787327496557-9daggljg4g.jpg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
@@ -2546,7 +2546,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>甘肃嘉峪关</v>
+        <v>黑龙江哈尔滨</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2590,13 +2590,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B38" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
+        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>安徽合肥</v>
+        <v>甘肃嘉峪关</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B39" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1787327337811-u5u2pdew3.jpg</v>
+        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2708,13 +2708,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B40" t="str">
         <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1787327309143-6c1dan1sev.jpg</v>
+        <v>assets/1787327337811-u5u2pdew3.jpg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2723,7 +2723,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>四川成都</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2767,13 +2767,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B41" t="str">
         <v>弟弟</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1787327277453-w89ujg69fm.jpg</v>
+        <v>assets/1787327309143-6c1dan1sev.jpg</v>
       </c>
       <c r="D41" t="str">
         <v>是</v>
@@ -2826,13 +2826,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>蓝银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B42" t="str">
         <v>弟弟</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1787327232159-lkrcl588a5.jpg</v>
+        <v>assets/1787327277453-w89ujg69fm.jpg</v>
       </c>
       <c r="D42" t="str">
         <v>是</v>
@@ -2885,13 +2885,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>玳瑁色</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B43" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1787327182347-3az0z7sys2.jpg</v>
+        <v>assets/1787327232159-lkrcl588a5.jpg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
@@ -2900,7 +2900,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>四川内江</v>
+        <v>四川成都</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>棕虎补丁</v>
+        <v>玳瑁色</v>
       </c>
       <c r="B44" t="str">
         <v>妹妹</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
+        <v>assets/1787327182347-3az0z7sys2.jpg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>贵州贵阳</v>
+        <v>四川内江</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3003,13 +3003,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>黑烟色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B45" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1787327101790-tqjlseog5y.jpg</v>
+        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
@@ -3018,7 +3018,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>浙江杭州</v>
+        <v>贵州贵阳</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>烟灰色</v>
+        <v>黑烟色</v>
       </c>
       <c r="B46" t="str">
         <v>弟弟</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1787327019632-l1780lu2hj.jpg</v>
+        <v>assets/1787327101790-tqjlseog5y.jpg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>山东威海</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3121,13 +3121,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>棕虎补丁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B47" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1787326905275-plz3fpgo97.jpg</v>
+        <v>assets/1787327019632-l1780lu2hj.jpg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>浙江杭州</v>
+        <v>山东威海</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3180,13 +3180,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B48" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
+        <v>assets/1787326905275-plz3fpgo97.jpg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>凯米尔色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B49" t="str">
         <v>弟弟</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
+        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -3298,13 +3298,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>凯米尔</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B50" t="str">
         <v>弟弟</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1787326814713-p5oavnlulg.jpg</v>
+        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
@@ -3357,13 +3357,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B51" t="str">
         <v>弟弟</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1787326773577-13q5out2d0.jpg</v>
+        <v>assets/1787326814713-p5oavnlulg.jpg</v>
       </c>
       <c r="D51" t="str">
         <v>是</v>
@@ -3372,7 +3372,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>四川宜宾</v>
+        <v>四川成都</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,13 +3416,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>金棕虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B52" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1787326548993-89s929m2hg.jpg</v>
+        <v>assets/1787326773577-13q5out2d0.jpg</v>
       </c>
       <c r="D52" t="str">
         <v>是</v>
@@ -3431,7 +3431,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>上海</v>
+        <v>四川宜宾</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3475,13 +3475,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>凯米尔色</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B53" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1787326449218-09s9ucram4.jpg</v>
+        <v>assets/1787326548993-89s929m2hg.jpg</v>
       </c>
       <c r="D53" t="str">
         <v>是</v>
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>德国</v>
+        <v>上海</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3534,13 +3534,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>棕虎补丁</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B54" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1787326277374-8ti107m5ki.jpg</v>
+        <v>assets/1787326449218-09s9ucram4.jpg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
@@ -3549,7 +3549,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>广东深圳</v>
+        <v>德国</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3593,13 +3593,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>烟灰色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B55" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1787326236952-2pmwche4t3.jpg</v>
+        <v>assets/1787326277374-8ti107m5ki.jpg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
@@ -3608,7 +3608,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>福建泉州</v>
+        <v>广东深圳</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B56" t="str">
         <v>弟弟</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1787326184557-90v6clkwen.jpg</v>
+        <v>assets/1787326236952-2pmwche4t3.jpg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
@@ -3667,7 +3667,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>福建福州</v>
+        <v>福建泉州</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3711,13 +3711,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B57" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
+        <v>assets/1787326184557-90v6clkwen.jpg</v>
       </c>
       <c r="D57" t="str">
         <v>是</v>
@@ -3726,7 +3726,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>广西贵港</v>
+        <v>福建福州</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3770,13 +3770,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B58" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1787325862706-wq18k3ej56.jpg</v>
+        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
@@ -3785,7 +3785,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>江苏苏州</v>
+        <v>广西贵港</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3835,7 +3835,7 @@
         <v>弟弟</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
+        <v>assets/1787325862706-wq18k3ej56.jpg</v>
       </c>
       <c r="D59" t="str">
         <v>是</v>
@@ -3888,13 +3888,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B60" t="str">
         <v>弟弟</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1787325706797-kgk81ghccy.jpg</v>
+        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
       </c>
       <c r="D60" t="str">
         <v>是</v>
@@ -3903,7 +3903,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>北京</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3947,13 +3947,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B61" t="str">
         <v>弟弟</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
+        <v>assets/1787325706797-kgk81ghccy.jpg</v>
       </c>
       <c r="D61" t="str">
         <v>是</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>上海</v>
+        <v>北京</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4006,13 +4006,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B62" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1787325554341-608thexrne.jpg</v>
+        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
       </c>
       <c r="D62" t="str">
         <v>是</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>江苏苏州</v>
+        <v>上海</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4065,13 +4065,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B63" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1787325480828-q90pskoiw3.jpg</v>
+        <v>assets/1787325554341-608thexrne.jpg</v>
       </c>
       <c r="D63" t="str">
         <v>是</v>
@@ -4080,7 +4080,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>四川成都</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -4127,10 +4127,10 @@
         <v>浅色银虎斑</v>
       </c>
       <c r="B64" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C64" t="str">
-        <v>assets/1787325448999-a2pg8176fu.jpg</v>
+        <v>assets/1787325480828-q90pskoiw3.jpg</v>
       </c>
       <c r="D64" t="str">
         <v>是</v>
@@ -4139,7 +4139,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>中国台湾</v>
+        <v>四川成都</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -4183,13 +4183,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>棕虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B65" t="str">
         <v>妹妹</v>
       </c>
       <c r="C65" t="str">
-        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
+        <v>assets/1787325448999-a2pg8176fu.jpg</v>
       </c>
       <c r="D65" t="str">
         <v>是</v>
@@ -4198,7 +4198,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>浙江杭州</v>
+        <v>中国台湾</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -4242,13 +4242,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B66" t="str">
         <v>妹妹</v>
       </c>
       <c r="C66" t="str">
-        <v>assets/1787325237876-t19isaq5gu.jpg</v>
+        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
       </c>
       <c r="D66" t="str">
         <v>是</v>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>辽宁沈阳</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -4301,13 +4301,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>金棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B67" t="str">
         <v>妹妹</v>
       </c>
       <c r="C67" t="str">
-        <v>assets/1787325199931-e7wms9qtya.jpg</v>
+        <v>assets/1787325237876-t19isaq5gu.jpg</v>
       </c>
       <c r="D67" t="str">
         <v>是</v>
@@ -4316,7 +4316,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>四川成都</v>
+        <v>辽宁沈阳</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4360,13 +4360,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>蓝虎斑</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B68" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C68" t="str">
-        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
+        <v>assets/1787325199931-e7wms9qtya.jpg</v>
       </c>
       <c r="D68" t="str">
         <v>是</v>
@@ -4375,7 +4375,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>中国香港</v>
+        <v>四川成都</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -4419,13 +4419,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B69" t="str">
         <v>弟弟</v>
       </c>
       <c r="C69" t="str">
-        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
+        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
       </c>
       <c r="D69" t="str">
         <v>是</v>
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>中国澳门</v>
+        <v>中国香港</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4478,13 +4478,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B70" t="str">
         <v>弟弟</v>
       </c>
       <c r="C70" t="str">
-        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
+        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
       </c>
       <c r="D70" t="str">
         <v>是</v>
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>山东青岛</v>
+        <v>中国澳门</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -4537,13 +4537,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B71" t="str">
         <v>弟弟</v>
       </c>
       <c r="C71" t="str">
-        <v>assets/1787324954998-w5m5jox439.jpg</v>
+        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
       </c>
       <c r="D71" t="str">
         <v>是</v>
@@ -4552,7 +4552,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>海南海口</v>
+        <v>山东青岛</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -4596,13 +4596,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B72" t="str">
         <v>弟弟</v>
       </c>
       <c r="C72" t="str">
-        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
+        <v>assets/1787324954998-w5m5jox439.jpg</v>
       </c>
       <c r="D72" t="str">
         <v>是</v>
@@ -4611,7 +4611,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>内蒙古</v>
+        <v>海南海口</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -4655,13 +4655,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B73" t="str">
         <v>弟弟</v>
       </c>
       <c r="C73" t="str">
-        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
+        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
       </c>
       <c r="D73" t="str">
         <v>是</v>
@@ -4670,7 +4670,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>中国香港</v>
+        <v>内蒙古</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4720,7 +4720,7 @@
         <v>弟弟</v>
       </c>
       <c r="C74" t="str">
-        <v>assets/1787324806613-31yyz14tsf.jpg</v>
+        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
       </c>
       <c r="D74" t="str">
         <v>是</v>
@@ -4729,7 +4729,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>四川成都</v>
+        <v>中国香港</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4773,13 +4773,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B75" t="str">
         <v>弟弟</v>
       </c>
       <c r="C75" t="str">
-        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
+        <v>assets/1787324806613-31yyz14tsf.jpg</v>
       </c>
       <c r="D75" t="str">
         <v>是</v>
@@ -4788,7 +4788,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>湖北武汉</v>
+        <v>四川成都</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -4832,13 +4832,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>烟灰色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B76" t="str">
         <v>弟弟</v>
       </c>
       <c r="C76" t="str">
-        <v>assets/1787324522658-smn44crast.jpg</v>
+        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
       </c>
       <c r="D76" t="str">
         <v>是</v>
@@ -4891,13 +4891,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B77" t="str">
         <v>弟弟</v>
       </c>
       <c r="C77" t="str">
-        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
+        <v>assets/1787324522658-smn44crast.jpg</v>
       </c>
       <c r="D77" t="str">
         <v>是</v>
@@ -4906,7 +4906,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>新疆</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4950,13 +4950,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>浅凯米尔</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B78" t="str">
         <v>弟弟</v>
       </c>
       <c r="C78" t="str">
-        <v>assets/1787324331029-d74lcuycf6.jpg</v>
+        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
       </c>
       <c r="D78" t="str">
         <v>是</v>
@@ -4965,7 +4965,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>四川成都</v>
+        <v>新疆</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -5009,13 +5009,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>红虎斑</v>
+        <v>浅凯米尔</v>
       </c>
       <c r="B79" t="str">
         <v>弟弟</v>
       </c>
       <c r="C79" t="str">
-        <v>assets/1787324297469-ans1lse2l5.jpg</v>
+        <v>assets/1787324331029-d74lcuycf6.jpg</v>
       </c>
       <c r="D79" t="str">
         <v>是</v>
@@ -5024,7 +5024,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>四川乐山</v>
+        <v>四川成都</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -5074,7 +5074,7 @@
         <v>弟弟</v>
       </c>
       <c r="C80" t="str">
-        <v>assets/1787324256827-7w383z4bg1.jpg</v>
+        <v>assets/1787324297469-ans1lse2l5.jpg</v>
       </c>
       <c r="D80" t="str">
         <v>是</v>
@@ -5083,7 +5083,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>中国台湾</v>
+        <v>四川乐山</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -5127,13 +5127,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B81" t="str">
         <v>弟弟</v>
       </c>
       <c r="C81" t="str">
-        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
+        <v>assets/1787324256827-7w383z4bg1.jpg</v>
       </c>
       <c r="D81" t="str">
         <v>是</v>
@@ -5142,7 +5142,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>四川成都</v>
+        <v>中国台湾</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -5186,13 +5186,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B82" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C82" t="str">
-        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
+        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
       </c>
       <c r="D82" t="str">
         <v>是</v>
@@ -5201,7 +5201,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>江苏南京</v>
+        <v>四川成都</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -5245,13 +5245,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B83" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C83" t="str">
-        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
+        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
       </c>
       <c r="D83" t="str">
         <v>是</v>
@@ -5304,13 +5304,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B84" t="str">
         <v>弟弟</v>
       </c>
       <c r="C84" t="str">
-        <v>assets/1787323318612-soge38hpsf.jpg</v>
+        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
       </c>
       <c r="D84" t="str">
         <v>是</v>
@@ -5319,7 +5319,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>上海</v>
+        <v>江苏南京</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -5363,13 +5363,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B85" t="str">
         <v>弟弟</v>
       </c>
       <c r="C85" t="str">
-        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
+        <v>assets/1787323318612-soge38hpsf.jpg</v>
       </c>
       <c r="D85" t="str">
         <v>是</v>
@@ -5378,7 +5378,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>四川成都</v>
+        <v>上海</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -5422,13 +5422,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B86" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C86" t="str">
-        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
+        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
       </c>
       <c r="D86" t="str">
         <v>是</v>
@@ -5437,7 +5437,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>浙江宁波</v>
+        <v>四川成都</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -5481,13 +5481,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>银虎斑补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B87" t="str">
         <v>妹妹</v>
       </c>
       <c r="C87" t="str">
-        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
+        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
       </c>
       <c r="D87" t="str">
         <v>是</v>
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>马来西亚</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -5540,13 +5540,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B88" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C88" t="str">
-        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
+        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
       </c>
       <c r="D88" t="str">
         <v>是</v>
@@ -5555,7 +5555,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>陕西西安</v>
+        <v>马来西亚</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -5599,13 +5599,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B89" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C89" t="str">
-        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
+        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
       </c>
       <c r="D89" t="str">
         <v>是</v>
@@ -5614,7 +5614,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>广西南宁</v>
+        <v>陕西西安</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -5658,13 +5658,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B90" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C90" t="str">
-        <v>assets/1787322760950-gn3qgego4s.jpg</v>
+        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
       </c>
       <c r="D90" t="str">
         <v>是</v>
@@ -5717,13 +5717,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B91" t="str">
         <v>弟弟</v>
       </c>
       <c r="C91" t="str">
-        <v>assets/1787322605982-04n50xegt2.jpg</v>
+        <v>assets/1787322760950-gn3qgego4s.jpg</v>
       </c>
       <c r="D91" t="str">
         <v>是</v>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>上海</v>
+        <v>广西南宁</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -5776,13 +5776,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>蓝虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B92" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C92" t="str">
-        <v>assets/1787322490045-kog3ru43dy.jpg</v>
+        <v>assets/1787322605982-04n50xegt2.jpg</v>
       </c>
       <c r="D92" t="str">
         <v>是</v>
@@ -5835,13 +5835,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B93" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C93" t="str">
-        <v>assets/1787322419996-0m33yx89nm.jpg</v>
+        <v>assets/1787322490045-kog3ru43dy.jpg</v>
       </c>
       <c r="D93" t="str">
         <v>是</v>
@@ -5850,7 +5850,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>广东广州</v>
+        <v>上海</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -5894,13 +5894,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>浅色银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B94" t="str">
         <v>弟弟</v>
       </c>
       <c r="C94" t="str">
-        <v>assets/1787322377730-vj5csj2mll.jpg</v>
+        <v>assets/1787322419996-0m33yx89nm.jpg</v>
       </c>
       <c r="D94" t="str">
         <v>是</v>
@@ -5909,7 +5909,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>柬埔寨</v>
+        <v>广东广州</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -5953,13 +5953,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>蓝虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B95" t="str">
         <v>弟弟</v>
       </c>
       <c r="C95" t="str">
-        <v>assets/1787322269611-53yaj5ideu.jpg</v>
+        <v>assets/1787322377730-vj5csj2mll.jpg</v>
       </c>
       <c r="D95" t="str">
         <v>是</v>
@@ -5968,7 +5968,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>山东枣庄</v>
+        <v>柬埔寨</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -6012,13 +6012,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B96" t="str">
         <v>弟弟</v>
       </c>
       <c r="C96" t="str">
-        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
+        <v>assets/1787322269611-53yaj5ideu.jpg</v>
       </c>
       <c r="D96" t="str">
         <v>是</v>
@@ -6027,7 +6027,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>陕西西安</v>
+        <v>山东枣庄</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -6077,7 +6077,7 @@
         <v>弟弟</v>
       </c>
       <c r="C97" t="str">
-        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
+        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
       </c>
       <c r="D97" t="str">
         <v>是</v>
@@ -6086,7 +6086,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>山东东营</v>
+        <v>陕西西安</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -6130,13 +6130,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B98" t="str">
         <v>弟弟</v>
       </c>
       <c r="C98" t="str">
-        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
+        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
       </c>
       <c r="D98" t="str">
         <v>是</v>
@@ -6145,7 +6145,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>中国台湾</v>
+        <v>山东东营</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -6189,13 +6189,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B99" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C99" t="str">
-        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
+        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
       </c>
       <c r="D99" t="str">
         <v>是</v>
@@ -6248,13 +6248,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B100" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C100" t="str">
-        <v>assets/1787321834306-efgnyhujon.jpg</v>
+        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
       </c>
       <c r="D100" t="str">
         <v>是</v>
@@ -6263,7 +6263,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -6313,7 +6313,7 @@
         <v>弟弟</v>
       </c>
       <c r="C101" t="str">
-        <v>assets/1787321439916-uttgpbkogb.jpg</v>
+        <v>assets/1787321834306-efgnyhujon.jpg</v>
       </c>
       <c r="D101" t="str">
         <v>是</v>
@@ -6322,7 +6322,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>安徽合肥</v>
+        <v>北京</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -6372,7 +6372,7 @@
         <v>弟弟</v>
       </c>
       <c r="C102" t="str">
-        <v>assets/1787321419210-51hhgurygq.jpg</v>
+        <v>assets/1787321439916-uttgpbkogb.jpg</v>
       </c>
       <c r="D102" t="str">
         <v>是</v>
@@ -6381,7 +6381,7 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>上海</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -6425,13 +6425,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B103" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C103" t="str">
-        <v>assets/1787321363369-bzjn51j5il.jpg</v>
+        <v>assets/1787321419210-51hhgurygq.jpg</v>
       </c>
       <c r="D103" t="str">
         <v>是</v>
@@ -6440,7 +6440,7 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>中国台湾</v>
+        <v>上海</v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -6484,13 +6484,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B104" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C104" t="str">
-        <v>assets/1787321332559-87p6spuch3.jpg</v>
+        <v>assets/1787321363369-bzjn51j5il.jpg</v>
       </c>
       <c r="D104" t="str">
         <v>是</v>
@@ -6546,10 +6546,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B105" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C105" t="str">
-        <v>assets/1787321232531-59lnzv8y98.jpg</v>
+        <v>assets/1787321332559-87p6spuch3.jpg</v>
       </c>
       <c r="D105" t="str">
         <v>是</v>
@@ -6558,7 +6558,7 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G105" t="str">
         <v/>
@@ -6602,13 +6602,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B106" t="str">
         <v>妹妹</v>
       </c>
       <c r="C106" t="str">
-        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
+        <v>assets/1787321232531-59lnzv8y98.jpg</v>
       </c>
       <c r="D106" t="str">
         <v>是</v>
@@ -6617,7 +6617,7 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>浙江宁波</v>
+        <v>北京</v>
       </c>
       <c r="G106" t="str">
         <v/>
@@ -6667,7 +6667,7 @@
         <v>妹妹</v>
       </c>
       <c r="C107" t="str">
-        <v>assets/1787319800704-v3qeu062ak.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D107" t="str">
         <v>是</v>
@@ -6676,7 +6676,7 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>河北唐山</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G107" t="str">
         <v/>
@@ -6726,7 +6726,7 @@
         <v>妹妹</v>
       </c>
       <c r="C108" t="str">
-        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D108" t="str">
         <v>是</v>
@@ -6735,7 +6735,7 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>河北石家庄</v>
+        <v>河北唐山</v>
       </c>
       <c r="G108" t="str">
         <v/>
@@ -6779,13 +6779,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B109" t="str">
         <v>妹妹</v>
       </c>
       <c r="C109" t="str">
-        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D109" t="str">
         <v>是</v>
@@ -6794,7 +6794,7 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>韩国</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G109" t="str">
         <v/>
@@ -6838,13 +6838,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>蓝银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B110" t="str">
         <v>妹妹</v>
       </c>
       <c r="C110" t="str">
-        <v>assets/1787319501376-xscwljnu1j.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D110" t="str">
         <v>是</v>
@@ -6853,7 +6853,7 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>美国</v>
+        <v>韩国</v>
       </c>
       <c r="G110" t="str">
         <v/>
@@ -6897,13 +6897,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>棕虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B111" t="str">
         <v>妹妹</v>
       </c>
       <c r="C111" t="str">
-        <v>assets/1787319443529-4a0zqikufx.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D111" t="str">
         <v>是</v>
@@ -6912,7 +6912,7 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>中国台湾</v>
+        <v>美国</v>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -6956,13 +6956,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B112" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C112" t="str">
-        <v>assets/1787319356194-lr2d5680i9.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D112" t="str">
         <v>是</v>
@@ -7015,13 +7015,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B113" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C113" t="str">
-        <v>assets/1787319208828-aizqo4blcv.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D113" t="str">
         <v>是</v>
@@ -7030,7 +7030,7 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>山东淄博</v>
+        <v>中国台湾</v>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -7074,13 +7074,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B114" t="str">
         <v>妹妹</v>
       </c>
       <c r="C114" t="str">
-        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D114" t="str">
         <v>是</v>
@@ -7089,7 +7089,7 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>韩国</v>
+        <v>山东淄博</v>
       </c>
       <c r="G114" t="str">
         <v/>
@@ -7133,13 +7133,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B115" t="str">
         <v>妹妹</v>
       </c>
       <c r="C115" t="str">
-        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D115" t="str">
         <v>是</v>
@@ -7148,7 +7148,7 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>四川成都</v>
+        <v>韩国</v>
       </c>
       <c r="G115" t="str">
         <v/>
@@ -7192,13 +7192,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B116" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C116" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D116" t="str">
         <v>是</v>
@@ -7207,7 +7207,7 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>广东广州</v>
+        <v>四川成都</v>
       </c>
       <c r="G116" t="str">
         <v/>
@@ -7257,7 +7257,7 @@
         <v>弟弟</v>
       </c>
       <c r="C117" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D117" t="str">
         <v>是</v>
@@ -7266,7 +7266,7 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>广东广州</v>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -7310,13 +7310,13 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B118" t="str">
         <v>弟弟</v>
       </c>
       <c r="C118" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D118" t="str">
         <v>是</v>
@@ -7325,7 +7325,7 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>天津</v>
+        <v>黑龙江鹤岗</v>
       </c>
       <c r="G118" t="str">
         <v/>
@@ -7369,13 +7369,13 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B119" t="str">
         <v>弟弟</v>
       </c>
       <c r="C119" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D119" t="str">
         <v>是</v>
@@ -7384,7 +7384,7 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>山西朔州</v>
+        <v>天津</v>
       </c>
       <c r="G119" t="str">
         <v/>
@@ -7414,7 +7414,7 @@
         <v/>
       </c>
       <c r="P119" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q119" t="str">
         <v/>
@@ -7431,10 +7431,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B120" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C120" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D120" t="str">
         <v>是</v>
@@ -7443,7 +7443,7 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>贵州</v>
+        <v>山西朔州</v>
       </c>
       <c r="G120" t="str">
         <v/>
@@ -7473,7 +7473,7 @@
         <v/>
       </c>
       <c r="P120" t="str">
-        <v/>
+        <v>已接猫</v>
       </c>
       <c r="Q120" t="str">
         <v/>
@@ -7487,22 +7487,22 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B121" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C121" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D121" t="str">
         <v>是</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F121" t="str">
-        <v>北京</v>
+        <v>贵州</v>
       </c>
       <c r="G121" t="str">
         <v/>
@@ -7541,27 +7541,27 @@
         <v/>
       </c>
       <c r="S121" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B122" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C122" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D122" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-02-20</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F122" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G122" t="str">
         <v/>
@@ -7605,19 +7605,19 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>阴影色NS12</v>
+        <v>纯黑色</v>
       </c>
       <c r="B123" t="str">
         <v>妹妹</v>
       </c>
       <c r="C123" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D123" t="str">
         <v>否</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-05-28</v>
+        <v>2026-02-20</v>
       </c>
       <c r="F123" t="str">
         <v/>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>阴影色NS11</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B124" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C124" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D124" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F124" t="str">
-        <v>重庆</v>
+        <v/>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B125" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C125" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D125" t="str">
         <v>是</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F125" t="str">
-        <v>中国澳门</v>
+        <v>重庆</v>
       </c>
       <c r="G125" t="str">
         <v/>
@@ -7782,22 +7782,22 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B126" t="str">
         <v>妹妹</v>
       </c>
       <c r="C126" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D126" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F126" t="str">
-        <v/>
+        <v>中国澳门</v>
       </c>
       <c r="G126" t="str">
         <v/>
@@ -7847,7 +7847,7 @@
         <v>妹妹</v>
       </c>
       <c r="C127" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D127" t="str">
         <v>否</v>
@@ -7906,13 +7906,13 @@
         <v>妹妹</v>
       </c>
       <c r="C128" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D128" t="str">
         <v>否</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F128" t="str">
         <v/>
@@ -7962,19 +7962,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B129" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C129" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D129" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F129" t="str">
-        <v>北京</v>
+        <v/>
       </c>
       <c r="G129" t="str">
         <v/>
@@ -8021,19 +8021,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B130" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C130" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D130" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E130" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F130" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G130" t="str">
         <v/>
@@ -8077,13 +8077,13 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B131" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C131" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D131" t="str">
         <v>否</v>
@@ -8139,10 +8139,10 @@
         <v>烟灰色</v>
       </c>
       <c r="B132" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C132" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D132" t="str">
         <v>否</v>
@@ -8198,10 +8198,10 @@
         <v>烟灰色</v>
       </c>
       <c r="B133" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C133" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D133" t="str">
         <v>否</v>
@@ -8254,19 +8254,19 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>纯黑色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B134" t="str">
         <v>弟弟</v>
       </c>
       <c r="C134" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D134" t="str">
         <v>否</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F134" t="str">
         <v/>
@@ -8313,19 +8313,19 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B135" t="str">
         <v>弟弟</v>
       </c>
       <c r="C135" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
       </c>
       <c r="D135" t="str">
         <v>否</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-06-10</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F135" t="str">
         <v/>
@@ -8372,19 +8372,19 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>阴影色NS11</v>
+        <v>银虎斑</v>
       </c>
       <c r="B136" t="str">
         <v>弟弟</v>
       </c>
       <c r="C136" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
       </c>
       <c r="D136" t="str">
         <v>否</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F136" t="str">
         <v/>
@@ -8431,19 +8431,19 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>浅色银虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B137" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C137" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D137" t="str">
         <v>否</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F137" t="str">
         <v/>
@@ -8490,22 +8490,22 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>浅烟灰色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B138" t="str">
         <v>妹妹</v>
       </c>
       <c r="C138" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D138" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F138" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G138" t="str">
         <v/>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>凯米尔色</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B139" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C139" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D139" t="str">
         <v>是</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-02-14</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F139" t="str">
-        <v>上海浦东</v>
+        <v>四川成都</v>
       </c>
       <c r="G139" t="str">
         <v/>
@@ -8608,22 +8608,22 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>银虎斑补丁</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B140" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C140" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D140" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-03-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F140" t="str">
-        <v/>
+        <v>上海浦东</v>
       </c>
       <c r="G140" t="str">
         <v/>
@@ -8667,19 +8667,19 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B141" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C141" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D141" t="str">
         <v>否</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-05-18</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F141" t="str">
         <v/>
@@ -8726,19 +8726,19 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B142" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C142" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D142" t="str">
         <v>否</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-02-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F142" t="str">
         <v/>
@@ -8785,19 +8785,19 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B143" t="str">
         <v>妹妹</v>
       </c>
       <c r="C143" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D143" t="str">
         <v>否</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-05-24</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F143" t="str">
         <v/>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B144" t="str">
         <v>妹妹</v>
       </c>
       <c r="C144" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D144" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F144" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G144" t="str">
         <v/>
@@ -8906,10 +8906,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B145" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C145" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D145" t="str">
         <v>是</v>
@@ -8968,16 +8968,16 @@
         <v>弟弟</v>
       </c>
       <c r="C146" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D146" t="str">
         <v>是</v>
       </c>
       <c r="E146" t="str">
-        <v>2025-11-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F146" t="str">
-        <v>韩国</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -9024,19 +9024,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B147" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C147" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D147" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-05-18</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F147" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -9080,22 +9080,22 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B148" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C148" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D148" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F148" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G148" t="str">
         <v/>
@@ -9142,19 +9142,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B149" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C149" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D149" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F149" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G149" t="str">
         <v/>
@@ -9198,19 +9198,19 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B150" t="str">
         <v>妹妹</v>
       </c>
       <c r="C150" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D150" t="str">
         <v>否</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F150" t="str">
         <v/>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B151" t="str">
         <v>妹妹</v>
       </c>
       <c r="C151" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
       </c>
       <c r="D151" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E151" t="str">
         <v>2026-03-05</v>
       </c>
       <c r="F151" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G151" t="str">
         <v/>
@@ -9316,22 +9316,22 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B152" t="str">
         <v>妹妹</v>
       </c>
       <c r="C152" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D152" t="str">
         <v>是</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F152" t="str">
-        <v>河北邢台</v>
+        <v>韩国</v>
       </c>
       <c r="G152" t="str">
         <v/>
@@ -9375,13 +9375,13 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>棕虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B153" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C153" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D153" t="str">
         <v>是</v>
@@ -9390,7 +9390,7 @@
         <v>2026-06-05</v>
       </c>
       <c r="F153" t="str">
-        <v>四川自贡</v>
+        <v>河北邢台</v>
       </c>
       <c r="G153" t="str">
         <v/>
@@ -9434,22 +9434,22 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B154" t="str">
         <v>弟弟</v>
       </c>
       <c r="C154" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D154" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F154" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G154" t="str">
         <v/>
@@ -9493,13 +9493,13 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>棕虎斑补丁</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B155" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C155" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785843237517-ga449iqess5.jpg</v>
       </c>
       <c r="D155" t="str">
         <v>否</v>
@@ -9552,19 +9552,19 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B156" t="str">
         <v>妹妹</v>
       </c>
       <c r="C156" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D156" t="str">
         <v>否</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F156" t="str">
         <v/>
@@ -9611,19 +9611,19 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B157" t="str">
         <v>妹妹</v>
       </c>
       <c r="C157" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D157" t="str">
         <v>否</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-03-05</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F157" t="str">
         <v/>
@@ -9676,7 +9676,7 @@
         <v>妹妹</v>
       </c>
       <c r="C158" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D158" t="str">
         <v>否</v>
@@ -9729,52 +9729,52 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B159" t="str">
         <v>妹妹</v>
       </c>
       <c r="C159" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D159" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-02-20</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F159" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G159" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H159" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I159" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J159" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K159" t="str">
         <v/>
       </c>
       <c r="L159" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M159" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N159" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O159" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P159" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q159" t="str">
         <v/>
@@ -9783,57 +9783,57 @@
         <v/>
       </c>
       <c r="S159" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B160" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C160" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D160" t="str">
         <v>是</v>
       </c>
       <c r="E160" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F160" t="str">
-        <v>广东广州</v>
+        <v>荷兰</v>
       </c>
       <c r="G160" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H160" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I160" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J160" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K160" t="str">
         <v/>
       </c>
       <c r="L160" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M160" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N160" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O160" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P160" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q160" t="str">
         <v/>
@@ -9842,7 +9842,7 @@
         <v/>
       </c>
       <c r="S160" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="161">
@@ -9853,7 +9853,7 @@
         <v>弟弟</v>
       </c>
       <c r="C161" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D161" t="str">
         <v>是</v>
@@ -9906,13 +9906,13 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B162" t="str">
         <v>弟弟</v>
       </c>
       <c r="C162" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D162" t="str">
         <v>是</v>
@@ -9921,7 +9921,7 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>山西朔州</v>
+        <v>广东广州</v>
       </c>
       <c r="G162" t="str">
         <v/>
@@ -9968,10 +9968,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B163" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C163" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D163" t="str">
         <v>是</v>
@@ -9980,7 +9980,7 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>浙江宁波</v>
+        <v>山西朔州</v>
       </c>
       <c r="G163" t="str">
         <v/>
@@ -10027,10 +10027,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B164" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C164" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D164" t="str">
         <v>是</v>
@@ -10039,7 +10039,7 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>陕西西安</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G164" t="str">
         <v/>
@@ -10089,7 +10089,7 @@
         <v>弟弟</v>
       </c>
       <c r="C165" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D165" t="str">
         <v>是</v>
@@ -10098,7 +10098,7 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>黑龙江漠河</v>
+        <v>陕西西安</v>
       </c>
       <c r="G165" t="str">
         <v/>
@@ -10142,13 +10142,13 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B166" t="str">
         <v>弟弟</v>
       </c>
       <c r="C166" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D166" t="str">
         <v>是</v>
@@ -10157,7 +10157,7 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>日本</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G166" t="str">
         <v/>
@@ -10201,13 +10201,13 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B167" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C167" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D167" t="str">
         <v>是</v>
@@ -10216,7 +10216,7 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>浙江杭州</v>
+        <v>日本</v>
       </c>
       <c r="G167" t="str">
         <v/>
@@ -10266,7 +10266,7 @@
         <v>妹妹</v>
       </c>
       <c r="C168" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D168" t="str">
         <v>是</v>
@@ -10275,7 +10275,7 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>贵州安顺</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G168" t="str">
         <v/>
@@ -10325,7 +10325,7 @@
         <v>妹妹</v>
       </c>
       <c r="C169" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D169" t="str">
         <v>是</v>
@@ -10334,7 +10334,7 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>山东青岛</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G169" t="str">
         <v/>
@@ -10381,10 +10381,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B170" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C170" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D170" t="str">
         <v>是</v>
@@ -10393,7 +10393,7 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>黑龙江漠河</v>
+        <v>山东青岛</v>
       </c>
       <c r="G170" t="str">
         <v/>
@@ -10437,13 +10437,13 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B171" t="str">
         <v>弟弟</v>
       </c>
       <c r="C171" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D171" t="str">
         <v>是</v>
@@ -10452,7 +10452,7 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>河南鹤壁</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G171" t="str">
         <v/>
@@ -10496,13 +10496,13 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>银虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B172" t="str">
         <v>弟弟</v>
       </c>
       <c r="C172" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D172" t="str">
         <v>是</v>
@@ -10511,7 +10511,7 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>陕西西安</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G172" t="str">
         <v/>
@@ -10555,13 +10555,13 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B173" t="str">
         <v>弟弟</v>
       </c>
       <c r="C173" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D173" t="str">
         <v>是</v>
@@ -10570,7 +10570,7 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>四川成都</v>
+        <v>陕西西安</v>
       </c>
       <c r="G173" t="str">
         <v/>
@@ -10614,19 +10614,19 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B174" t="str">
         <v>弟弟</v>
       </c>
       <c r="C174" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
       </c>
       <c r="D174" t="str">
         <v>是</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F174" t="str">
         <v>四川成都</v>
@@ -10673,22 +10673,22 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B175" t="str">
         <v>弟弟</v>
       </c>
       <c r="C175" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
       </c>
       <c r="D175" t="str">
         <v>是</v>
       </c>
       <c r="E175" t="str">
-        <v/>
+        <v>2026-05-18</v>
       </c>
       <c r="F175" t="str">
-        <v>新加坡</v>
+        <v>四川成都</v>
       </c>
       <c r="G175" t="str">
         <v/>
@@ -10732,13 +10732,13 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B176" t="str">
         <v>弟弟</v>
       </c>
       <c r="C176" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
       </c>
       <c r="D176" t="str">
         <v>是</v>
@@ -10747,7 +10747,7 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>上海浦东</v>
+        <v>新加坡</v>
       </c>
       <c r="G176" t="str">
         <v/>
@@ -10791,22 +10791,22 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B177" t="str">
         <v>弟弟</v>
       </c>
       <c r="C177" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
       </c>
       <c r="D177" t="str">
         <v>是</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F177" t="str">
-        <v>浙江温州</v>
+        <v>上海浦东</v>
       </c>
       <c r="G177" t="str">
         <v/>
@@ -10853,19 +10853,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B178" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C178" t="str">
-        <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
       </c>
       <c r="D178" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E178" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F178" t="str">
-        <v/>
+        <v>浙江温州</v>
       </c>
       <c r="G178" t="str">
         <v/>
@@ -10904,12 +10904,71 @@
         <v/>
       </c>
       <c r="S178" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B179" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C179" t="str">
+        <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
+      </c>
+      <c r="D179" t="str">
+        <v>否</v>
+      </c>
+      <c r="E179" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F179" t="str">
+        <v/>
+      </c>
+      <c r="G179" t="str">
+        <v/>
+      </c>
+      <c r="H179" t="str">
+        <v/>
+      </c>
+      <c r="I179" t="str">
+        <v/>
+      </c>
+      <c r="J179" t="str">
+        <v/>
+      </c>
+      <c r="K179" t="str">
+        <v/>
+      </c>
+      <c r="L179" t="str">
+        <v/>
+      </c>
+      <c r="M179" t="str">
+        <v/>
+      </c>
+      <c r="N179" t="str">
+        <v/>
+      </c>
+      <c r="O179" t="str">
+        <v/>
+      </c>
+      <c r="P179" t="str">
+        <v/>
+      </c>
+      <c r="Q179" t="str">
+        <v/>
+      </c>
+      <c r="R179" t="str">
+        <v/>
+      </c>
+      <c r="S179" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S178"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S179"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -534,13 +534,13 @@
         <v>assets/1789654858942-ws3mqfv0zf.jpg</v>
       </c>
       <c r="D3" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E3" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>浙江杭州</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -711,13 +711,13 @@
         <v>assets/1789654628929-2wok5d7b71.jpg</v>
       </c>
       <c r="D6" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E6" t="str">
         <v>2026-05-18</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>新加坡</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -1065,13 +1065,13 @@
         <v>assets/1788442221802-et3crh0tww.jpg</v>
       </c>
       <c r="D12" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E12" t="str">
         <v>2026-03-21</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>成都</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1360,13 +1360,13 @@
         <v>assets/1788013810551-b90h1mwfiq.jpg</v>
       </c>
       <c r="D17" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E17" t="str">
         <v>2026-06-26</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>新疆</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1478,13 +1478,13 @@
         <v>assets/1787837846581-6q9nxgad35.jpg</v>
       </c>
       <c r="D19" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E19" t="str">
         <v>2026-06-10</v>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>天津</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1832,13 +1832,13 @@
         <v>assets/1787479242639-32zuh5lham.jpg</v>
       </c>
       <c r="D25" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E25" t="str">
         <v>2026-06-10</v>
       </c>
       <c r="F25" t="str">
-        <v/>
+        <v>天津</v>
       </c>
       <c r="G25" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -1534,7 +1534,7 @@
         <v>弟弟</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1787837779354-hkuyvt39iz.jpg</v>
+        <v>assets/1790733533511-l0g7pujklm.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>否</v>
@@ -7617,7 +7617,7 @@
         <v>否</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-02-20</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F123" t="str">
         <v/>
@@ -8145,13 +8145,13 @@
         <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D132" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E132" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F132" t="str">
-        <v/>
+        <v>河北石家庄</v>
       </c>
       <c r="G132" t="str">
         <v/>
@@ -8204,13 +8204,13 @@
         <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D133" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E133" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F133" t="str">
-        <v/>
+        <v>浙江宁波</v>
       </c>
       <c r="G133" t="str">
         <v/>
@@ -8263,13 +8263,13 @@
         <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D134" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E134" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F134" t="str">
-        <v/>
+        <v>上海</v>
       </c>
       <c r="G134" t="str">
         <v/>
@@ -8319,13 +8319,13 @@
         <v>弟弟</v>
       </c>
       <c r="C135" t="str">
-        <v>assets/1787282349942-2cfuyn7xlc.jpg</v>
+        <v>assets/1790733778469-jt9fswxe9w.jpg</v>
       </c>
       <c r="D135" t="str">
         <v>否</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-03-21</v>
+        <v>2026-04-17</v>
       </c>
       <c r="F135" t="str">
         <v/>
@@ -8378,7 +8378,7 @@
         <v>弟弟</v>
       </c>
       <c r="C136" t="str">
-        <v>assets/1787282064159-6b4z8c5msd.jpg</v>
+        <v>assets/1790734215453-0zvw0v9uja.jpg</v>
       </c>
       <c r="D136" t="str">
         <v>否</v>
@@ -8499,13 +8499,13 @@
         <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D138" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E138" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="F138" t="str">
-        <v/>
+        <v>香港</v>
       </c>
       <c r="G138" t="str">
         <v/>
@@ -8679,7 +8679,7 @@
         <v>否</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-03-05</v>
+        <v>2026-04-09</v>
       </c>
       <c r="F141" t="str">
         <v/>
@@ -8735,13 +8735,13 @@
         <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D142" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E142" t="str">
         <v>2026-05-18</v>
       </c>
       <c r="F142" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -9263,13 +9263,13 @@
         <v>妹妹</v>
       </c>
       <c r="C151" t="str">
-        <v>assets/1785842779532-5u1j0igrw1s.jpg</v>
+        <v>assets/1790733648123-636cut584p.jpg</v>
       </c>
       <c r="D151" t="str">
         <v>否</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-03-05</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F151" t="str">
         <v/>
@@ -9499,7 +9499,7 @@
         <v>弟弟</v>
       </c>
       <c r="C155" t="str">
-        <v>assets/1785843237517-ga449iqess5.jpg</v>
+        <v>assets/1790734248143-kaxbucmf2v.jpg</v>
       </c>
       <c r="D155" t="str">
         <v>否</v>
@@ -9682,7 +9682,7 @@
         <v>否</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-03-05</v>
+        <v>2026-04-17</v>
       </c>
       <c r="F158" t="str">
         <v/>
@@ -9741,7 +9741,7 @@
         <v>否</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-03-05</v>
+        <v>2026-04-30</v>
       </c>
       <c r="F159" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S179"/>
+  <dimension ref="A1:S184"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -466,19 +466,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>阴影色NS11</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B2" t="str">
         <v>弟弟</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1789655131156-6ywyod2pgz.jpg</v>
+        <v>assets/1790734752606-rusbv65ug8.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>否</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-06-15</v>
+        <v>2026-04-28</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -525,22 +525,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>浅银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B3" t="str">
         <v>妹妹</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1789654858942-ws3mqfv0zf.jpg</v>
+        <v>assets/1790734688874-ldibzixi2g.jpg</v>
       </c>
       <c r="D3" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F3" t="str">
-        <v>浙江杭州</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -584,19 +584,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B4" t="str">
         <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1789654723483-fyl8c7wdqg.jpg</v>
+        <v>assets/1790734651251-a58tdtmhnx.jpg</v>
       </c>
       <c r="D4" t="str">
         <v>否</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-06-26</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -643,19 +643,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>银虎班补丁</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B5" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1789654675792-6d4kyyncmf.jpg</v>
+        <v>assets/1790734595573-u465hv1hyg.jpg</v>
       </c>
       <c r="D5" t="str">
         <v>否</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -702,22 +702,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>烟灰色</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B6" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1789654628929-2wok5d7b71.jpg</v>
+        <v>assets/1790734548586-cztim8ip4y.jpg</v>
       </c>
       <c r="D6" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F6" t="str">
-        <v>新加坡</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -761,19 +761,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>阴影色NS11</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B7" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1789654549268-68uab4pdoy.jpg</v>
+        <v>assets/1790734499008-43htmo2xuw.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>否</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-06-15</v>
+        <v>2026-03-20</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -820,19 +820,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>阴影色NS12</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B8" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1788534744815-pzs6jqs2pm.jpg</v>
+        <v>assets/1789655131156-6ywyod2pgz.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>否</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -879,22 +879,22 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>棕虎斑</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B9" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1788534522775-my4ggv0pwo.jpg</v>
+        <v>assets/1789654858942-ws3mqfv0zf.jpg</v>
       </c>
       <c r="D9" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E9" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>浙江杭州</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -944,7 +944,7 @@
         <v>弟弟</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1788442386268-ilpasqz91m.jpg</v>
+        <v>assets/1789654723483-fyl8c7wdqg.jpg</v>
       </c>
       <c r="D10" t="str">
         <v>否</v>
@@ -997,19 +997,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>浅银虎斑</v>
+        <v>银虎班补丁</v>
       </c>
       <c r="B11" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1788442356842-bbleakpy85.jpg</v>
+        <v>assets/1789654675792-6d4kyyncmf.jpg</v>
       </c>
       <c r="D11" t="str">
         <v>否</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1056,22 +1056,22 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>浅烟灰色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B12" t="str">
         <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1788442221802-et3crh0tww.jpg</v>
+        <v>assets/1789654628929-2wok5d7b71.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>是</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-03-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F12" t="str">
-        <v>成都</v>
+        <v>新加坡</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1115,22 +1115,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>凯米尔</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B13" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1788014088852-oqkg79cki9.jpg</v>
+        <v>assets/1789654549268-68uab4pdoy.jpg</v>
       </c>
       <c r="D13" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F13" t="str">
-        <v>湖北襄阳</v>
+        <v/>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1174,19 +1174,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B14" t="str">
         <v>妹妹</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1788014050978-9a2sguuo1u.jpg</v>
+        <v>assets/1788534744815-pzs6jqs2pm.jpg</v>
       </c>
       <c r="D14" t="str">
         <v>否</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -1239,16 +1239,16 @@
         <v>弟弟</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1788013924404-gmlh0hfjae.jpg</v>
+        <v>assets/1788534522775-my4ggv0pwo.jpg</v>
       </c>
       <c r="D15" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E15" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="F15" t="str">
-        <v>浙江嘉兴</v>
+        <v/>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1292,22 +1292,22 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>凯米尔色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B16" t="str">
         <v>弟弟</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1788013889955-wpykaycfde.jpg</v>
+        <v>assets/1788442386268-ilpasqz91m.jpg</v>
       </c>
       <c r="D16" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E16" t="str">
         <v>2026-06-26</v>
       </c>
       <c r="F16" t="str">
-        <v>湖北襄阳</v>
+        <v/>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1351,22 +1351,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B17" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1788013810551-b90h1mwfiq.jpg</v>
+        <v>assets/1788442356842-bbleakpy85.jpg</v>
       </c>
       <c r="D17" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F17" t="str">
-        <v>新疆</v>
+        <v/>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1410,22 +1410,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>银虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B18" t="str">
         <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1787837910484-r7urrsuib0.jpg</v>
+        <v>assets/1788442221802-et3crh0tww.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>是</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-05-18</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F18" t="str">
-        <v>香港</v>
+        <v>成都</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1469,22 +1469,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>纯黑色</v>
+        <v>凯米尔</v>
       </c>
       <c r="B19" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1787837846581-6q9nxgad35.jpg</v>
+        <v>assets/1788014088852-oqkg79cki9.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>是</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F19" t="str">
-        <v>天津</v>
+        <v>湖北襄阳</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1528,19 +1528,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>凯米尔</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B20" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1790733533511-l0g7pujklm.jpg</v>
+        <v>assets/1788014050978-9a2sguuo1u.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>否</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B21" t="str">
         <v>弟弟</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
+        <v>assets/1788013924404-gmlh0hfjae.jpg</v>
       </c>
       <c r="D21" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>浙江嘉兴</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1646,22 +1646,22 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B22" t="str">
         <v>弟弟</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1787837648423-9riberz3tq.jpg</v>
+        <v>assets/1788013889955-wpykaycfde.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>是</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F22" t="str">
-        <v>北京</v>
+        <v>湖北襄阳</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1705,22 +1705,22 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B23" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
+        <v>assets/1788013810551-b90h1mwfiq.jpg</v>
       </c>
       <c r="D23" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F23" t="str">
-        <v/>
+        <v>新疆</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1764,22 +1764,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B24" t="str">
         <v>弟弟</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1787479268842-7en9nzy302.jpg</v>
+        <v>assets/1787837910484-r7urrsuib0.jpg</v>
       </c>
       <c r="D24" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-06-10</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F24" t="str">
-        <v/>
+        <v>香港</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1791,7 +1791,7 @@
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>2026-06-10</v>
+        <v/>
       </c>
       <c r="K24" t="str">
         <v/>
@@ -1829,7 +1829,7 @@
         <v>妹妹</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1787479242639-32zuh5lham.jpg</v>
+        <v>assets/1787837846581-6q9nxgad35.jpg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
@@ -1882,22 +1882,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B26" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1787466121255-21jto2cugv.jpg</v>
+        <v>assets/1790734407566-tge3si2tw9.jpg</v>
       </c>
       <c r="D26" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E26" t="str">
-        <v/>
+        <v>2026-06-26</v>
       </c>
       <c r="F26" t="str">
-        <v>四川广安</v>
+        <v/>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1944,10 +1944,10 @@
         <v>烟灰色</v>
       </c>
       <c r="B27" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
+        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
       </c>
       <c r="D27" t="str">
         <v>否</v>
@@ -2003,19 +2003,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B28" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1787388277490-e6u506cx0r.jpg</v>
+        <v>assets/1787837648423-9riberz3tq.jpg</v>
       </c>
       <c r="D28" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E28" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B29" t="str">
         <v>弟弟</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1787328436957-x30od0gw28.jpg</v>
+        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
       </c>
       <c r="D29" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F29" t="str">
-        <v>江苏苏州</v>
+        <v/>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2118,22 +2118,22 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B30" t="str">
         <v>弟弟</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
+        <v>assets/1787479268842-7en9nzy302.jpg</v>
       </c>
       <c r="D30" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E30" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F30" t="str">
-        <v>辽宁东港</v>
+        <v/>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2145,7 +2145,7 @@
         <v/>
       </c>
       <c r="J30" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="K30" t="str">
         <v/>
@@ -2177,22 +2177,22 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B31" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1787327967245-m62ohievcl.jpg</v>
+        <v>assets/1787479242639-32zuh5lham.jpg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
       </c>
       <c r="E31" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F31" t="str">
-        <v>福建福州</v>
+        <v>天津</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2236,13 +2236,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B32" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
+        <v>assets/1787466121255-21jto2cugv.jpg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
@@ -2251,7 +2251,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>上海</v>
+        <v>四川广安</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2295,22 +2295,22 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>纯蓝色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B33" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1787327793837-znk2knoo6p.jpg</v>
+        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
       </c>
       <c r="D33" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E33" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F33" t="str">
-        <v>河南鹤壁</v>
+        <v/>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B34" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1787327752832-kkpmp21os3.jpg</v>
+        <v>assets/1787388277490-e6u506cx0r.jpg</v>
       </c>
       <c r="D34" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E34" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F34" t="str">
-        <v>陕西西安</v>
+        <v/>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2416,10 +2416,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B35" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
+        <v>assets/1787328436957-x30od0gw28.jpg</v>
       </c>
       <c r="D35" t="str">
         <v>是</v>
@@ -2428,7 +2428,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>陕西西安</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B36" t="str">
         <v>弟弟</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1787327573762-h23cux94p2.jpg</v>
+        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
       </c>
       <c r="D36" t="str">
         <v>是</v>
@@ -2487,7 +2487,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>北京</v>
+        <v>辽宁东港</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B37" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1787327496557-9daggljg4g.jpg</v>
+        <v>assets/1787327967245-m62ohievcl.jpg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
@@ -2546,7 +2546,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>黑龙江哈尔滨</v>
+        <v>福建福州</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2590,13 +2590,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B38" t="str">
         <v>弟弟</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
+        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>甘肃嘉峪关</v>
+        <v>上海</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>蓝虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B39" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
+        <v>assets/1787327793837-znk2knoo6p.jpg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2664,7 +2664,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>安徽合肥</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2714,7 +2714,7 @@
         <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1787327337811-u5u2pdew3.jpg</v>
+        <v>assets/1787327752832-kkpmp21os3.jpg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2723,7 +2723,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>安徽合肥</v>
+        <v>陕西西安</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2767,13 +2767,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B41" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1787327309143-6c1dan1sev.jpg</v>
+        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
       </c>
       <c r="D41" t="str">
         <v>是</v>
@@ -2782,7 +2782,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>四川成都</v>
+        <v>陕西西安</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2832,7 +2832,7 @@
         <v>弟弟</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1787327277453-w89ujg69fm.jpg</v>
+        <v>assets/1787327573762-h23cux94p2.jpg</v>
       </c>
       <c r="D42" t="str">
         <v>是</v>
@@ -2841,7 +2841,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>四川成都</v>
+        <v>北京</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2885,13 +2885,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>蓝银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B43" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1787327232159-lkrcl588a5.jpg</v>
+        <v>assets/1787327496557-9daggljg4g.jpg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
@@ -2900,7 +2900,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>四川成都</v>
+        <v>黑龙江哈尔滨</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>玳瑁色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B44" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1787327182347-3az0z7sys2.jpg</v>
+        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>四川内江</v>
+        <v>甘肃嘉峪关</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3003,13 +3003,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>棕虎补丁</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B45" t="str">
         <v>妹妹</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
+        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
@@ -3018,7 +3018,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>贵州贵阳</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>黑烟色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B46" t="str">
         <v>弟弟</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1787327101790-tqjlseog5y.jpg</v>
+        <v>assets/1787327337811-u5u2pdew3.jpg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>浙江杭州</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3121,13 +3121,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B47" t="str">
         <v>弟弟</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1787327019632-l1780lu2hj.jpg</v>
+        <v>assets/1787327309143-6c1dan1sev.jpg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>山东威海</v>
+        <v>四川成都</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3180,13 +3180,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B48" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1787326905275-plz3fpgo97.jpg</v>
+        <v>assets/1787327277453-w89ujg69fm.jpg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>浙江杭州</v>
+        <v>四川成都</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>蓝虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B49" t="str">
         <v>弟弟</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
+        <v>assets/1787327232159-lkrcl588a5.jpg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -3298,13 +3298,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>凯米尔色</v>
+        <v>玳瑁色</v>
       </c>
       <c r="B50" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
+        <v>assets/1787327182347-3az0z7sys2.jpg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
@@ -3313,7 +3313,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>四川成都</v>
+        <v>四川内江</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3357,13 +3357,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>凯米尔</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B51" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1787326814713-p5oavnlulg.jpg</v>
+        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
       </c>
       <c r="D51" t="str">
         <v>是</v>
@@ -3372,7 +3372,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>四川成都</v>
+        <v>贵州贵阳</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,13 +3416,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>棕虎斑</v>
+        <v>黑烟色</v>
       </c>
       <c r="B52" t="str">
         <v>弟弟</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1787326773577-13q5out2d0.jpg</v>
+        <v>assets/1787327101790-tqjlseog5y.jpg</v>
       </c>
       <c r="D52" t="str">
         <v>是</v>
@@ -3431,7 +3431,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>四川宜宾</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3475,13 +3475,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>金棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B53" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1787326548993-89s929m2hg.jpg</v>
+        <v>assets/1787327019632-l1780lu2hj.jpg</v>
       </c>
       <c r="D53" t="str">
         <v>是</v>
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>上海</v>
+        <v>山东威海</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3534,13 +3534,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B54" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1787326449218-09s9ucram4.jpg</v>
+        <v>assets/1787326905275-plz3fpgo97.jpg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
@@ -3549,7 +3549,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>德国</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3593,13 +3593,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>棕虎补丁</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B55" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1787326277374-8ti107m5ki.jpg</v>
+        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
@@ -3608,7 +3608,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>广东深圳</v>
+        <v>四川成都</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B56" t="str">
         <v>弟弟</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1787326236952-2pmwche4t3.jpg</v>
+        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
@@ -3667,7 +3667,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>福建泉州</v>
+        <v>四川成都</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3711,13 +3711,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B57" t="str">
         <v>弟弟</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1787326184557-90v6clkwen.jpg</v>
+        <v>assets/1787326814713-p5oavnlulg.jpg</v>
       </c>
       <c r="D57" t="str">
         <v>是</v>
@@ -3726,7 +3726,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>福建福州</v>
+        <v>四川成都</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3773,10 +3773,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B58" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
+        <v>assets/1787326773577-13q5out2d0.jpg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
@@ -3785,7 +3785,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>广西贵港</v>
+        <v>四川宜宾</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>凯米尔色</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B59" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1787325862706-wq18k3ej56.jpg</v>
+        <v>assets/1787326548993-89s929m2hg.jpg</v>
       </c>
       <c r="D59" t="str">
         <v>是</v>
@@ -3844,7 +3844,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>江苏苏州</v>
+        <v>上海</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3894,7 +3894,7 @@
         <v>弟弟</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
+        <v>assets/1787326449218-09s9ucram4.jpg</v>
       </c>
       <c r="D60" t="str">
         <v>是</v>
@@ -3903,7 +3903,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>江苏苏州</v>
+        <v>德国</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3947,13 +3947,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B61" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1787325706797-kgk81ghccy.jpg</v>
+        <v>assets/1787326277374-8ti107m5ki.jpg</v>
       </c>
       <c r="D61" t="str">
         <v>是</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>北京</v>
+        <v>广东深圳</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4006,13 +4006,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B62" t="str">
         <v>弟弟</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
+        <v>assets/1787326236952-2pmwche4t3.jpg</v>
       </c>
       <c r="D62" t="str">
         <v>是</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>上海</v>
+        <v>福建泉州</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4065,13 +4065,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B63" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1787325554341-608thexrne.jpg</v>
+        <v>assets/1787326184557-90v6clkwen.jpg</v>
       </c>
       <c r="D63" t="str">
         <v>是</v>
@@ -4080,7 +4080,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>江苏苏州</v>
+        <v>福建福州</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -4124,13 +4124,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B64" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C64" t="str">
-        <v>assets/1787325480828-q90pskoiw3.jpg</v>
+        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
       </c>
       <c r="D64" t="str">
         <v>是</v>
@@ -4139,7 +4139,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>四川成都</v>
+        <v>广西贵港</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -4183,13 +4183,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>浅色银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B65" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C65" t="str">
-        <v>assets/1787325448999-a2pg8176fu.jpg</v>
+        <v>assets/1787325862706-wq18k3ej56.jpg</v>
       </c>
       <c r="D65" t="str">
         <v>是</v>
@@ -4198,7 +4198,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>中国台湾</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -4242,13 +4242,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B66" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C66" t="str">
-        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
+        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
       </c>
       <c r="D66" t="str">
         <v>是</v>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>浙江杭州</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -4301,13 +4301,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B67" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C67" t="str">
-        <v>assets/1787325237876-t19isaq5gu.jpg</v>
+        <v>assets/1787325706797-kgk81ghccy.jpg</v>
       </c>
       <c r="D67" t="str">
         <v>是</v>
@@ -4316,7 +4316,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>辽宁沈阳</v>
+        <v>北京</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4360,13 +4360,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>金棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B68" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C68" t="str">
-        <v>assets/1787325199931-e7wms9qtya.jpg</v>
+        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
       </c>
       <c r="D68" t="str">
         <v>是</v>
@@ -4375,7 +4375,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>四川成都</v>
+        <v>上海</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -4419,13 +4419,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B69" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C69" t="str">
-        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
+        <v>assets/1787325554341-608thexrne.jpg</v>
       </c>
       <c r="D69" t="str">
         <v>是</v>
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>中国香港</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4478,13 +4478,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>烟灰色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B70" t="str">
         <v>弟弟</v>
       </c>
       <c r="C70" t="str">
-        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
+        <v>assets/1787325480828-q90pskoiw3.jpg</v>
       </c>
       <c r="D70" t="str">
         <v>是</v>
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>中国澳门</v>
+        <v>四川成都</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -4537,13 +4537,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>蓝虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B71" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C71" t="str">
-        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
+        <v>assets/1787325448999-a2pg8176fu.jpg</v>
       </c>
       <c r="D71" t="str">
         <v>是</v>
@@ -4552,7 +4552,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>山东青岛</v>
+        <v>中国台湾</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -4596,13 +4596,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B72" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C72" t="str">
-        <v>assets/1787324954998-w5m5jox439.jpg</v>
+        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
       </c>
       <c r="D72" t="str">
         <v>是</v>
@@ -4611,7 +4611,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>海南海口</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -4655,13 +4655,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B73" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C73" t="str">
-        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
+        <v>assets/1787325237876-t19isaq5gu.jpg</v>
       </c>
       <c r="D73" t="str">
         <v>是</v>
@@ -4670,7 +4670,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>内蒙古</v>
+        <v>辽宁沈阳</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4714,13 +4714,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>烟灰色</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B74" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C74" t="str">
-        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
+        <v>assets/1787325199931-e7wms9qtya.jpg</v>
       </c>
       <c r="D74" t="str">
         <v>是</v>
@@ -4729,7 +4729,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>中国香港</v>
+        <v>四川成都</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4773,13 +4773,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B75" t="str">
         <v>弟弟</v>
       </c>
       <c r="C75" t="str">
-        <v>assets/1787324806613-31yyz14tsf.jpg</v>
+        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
       </c>
       <c r="D75" t="str">
         <v>是</v>
@@ -4788,7 +4788,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>四川成都</v>
+        <v>中国香港</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -4832,13 +4832,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B76" t="str">
         <v>弟弟</v>
       </c>
       <c r="C76" t="str">
-        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
+        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
       </c>
       <c r="D76" t="str">
         <v>是</v>
@@ -4847,7 +4847,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>湖北武汉</v>
+        <v>中国澳门</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4891,13 +4891,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B77" t="str">
         <v>弟弟</v>
       </c>
       <c r="C77" t="str">
-        <v>assets/1787324522658-smn44crast.jpg</v>
+        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
       </c>
       <c r="D77" t="str">
         <v>是</v>
@@ -4906,7 +4906,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>湖北武汉</v>
+        <v>山东青岛</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4950,13 +4950,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B78" t="str">
         <v>弟弟</v>
       </c>
       <c r="C78" t="str">
-        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
+        <v>assets/1787324954998-w5m5jox439.jpg</v>
       </c>
       <c r="D78" t="str">
         <v>是</v>
@@ -4965,7 +4965,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>新疆</v>
+        <v>海南海口</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -5009,13 +5009,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>浅凯米尔</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B79" t="str">
         <v>弟弟</v>
       </c>
       <c r="C79" t="str">
-        <v>assets/1787324331029-d74lcuycf6.jpg</v>
+        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
       </c>
       <c r="D79" t="str">
         <v>是</v>
@@ -5024,7 +5024,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>四川成都</v>
+        <v>内蒙古</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -5068,13 +5068,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B80" t="str">
         <v>弟弟</v>
       </c>
       <c r="C80" t="str">
-        <v>assets/1787324297469-ans1lse2l5.jpg</v>
+        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
       </c>
       <c r="D80" t="str">
         <v>是</v>
@@ -5083,7 +5083,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>四川乐山</v>
+        <v>中国香港</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -5127,13 +5127,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B81" t="str">
         <v>弟弟</v>
       </c>
       <c r="C81" t="str">
-        <v>assets/1787324256827-7w383z4bg1.jpg</v>
+        <v>assets/1787324806613-31yyz14tsf.jpg</v>
       </c>
       <c r="D81" t="str">
         <v>是</v>
@@ -5142,7 +5142,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>中国台湾</v>
+        <v>四川成都</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -5186,13 +5186,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B82" t="str">
         <v>弟弟</v>
       </c>
       <c r="C82" t="str">
-        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
+        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
       </c>
       <c r="D82" t="str">
         <v>是</v>
@@ -5201,7 +5201,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>四川成都</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -5245,13 +5245,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>凯米尔色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B83" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C83" t="str">
-        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
+        <v>assets/1787324522658-smn44crast.jpg</v>
       </c>
       <c r="D83" t="str">
         <v>是</v>
@@ -5260,7 +5260,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>江苏南京</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -5310,7 +5310,7 @@
         <v>弟弟</v>
       </c>
       <c r="C84" t="str">
-        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
+        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
       </c>
       <c r="D84" t="str">
         <v>是</v>
@@ -5319,7 +5319,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>江苏南京</v>
+        <v>新疆</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -5363,13 +5363,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>银虎斑</v>
+        <v>浅凯米尔</v>
       </c>
       <c r="B85" t="str">
         <v>弟弟</v>
       </c>
       <c r="C85" t="str">
-        <v>assets/1787323318612-soge38hpsf.jpg</v>
+        <v>assets/1787324331029-d74lcuycf6.jpg</v>
       </c>
       <c r="D85" t="str">
         <v>是</v>
@@ -5378,7 +5378,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>上海</v>
+        <v>四川成都</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -5422,13 +5422,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B86" t="str">
         <v>弟弟</v>
       </c>
       <c r="C86" t="str">
-        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
+        <v>assets/1787324297469-ans1lse2l5.jpg</v>
       </c>
       <c r="D86" t="str">
         <v>是</v>
@@ -5437,7 +5437,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>四川成都</v>
+        <v>四川乐山</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -5481,13 +5481,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B87" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C87" t="str">
-        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
+        <v>assets/1787324256827-7w383z4bg1.jpg</v>
       </c>
       <c r="D87" t="str">
         <v>是</v>
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>浙江宁波</v>
+        <v>中国台湾</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -5540,13 +5540,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>银虎斑补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B88" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C88" t="str">
-        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
+        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
       </c>
       <c r="D88" t="str">
         <v>是</v>
@@ -5555,7 +5555,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>马来西亚</v>
+        <v>四川成都</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -5599,13 +5599,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B89" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C89" t="str">
-        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
+        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
       </c>
       <c r="D89" t="str">
         <v>是</v>
@@ -5614,7 +5614,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>陕西西安</v>
+        <v>江苏南京</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -5658,13 +5658,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B90" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C90" t="str">
-        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
+        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
       </c>
       <c r="D90" t="str">
         <v>是</v>
@@ -5673,7 +5673,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>广西南宁</v>
+        <v>江苏南京</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -5717,13 +5717,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B91" t="str">
         <v>弟弟</v>
       </c>
       <c r="C91" t="str">
-        <v>assets/1787322760950-gn3qgego4s.jpg</v>
+        <v>assets/1787323318612-soge38hpsf.jpg</v>
       </c>
       <c r="D91" t="str">
         <v>是</v>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>广西南宁</v>
+        <v>上海</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -5776,13 +5776,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B92" t="str">
         <v>弟弟</v>
       </c>
       <c r="C92" t="str">
-        <v>assets/1787322605982-04n50xegt2.jpg</v>
+        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
       </c>
       <c r="D92" t="str">
         <v>是</v>
@@ -5791,7 +5791,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>上海</v>
+        <v>四川成都</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -5835,13 +5835,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B93" t="str">
         <v>妹妹</v>
       </c>
       <c r="C93" t="str">
-        <v>assets/1787322490045-kog3ru43dy.jpg</v>
+        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
       </c>
       <c r="D93" t="str">
         <v>是</v>
@@ -5850,7 +5850,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>上海</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -5894,13 +5894,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B94" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C94" t="str">
-        <v>assets/1787322419996-0m33yx89nm.jpg</v>
+        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
       </c>
       <c r="D94" t="str">
         <v>是</v>
@@ -5909,7 +5909,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>广东广州</v>
+        <v>马来西亚</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -5953,13 +5953,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B95" t="str">
         <v>弟弟</v>
       </c>
       <c r="C95" t="str">
-        <v>assets/1787322377730-vj5csj2mll.jpg</v>
+        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
       </c>
       <c r="D95" t="str">
         <v>是</v>
@@ -5968,7 +5968,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>柬埔寨</v>
+        <v>陕西西安</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -6012,13 +6012,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>蓝虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B96" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C96" t="str">
-        <v>assets/1787322269611-53yaj5ideu.jpg</v>
+        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
       </c>
       <c r="D96" t="str">
         <v>是</v>
@@ -6027,7 +6027,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>山东枣庄</v>
+        <v>广西南宁</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -6071,13 +6071,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B97" t="str">
         <v>弟弟</v>
       </c>
       <c r="C97" t="str">
-        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
+        <v>assets/1787322760950-gn3qgego4s.jpg</v>
       </c>
       <c r="D97" t="str">
         <v>是</v>
@@ -6086,7 +6086,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>陕西西安</v>
+        <v>广西南宁</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -6130,13 +6130,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B98" t="str">
         <v>弟弟</v>
       </c>
       <c r="C98" t="str">
-        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
+        <v>assets/1787322605982-04n50xegt2.jpg</v>
       </c>
       <c r="D98" t="str">
         <v>是</v>
@@ -6145,7 +6145,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>山东东营</v>
+        <v>上海</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -6189,13 +6189,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>凯米尔色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B99" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C99" t="str">
-        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
+        <v>assets/1787322490045-kog3ru43dy.jpg</v>
       </c>
       <c r="D99" t="str">
         <v>是</v>
@@ -6204,7 +6204,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>中国台湾</v>
+        <v>上海</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -6248,13 +6248,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>烟灰色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B100" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C100" t="str">
-        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
+        <v>assets/1787322419996-0m33yx89nm.jpg</v>
       </c>
       <c r="D100" t="str">
         <v>是</v>
@@ -6263,7 +6263,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>中国台湾</v>
+        <v>广东广州</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -6307,13 +6307,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B101" t="str">
         <v>弟弟</v>
       </c>
       <c r="C101" t="str">
-        <v>assets/1787321834306-efgnyhujon.jpg</v>
+        <v>assets/1787322377730-vj5csj2mll.jpg</v>
       </c>
       <c r="D101" t="str">
         <v>是</v>
@@ -6322,7 +6322,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>北京</v>
+        <v>柬埔寨</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -6366,13 +6366,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B102" t="str">
         <v>弟弟</v>
       </c>
       <c r="C102" t="str">
-        <v>assets/1787321439916-uttgpbkogb.jpg</v>
+        <v>assets/1787322269611-53yaj5ideu.jpg</v>
       </c>
       <c r="D102" t="str">
         <v>是</v>
@@ -6381,7 +6381,7 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>安徽合肥</v>
+        <v>山东枣庄</v>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -6431,7 +6431,7 @@
         <v>弟弟</v>
       </c>
       <c r="C103" t="str">
-        <v>assets/1787321419210-51hhgurygq.jpg</v>
+        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
       </c>
       <c r="D103" t="str">
         <v>是</v>
@@ -6440,7 +6440,7 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>上海</v>
+        <v>陕西西安</v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -6484,13 +6484,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B104" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C104" t="str">
-        <v>assets/1787321363369-bzjn51j5il.jpg</v>
+        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
       </c>
       <c r="D104" t="str">
         <v>是</v>
@@ -6499,7 +6499,7 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>中国台湾</v>
+        <v>山东东营</v>
       </c>
       <c r="G104" t="str">
         <v/>
@@ -6543,13 +6543,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B105" t="str">
         <v>弟弟</v>
       </c>
       <c r="C105" t="str">
-        <v>assets/1787321332559-87p6spuch3.jpg</v>
+        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
       </c>
       <c r="D105" t="str">
         <v>是</v>
@@ -6602,13 +6602,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B106" t="str">
         <v>妹妹</v>
       </c>
       <c r="C106" t="str">
-        <v>assets/1787321232531-59lnzv8y98.jpg</v>
+        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
       </c>
       <c r="D106" t="str">
         <v>是</v>
@@ -6617,7 +6617,7 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G106" t="str">
         <v/>
@@ -6664,10 +6664,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B107" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C107" t="str">
-        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
+        <v>assets/1787321834306-efgnyhujon.jpg</v>
       </c>
       <c r="D107" t="str">
         <v>是</v>
@@ -6676,7 +6676,7 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>浙江宁波</v>
+        <v>北京</v>
       </c>
       <c r="G107" t="str">
         <v/>
@@ -6723,10 +6723,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B108" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C108" t="str">
-        <v>assets/1787319800704-v3qeu062ak.jpg</v>
+        <v>assets/1787321439916-uttgpbkogb.jpg</v>
       </c>
       <c r="D108" t="str">
         <v>是</v>
@@ -6735,7 +6735,7 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>河北唐山</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G108" t="str">
         <v/>
@@ -6782,10 +6782,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B109" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C109" t="str">
-        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
+        <v>assets/1787321419210-51hhgurygq.jpg</v>
       </c>
       <c r="D109" t="str">
         <v>是</v>
@@ -6794,7 +6794,7 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>河北石家庄</v>
+        <v>上海</v>
       </c>
       <c r="G109" t="str">
         <v/>
@@ -6838,13 +6838,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>棕虎补丁</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B110" t="str">
         <v>妹妹</v>
       </c>
       <c r="C110" t="str">
-        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
+        <v>assets/1787321363369-bzjn51j5il.jpg</v>
       </c>
       <c r="D110" t="str">
         <v>是</v>
@@ -6853,7 +6853,7 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>韩国</v>
+        <v>中国台湾</v>
       </c>
       <c r="G110" t="str">
         <v/>
@@ -6897,13 +6897,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>蓝银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B111" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C111" t="str">
-        <v>assets/1787319501376-xscwljnu1j.jpg</v>
+        <v>assets/1787321332559-87p6spuch3.jpg</v>
       </c>
       <c r="D111" t="str">
         <v>是</v>
@@ -6912,7 +6912,7 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>美国</v>
+        <v>中国台湾</v>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -6962,7 +6962,7 @@
         <v>妹妹</v>
       </c>
       <c r="C112" t="str">
-        <v>assets/1787319443529-4a0zqikufx.jpg</v>
+        <v>assets/1787321232531-59lnzv8y98.jpg</v>
       </c>
       <c r="D112" t="str">
         <v>是</v>
@@ -6971,7 +6971,7 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>中国台湾</v>
+        <v>北京</v>
       </c>
       <c r="G112" t="str">
         <v/>
@@ -7015,13 +7015,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B113" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C113" t="str">
-        <v>assets/1787319356194-lr2d5680i9.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D113" t="str">
         <v>是</v>
@@ -7030,7 +7030,7 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>中国台湾</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -7074,13 +7074,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B114" t="str">
         <v>妹妹</v>
       </c>
       <c r="C114" t="str">
-        <v>assets/1787319208828-aizqo4blcv.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D114" t="str">
         <v>是</v>
@@ -7089,7 +7089,7 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>山东淄博</v>
+        <v>河北唐山</v>
       </c>
       <c r="G114" t="str">
         <v/>
@@ -7139,7 +7139,7 @@
         <v>妹妹</v>
       </c>
       <c r="C115" t="str">
-        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D115" t="str">
         <v>是</v>
@@ -7148,7 +7148,7 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>韩国</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G115" t="str">
         <v/>
@@ -7198,7 +7198,7 @@
         <v>妹妹</v>
       </c>
       <c r="C116" t="str">
-        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D116" t="str">
         <v>是</v>
@@ -7207,7 +7207,7 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>四川成都</v>
+        <v>韩国</v>
       </c>
       <c r="G116" t="str">
         <v/>
@@ -7251,13 +7251,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>银虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B117" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C117" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D117" t="str">
         <v>是</v>
@@ -7266,7 +7266,7 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>广东广州</v>
+        <v>美国</v>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -7310,13 +7310,13 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B118" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C118" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D118" t="str">
         <v>是</v>
@@ -7325,7 +7325,7 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>中国台湾</v>
       </c>
       <c r="G118" t="str">
         <v/>
@@ -7375,7 +7375,7 @@
         <v>弟弟</v>
       </c>
       <c r="C119" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D119" t="str">
         <v>是</v>
@@ -7384,7 +7384,7 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>天津</v>
+        <v>中国台湾</v>
       </c>
       <c r="G119" t="str">
         <v/>
@@ -7428,13 +7428,13 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B120" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C120" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D120" t="str">
         <v>是</v>
@@ -7443,7 +7443,7 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>山西朔州</v>
+        <v>山东淄博</v>
       </c>
       <c r="G120" t="str">
         <v/>
@@ -7473,7 +7473,7 @@
         <v/>
       </c>
       <c r="P120" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q120" t="str">
         <v/>
@@ -7493,7 +7493,7 @@
         <v>妹妹</v>
       </c>
       <c r="C121" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D121" t="str">
         <v>是</v>
@@ -7502,7 +7502,7 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>贵州</v>
+        <v>韩国</v>
       </c>
       <c r="G121" t="str">
         <v/>
@@ -7546,22 +7546,22 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>棕虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B122" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C122" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D122" t="str">
         <v>是</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F122" t="str">
-        <v>北京</v>
+        <v>四川成都</v>
       </c>
       <c r="G122" t="str">
         <v/>
@@ -7600,27 +7600,27 @@
         <v/>
       </c>
       <c r="S122" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B123" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C123" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D123" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-04-10</v>
+        <v/>
       </c>
       <c r="F123" t="str">
-        <v/>
+        <v>广东广州</v>
       </c>
       <c r="G123" t="str">
         <v/>
@@ -7659,27 +7659,27 @@
         <v/>
       </c>
       <c r="S123" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>阴影色NS12</v>
+        <v>银虎斑</v>
       </c>
       <c r="B124" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C124" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D124" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-05-28</v>
+        <v/>
       </c>
       <c r="F124" t="str">
-        <v/>
+        <v>黑龙江鹤岗</v>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -7718,27 +7718,27 @@
         <v/>
       </c>
       <c r="S124" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>阴影色NS11</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B125" t="str">
         <v>弟弟</v>
       </c>
       <c r="C125" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D125" t="str">
         <v>是</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-06-15</v>
+        <v/>
       </c>
       <c r="F125" t="str">
-        <v>重庆</v>
+        <v>天津</v>
       </c>
       <c r="G125" t="str">
         <v/>
@@ -7777,27 +7777,27 @@
         <v/>
       </c>
       <c r="S125" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>浅烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B126" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C126" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D126" t="str">
         <v>是</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-03-21</v>
+        <v/>
       </c>
       <c r="F126" t="str">
-        <v>中国澳门</v>
+        <v>山西朔州</v>
       </c>
       <c r="G126" t="str">
         <v/>
@@ -7827,7 +7827,7 @@
         <v/>
       </c>
       <c r="P126" t="str">
-        <v/>
+        <v>已接猫</v>
       </c>
       <c r="Q126" t="str">
         <v/>
@@ -7836,27 +7836,27 @@
         <v/>
       </c>
       <c r="S126" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B127" t="str">
         <v>妹妹</v>
       </c>
       <c r="C127" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D127" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F127" t="str">
-        <v/>
+        <v>贵州</v>
       </c>
       <c r="G127" t="str">
         <v/>
@@ -7895,7 +7895,7 @@
         <v/>
       </c>
       <c r="S127" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="128">
@@ -7903,19 +7903,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B128" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C128" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D128" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E128" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F128" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G128" t="str">
         <v/>
@@ -7959,19 +7959,19 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B129" t="str">
         <v>妹妹</v>
       </c>
       <c r="C129" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D129" t="str">
         <v>否</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-06-15</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F129" t="str">
         <v/>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B130" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C130" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D130" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F130" t="str">
-        <v>北京</v>
+        <v/>
       </c>
       <c r="G130" t="str">
         <v/>
@@ -8077,22 +8077,22 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B131" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C131" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D131" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F131" t="str">
-        <v/>
+        <v>重庆</v>
       </c>
       <c r="G131" t="str">
         <v/>
@@ -8136,22 +8136,22 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>烟灰色</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B132" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C132" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D132" t="str">
         <v>是</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F132" t="str">
-        <v>河北石家庄</v>
+        <v>中国澳门</v>
       </c>
       <c r="G132" t="str">
         <v/>
@@ -8195,22 +8195,22 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B133" t="str">
         <v>妹妹</v>
       </c>
       <c r="C133" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D133" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E133" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F133" t="str">
-        <v>浙江宁波</v>
+        <v/>
       </c>
       <c r="G133" t="str">
         <v/>
@@ -8254,13 +8254,13 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B134" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C134" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D134" t="str">
         <v>是</v>
@@ -8269,7 +8269,7 @@
         <v>2026-06-06</v>
       </c>
       <c r="F134" t="str">
-        <v>上海</v>
+        <v>浙江温州</v>
       </c>
       <c r="G134" t="str">
         <v/>
@@ -8313,19 +8313,19 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B135" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C135" t="str">
-        <v>assets/1790733778469-jt9fswxe9w.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D135" t="str">
         <v>否</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-04-17</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F135" t="str">
         <v/>
@@ -8372,22 +8372,22 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B136" t="str">
         <v>弟弟</v>
       </c>
       <c r="C136" t="str">
-        <v>assets/1790734215453-0zvw0v9uja.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D136" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F136" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G136" t="str">
         <v/>
@@ -8431,19 +8431,19 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>阴影色NS11</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B137" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C137" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D137" t="str">
         <v>否</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F137" t="str">
         <v/>
@@ -8490,22 +8490,22 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>浅色银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B138" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C138" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D138" t="str">
         <v>是</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F138" t="str">
-        <v>香港</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G138" t="str">
         <v/>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>浅烟灰色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B139" t="str">
         <v>妹妹</v>
       </c>
       <c r="C139" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D139" t="str">
         <v>是</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F139" t="str">
-        <v>四川成都</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G139" t="str">
         <v/>
@@ -8608,22 +8608,22 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>凯米尔色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B140" t="str">
         <v>弟弟</v>
       </c>
       <c r="C140" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D140" t="str">
         <v>是</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F140" t="str">
-        <v>上海浦东</v>
+        <v>上海</v>
       </c>
       <c r="G140" t="str">
         <v/>
@@ -8667,19 +8667,19 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>银虎斑补丁</v>
+        <v>纯黑色</v>
       </c>
       <c r="B141" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C141" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1790733778469-jt9fswxe9w.jpg</v>
       </c>
       <c r="D141" t="str">
         <v>否</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-17</v>
       </c>
       <c r="F141" t="str">
         <v/>
@@ -8726,22 +8726,22 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B142" t="str">
         <v>弟弟</v>
       </c>
       <c r="C142" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1790734215453-0zvw0v9uja.jpg</v>
       </c>
       <c r="D142" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F142" t="str">
-        <v>北京</v>
+        <v/>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -8785,19 +8785,19 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B143" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C143" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D143" t="str">
         <v>否</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-02-14</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F143" t="str">
         <v/>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B144" t="str">
         <v>妹妹</v>
       </c>
       <c r="C144" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D144" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-05-24</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F144" t="str">
-        <v/>
+        <v>香港</v>
       </c>
       <c r="G144" t="str">
         <v/>
@@ -8903,22 +8903,22 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>银虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B145" t="str">
         <v>妹妹</v>
       </c>
       <c r="C145" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D145" t="str">
         <v>是</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F145" t="str">
-        <v>湖北恩施</v>
+        <v>四川成都</v>
       </c>
       <c r="G145" t="str">
         <v/>
@@ -8962,22 +8962,22 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B146" t="str">
         <v>弟弟</v>
       </c>
       <c r="C146" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D146" t="str">
         <v>是</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F146" t="str">
-        <v>湖北恩施</v>
+        <v>上海浦东</v>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -9021,22 +9021,22 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B147" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C147" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D147" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E147" t="str">
-        <v>2025-11-05</v>
+        <v>2026-04-09</v>
       </c>
       <c r="F147" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -9080,22 +9080,22 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B148" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C148" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D148" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E148" t="str">
         <v>2026-05-18</v>
       </c>
       <c r="F148" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G148" t="str">
         <v/>
@@ -9139,22 +9139,22 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>棕虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B149" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C149" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D149" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-05-28</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F149" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G149" t="str">
         <v/>
@@ -9198,19 +9198,19 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B150" t="str">
         <v>妹妹</v>
       </c>
       <c r="C150" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D150" t="str">
         <v>否</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F150" t="str">
         <v/>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B151" t="str">
         <v>妹妹</v>
       </c>
       <c r="C151" t="str">
-        <v>assets/1790733648123-636cut584p.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D151" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-04-10</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F151" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G151" t="str">
         <v/>
@@ -9319,19 +9319,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B152" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C152" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D152" t="str">
         <v>是</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F152" t="str">
-        <v>韩国</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G152" t="str">
         <v/>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B153" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C153" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D153" t="str">
         <v>是</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-06-05</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F153" t="str">
-        <v>河北邢台</v>
+        <v>韩国</v>
       </c>
       <c r="G153" t="str">
         <v/>
@@ -9434,22 +9434,22 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B154" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C154" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D154" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F154" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G154" t="str">
         <v/>
@@ -9493,22 +9493,22 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B155" t="str">
         <v>弟弟</v>
       </c>
       <c r="C155" t="str">
-        <v>assets/1790734248143-kaxbucmf2v.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D155" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F155" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G155" t="str">
         <v/>
@@ -9552,19 +9552,19 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>棕虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B156" t="str">
         <v>妹妹</v>
       </c>
       <c r="C156" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D156" t="str">
         <v>否</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F156" t="str">
         <v/>
@@ -9611,19 +9611,19 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>蓝虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B157" t="str">
         <v>妹妹</v>
       </c>
       <c r="C157" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1790733648123-636cut584p.jpg</v>
       </c>
       <c r="D157" t="str">
         <v>否</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-04-05</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F157" t="str">
         <v/>
@@ -9676,16 +9676,16 @@
         <v>妹妹</v>
       </c>
       <c r="C158" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D158" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-04-17</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F158" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G158" t="str">
         <v/>
@@ -9729,22 +9729,22 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B159" t="str">
         <v>妹妹</v>
       </c>
       <c r="C159" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D159" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-04-30</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F159" t="str">
-        <v/>
+        <v>河北邢台</v>
       </c>
       <c r="G159" t="str">
         <v/>
@@ -9788,52 +9788,52 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B160" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C160" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D160" t="str">
         <v>是</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-02-20</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F160" t="str">
-        <v>荷兰</v>
+        <v>四川自贡</v>
       </c>
       <c r="G160" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H160" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I160" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J160" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K160" t="str">
         <v/>
       </c>
       <c r="L160" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M160" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N160" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O160" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P160" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q160" t="str">
         <v/>
@@ -9842,27 +9842,27 @@
         <v/>
       </c>
       <c r="S160" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B161" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C161" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D161" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E161" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F161" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G161" t="str">
         <v/>
@@ -9906,22 +9906,22 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B162" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C162" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D162" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E162" t="str">
-        <v/>
+        <v>2026-04-05</v>
       </c>
       <c r="F162" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G162" t="str">
         <v/>
@@ -9968,19 +9968,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B163" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C163" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D163" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E163" t="str">
-        <v/>
+        <v>2026-04-17</v>
       </c>
       <c r="F163" t="str">
-        <v>山西朔州</v>
+        <v/>
       </c>
       <c r="G163" t="str">
         <v/>
@@ -10030,16 +10030,16 @@
         <v>妹妹</v>
       </c>
       <c r="C164" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D164" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E164" t="str">
-        <v/>
+        <v>2026-04-30</v>
       </c>
       <c r="F164" t="str">
-        <v>浙江宁波</v>
+        <v/>
       </c>
       <c r="G164" t="str">
         <v/>
@@ -10083,52 +10083,52 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B165" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C165" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D165" t="str">
         <v>是</v>
       </c>
       <c r="E165" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F165" t="str">
-        <v>陕西西安</v>
+        <v>荷兰</v>
       </c>
       <c r="G165" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H165" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I165" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J165" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K165" t="str">
         <v/>
       </c>
       <c r="L165" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M165" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N165" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O165" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P165" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q165" t="str">
         <v/>
@@ -10137,18 +10137,18 @@
         <v/>
       </c>
       <c r="S165" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B166" t="str">
         <v>弟弟</v>
       </c>
       <c r="C166" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D166" t="str">
         <v>是</v>
@@ -10157,7 +10157,7 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>黑龙江漠河</v>
+        <v>广东广州</v>
       </c>
       <c r="G166" t="str">
         <v/>
@@ -10201,13 +10201,13 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B167" t="str">
         <v>弟弟</v>
       </c>
       <c r="C167" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D167" t="str">
         <v>是</v>
@@ -10216,7 +10216,7 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>日本</v>
+        <v>广东广州</v>
       </c>
       <c r="G167" t="str">
         <v/>
@@ -10263,10 +10263,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B168" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C168" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D168" t="str">
         <v>是</v>
@@ -10275,7 +10275,7 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>浙江杭州</v>
+        <v>山西朔州</v>
       </c>
       <c r="G168" t="str">
         <v/>
@@ -10325,7 +10325,7 @@
         <v>妹妹</v>
       </c>
       <c r="C169" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D169" t="str">
         <v>是</v>
@@ -10334,7 +10334,7 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>贵州安顺</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G169" t="str">
         <v/>
@@ -10381,10 +10381,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B170" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C170" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D170" t="str">
         <v>是</v>
@@ -10393,7 +10393,7 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>山东青岛</v>
+        <v>陕西西安</v>
       </c>
       <c r="G170" t="str">
         <v/>
@@ -10443,7 +10443,7 @@
         <v>弟弟</v>
       </c>
       <c r="C171" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D171" t="str">
         <v>是</v>
@@ -10496,13 +10496,13 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>纯蓝色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B172" t="str">
         <v>弟弟</v>
       </c>
       <c r="C172" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D172" t="str">
         <v>是</v>
@@ -10511,7 +10511,7 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>河南鹤壁</v>
+        <v>日本</v>
       </c>
       <c r="G172" t="str">
         <v/>
@@ -10558,10 +10558,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B173" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C173" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D173" t="str">
         <v>是</v>
@@ -10570,7 +10570,7 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>陕西西安</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G173" t="str">
         <v/>
@@ -10614,13 +10614,13 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B174" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C174" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D174" t="str">
         <v>是</v>
@@ -10629,7 +10629,7 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>四川成都</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G174" t="str">
         <v/>
@@ -10673,22 +10673,22 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B175" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C175" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D175" t="str">
         <v>是</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F175" t="str">
-        <v>四川成都</v>
+        <v>山东青岛</v>
       </c>
       <c r="G175" t="str">
         <v/>
@@ -10738,7 +10738,7 @@
         <v>弟弟</v>
       </c>
       <c r="C176" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D176" t="str">
         <v>是</v>
@@ -10747,7 +10747,7 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>新加坡</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G176" t="str">
         <v/>
@@ -10791,13 +10791,13 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>凯米尔色</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B177" t="str">
         <v>弟弟</v>
       </c>
       <c r="C177" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D177" t="str">
         <v>是</v>
@@ -10806,7 +10806,7 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>上海浦东</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G177" t="str">
         <v/>
@@ -10850,22 +10850,22 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B178" t="str">
         <v>弟弟</v>
       </c>
       <c r="C178" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D178" t="str">
         <v>是</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F178" t="str">
-        <v>浙江温州</v>
+        <v>陕西西安</v>
       </c>
       <c r="G178" t="str">
         <v/>
@@ -10912,63 +10912,358 @@
         <v>棕虎斑</v>
       </c>
       <c r="B179" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C179" t="str">
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+      </c>
+      <c r="D179" t="str">
+        <v>是</v>
+      </c>
+      <c r="E179" t="str">
+        <v/>
+      </c>
+      <c r="F179" t="str">
+        <v>四川成都</v>
+      </c>
+      <c r="G179" t="str">
+        <v/>
+      </c>
+      <c r="H179" t="str">
+        <v/>
+      </c>
+      <c r="I179" t="str">
+        <v/>
+      </c>
+      <c r="J179" t="str">
+        <v/>
+      </c>
+      <c r="K179" t="str">
+        <v/>
+      </c>
+      <c r="L179" t="str">
+        <v/>
+      </c>
+      <c r="M179" t="str">
+        <v/>
+      </c>
+      <c r="N179" t="str">
+        <v/>
+      </c>
+      <c r="O179" t="str">
+        <v/>
+      </c>
+      <c r="P179" t="str">
+        <v/>
+      </c>
+      <c r="Q179" t="str">
+        <v/>
+      </c>
+      <c r="R179" t="str">
+        <v/>
+      </c>
+      <c r="S179" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>烟灰色</v>
+      </c>
+      <c r="B180" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C180" t="str">
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+      </c>
+      <c r="D180" t="str">
+        <v>是</v>
+      </c>
+      <c r="E180" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="F180" t="str">
+        <v>四川成都</v>
+      </c>
+      <c r="G180" t="str">
+        <v/>
+      </c>
+      <c r="H180" t="str">
+        <v/>
+      </c>
+      <c r="I180" t="str">
+        <v/>
+      </c>
+      <c r="J180" t="str">
+        <v/>
+      </c>
+      <c r="K180" t="str">
+        <v/>
+      </c>
+      <c r="L180" t="str">
+        <v/>
+      </c>
+      <c r="M180" t="str">
+        <v/>
+      </c>
+      <c r="N180" t="str">
+        <v/>
+      </c>
+      <c r="O180" t="str">
+        <v/>
+      </c>
+      <c r="P180" t="str">
+        <v/>
+      </c>
+      <c r="Q180" t="str">
+        <v/>
+      </c>
+      <c r="R180" t="str">
+        <v/>
+      </c>
+      <c r="S180" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B181" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C181" t="str">
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+      </c>
+      <c r="D181" t="str">
+        <v>是</v>
+      </c>
+      <c r="E181" t="str">
+        <v/>
+      </c>
+      <c r="F181" t="str">
+        <v>新加坡</v>
+      </c>
+      <c r="G181" t="str">
+        <v/>
+      </c>
+      <c r="H181" t="str">
+        <v/>
+      </c>
+      <c r="I181" t="str">
+        <v/>
+      </c>
+      <c r="J181" t="str">
+        <v/>
+      </c>
+      <c r="K181" t="str">
+        <v/>
+      </c>
+      <c r="L181" t="str">
+        <v/>
+      </c>
+      <c r="M181" t="str">
+        <v/>
+      </c>
+      <c r="N181" t="str">
+        <v/>
+      </c>
+      <c r="O181" t="str">
+        <v/>
+      </c>
+      <c r="P181" t="str">
+        <v/>
+      </c>
+      <c r="Q181" t="str">
+        <v/>
+      </c>
+      <c r="R181" t="str">
+        <v/>
+      </c>
+      <c r="S181" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B182" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C182" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D182" t="str">
+        <v>是</v>
+      </c>
+      <c r="E182" t="str">
+        <v/>
+      </c>
+      <c r="F182" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G182" t="str">
+        <v/>
+      </c>
+      <c r="H182" t="str">
+        <v/>
+      </c>
+      <c r="I182" t="str">
+        <v/>
+      </c>
+      <c r="J182" t="str">
+        <v/>
+      </c>
+      <c r="K182" t="str">
+        <v/>
+      </c>
+      <c r="L182" t="str">
+        <v/>
+      </c>
+      <c r="M182" t="str">
+        <v/>
+      </c>
+      <c r="N182" t="str">
+        <v/>
+      </c>
+      <c r="O182" t="str">
+        <v/>
+      </c>
+      <c r="P182" t="str">
+        <v/>
+      </c>
+      <c r="Q182" t="str">
+        <v/>
+      </c>
+      <c r="R182" t="str">
+        <v/>
+      </c>
+      <c r="S182" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B183" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C183" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D183" t="str">
+        <v>是</v>
+      </c>
+      <c r="E183" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F183" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G183" t="str">
+        <v/>
+      </c>
+      <c r="H183" t="str">
+        <v/>
+      </c>
+      <c r="I183" t="str">
+        <v/>
+      </c>
+      <c r="J183" t="str">
+        <v/>
+      </c>
+      <c r="K183" t="str">
+        <v/>
+      </c>
+      <c r="L183" t="str">
+        <v/>
+      </c>
+      <c r="M183" t="str">
+        <v/>
+      </c>
+      <c r="N183" t="str">
+        <v/>
+      </c>
+      <c r="O183" t="str">
+        <v/>
+      </c>
+      <c r="P183" t="str">
+        <v/>
+      </c>
+      <c r="Q183" t="str">
+        <v/>
+      </c>
+      <c r="R183" t="str">
+        <v/>
+      </c>
+      <c r="S183" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B184" t="str">
         <v>妹妹</v>
       </c>
-      <c r="C179" t="str">
+      <c r="C184" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D179" t="str">
-        <v>否</v>
-      </c>
-      <c r="E179" t="str">
+      <c r="D184" t="str">
+        <v>否</v>
+      </c>
+      <c r="E184" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F179" t="str">
-        <v/>
-      </c>
-      <c r="G179" t="str">
-        <v/>
-      </c>
-      <c r="H179" t="str">
-        <v/>
-      </c>
-      <c r="I179" t="str">
-        <v/>
-      </c>
-      <c r="J179" t="str">
-        <v/>
-      </c>
-      <c r="K179" t="str">
-        <v/>
-      </c>
-      <c r="L179" t="str">
-        <v/>
-      </c>
-      <c r="M179" t="str">
-        <v/>
-      </c>
-      <c r="N179" t="str">
-        <v/>
-      </c>
-      <c r="O179" t="str">
-        <v/>
-      </c>
-      <c r="P179" t="str">
-        <v/>
-      </c>
-      <c r="Q179" t="str">
-        <v/>
-      </c>
-      <c r="R179" t="str">
-        <v/>
-      </c>
-      <c r="S179" t="str">
+      <c r="F184" t="str">
+        <v/>
+      </c>
+      <c r="G184" t="str">
+        <v/>
+      </c>
+      <c r="H184" t="str">
+        <v/>
+      </c>
+      <c r="I184" t="str">
+        <v/>
+      </c>
+      <c r="J184" t="str">
+        <v/>
+      </c>
+      <c r="K184" t="str">
+        <v/>
+      </c>
+      <c r="L184" t="str">
+        <v/>
+      </c>
+      <c r="M184" t="str">
+        <v/>
+      </c>
+      <c r="N184" t="str">
+        <v/>
+      </c>
+      <c r="O184" t="str">
+        <v/>
+      </c>
+      <c r="P184" t="str">
+        <v/>
+      </c>
+      <c r="Q184" t="str">
+        <v/>
+      </c>
+      <c r="R184" t="str">
+        <v/>
+      </c>
+      <c r="S184" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S179"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S184"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -593,13 +593,13 @@
         <v>assets/1790734651251-a58tdtmhnx.jpg</v>
       </c>
       <c r="D4" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E4" t="str">
         <v>2026-05-18</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>成都</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -652,13 +652,13 @@
         <v>assets/1790734595573-u465hv1hyg.jpg</v>
       </c>
       <c r="D5" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E5" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>浙江嘉兴</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -1360,13 +1360,13 @@
         <v>assets/1788442356842-bbleakpy85.jpg</v>
       </c>
       <c r="D17" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E17" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>浙江嘉兴</v>
       </c>
       <c r="G17" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -711,13 +711,13 @@
         <v>assets/1790734548586-cztim8ip4y.jpg</v>
       </c>
       <c r="D6" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E6" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>西安</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -947,13 +947,13 @@
         <v>assets/1789654723483-fyl8c7wdqg.jpg</v>
       </c>
       <c r="D10" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E10" t="str">
         <v>2026-06-26</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>天津</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -1242,13 +1242,13 @@
         <v>assets/1788534522775-my4ggv0pwo.jpg</v>
       </c>
       <c r="D15" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E15" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>西藏</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1301,13 +1301,13 @@
         <v>assets/1788442386268-ilpasqz91m.jpg</v>
       </c>
       <c r="D16" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E16" t="str">
         <v>2026-06-26</v>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>成都</v>
       </c>
       <c r="G16" t="str">
         <v/>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S184"/>
+  <dimension ref="A1:S186"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -466,19 +466,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>浅烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B2" t="str">
         <v>弟弟</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1790734752606-rusbv65ug8.jpg</v>
+        <v>assets/1791288567764-tti55g9g1q.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>否</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-04-28</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -528,16 +528,16 @@
         <v>棕虎斑</v>
       </c>
       <c r="B3" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1790734688874-ldibzixi2g.jpg</v>
+        <v>assets/1791288502036-4v43o0otqq.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>否</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -584,22 +584,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>烟灰色</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B4" t="str">
         <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1790734651251-a58tdtmhnx.jpg</v>
+        <v>assets/1790734752606-rusbv65ug8.jpg</v>
       </c>
       <c r="D4" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-05-18</v>
+        <v>2026-04-28</v>
       </c>
       <c r="F4" t="str">
-        <v>成都</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -643,22 +643,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>浅银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B5" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1790734595573-u465hv1hyg.jpg</v>
+        <v>assets/1790734688874-ldibzixi2g.jpg</v>
       </c>
       <c r="D5" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F5" t="str">
-        <v>浙江嘉兴</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -702,22 +702,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>浅银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B6" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1790734548586-cztim8ip4y.jpg</v>
+        <v>assets/1790734651251-a58tdtmhnx.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>是</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F6" t="str">
-        <v>西安</v>
+        <v>成都</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -761,22 +761,22 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>蓝虎斑</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B7" t="str">
         <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1790734499008-43htmo2xuw.jpg</v>
+        <v>assets/1790734595573-u465hv1hyg.jpg</v>
       </c>
       <c r="D7" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-03-20</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>浙江嘉兴</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -820,22 +820,22 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>阴影色NS11</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B8" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1789655131156-6ywyod2pgz.jpg</v>
+        <v>assets/1790734548586-cztim8ip4y.jpg</v>
       </c>
       <c r="D8" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E8" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>西安</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -879,22 +879,22 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>浅银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B9" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1789654858942-ws3mqfv0zf.jpg</v>
+        <v>assets/1790734499008-43htmo2xuw.jpg</v>
       </c>
       <c r="D9" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-06-15</v>
+        <v>2026-03-20</v>
       </c>
       <c r="F9" t="str">
-        <v>浙江杭州</v>
+        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -938,22 +938,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>红虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B10" t="str">
         <v>弟弟</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1789654723483-fyl8c7wdqg.jpg</v>
+        <v>assets/1789655131156-6ywyod2pgz.jpg</v>
       </c>
       <c r="D10" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F10" t="str">
-        <v>天津</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -997,22 +997,22 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>银虎班补丁</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B11" t="str">
         <v>妹妹</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1789654675792-6d4kyyncmf.jpg</v>
+        <v>assets/1789654858942-ws3mqfv0zf.jpg</v>
       </c>
       <c r="D11" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>浙江杭州</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1056,22 +1056,22 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>烟灰色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B12" t="str">
         <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1789654628929-2wok5d7b71.jpg</v>
+        <v>assets/1789654723483-fyl8c7wdqg.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>是</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F12" t="str">
-        <v>新加坡</v>
+        <v>天津</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1115,19 +1115,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>阴影色NS11</v>
+        <v>银虎班补丁</v>
       </c>
       <c r="B13" t="str">
         <v>妹妹</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1789654549268-68uab4pdoy.jpg</v>
+        <v>assets/1789654675792-6d4kyyncmf.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>否</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -1174,22 +1174,22 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>阴影色NS12</v>
+        <v>烟灰色</v>
       </c>
       <c r="B14" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1788534744815-pzs6jqs2pm.jpg</v>
+        <v>assets/1789654628929-2wok5d7b71.jpg</v>
       </c>
       <c r="D14" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>新加坡</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1233,22 +1233,22 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B15" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1788534522775-my4ggv0pwo.jpg</v>
+        <v>assets/1789654549268-68uab4pdoy.jpg</v>
       </c>
       <c r="D15" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E15" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="F15" t="str">
-        <v>西藏</v>
+        <v/>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1292,22 +1292,22 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>红虎斑</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B16" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1788442386268-ilpasqz91m.jpg</v>
+        <v>assets/1788534744815-pzs6jqs2pm.jpg</v>
       </c>
       <c r="D16" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-06-26</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F16" t="str">
-        <v>成都</v>
+        <v/>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1351,13 +1351,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>浅银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B17" t="str">
         <v>弟弟</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1788442356842-bbleakpy85.jpg</v>
+        <v>assets/1788534522775-my4ggv0pwo.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>是</v>
@@ -1366,7 +1366,7 @@
         <v>2026-06-15</v>
       </c>
       <c r="F17" t="str">
-        <v>浙江嘉兴</v>
+        <v>西藏</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1410,19 +1410,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>浅烟灰色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B18" t="str">
         <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1788442221802-et3crh0tww.jpg</v>
+        <v>assets/1788442386268-ilpasqz91m.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>是</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F18" t="str">
         <v>成都</v>
@@ -1469,22 +1469,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>凯米尔</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B19" t="str">
         <v>弟弟</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1788014088852-oqkg79cki9.jpg</v>
+        <v>assets/1788442356842-bbleakpy85.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>是</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F19" t="str">
-        <v>湖北襄阳</v>
+        <v>浙江嘉兴</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1528,22 +1528,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B20" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1788014050978-9a2sguuo1u.jpg</v>
+        <v>assets/1788442221802-et3crh0tww.jpg</v>
       </c>
       <c r="D20" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>成都</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B21" t="str">
         <v>弟弟</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1788013924404-gmlh0hfjae.jpg</v>
+        <v>assets/1788014088852-oqkg79cki9.jpg</v>
       </c>
       <c r="D21" t="str">
         <v>是</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F21" t="str">
-        <v>浙江嘉兴</v>
+        <v>湖北襄阳</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1646,22 +1646,22 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B22" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1788013889955-wpykaycfde.jpg</v>
+        <v>assets/1788014050978-9a2sguuo1u.jpg</v>
       </c>
       <c r="D22" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F22" t="str">
-        <v>湖北襄阳</v>
+        <v/>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1705,22 +1705,22 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B23" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1788013810551-b90h1mwfiq.jpg</v>
+        <v>assets/1788013924404-gmlh0hfjae.jpg</v>
       </c>
       <c r="D23" t="str">
         <v>是</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F23" t="str">
-        <v>新疆</v>
+        <v>浙江嘉兴</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1764,22 +1764,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B24" t="str">
         <v>弟弟</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1787837910484-r7urrsuib0.jpg</v>
+        <v>assets/1788013889955-wpykaycfde.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>是</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F24" t="str">
-        <v>香港</v>
+        <v>湖北襄阳</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1823,22 +1823,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B25" t="str">
         <v>妹妹</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1787837846581-6q9nxgad35.jpg</v>
+        <v>assets/1788013810551-b90h1mwfiq.jpg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F25" t="str">
-        <v>天津</v>
+        <v>新疆</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1882,22 +1882,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>凯米尔</v>
+        <v>银虎斑</v>
       </c>
       <c r="B26" t="str">
         <v>弟弟</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1790734407566-tge3si2tw9.jpg</v>
+        <v>assets/1787837910484-r7urrsuib0.jpg</v>
       </c>
       <c r="D26" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-06-26</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F26" t="str">
-        <v/>
+        <v>香港</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1941,22 +1941,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>烟灰色</v>
+        <v>纯黑色</v>
       </c>
       <c r="B27" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
+        <v>assets/1787837846581-6q9nxgad35.jpg</v>
       </c>
       <c r="D27" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F27" t="str">
-        <v/>
+        <v>天津</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -2000,22 +2000,22 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B28" t="str">
         <v>弟弟</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1787837648423-9riberz3tq.jpg</v>
+        <v>assets/1790734407566-tge3si2tw9.jpg</v>
       </c>
       <c r="D28" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F28" t="str">
-        <v>北京</v>
+        <v/>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2059,19 +2059,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B29" t="str">
         <v>弟弟</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
+        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>否</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -2124,16 +2124,16 @@
         <v>弟弟</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1787479268842-7en9nzy302.jpg</v>
+        <v>assets/1787837648423-9riberz3tq.jpg</v>
       </c>
       <c r="D30" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F30" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2145,7 +2145,7 @@
         <v/>
       </c>
       <c r="J30" t="str">
-        <v>2026-06-10</v>
+        <v/>
       </c>
       <c r="K30" t="str">
         <v/>
@@ -2177,22 +2177,22 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B31" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1787479242639-32zuh5lham.jpg</v>
+        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
       </c>
       <c r="D31" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E31" t="str">
         <v>2026-06-10</v>
       </c>
       <c r="F31" t="str">
-        <v>天津</v>
+        <v/>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2239,19 +2239,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B32" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1787466121255-21jto2cugv.jpg</v>
+        <v>assets/1787479268842-7en9nzy302.jpg</v>
       </c>
       <c r="D32" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E32" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F32" t="str">
-        <v>四川广安</v>
+        <v/>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v/>
       </c>
       <c r="J32" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="K32" t="str">
         <v/>
@@ -2295,22 +2295,22 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>烟灰色</v>
+        <v>纯黑色</v>
       </c>
       <c r="B33" t="str">
         <v>妹妹</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
+        <v>assets/1787479242639-32zuh5lham.jpg</v>
       </c>
       <c r="D33" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F33" t="str">
-        <v/>
+        <v>天津</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2360,16 +2360,16 @@
         <v>妹妹</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1787388277490-e6u506cx0r.jpg</v>
+        <v>assets/1787466121255-21jto2cugv.jpg</v>
       </c>
       <c r="D34" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F34" t="str">
-        <v/>
+        <v>四川广安</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2413,22 +2413,22 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B35" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1787328436957-x30od0gw28.jpg</v>
+        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
       </c>
       <c r="D35" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E35" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F35" t="str">
-        <v>江苏苏州</v>
+        <v/>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2472,22 +2472,22 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B36" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
+        <v>assets/1787388277490-e6u506cx0r.jpg</v>
       </c>
       <c r="D36" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E36" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F36" t="str">
-        <v>辽宁东港</v>
+        <v/>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B37" t="str">
         <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1787327967245-m62ohievcl.jpg</v>
+        <v>assets/1787328436957-x30od0gw28.jpg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
@@ -2546,7 +2546,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>福建福州</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2596,7 +2596,7 @@
         <v>弟弟</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
+        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>上海</v>
+        <v>辽宁东港</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>纯蓝色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B39" t="str">
         <v>弟弟</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1787327793837-znk2knoo6p.jpg</v>
+        <v>assets/1787327967245-m62ohievcl.jpg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2664,7 +2664,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>河南鹤壁</v>
+        <v>福建福州</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2708,13 +2708,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B40" t="str">
         <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1787327752832-kkpmp21os3.jpg</v>
+        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2723,7 +2723,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>陕西西安</v>
+        <v>上海</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2767,13 +2767,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>银虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B41" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
+        <v>assets/1787327793837-znk2knoo6p.jpg</v>
       </c>
       <c r="D41" t="str">
         <v>是</v>
@@ -2782,7 +2782,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>陕西西安</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2832,7 +2832,7 @@
         <v>弟弟</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1787327573762-h23cux94p2.jpg</v>
+        <v>assets/1787327752832-kkpmp21os3.jpg</v>
       </c>
       <c r="D42" t="str">
         <v>是</v>
@@ -2841,7 +2841,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>北京</v>
+        <v>陕西西安</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2891,7 +2891,7 @@
         <v>妹妹</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1787327496557-9daggljg4g.jpg</v>
+        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
@@ -2900,7 +2900,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>黑龙江哈尔滨</v>
+        <v>陕西西安</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B44" t="str">
         <v>弟弟</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
+        <v>assets/1787327573762-h23cux94p2.jpg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>甘肃嘉峪关</v>
+        <v>北京</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3003,13 +3003,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B45" t="str">
         <v>妹妹</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
+        <v>assets/1787327496557-9daggljg4g.jpg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
@@ -3018,7 +3018,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>安徽合肥</v>
+        <v>黑龙江哈尔滨</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B46" t="str">
         <v>弟弟</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1787327337811-u5u2pdew3.jpg</v>
+        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>安徽合肥</v>
+        <v>甘肃嘉峪关</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3121,13 +3121,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B47" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1787327309143-6c1dan1sev.jpg</v>
+        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>四川成都</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3186,7 +3186,7 @@
         <v>弟弟</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1787327277453-w89ujg69fm.jpg</v>
+        <v>assets/1787327337811-u5u2pdew3.jpg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>四川成都</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>蓝银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B49" t="str">
         <v>弟弟</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1787327232159-lkrcl588a5.jpg</v>
+        <v>assets/1787327309143-6c1dan1sev.jpg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -3298,13 +3298,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>玳瑁色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B50" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1787327182347-3az0z7sys2.jpg</v>
+        <v>assets/1787327277453-w89ujg69fm.jpg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
@@ -3313,7 +3313,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>四川内江</v>
+        <v>四川成都</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3357,13 +3357,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>棕虎补丁</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B51" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
+        <v>assets/1787327232159-lkrcl588a5.jpg</v>
       </c>
       <c r="D51" t="str">
         <v>是</v>
@@ -3372,7 +3372,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>贵州贵阳</v>
+        <v>四川成都</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,13 +3416,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>黑烟色</v>
+        <v>玳瑁色</v>
       </c>
       <c r="B52" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1787327101790-tqjlseog5y.jpg</v>
+        <v>assets/1787327182347-3az0z7sys2.jpg</v>
       </c>
       <c r="D52" t="str">
         <v>是</v>
@@ -3431,7 +3431,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>浙江杭州</v>
+        <v>四川内江</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3475,13 +3475,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>烟灰色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B53" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1787327019632-l1780lu2hj.jpg</v>
+        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
       </c>
       <c r="D53" t="str">
         <v>是</v>
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>山东威海</v>
+        <v>贵州贵阳</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3534,13 +3534,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>棕虎补丁</v>
+        <v>黑烟色</v>
       </c>
       <c r="B54" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1787326905275-plz3fpgo97.jpg</v>
+        <v>assets/1787327101790-tqjlseog5y.jpg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
@@ -3593,13 +3593,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B55" t="str">
         <v>弟弟</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
+        <v>assets/1787327019632-l1780lu2hj.jpg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
@@ -3608,7 +3608,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>四川成都</v>
+        <v>山东威海</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B56" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
+        <v>assets/1787326905275-plz3fpgo97.jpg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
@@ -3667,7 +3667,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3711,13 +3711,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>凯米尔</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B57" t="str">
         <v>弟弟</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1787326814713-p5oavnlulg.jpg</v>
+        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
       </c>
       <c r="D57" t="str">
         <v>是</v>
@@ -3770,13 +3770,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B58" t="str">
         <v>弟弟</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1787326773577-13q5out2d0.jpg</v>
+        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
@@ -3785,7 +3785,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>四川宜宾</v>
+        <v>四川成都</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>金棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B59" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1787326548993-89s929m2hg.jpg</v>
+        <v>assets/1787326814713-p5oavnlulg.jpg</v>
       </c>
       <c r="D59" t="str">
         <v>是</v>
@@ -3844,7 +3844,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>上海</v>
+        <v>四川成都</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3888,13 +3888,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B60" t="str">
         <v>弟弟</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1787326449218-09s9ucram4.jpg</v>
+        <v>assets/1787326773577-13q5out2d0.jpg</v>
       </c>
       <c r="D60" t="str">
         <v>是</v>
@@ -3903,7 +3903,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>德国</v>
+        <v>四川宜宾</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3947,13 +3947,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>棕虎补丁</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B61" t="str">
         <v>妹妹</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1787326277374-8ti107m5ki.jpg</v>
+        <v>assets/1787326548993-89s929m2hg.jpg</v>
       </c>
       <c r="D61" t="str">
         <v>是</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>广东深圳</v>
+        <v>上海</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4006,13 +4006,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B62" t="str">
         <v>弟弟</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1787326236952-2pmwche4t3.jpg</v>
+        <v>assets/1787326449218-09s9ucram4.jpg</v>
       </c>
       <c r="D62" t="str">
         <v>是</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>福建泉州</v>
+        <v>德国</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4065,13 +4065,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B63" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1787326184557-90v6clkwen.jpg</v>
+        <v>assets/1787326277374-8ti107m5ki.jpg</v>
       </c>
       <c r="D63" t="str">
         <v>是</v>
@@ -4080,7 +4080,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>福建福州</v>
+        <v>广东深圳</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -4124,13 +4124,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B64" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C64" t="str">
-        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
+        <v>assets/1787326236952-2pmwche4t3.jpg</v>
       </c>
       <c r="D64" t="str">
         <v>是</v>
@@ -4139,7 +4139,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>广西贵港</v>
+        <v>福建泉州</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -4183,13 +4183,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B65" t="str">
         <v>弟弟</v>
       </c>
       <c r="C65" t="str">
-        <v>assets/1787325862706-wq18k3ej56.jpg</v>
+        <v>assets/1787326184557-90v6clkwen.jpg</v>
       </c>
       <c r="D65" t="str">
         <v>是</v>
@@ -4198,7 +4198,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>江苏苏州</v>
+        <v>福建福州</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -4242,13 +4242,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B66" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C66" t="str">
-        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
+        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
       </c>
       <c r="D66" t="str">
         <v>是</v>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>江苏苏州</v>
+        <v>广西贵港</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -4301,13 +4301,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B67" t="str">
         <v>弟弟</v>
       </c>
       <c r="C67" t="str">
-        <v>assets/1787325706797-kgk81ghccy.jpg</v>
+        <v>assets/1787325862706-wq18k3ej56.jpg</v>
       </c>
       <c r="D67" t="str">
         <v>是</v>
@@ -4316,7 +4316,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>北京</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4360,13 +4360,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>蓝虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B68" t="str">
         <v>弟弟</v>
       </c>
       <c r="C68" t="str">
-        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
+        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
       </c>
       <c r="D68" t="str">
         <v>是</v>
@@ -4375,7 +4375,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>上海</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -4419,13 +4419,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B69" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C69" t="str">
-        <v>assets/1787325554341-608thexrne.jpg</v>
+        <v>assets/1787325706797-kgk81ghccy.jpg</v>
       </c>
       <c r="D69" t="str">
         <v>是</v>
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>江苏苏州</v>
+        <v>北京</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4478,13 +4478,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>浅色银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B70" t="str">
         <v>弟弟</v>
       </c>
       <c r="C70" t="str">
-        <v>assets/1787325480828-q90pskoiw3.jpg</v>
+        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
       </c>
       <c r="D70" t="str">
         <v>是</v>
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>四川成都</v>
+        <v>上海</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -4537,13 +4537,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B71" t="str">
         <v>妹妹</v>
       </c>
       <c r="C71" t="str">
-        <v>assets/1787325448999-a2pg8176fu.jpg</v>
+        <v>assets/1787325554341-608thexrne.jpg</v>
       </c>
       <c r="D71" t="str">
         <v>是</v>
@@ -4552,7 +4552,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>中国台湾</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -4596,13 +4596,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>棕虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B72" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C72" t="str">
-        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
+        <v>assets/1787325480828-q90pskoiw3.jpg</v>
       </c>
       <c r="D72" t="str">
         <v>是</v>
@@ -4611,7 +4611,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>浙江杭州</v>
+        <v>四川成都</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -4655,13 +4655,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>烟灰色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B73" t="str">
         <v>妹妹</v>
       </c>
       <c r="C73" t="str">
-        <v>assets/1787325237876-t19isaq5gu.jpg</v>
+        <v>assets/1787325448999-a2pg8176fu.jpg</v>
       </c>
       <c r="D73" t="str">
         <v>是</v>
@@ -4670,7 +4670,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>辽宁沈阳</v>
+        <v>中国台湾</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4714,13 +4714,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>金棕虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B74" t="str">
         <v>妹妹</v>
       </c>
       <c r="C74" t="str">
-        <v>assets/1787325199931-e7wms9qtya.jpg</v>
+        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
       </c>
       <c r="D74" t="str">
         <v>是</v>
@@ -4729,7 +4729,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4773,13 +4773,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B75" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C75" t="str">
-        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
+        <v>assets/1787325237876-t19isaq5gu.jpg</v>
       </c>
       <c r="D75" t="str">
         <v>是</v>
@@ -4788,7 +4788,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>中国香港</v>
+        <v>辽宁沈阳</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -4832,13 +4832,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>烟灰色</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B76" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C76" t="str">
-        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
+        <v>assets/1787325199931-e7wms9qtya.jpg</v>
       </c>
       <c r="D76" t="str">
         <v>是</v>
@@ -4847,7 +4847,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>中国澳门</v>
+        <v>四川成都</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4897,7 +4897,7 @@
         <v>弟弟</v>
       </c>
       <c r="C77" t="str">
-        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
+        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
       </c>
       <c r="D77" t="str">
         <v>是</v>
@@ -4906,7 +4906,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>山东青岛</v>
+        <v>中国香港</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4956,7 +4956,7 @@
         <v>弟弟</v>
       </c>
       <c r="C78" t="str">
-        <v>assets/1787324954998-w5m5jox439.jpg</v>
+        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
       </c>
       <c r="D78" t="str">
         <v>是</v>
@@ -4965,7 +4965,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>海南海口</v>
+        <v>中国澳门</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -5009,13 +5009,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B79" t="str">
         <v>弟弟</v>
       </c>
       <c r="C79" t="str">
-        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
+        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
       </c>
       <c r="D79" t="str">
         <v>是</v>
@@ -5024,7 +5024,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>内蒙古</v>
+        <v>山东青岛</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -5074,7 +5074,7 @@
         <v>弟弟</v>
       </c>
       <c r="C80" t="str">
-        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
+        <v>assets/1787324954998-w5m5jox439.jpg</v>
       </c>
       <c r="D80" t="str">
         <v>是</v>
@@ -5083,7 +5083,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>中国香港</v>
+        <v>海南海口</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -5127,13 +5127,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B81" t="str">
         <v>弟弟</v>
       </c>
       <c r="C81" t="str">
-        <v>assets/1787324806613-31yyz14tsf.jpg</v>
+        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
       </c>
       <c r="D81" t="str">
         <v>是</v>
@@ -5142,7 +5142,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>四川成都</v>
+        <v>内蒙古</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -5186,13 +5186,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B82" t="str">
         <v>弟弟</v>
       </c>
       <c r="C82" t="str">
-        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
+        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
       </c>
       <c r="D82" t="str">
         <v>是</v>
@@ -5201,7 +5201,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>湖北武汉</v>
+        <v>中国香港</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -5251,7 +5251,7 @@
         <v>弟弟</v>
       </c>
       <c r="C83" t="str">
-        <v>assets/1787324522658-smn44crast.jpg</v>
+        <v>assets/1787324806613-31yyz14tsf.jpg</v>
       </c>
       <c r="D83" t="str">
         <v>是</v>
@@ -5260,7 +5260,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>湖北武汉</v>
+        <v>四川成都</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -5304,13 +5304,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B84" t="str">
         <v>弟弟</v>
       </c>
       <c r="C84" t="str">
-        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
+        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
       </c>
       <c r="D84" t="str">
         <v>是</v>
@@ -5319,7 +5319,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>新疆</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -5363,13 +5363,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>浅凯米尔</v>
+        <v>烟灰色</v>
       </c>
       <c r="B85" t="str">
         <v>弟弟</v>
       </c>
       <c r="C85" t="str">
-        <v>assets/1787324331029-d74lcuycf6.jpg</v>
+        <v>assets/1787324522658-smn44crast.jpg</v>
       </c>
       <c r="D85" t="str">
         <v>是</v>
@@ -5378,7 +5378,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>四川成都</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -5422,13 +5422,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B86" t="str">
         <v>弟弟</v>
       </c>
       <c r="C86" t="str">
-        <v>assets/1787324297469-ans1lse2l5.jpg</v>
+        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
       </c>
       <c r="D86" t="str">
         <v>是</v>
@@ -5437,7 +5437,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>四川乐山</v>
+        <v>新疆</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -5481,13 +5481,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>红虎斑</v>
+        <v>浅凯米尔</v>
       </c>
       <c r="B87" t="str">
         <v>弟弟</v>
       </c>
       <c r="C87" t="str">
-        <v>assets/1787324256827-7w383z4bg1.jpg</v>
+        <v>assets/1787324331029-d74lcuycf6.jpg</v>
       </c>
       <c r="D87" t="str">
         <v>是</v>
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>中国台湾</v>
+        <v>四川成都</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -5540,13 +5540,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B88" t="str">
         <v>弟弟</v>
       </c>
       <c r="C88" t="str">
-        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
+        <v>assets/1787324297469-ans1lse2l5.jpg</v>
       </c>
       <c r="D88" t="str">
         <v>是</v>
@@ -5555,7 +5555,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>四川成都</v>
+        <v>四川乐山</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -5599,13 +5599,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>凯米尔色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B89" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C89" t="str">
-        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
+        <v>assets/1787324256827-7w383z4bg1.jpg</v>
       </c>
       <c r="D89" t="str">
         <v>是</v>
@@ -5614,7 +5614,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>江苏南京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -5658,13 +5658,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B90" t="str">
         <v>弟弟</v>
       </c>
       <c r="C90" t="str">
-        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
+        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
       </c>
       <c r="D90" t="str">
         <v>是</v>
@@ -5673,7 +5673,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>江苏南京</v>
+        <v>四川成都</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -5717,13 +5717,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B91" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C91" t="str">
-        <v>assets/1787323318612-soge38hpsf.jpg</v>
+        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
       </c>
       <c r="D91" t="str">
         <v>是</v>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>上海</v>
+        <v>江苏南京</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -5782,7 +5782,7 @@
         <v>弟弟</v>
       </c>
       <c r="C92" t="str">
-        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
+        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
       </c>
       <c r="D92" t="str">
         <v>是</v>
@@ -5791,7 +5791,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>四川成都</v>
+        <v>江苏南京</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -5838,10 +5838,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B93" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C93" t="str">
-        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
+        <v>assets/1787323318612-soge38hpsf.jpg</v>
       </c>
       <c r="D93" t="str">
         <v>是</v>
@@ -5850,7 +5850,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>浙江宁波</v>
+        <v>上海</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -5894,13 +5894,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B94" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C94" t="str">
-        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
+        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
       </c>
       <c r="D94" t="str">
         <v>是</v>
@@ -5909,7 +5909,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>马来西亚</v>
+        <v>四川成都</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -5956,10 +5956,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B95" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C95" t="str">
-        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
+        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
       </c>
       <c r="D95" t="str">
         <v>是</v>
@@ -5968,7 +5968,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>陕西西安</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -6012,13 +6012,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B96" t="str">
         <v>妹妹</v>
       </c>
       <c r="C96" t="str">
-        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
+        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
       </c>
       <c r="D96" t="str">
         <v>是</v>
@@ -6027,7 +6027,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>广西南宁</v>
+        <v>马来西亚</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -6071,13 +6071,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B97" t="str">
         <v>弟弟</v>
       </c>
       <c r="C97" t="str">
-        <v>assets/1787322760950-gn3qgego4s.jpg</v>
+        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
       </c>
       <c r="D97" t="str">
         <v>是</v>
@@ -6086,7 +6086,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>广西南宁</v>
+        <v>陕西西安</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -6130,13 +6130,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>红虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B98" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C98" t="str">
-        <v>assets/1787322605982-04n50xegt2.jpg</v>
+        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
       </c>
       <c r="D98" t="str">
         <v>是</v>
@@ -6145,7 +6145,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>上海</v>
+        <v>广西南宁</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -6189,13 +6189,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B99" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C99" t="str">
-        <v>assets/1787322490045-kog3ru43dy.jpg</v>
+        <v>assets/1787322760950-gn3qgego4s.jpg</v>
       </c>
       <c r="D99" t="str">
         <v>是</v>
@@ -6204,7 +6204,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>上海</v>
+        <v>广西南宁</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -6254,7 +6254,7 @@
         <v>弟弟</v>
       </c>
       <c r="C100" t="str">
-        <v>assets/1787322419996-0m33yx89nm.jpg</v>
+        <v>assets/1787322605982-04n50xegt2.jpg</v>
       </c>
       <c r="D100" t="str">
         <v>是</v>
@@ -6263,7 +6263,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>广东广州</v>
+        <v>上海</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -6307,13 +6307,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>浅色银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B101" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C101" t="str">
-        <v>assets/1787322377730-vj5csj2mll.jpg</v>
+        <v>assets/1787322490045-kog3ru43dy.jpg</v>
       </c>
       <c r="D101" t="str">
         <v>是</v>
@@ -6322,7 +6322,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>柬埔寨</v>
+        <v>上海</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -6366,13 +6366,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>蓝虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B102" t="str">
         <v>弟弟</v>
       </c>
       <c r="C102" t="str">
-        <v>assets/1787322269611-53yaj5ideu.jpg</v>
+        <v>assets/1787322419996-0m33yx89nm.jpg</v>
       </c>
       <c r="D102" t="str">
         <v>是</v>
@@ -6381,7 +6381,7 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>山东枣庄</v>
+        <v>广东广州</v>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -6425,13 +6425,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B103" t="str">
         <v>弟弟</v>
       </c>
       <c r="C103" t="str">
-        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
+        <v>assets/1787322377730-vj5csj2mll.jpg</v>
       </c>
       <c r="D103" t="str">
         <v>是</v>
@@ -6440,7 +6440,7 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>陕西西安</v>
+        <v>柬埔寨</v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -6484,13 +6484,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B104" t="str">
         <v>弟弟</v>
       </c>
       <c r="C104" t="str">
-        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
+        <v>assets/1787322269611-53yaj5ideu.jpg</v>
       </c>
       <c r="D104" t="str">
         <v>是</v>
@@ -6499,7 +6499,7 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>山东东营</v>
+        <v>山东枣庄</v>
       </c>
       <c r="G104" t="str">
         <v/>
@@ -6543,13 +6543,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B105" t="str">
         <v>弟弟</v>
       </c>
       <c r="C105" t="str">
-        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
+        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
       </c>
       <c r="D105" t="str">
         <v>是</v>
@@ -6558,7 +6558,7 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>中国台湾</v>
+        <v>陕西西安</v>
       </c>
       <c r="G105" t="str">
         <v/>
@@ -6602,13 +6602,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B106" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C106" t="str">
-        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
+        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
       </c>
       <c r="D106" t="str">
         <v>是</v>
@@ -6617,7 +6617,7 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>中国台湾</v>
+        <v>山东东营</v>
       </c>
       <c r="G106" t="str">
         <v/>
@@ -6661,13 +6661,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B107" t="str">
         <v>弟弟</v>
       </c>
       <c r="C107" t="str">
-        <v>assets/1787321834306-efgnyhujon.jpg</v>
+        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
       </c>
       <c r="D107" t="str">
         <v>是</v>
@@ -6676,7 +6676,7 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G107" t="str">
         <v/>
@@ -6720,13 +6720,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B108" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C108" t="str">
-        <v>assets/1787321439916-uttgpbkogb.jpg</v>
+        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
       </c>
       <c r="D108" t="str">
         <v>是</v>
@@ -6735,7 +6735,7 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>安徽合肥</v>
+        <v>中国台湾</v>
       </c>
       <c r="G108" t="str">
         <v/>
@@ -6785,7 +6785,7 @@
         <v>弟弟</v>
       </c>
       <c r="C109" t="str">
-        <v>assets/1787321419210-51hhgurygq.jpg</v>
+        <v>assets/1787321834306-efgnyhujon.jpg</v>
       </c>
       <c r="D109" t="str">
         <v>是</v>
@@ -6794,7 +6794,7 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>上海</v>
+        <v>北京</v>
       </c>
       <c r="G109" t="str">
         <v/>
@@ -6838,13 +6838,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B110" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C110" t="str">
-        <v>assets/1787321363369-bzjn51j5il.jpg</v>
+        <v>assets/1787321439916-uttgpbkogb.jpg</v>
       </c>
       <c r="D110" t="str">
         <v>是</v>
@@ -6853,7 +6853,7 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>中国台湾</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G110" t="str">
         <v/>
@@ -6897,13 +6897,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B111" t="str">
         <v>弟弟</v>
       </c>
       <c r="C111" t="str">
-        <v>assets/1787321332559-87p6spuch3.jpg</v>
+        <v>assets/1787321419210-51hhgurygq.jpg</v>
       </c>
       <c r="D111" t="str">
         <v>是</v>
@@ -6912,7 +6912,7 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>中国台湾</v>
+        <v>上海</v>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -6956,13 +6956,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B112" t="str">
         <v>妹妹</v>
       </c>
       <c r="C112" t="str">
-        <v>assets/1787321232531-59lnzv8y98.jpg</v>
+        <v>assets/1787321363369-bzjn51j5il.jpg</v>
       </c>
       <c r="D112" t="str">
         <v>是</v>
@@ -6971,7 +6971,7 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G112" t="str">
         <v/>
@@ -7015,13 +7015,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B113" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C113" t="str">
-        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
+        <v>assets/1787321332559-87p6spuch3.jpg</v>
       </c>
       <c r="D113" t="str">
         <v>是</v>
@@ -7030,7 +7030,7 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>浙江宁波</v>
+        <v>中国台湾</v>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -7074,13 +7074,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B114" t="str">
         <v>妹妹</v>
       </c>
       <c r="C114" t="str">
-        <v>assets/1787319800704-v3qeu062ak.jpg</v>
+        <v>assets/1787321232531-59lnzv8y98.jpg</v>
       </c>
       <c r="D114" t="str">
         <v>是</v>
@@ -7089,7 +7089,7 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>河北唐山</v>
+        <v>北京</v>
       </c>
       <c r="G114" t="str">
         <v/>
@@ -7139,7 +7139,7 @@
         <v>妹妹</v>
       </c>
       <c r="C115" t="str">
-        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D115" t="str">
         <v>是</v>
@@ -7148,7 +7148,7 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>河北石家庄</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G115" t="str">
         <v/>
@@ -7192,13 +7192,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B116" t="str">
         <v>妹妹</v>
       </c>
       <c r="C116" t="str">
-        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D116" t="str">
         <v>是</v>
@@ -7207,7 +7207,7 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>韩国</v>
+        <v>河北唐山</v>
       </c>
       <c r="G116" t="str">
         <v/>
@@ -7251,13 +7251,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>蓝银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B117" t="str">
         <v>妹妹</v>
       </c>
       <c r="C117" t="str">
-        <v>assets/1787319501376-xscwljnu1j.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D117" t="str">
         <v>是</v>
@@ -7266,7 +7266,7 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>美国</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -7310,13 +7310,13 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>棕虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B118" t="str">
         <v>妹妹</v>
       </c>
       <c r="C118" t="str">
-        <v>assets/1787319443529-4a0zqikufx.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D118" t="str">
         <v>是</v>
@@ -7325,7 +7325,7 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>中国台湾</v>
+        <v>韩国</v>
       </c>
       <c r="G118" t="str">
         <v/>
@@ -7369,13 +7369,13 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>蓝虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B119" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C119" t="str">
-        <v>assets/1787319356194-lr2d5680i9.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D119" t="str">
         <v>是</v>
@@ -7384,7 +7384,7 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>中国台湾</v>
+        <v>美国</v>
       </c>
       <c r="G119" t="str">
         <v/>
@@ -7434,7 +7434,7 @@
         <v>妹妹</v>
       </c>
       <c r="C120" t="str">
-        <v>assets/1787319208828-aizqo4blcv.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D120" t="str">
         <v>是</v>
@@ -7443,7 +7443,7 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>山东淄博</v>
+        <v>中国台湾</v>
       </c>
       <c r="G120" t="str">
         <v/>
@@ -7487,13 +7487,13 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B121" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C121" t="str">
-        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D121" t="str">
         <v>是</v>
@@ -7502,7 +7502,7 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>韩国</v>
+        <v>中国台湾</v>
       </c>
       <c r="G121" t="str">
         <v/>
@@ -7546,13 +7546,13 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>棕虎补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B122" t="str">
         <v>妹妹</v>
       </c>
       <c r="C122" t="str">
-        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D122" t="str">
         <v>是</v>
@@ -7561,7 +7561,7 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>四川成都</v>
+        <v>山东淄博</v>
       </c>
       <c r="G122" t="str">
         <v/>
@@ -7608,10 +7608,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B123" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C123" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D123" t="str">
         <v>是</v>
@@ -7620,7 +7620,7 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>广东广州</v>
+        <v>韩国</v>
       </c>
       <c r="G123" t="str">
         <v/>
@@ -7664,13 +7664,13 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B124" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C124" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D124" t="str">
         <v>是</v>
@@ -7679,7 +7679,7 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>四川成都</v>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -7723,13 +7723,13 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B125" t="str">
         <v>弟弟</v>
       </c>
       <c r="C125" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D125" t="str">
         <v>是</v>
@@ -7738,7 +7738,7 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>天津</v>
+        <v>广东广州</v>
       </c>
       <c r="G125" t="str">
         <v/>
@@ -7788,7 +7788,7 @@
         <v>弟弟</v>
       </c>
       <c r="C126" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D126" t="str">
         <v>是</v>
@@ -7797,7 +7797,7 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>山西朔州</v>
+        <v>黑龙江鹤岗</v>
       </c>
       <c r="G126" t="str">
         <v/>
@@ -7827,7 +7827,7 @@
         <v/>
       </c>
       <c r="P126" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q126" t="str">
         <v/>
@@ -7841,13 +7841,13 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B127" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C127" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D127" t="str">
         <v>是</v>
@@ -7856,7 +7856,7 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>贵州</v>
+        <v>天津</v>
       </c>
       <c r="G127" t="str">
         <v/>
@@ -7900,22 +7900,22 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B128" t="str">
         <v>弟弟</v>
       </c>
       <c r="C128" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D128" t="str">
         <v>是</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F128" t="str">
-        <v>北京</v>
+        <v>山西朔州</v>
       </c>
       <c r="G128" t="str">
         <v/>
@@ -7945,7 +7945,7 @@
         <v/>
       </c>
       <c r="P128" t="str">
-        <v/>
+        <v>已接猫</v>
       </c>
       <c r="Q128" t="str">
         <v/>
@@ -7954,27 +7954,27 @@
         <v/>
       </c>
       <c r="S128" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B129" t="str">
         <v>妹妹</v>
       </c>
       <c r="C129" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D129" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-04-10</v>
+        <v/>
       </c>
       <c r="F129" t="str">
-        <v/>
+        <v>贵州</v>
       </c>
       <c r="G129" t="str">
         <v/>
@@ -8013,27 +8013,27 @@
         <v/>
       </c>
       <c r="S129" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>阴影色NS12</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B130" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C130" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D130" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F130" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G130" t="str">
         <v/>
@@ -8077,22 +8077,22 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>阴影色NS11</v>
+        <v>纯黑色</v>
       </c>
       <c r="B131" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C131" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D131" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-06-15</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F131" t="str">
-        <v>重庆</v>
+        <v/>
       </c>
       <c r="G131" t="str">
         <v/>
@@ -8136,22 +8136,22 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B132" t="str">
         <v>妹妹</v>
       </c>
       <c r="C132" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D132" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-03-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F132" t="str">
-        <v>中国澳门</v>
+        <v/>
       </c>
       <c r="G132" t="str">
         <v/>
@@ -8195,22 +8195,22 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B133" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C133" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D133" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F133" t="str">
-        <v/>
+        <v>重庆</v>
       </c>
       <c r="G133" t="str">
         <v/>
@@ -8254,22 +8254,22 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B134" t="str">
         <v>妹妹</v>
       </c>
       <c r="C134" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D134" t="str">
         <v>是</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F134" t="str">
-        <v>浙江温州</v>
+        <v>中国澳门</v>
       </c>
       <c r="G134" t="str">
         <v/>
@@ -8319,13 +8319,13 @@
         <v>妹妹</v>
       </c>
       <c r="C135" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D135" t="str">
         <v>否</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F135" t="str">
         <v/>
@@ -8375,10 +8375,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B136" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C136" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D136" t="str">
         <v>是</v>
@@ -8387,7 +8387,7 @@
         <v>2026-06-06</v>
       </c>
       <c r="F136" t="str">
-        <v>北京</v>
+        <v>浙江温州</v>
       </c>
       <c r="G136" t="str">
         <v/>
@@ -8437,13 +8437,13 @@
         <v>妹妹</v>
       </c>
       <c r="C137" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D137" t="str">
         <v>否</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F137" t="str">
         <v/>
@@ -8490,13 +8490,13 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B138" t="str">
         <v>弟弟</v>
       </c>
       <c r="C138" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D138" t="str">
         <v>是</v>
@@ -8505,7 +8505,7 @@
         <v>2026-06-06</v>
       </c>
       <c r="F138" t="str">
-        <v>河北石家庄</v>
+        <v>北京</v>
       </c>
       <c r="G138" t="str">
         <v/>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B139" t="str">
         <v>妹妹</v>
       </c>
       <c r="C139" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D139" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E139" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F139" t="str">
-        <v>浙江宁波</v>
+        <v/>
       </c>
       <c r="G139" t="str">
         <v/>
@@ -8614,7 +8614,7 @@
         <v>弟弟</v>
       </c>
       <c r="C140" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D140" t="str">
         <v>是</v>
@@ -8623,7 +8623,7 @@
         <v>2026-06-06</v>
       </c>
       <c r="F140" t="str">
-        <v>上海</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G140" t="str">
         <v/>
@@ -8667,22 +8667,22 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>纯黑色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B141" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C141" t="str">
-        <v>assets/1790733778469-jt9fswxe9w.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D141" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-04-17</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F141" t="str">
-        <v/>
+        <v>浙江宁波</v>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -8726,22 +8726,22 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B142" t="str">
         <v>弟弟</v>
       </c>
       <c r="C142" t="str">
-        <v>assets/1790734215453-0zvw0v9uja.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D142" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F142" t="str">
-        <v/>
+        <v>上海</v>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -8785,19 +8785,19 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>阴影色NS11</v>
+        <v>纯黑色</v>
       </c>
       <c r="B143" t="str">
         <v>弟弟</v>
       </c>
       <c r="C143" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1790733778469-jt9fswxe9w.jpg</v>
       </c>
       <c r="D143" t="str">
         <v>否</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-05-28</v>
+        <v>2026-04-17</v>
       </c>
       <c r="F143" t="str">
         <v/>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B144" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C144" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1790734215453-0zvw0v9uja.jpg</v>
       </c>
       <c r="D144" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F144" t="str">
-        <v>香港</v>
+        <v/>
       </c>
       <c r="G144" t="str">
         <v/>
@@ -8903,22 +8903,22 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B145" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C145" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D145" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-03-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F145" t="str">
-        <v>四川成都</v>
+        <v/>
       </c>
       <c r="G145" t="str">
         <v/>
@@ -8962,22 +8962,22 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>凯米尔色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B146" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C146" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D146" t="str">
         <v>是</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F146" t="str">
-        <v>上海浦东</v>
+        <v>香港</v>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -9021,22 +9021,22 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B147" t="str">
         <v>妹妹</v>
       </c>
       <c r="C147" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D147" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-04-09</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F147" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -9080,22 +9080,22 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B148" t="str">
         <v>弟弟</v>
       </c>
       <c r="C148" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D148" t="str">
         <v>是</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-05-18</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F148" t="str">
-        <v>北京</v>
+        <v>上海浦东</v>
       </c>
       <c r="G148" t="str">
         <v/>
@@ -9139,19 +9139,19 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B149" t="str">
         <v>妹妹</v>
       </c>
       <c r="C149" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D149" t="str">
         <v>否</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-02-14</v>
+        <v>2026-04-09</v>
       </c>
       <c r="F149" t="str">
         <v/>
@@ -9198,22 +9198,22 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>银虎斑补丁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B150" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C150" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D150" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F150" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G150" t="str">
         <v/>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B151" t="str">
         <v>妹妹</v>
       </c>
       <c r="C151" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D151" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F151" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G151" t="str">
         <v/>
@@ -9316,22 +9316,22 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B152" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C152" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D152" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F152" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G152" t="str">
         <v/>
@@ -9378,19 +9378,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B153" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C153" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D153" t="str">
         <v>是</v>
       </c>
       <c r="E153" t="str">
-        <v>2025-11-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F153" t="str">
-        <v>韩国</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G153" t="str">
         <v/>
@@ -9437,19 +9437,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B154" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C154" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D154" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F154" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G154" t="str">
         <v/>
@@ -9493,22 +9493,22 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B155" t="str">
         <v>弟弟</v>
       </c>
       <c r="C155" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D155" t="str">
         <v>是</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-05-28</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F155" t="str">
-        <v>四川自贡</v>
+        <v>韩国</v>
       </c>
       <c r="G155" t="str">
         <v/>
@@ -9552,19 +9552,19 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B156" t="str">
         <v>妹妹</v>
       </c>
       <c r="C156" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D156" t="str">
         <v>否</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F156" t="str">
         <v/>
@@ -9611,22 +9611,22 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B157" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C157" t="str">
-        <v>assets/1790733648123-636cut584p.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D157" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-04-10</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F157" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G157" t="str">
         <v/>
@@ -9670,22 +9670,22 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B158" t="str">
         <v>妹妹</v>
       </c>
       <c r="C158" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D158" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F158" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G158" t="str">
         <v/>
@@ -9729,22 +9729,22 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>浅色银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B159" t="str">
         <v>妹妹</v>
       </c>
       <c r="C159" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1790733648123-636cut584p.jpg</v>
       </c>
       <c r="D159" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-06-05</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F159" t="str">
-        <v>河北邢台</v>
+        <v/>
       </c>
       <c r="G159" t="str">
         <v/>
@@ -9788,22 +9788,22 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B160" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C160" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D160" t="str">
         <v>是</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F160" t="str">
-        <v>四川自贡</v>
+        <v>韩国</v>
       </c>
       <c r="G160" t="str">
         <v/>
@@ -9847,22 +9847,22 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>棕虎斑补丁</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B161" t="str">
         <v>妹妹</v>
       </c>
       <c r="C161" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D161" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F161" t="str">
-        <v/>
+        <v>河北邢台</v>
       </c>
       <c r="G161" t="str">
         <v/>
@@ -9906,22 +9906,22 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B162" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C162" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D162" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-04-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F162" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G162" t="str">
         <v/>
@@ -9965,19 +9965,19 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B163" t="str">
         <v>妹妹</v>
       </c>
       <c r="C163" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D163" t="str">
         <v>否</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-04-17</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F163" t="str">
         <v/>
@@ -10024,19 +10024,19 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B164" t="str">
         <v>妹妹</v>
       </c>
       <c r="C164" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D164" t="str">
         <v>否</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-04-30</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F164" t="str">
         <v/>
@@ -10083,52 +10083,52 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B165" t="str">
         <v>妹妹</v>
       </c>
       <c r="C165" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D165" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-02-20</v>
+        <v>2026-04-17</v>
       </c>
       <c r="F165" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G165" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H165" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I165" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J165" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K165" t="str">
         <v/>
       </c>
       <c r="L165" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M165" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N165" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O165" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P165" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q165" t="str">
         <v/>
@@ -10137,27 +10137,27 @@
         <v/>
       </c>
       <c r="S165" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B166" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C166" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D166" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E166" t="str">
-        <v/>
+        <v>2026-04-30</v>
       </c>
       <c r="F166" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G166" t="str">
         <v/>
@@ -10201,52 +10201,52 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B167" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C167" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D167" t="str">
         <v>是</v>
       </c>
       <c r="E167" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F167" t="str">
-        <v>广东广州</v>
+        <v>荷兰</v>
       </c>
       <c r="G167" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H167" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I167" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J167" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K167" t="str">
         <v/>
       </c>
       <c r="L167" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M167" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N167" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O167" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P167" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q167" t="str">
         <v/>
@@ -10255,18 +10255,18 @@
         <v/>
       </c>
       <c r="S167" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B168" t="str">
         <v>弟弟</v>
       </c>
       <c r="C168" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D168" t="str">
         <v>是</v>
@@ -10275,7 +10275,7 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>山西朔州</v>
+        <v>广东广州</v>
       </c>
       <c r="G168" t="str">
         <v/>
@@ -10319,13 +10319,13 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B169" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C169" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D169" t="str">
         <v>是</v>
@@ -10334,7 +10334,7 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>浙江宁波</v>
+        <v>广东广州</v>
       </c>
       <c r="G169" t="str">
         <v/>
@@ -10384,7 +10384,7 @@
         <v>弟弟</v>
       </c>
       <c r="C170" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D170" t="str">
         <v>是</v>
@@ -10393,7 +10393,7 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>陕西西安</v>
+        <v>山西朔州</v>
       </c>
       <c r="G170" t="str">
         <v/>
@@ -10440,10 +10440,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B171" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C171" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D171" t="str">
         <v>是</v>
@@ -10452,7 +10452,7 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>黑龙江漠河</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G171" t="str">
         <v/>
@@ -10496,13 +10496,13 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B172" t="str">
         <v>弟弟</v>
       </c>
       <c r="C172" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D172" t="str">
         <v>是</v>
@@ -10511,7 +10511,7 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>日本</v>
+        <v>陕西西安</v>
       </c>
       <c r="G172" t="str">
         <v/>
@@ -10558,10 +10558,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B173" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C173" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D173" t="str">
         <v>是</v>
@@ -10570,7 +10570,7 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>浙江杭州</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G173" t="str">
         <v/>
@@ -10614,13 +10614,13 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B174" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C174" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D174" t="str">
         <v>是</v>
@@ -10629,7 +10629,7 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>贵州安顺</v>
+        <v>日本</v>
       </c>
       <c r="G174" t="str">
         <v/>
@@ -10679,7 +10679,7 @@
         <v>妹妹</v>
       </c>
       <c r="C175" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D175" t="str">
         <v>是</v>
@@ -10688,7 +10688,7 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>山东青岛</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G175" t="str">
         <v/>
@@ -10735,10 +10735,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B176" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C176" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D176" t="str">
         <v>是</v>
@@ -10747,7 +10747,7 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>黑龙江漠河</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G176" t="str">
         <v/>
@@ -10791,13 +10791,13 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B177" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C177" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D177" t="str">
         <v>是</v>
@@ -10806,7 +10806,7 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>河南鹤壁</v>
+        <v>山东青岛</v>
       </c>
       <c r="G177" t="str">
         <v/>
@@ -10856,7 +10856,7 @@
         <v>弟弟</v>
       </c>
       <c r="C178" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D178" t="str">
         <v>是</v>
@@ -10865,7 +10865,7 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>陕西西安</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G178" t="str">
         <v/>
@@ -10909,13 +10909,13 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>棕虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B179" t="str">
         <v>弟弟</v>
       </c>
       <c r="C179" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D179" t="str">
         <v>是</v>
@@ -10924,7 +10924,7 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>四川成都</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G179" t="str">
         <v/>
@@ -10968,22 +10968,22 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B180" t="str">
         <v>弟弟</v>
       </c>
       <c r="C180" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D180" t="str">
         <v>是</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F180" t="str">
-        <v>四川成都</v>
+        <v>陕西西安</v>
       </c>
       <c r="G180" t="str">
         <v/>
@@ -11027,13 +11027,13 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B181" t="str">
         <v>弟弟</v>
       </c>
       <c r="C181" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
       </c>
       <c r="D181" t="str">
         <v>是</v>
@@ -11042,7 +11042,7 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>新加坡</v>
+        <v>四川成都</v>
       </c>
       <c r="G181" t="str">
         <v/>
@@ -11086,22 +11086,22 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>凯米尔色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B182" t="str">
         <v>弟弟</v>
       </c>
       <c r="C182" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
       </c>
       <c r="D182" t="str">
         <v>是</v>
       </c>
       <c r="E182" t="str">
-        <v/>
+        <v>2026-05-18</v>
       </c>
       <c r="F182" t="str">
-        <v>上海浦东</v>
+        <v>四川成都</v>
       </c>
       <c r="G182" t="str">
         <v/>
@@ -11145,22 +11145,22 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B183" t="str">
         <v>弟弟</v>
       </c>
       <c r="C183" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
       </c>
       <c r="D183" t="str">
         <v>是</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F183" t="str">
-        <v>浙江温州</v>
+        <v>新加坡</v>
       </c>
       <c r="G183" t="str">
         <v/>
@@ -11204,66 +11204,184 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B184" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C184" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D184" t="str">
+        <v>是</v>
+      </c>
+      <c r="E184" t="str">
+        <v/>
+      </c>
+      <c r="F184" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G184" t="str">
+        <v/>
+      </c>
+      <c r="H184" t="str">
+        <v/>
+      </c>
+      <c r="I184" t="str">
+        <v/>
+      </c>
+      <c r="J184" t="str">
+        <v/>
+      </c>
+      <c r="K184" t="str">
+        <v/>
+      </c>
+      <c r="L184" t="str">
+        <v/>
+      </c>
+      <c r="M184" t="str">
+        <v/>
+      </c>
+      <c r="N184" t="str">
+        <v/>
+      </c>
+      <c r="O184" t="str">
+        <v/>
+      </c>
+      <c r="P184" t="str">
+        <v/>
+      </c>
+      <c r="Q184" t="str">
+        <v/>
+      </c>
+      <c r="R184" t="str">
+        <v/>
+      </c>
+      <c r="S184" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
         <v>棕虎斑</v>
       </c>
-      <c r="B184" t="str">
+      <c r="B185" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C185" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D185" t="str">
+        <v>是</v>
+      </c>
+      <c r="E185" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F185" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G185" t="str">
+        <v/>
+      </c>
+      <c r="H185" t="str">
+        <v/>
+      </c>
+      <c r="I185" t="str">
+        <v/>
+      </c>
+      <c r="J185" t="str">
+        <v/>
+      </c>
+      <c r="K185" t="str">
+        <v/>
+      </c>
+      <c r="L185" t="str">
+        <v/>
+      </c>
+      <c r="M185" t="str">
+        <v/>
+      </c>
+      <c r="N185" t="str">
+        <v/>
+      </c>
+      <c r="O185" t="str">
+        <v/>
+      </c>
+      <c r="P185" t="str">
+        <v/>
+      </c>
+      <c r="Q185" t="str">
+        <v/>
+      </c>
+      <c r="R185" t="str">
+        <v/>
+      </c>
+      <c r="S185" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B186" t="str">
         <v>妹妹</v>
       </c>
-      <c r="C184" t="str">
+      <c r="C186" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D184" t="str">
-        <v>否</v>
-      </c>
-      <c r="E184" t="str">
+      <c r="D186" t="str">
+        <v>否</v>
+      </c>
+      <c r="E186" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F184" t="str">
-        <v/>
-      </c>
-      <c r="G184" t="str">
-        <v/>
-      </c>
-      <c r="H184" t="str">
-        <v/>
-      </c>
-      <c r="I184" t="str">
-        <v/>
-      </c>
-      <c r="J184" t="str">
-        <v/>
-      </c>
-      <c r="K184" t="str">
-        <v/>
-      </c>
-      <c r="L184" t="str">
-        <v/>
-      </c>
-      <c r="M184" t="str">
-        <v/>
-      </c>
-      <c r="N184" t="str">
-        <v/>
-      </c>
-      <c r="O184" t="str">
-        <v/>
-      </c>
-      <c r="P184" t="str">
-        <v/>
-      </c>
-      <c r="Q184" t="str">
-        <v/>
-      </c>
-      <c r="R184" t="str">
-        <v/>
-      </c>
-      <c r="S184" t="str">
+      <c r="F186" t="str">
+        <v/>
+      </c>
+      <c r="G186" t="str">
+        <v/>
+      </c>
+      <c r="H186" t="str">
+        <v/>
+      </c>
+      <c r="I186" t="str">
+        <v/>
+      </c>
+      <c r="J186" t="str">
+        <v/>
+      </c>
+      <c r="K186" t="str">
+        <v/>
+      </c>
+      <c r="L186" t="str">
+        <v/>
+      </c>
+      <c r="M186" t="str">
+        <v/>
+      </c>
+      <c r="N186" t="str">
+        <v/>
+      </c>
+      <c r="O186" t="str">
+        <v/>
+      </c>
+      <c r="P186" t="str">
+        <v/>
+      </c>
+      <c r="Q186" t="str">
+        <v/>
+      </c>
+      <c r="R186" t="str">
+        <v/>
+      </c>
+      <c r="S186" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S184"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S186"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S186"/>
+  <dimension ref="A1:S192"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -466,19 +466,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B2" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1791288567764-tti55g9g1q.jpg</v>
+        <v>assets/1791885799211-r54amxe2jp.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>否</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -525,13 +525,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色</v>
       </c>
       <c r="B3" t="str">
         <v>弟弟</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1791288502036-4v43o0otqq.jpg</v>
+        <v>assets/1791885766213-djh49zfdy8.jpg</v>
       </c>
       <c r="D3" t="str">
         <v>否</v>
@@ -584,19 +584,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色</v>
       </c>
       <c r="B4" t="str">
         <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1790734752606-rusbv65ug8.jpg</v>
+        <v>assets/1791885692087-flz5al0ukw.jpg</v>
       </c>
       <c r="D4" t="str">
         <v>否</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-04-28</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -643,19 +643,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B5" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1790734688874-ldibzixi2g.jpg</v>
+        <v>assets/1791885628374-op5p4tcc5c.jpg</v>
       </c>
       <c r="D5" t="str">
         <v>否</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -702,22 +702,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B6" t="str">
         <v>弟弟</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1790734651251-a58tdtmhnx.jpg</v>
+        <v>assets/1791885580674-a6onl6jgc.jpg</v>
       </c>
       <c r="D6" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F6" t="str">
-        <v>成都</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -761,22 +761,22 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>浅银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B7" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1790734595573-u465hv1hyg.jpg</v>
+        <v>assets/1791885502285-o86pddnxqc.jpg</v>
       </c>
       <c r="D7" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E7" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="F7" t="str">
-        <v>浙江嘉兴</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -820,22 +820,22 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>浅银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B8" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1790734548586-cztim8ip4y.jpg</v>
+        <v>assets/1791288567764-tti55g9g1q.jpg</v>
       </c>
       <c r="D8" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F8" t="str">
-        <v>西安</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -879,19 +879,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B9" t="str">
         <v>弟弟</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1790734499008-43htmo2xuw.jpg</v>
+        <v>assets/1791288502036-4v43o0otqq.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>否</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-03-20</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -938,19 +938,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>阴影色NS11</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B10" t="str">
         <v>弟弟</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1789655131156-6ywyod2pgz.jpg</v>
+        <v>assets/1790734752606-rusbv65ug8.jpg</v>
       </c>
       <c r="D10" t="str">
         <v>否</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-06-15</v>
+        <v>2026-04-28</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -997,22 +997,22 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>浅银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B11" t="str">
         <v>妹妹</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1789654858942-ws3mqfv0zf.jpg</v>
+        <v>assets/1790734688874-ldibzixi2g.jpg</v>
       </c>
       <c r="D11" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F11" t="str">
-        <v>浙江杭州</v>
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1056,22 +1056,22 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B12" t="str">
         <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1789654723483-fyl8c7wdqg.jpg</v>
+        <v>assets/1790734651251-a58tdtmhnx.jpg</v>
       </c>
       <c r="D12" t="str">
         <v>是</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-06-26</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F12" t="str">
-        <v>天津</v>
+        <v>成都</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1115,22 +1115,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>银虎班补丁</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B13" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1789654675792-6d4kyyncmf.jpg</v>
+        <v>assets/1790734595573-u465hv1hyg.jpg</v>
       </c>
       <c r="D13" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>浙江嘉兴</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1174,22 +1174,22 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>烟灰色</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B14" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1789654628929-2wok5d7b71.jpg</v>
+        <v>assets/1790734548586-cztim8ip4y.jpg</v>
       </c>
       <c r="D14" t="str">
         <v>是</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F14" t="str">
-        <v>新加坡</v>
+        <v>西安</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1233,19 +1233,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>阴影色NS11</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B15" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1789654549268-68uab4pdoy.jpg</v>
+        <v>assets/1790734499008-43htmo2xuw.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>否</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-06-15</v>
+        <v>2026-03-20</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -1292,22 +1292,22 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>阴影色NS12</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B16" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1788534744815-pzs6jqs2pm.jpg</v>
+        <v>assets/1789655131156-6ywyod2pgz.jpg</v>
       </c>
       <c r="D16" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>广州</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1351,13 +1351,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>棕虎斑</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B17" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1788534522775-my4ggv0pwo.jpg</v>
+        <v>assets/1789654858942-ws3mqfv0zf.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>是</v>
@@ -1366,7 +1366,7 @@
         <v>2026-06-15</v>
       </c>
       <c r="F17" t="str">
-        <v>西藏</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1416,7 +1416,7 @@
         <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1788442386268-ilpasqz91m.jpg</v>
+        <v>assets/1789654723483-fyl8c7wdqg.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>是</v>
@@ -1425,7 +1425,7 @@
         <v>2026-06-26</v>
       </c>
       <c r="F18" t="str">
-        <v>成都</v>
+        <v>天津</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1469,22 +1469,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>浅银虎斑</v>
+        <v>银虎班补丁</v>
       </c>
       <c r="B19" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1788442356842-bbleakpy85.jpg</v>
+        <v>assets/1789654675792-6d4kyyncmf.jpg</v>
       </c>
       <c r="D19" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F19" t="str">
-        <v>浙江嘉兴</v>
+        <v/>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1528,22 +1528,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>浅烟灰色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B20" t="str">
         <v>弟弟</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1788442221802-et3crh0tww.jpg</v>
+        <v>assets/1789654628929-2wok5d7b71.jpg</v>
       </c>
       <c r="D20" t="str">
         <v>是</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-03-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F20" t="str">
-        <v>成都</v>
+        <v>新加坡</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>凯米尔</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B21" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1788014088852-oqkg79cki9.jpg</v>
+        <v>assets/1789654549268-68uab4pdoy.jpg</v>
       </c>
       <c r="D21" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F21" t="str">
-        <v>湖北襄阳</v>
+        <v/>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1646,19 +1646,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B22" t="str">
         <v>妹妹</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1788014050978-9a2sguuo1u.jpg</v>
+        <v>assets/1788534744815-pzs6jqs2pm.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>否</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -1711,7 +1711,7 @@
         <v>弟弟</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1788013924404-gmlh0hfjae.jpg</v>
+        <v>assets/1788534522775-my4ggv0pwo.jpg</v>
       </c>
       <c r="D23" t="str">
         <v>是</v>
@@ -1720,7 +1720,7 @@
         <v>2026-06-15</v>
       </c>
       <c r="F23" t="str">
-        <v>浙江嘉兴</v>
+        <v>西藏</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1764,13 +1764,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>凯米尔色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B24" t="str">
         <v>弟弟</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1788013889955-wpykaycfde.jpg</v>
+        <v>assets/1788442386268-ilpasqz91m.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>是</v>
@@ -1779,7 +1779,7 @@
         <v>2026-06-26</v>
       </c>
       <c r="F24" t="str">
-        <v>湖北襄阳</v>
+        <v>成都</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1823,22 +1823,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B25" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1788013810551-b90h1mwfiq.jpg</v>
+        <v>assets/1788442356842-bbleakpy85.jpg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F25" t="str">
-        <v>新疆</v>
+        <v>浙江嘉兴</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1882,22 +1882,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>银虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B26" t="str">
         <v>弟弟</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1787837910484-r7urrsuib0.jpg</v>
+        <v>assets/1788442221802-et3crh0tww.jpg</v>
       </c>
       <c r="D26" t="str">
         <v>是</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-05-18</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F26" t="str">
-        <v>香港</v>
+        <v>成都</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1941,22 +1941,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>纯黑色</v>
+        <v>凯米尔</v>
       </c>
       <c r="B27" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1787837846581-6q9nxgad35.jpg</v>
+        <v>assets/1788014088852-oqkg79cki9.jpg</v>
       </c>
       <c r="D27" t="str">
         <v>是</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F27" t="str">
-        <v>天津</v>
+        <v>湖北襄阳</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -2000,22 +2000,22 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>凯米尔</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B28" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1790734407566-tge3si2tw9.jpg</v>
+        <v>assets/1788014050978-9a2sguuo1u.jpg</v>
       </c>
       <c r="D28" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B29" t="str">
         <v>弟弟</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
+        <v>assets/1788013924404-gmlh0hfjae.jpg</v>
       </c>
       <c r="D29" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F29" t="str">
-        <v/>
+        <v>浙江嘉兴</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2118,22 +2118,22 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B30" t="str">
         <v>弟弟</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1787837648423-9riberz3tq.jpg</v>
+        <v>assets/1788013889955-wpykaycfde.jpg</v>
       </c>
       <c r="D30" t="str">
         <v>是</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F30" t="str">
-        <v>北京</v>
+        <v>湖北襄阳</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2177,22 +2177,22 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B31" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
+        <v>assets/1788013810551-b90h1mwfiq.jpg</v>
       </c>
       <c r="D31" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F31" t="str">
-        <v/>
+        <v>新疆</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2236,22 +2236,22 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B32" t="str">
         <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1787479268842-7en9nzy302.jpg</v>
+        <v>assets/1787837910484-r7urrsuib0.jpg</v>
       </c>
       <c r="D32" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-06-10</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F32" t="str">
-        <v/>
+        <v>香港</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v/>
       </c>
       <c r="J32" t="str">
-        <v>2026-06-10</v>
+        <v/>
       </c>
       <c r="K32" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>妹妹</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1787479242639-32zuh5lham.jpg</v>
+        <v>assets/1787837846581-6q9nxgad35.jpg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B34" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1787466121255-21jto2cugv.jpg</v>
+        <v>assets/1790734407566-tge3si2tw9.jpg</v>
       </c>
       <c r="D34" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E34" t="str">
-        <v/>
+        <v>2026-06-26</v>
       </c>
       <c r="F34" t="str">
-        <v>四川广安</v>
+        <v/>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2416,10 +2416,10 @@
         <v>烟灰色</v>
       </c>
       <c r="B35" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
+        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
       </c>
       <c r="D35" t="str">
         <v>否</v>
@@ -2475,19 +2475,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B36" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1787388277490-e6u506cx0r.jpg</v>
+        <v>assets/1787837648423-9riberz3tq.jpg</v>
       </c>
       <c r="D36" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E36" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F36" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2531,22 +2531,22 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B37" t="str">
         <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1787328436957-x30od0gw28.jpg</v>
+        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
       </c>
       <c r="E37" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F37" t="str">
-        <v>江苏苏州</v>
+        <v>成都</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2590,22 +2590,22 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B38" t="str">
         <v>弟弟</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
+        <v>assets/1787479268842-7en9nzy302.jpg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
       </c>
       <c r="E38" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F38" t="str">
-        <v>辽宁东港</v>
+        <v>新疆</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="J38" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="K38" t="str">
         <v/>
@@ -2649,22 +2649,22 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B39" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1787327967245-m62ohievcl.jpg</v>
+        <v>assets/1787479242639-32zuh5lham.jpg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
       </c>
       <c r="E39" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F39" t="str">
-        <v>福建福州</v>
+        <v>天津</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2708,13 +2708,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B40" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
+        <v>assets/1787466121255-21jto2cugv.jpg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2723,7 +2723,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>上海</v>
+        <v>四川广安</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>纯蓝色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B41" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1787327793837-znk2knoo6p.jpg</v>
+        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
       </c>
       <c r="D41" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E41" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F41" t="str">
-        <v>河南鹤壁</v>
+        <v/>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2826,22 +2826,22 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B42" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1787327752832-kkpmp21os3.jpg</v>
+        <v>assets/1787388277490-e6u506cx0r.jpg</v>
       </c>
       <c r="D42" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E42" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F42" t="str">
-        <v>陕西西安</v>
+        <v/>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2888,10 +2888,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B43" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
+        <v>assets/1787328436957-x30od0gw28.jpg</v>
       </c>
       <c r="D43" t="str">
         <v>是</v>
@@ -2900,7 +2900,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>陕西西安</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B44" t="str">
         <v>弟弟</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1787327573762-h23cux94p2.jpg</v>
+        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>北京</v>
+        <v>辽宁东港</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3003,13 +3003,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B45" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1787327496557-9daggljg4g.jpg</v>
+        <v>assets/1787327967245-m62ohievcl.jpg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
@@ -3018,7 +3018,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>黑龙江哈尔滨</v>
+        <v>福建福州</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B46" t="str">
         <v>弟弟</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
+        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>甘肃嘉峪关</v>
+        <v>上海</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3121,13 +3121,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>蓝虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B47" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
+        <v>assets/1787327793837-znk2knoo6p.jpg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>安徽合肥</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3186,7 +3186,7 @@
         <v>弟弟</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1787327337811-u5u2pdew3.jpg</v>
+        <v>assets/1787327752832-kkpmp21os3.jpg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>安徽合肥</v>
+        <v>陕西西安</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B49" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1787327309143-6c1dan1sev.jpg</v>
+        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -3254,7 +3254,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>四川成都</v>
+        <v>陕西西安</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -3304,7 +3304,7 @@
         <v>弟弟</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1787327277453-w89ujg69fm.jpg</v>
+        <v>assets/1787327573762-h23cux94p2.jpg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
@@ -3313,7 +3313,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>四川成都</v>
+        <v>北京</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3357,13 +3357,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>蓝银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B51" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1787327232159-lkrcl588a5.jpg</v>
+        <v>assets/1787327496557-9daggljg4g.jpg</v>
       </c>
       <c r="D51" t="str">
         <v>是</v>
@@ -3372,7 +3372,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>四川成都</v>
+        <v>黑龙江哈尔滨</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,13 +3416,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>玳瑁色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B52" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1787327182347-3az0z7sys2.jpg</v>
+        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
       </c>
       <c r="D52" t="str">
         <v>是</v>
@@ -3431,7 +3431,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>四川内江</v>
+        <v>甘肃嘉峪关</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3475,13 +3475,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>棕虎补丁</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B53" t="str">
         <v>妹妹</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
+        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
       </c>
       <c r="D53" t="str">
         <v>是</v>
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>贵州贵阳</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3534,13 +3534,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>黑烟色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B54" t="str">
         <v>弟弟</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1787327101790-tqjlseog5y.jpg</v>
+        <v>assets/1787327337811-u5u2pdew3.jpg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
@@ -3549,7 +3549,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>浙江杭州</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3593,13 +3593,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B55" t="str">
         <v>弟弟</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1787327019632-l1780lu2hj.jpg</v>
+        <v>assets/1787327309143-6c1dan1sev.jpg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
@@ -3608,7 +3608,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>山东威海</v>
+        <v>四川成都</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B56" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1787326905275-plz3fpgo97.jpg</v>
+        <v>assets/1787327277453-w89ujg69fm.jpg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
@@ -3667,7 +3667,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>浙江杭州</v>
+        <v>四川成都</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3711,13 +3711,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>蓝虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B57" t="str">
         <v>弟弟</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
+        <v>assets/1787327232159-lkrcl588a5.jpg</v>
       </c>
       <c r="D57" t="str">
         <v>是</v>
@@ -3770,13 +3770,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>凯米尔色</v>
+        <v>玳瑁色</v>
       </c>
       <c r="B58" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
+        <v>assets/1787327182347-3az0z7sys2.jpg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
@@ -3785,7 +3785,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>四川成都</v>
+        <v>四川内江</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>凯米尔</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B59" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1787326814713-p5oavnlulg.jpg</v>
+        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
       </c>
       <c r="D59" t="str">
         <v>是</v>
@@ -3844,7 +3844,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>四川成都</v>
+        <v>贵州贵阳</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3888,13 +3888,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>棕虎斑</v>
+        <v>黑烟色</v>
       </c>
       <c r="B60" t="str">
         <v>弟弟</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1787326773577-13q5out2d0.jpg</v>
+        <v>assets/1787327101790-tqjlseog5y.jpg</v>
       </c>
       <c r="D60" t="str">
         <v>是</v>
@@ -3903,7 +3903,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>四川宜宾</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3947,13 +3947,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>金棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B61" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1787326548993-89s929m2hg.jpg</v>
+        <v>assets/1787327019632-l1780lu2hj.jpg</v>
       </c>
       <c r="D61" t="str">
         <v>是</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>上海</v>
+        <v>山东威海</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4006,13 +4006,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B62" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1787326449218-09s9ucram4.jpg</v>
+        <v>assets/1787326905275-plz3fpgo97.jpg</v>
       </c>
       <c r="D62" t="str">
         <v>是</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>德国</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4065,13 +4065,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>棕虎补丁</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B63" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1787326277374-8ti107m5ki.jpg</v>
+        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
       </c>
       <c r="D63" t="str">
         <v>是</v>
@@ -4080,7 +4080,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>广东深圳</v>
+        <v>四川成都</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -4124,13 +4124,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B64" t="str">
         <v>弟弟</v>
       </c>
       <c r="C64" t="str">
-        <v>assets/1787326236952-2pmwche4t3.jpg</v>
+        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
       </c>
       <c r="D64" t="str">
         <v>是</v>
@@ -4139,7 +4139,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>福建泉州</v>
+        <v>四川成都</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -4183,13 +4183,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B65" t="str">
         <v>弟弟</v>
       </c>
       <c r="C65" t="str">
-        <v>assets/1787326184557-90v6clkwen.jpg</v>
+        <v>assets/1787326814713-p5oavnlulg.jpg</v>
       </c>
       <c r="D65" t="str">
         <v>是</v>
@@ -4198,7 +4198,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>福建福州</v>
+        <v>四川成都</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -4245,10 +4245,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B66" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C66" t="str">
-        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
+        <v>assets/1787326773577-13q5out2d0.jpg</v>
       </c>
       <c r="D66" t="str">
         <v>是</v>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>广西贵港</v>
+        <v>四川宜宾</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -4301,13 +4301,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>凯米尔色</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B67" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C67" t="str">
-        <v>assets/1787325862706-wq18k3ej56.jpg</v>
+        <v>assets/1787326548993-89s929m2hg.jpg</v>
       </c>
       <c r="D67" t="str">
         <v>是</v>
@@ -4316,7 +4316,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>江苏苏州</v>
+        <v>上海</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4366,7 +4366,7 @@
         <v>弟弟</v>
       </c>
       <c r="C68" t="str">
-        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
+        <v>assets/1787326449218-09s9ucram4.jpg</v>
       </c>
       <c r="D68" t="str">
         <v>是</v>
@@ -4375,7 +4375,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>江苏苏州</v>
+        <v>德国</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -4419,13 +4419,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B69" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C69" t="str">
-        <v>assets/1787325706797-kgk81ghccy.jpg</v>
+        <v>assets/1787326277374-8ti107m5ki.jpg</v>
       </c>
       <c r="D69" t="str">
         <v>是</v>
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>北京</v>
+        <v>广东深圳</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4478,13 +4478,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B70" t="str">
         <v>弟弟</v>
       </c>
       <c r="C70" t="str">
-        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
+        <v>assets/1787326236952-2pmwche4t3.jpg</v>
       </c>
       <c r="D70" t="str">
         <v>是</v>
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>上海</v>
+        <v>福建泉州</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -4537,13 +4537,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B71" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C71" t="str">
-        <v>assets/1787325554341-608thexrne.jpg</v>
+        <v>assets/1787326184557-90v6clkwen.jpg</v>
       </c>
       <c r="D71" t="str">
         <v>是</v>
@@ -4552,7 +4552,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>江苏苏州</v>
+        <v>福建福州</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -4596,13 +4596,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B72" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C72" t="str">
-        <v>assets/1787325480828-q90pskoiw3.jpg</v>
+        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
       </c>
       <c r="D72" t="str">
         <v>是</v>
@@ -4611,7 +4611,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>四川成都</v>
+        <v>广西贵港</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -4655,13 +4655,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>浅色银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B73" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C73" t="str">
-        <v>assets/1787325448999-a2pg8176fu.jpg</v>
+        <v>assets/1787325862706-wq18k3ej56.jpg</v>
       </c>
       <c r="D73" t="str">
         <v>是</v>
@@ -4670,7 +4670,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>中国台湾</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4714,13 +4714,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B74" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C74" t="str">
-        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
+        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
       </c>
       <c r="D74" t="str">
         <v>是</v>
@@ -4729,7 +4729,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>浙江杭州</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4773,13 +4773,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B75" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C75" t="str">
-        <v>assets/1787325237876-t19isaq5gu.jpg</v>
+        <v>assets/1787325706797-kgk81ghccy.jpg</v>
       </c>
       <c r="D75" t="str">
         <v>是</v>
@@ -4788,7 +4788,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>辽宁沈阳</v>
+        <v>北京</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -4832,13 +4832,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>金棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B76" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C76" t="str">
-        <v>assets/1787325199931-e7wms9qtya.jpg</v>
+        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
       </c>
       <c r="D76" t="str">
         <v>是</v>
@@ -4847,7 +4847,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>四川成都</v>
+        <v>上海</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4891,13 +4891,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B77" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C77" t="str">
-        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
+        <v>assets/1787325554341-608thexrne.jpg</v>
       </c>
       <c r="D77" t="str">
         <v>是</v>
@@ -4906,7 +4906,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>中国香港</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4950,13 +4950,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>烟灰色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B78" t="str">
         <v>弟弟</v>
       </c>
       <c r="C78" t="str">
-        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
+        <v>assets/1787325480828-q90pskoiw3.jpg</v>
       </c>
       <c r="D78" t="str">
         <v>是</v>
@@ -4965,7 +4965,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>中国澳门</v>
+        <v>四川成都</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -5009,13 +5009,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>蓝虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B79" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C79" t="str">
-        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
+        <v>assets/1787325448999-a2pg8176fu.jpg</v>
       </c>
       <c r="D79" t="str">
         <v>是</v>
@@ -5024,7 +5024,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>山东青岛</v>
+        <v>中国台湾</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -5068,13 +5068,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B80" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C80" t="str">
-        <v>assets/1787324954998-w5m5jox439.jpg</v>
+        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
       </c>
       <c r="D80" t="str">
         <v>是</v>
@@ -5083,7 +5083,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>海南海口</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -5127,13 +5127,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B81" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C81" t="str">
-        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
+        <v>assets/1787325237876-t19isaq5gu.jpg</v>
       </c>
       <c r="D81" t="str">
         <v>是</v>
@@ -5142,7 +5142,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>内蒙古</v>
+        <v>辽宁沈阳</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -5186,13 +5186,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>烟灰色</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B82" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C82" t="str">
-        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
+        <v>assets/1787325199931-e7wms9qtya.jpg</v>
       </c>
       <c r="D82" t="str">
         <v>是</v>
@@ -5201,7 +5201,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>中国香港</v>
+        <v>四川成都</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -5245,13 +5245,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B83" t="str">
         <v>弟弟</v>
       </c>
       <c r="C83" t="str">
-        <v>assets/1787324806613-31yyz14tsf.jpg</v>
+        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
       </c>
       <c r="D83" t="str">
         <v>是</v>
@@ -5260,7 +5260,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>四川成都</v>
+        <v>中国香港</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -5304,13 +5304,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B84" t="str">
         <v>弟弟</v>
       </c>
       <c r="C84" t="str">
-        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
+        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
       </c>
       <c r="D84" t="str">
         <v>是</v>
@@ -5319,7 +5319,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>湖北武汉</v>
+        <v>中国澳门</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -5363,13 +5363,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B85" t="str">
         <v>弟弟</v>
       </c>
       <c r="C85" t="str">
-        <v>assets/1787324522658-smn44crast.jpg</v>
+        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
       </c>
       <c r="D85" t="str">
         <v>是</v>
@@ -5378,7 +5378,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>湖北武汉</v>
+        <v>山东青岛</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -5422,13 +5422,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B86" t="str">
         <v>弟弟</v>
       </c>
       <c r="C86" t="str">
-        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
+        <v>assets/1787324954998-w5m5jox439.jpg</v>
       </c>
       <c r="D86" t="str">
         <v>是</v>
@@ -5437,7 +5437,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>新疆</v>
+        <v>海南海口</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -5481,13 +5481,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>浅凯米尔</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B87" t="str">
         <v>弟弟</v>
       </c>
       <c r="C87" t="str">
-        <v>assets/1787324331029-d74lcuycf6.jpg</v>
+        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
       </c>
       <c r="D87" t="str">
         <v>是</v>
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>四川成都</v>
+        <v>内蒙古</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -5540,13 +5540,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B88" t="str">
         <v>弟弟</v>
       </c>
       <c r="C88" t="str">
-        <v>assets/1787324297469-ans1lse2l5.jpg</v>
+        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
       </c>
       <c r="D88" t="str">
         <v>是</v>
@@ -5555,7 +5555,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>四川乐山</v>
+        <v>中国香港</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -5599,13 +5599,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B89" t="str">
         <v>弟弟</v>
       </c>
       <c r="C89" t="str">
-        <v>assets/1787324256827-7w383z4bg1.jpg</v>
+        <v>assets/1787324806613-31yyz14tsf.jpg</v>
       </c>
       <c r="D89" t="str">
         <v>是</v>
@@ -5614,7 +5614,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>中国台湾</v>
+        <v>四川成都</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -5658,13 +5658,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B90" t="str">
         <v>弟弟</v>
       </c>
       <c r="C90" t="str">
-        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
+        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
       </c>
       <c r="D90" t="str">
         <v>是</v>
@@ -5673,7 +5673,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>四川成都</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -5717,13 +5717,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>凯米尔色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B91" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C91" t="str">
-        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
+        <v>assets/1787324522658-smn44crast.jpg</v>
       </c>
       <c r="D91" t="str">
         <v>是</v>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>江苏南京</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -5782,7 +5782,7 @@
         <v>弟弟</v>
       </c>
       <c r="C92" t="str">
-        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
+        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
       </c>
       <c r="D92" t="str">
         <v>是</v>
@@ -5791,7 +5791,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>江苏南京</v>
+        <v>新疆</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -5835,13 +5835,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>银虎斑</v>
+        <v>浅凯米尔</v>
       </c>
       <c r="B93" t="str">
         <v>弟弟</v>
       </c>
       <c r="C93" t="str">
-        <v>assets/1787323318612-soge38hpsf.jpg</v>
+        <v>assets/1787324331029-d74lcuycf6.jpg</v>
       </c>
       <c r="D93" t="str">
         <v>是</v>
@@ -5850,7 +5850,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>上海</v>
+        <v>四川成都</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -5894,13 +5894,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B94" t="str">
         <v>弟弟</v>
       </c>
       <c r="C94" t="str">
-        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
+        <v>assets/1787324297469-ans1lse2l5.jpg</v>
       </c>
       <c r="D94" t="str">
         <v>是</v>
@@ -5909,7 +5909,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>四川成都</v>
+        <v>四川乐山</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -5953,13 +5953,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B95" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C95" t="str">
-        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
+        <v>assets/1787324256827-7w383z4bg1.jpg</v>
       </c>
       <c r="D95" t="str">
         <v>是</v>
@@ -5968,7 +5968,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>浙江宁波</v>
+        <v>中国台湾</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -6012,13 +6012,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>银虎斑补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B96" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C96" t="str">
-        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
+        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
       </c>
       <c r="D96" t="str">
         <v>是</v>
@@ -6027,7 +6027,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>马来西亚</v>
+        <v>四川成都</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -6071,13 +6071,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B97" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C97" t="str">
-        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
+        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
       </c>
       <c r="D97" t="str">
         <v>是</v>
@@ -6086,7 +6086,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>陕西西安</v>
+        <v>江苏南京</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -6130,13 +6130,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B98" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C98" t="str">
-        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
+        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
       </c>
       <c r="D98" t="str">
         <v>是</v>
@@ -6145,7 +6145,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>广西南宁</v>
+        <v>江苏南京</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -6189,13 +6189,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B99" t="str">
         <v>弟弟</v>
       </c>
       <c r="C99" t="str">
-        <v>assets/1787322760950-gn3qgego4s.jpg</v>
+        <v>assets/1787323318612-soge38hpsf.jpg</v>
       </c>
       <c r="D99" t="str">
         <v>是</v>
@@ -6204,7 +6204,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>广西南宁</v>
+        <v>上海</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -6248,13 +6248,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B100" t="str">
         <v>弟弟</v>
       </c>
       <c r="C100" t="str">
-        <v>assets/1787322605982-04n50xegt2.jpg</v>
+        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
       </c>
       <c r="D100" t="str">
         <v>是</v>
@@ -6263,7 +6263,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>上海</v>
+        <v>四川成都</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -6307,13 +6307,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B101" t="str">
         <v>妹妹</v>
       </c>
       <c r="C101" t="str">
-        <v>assets/1787322490045-kog3ru43dy.jpg</v>
+        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
       </c>
       <c r="D101" t="str">
         <v>是</v>
@@ -6322,7 +6322,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>上海</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -6366,13 +6366,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B102" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C102" t="str">
-        <v>assets/1787322419996-0m33yx89nm.jpg</v>
+        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
       </c>
       <c r="D102" t="str">
         <v>是</v>
@@ -6381,7 +6381,7 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>广东广州</v>
+        <v>马来西亚</v>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -6425,13 +6425,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B103" t="str">
         <v>弟弟</v>
       </c>
       <c r="C103" t="str">
-        <v>assets/1787322377730-vj5csj2mll.jpg</v>
+        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
       </c>
       <c r="D103" t="str">
         <v>是</v>
@@ -6440,7 +6440,7 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>柬埔寨</v>
+        <v>陕西西安</v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -6484,13 +6484,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>蓝虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B104" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C104" t="str">
-        <v>assets/1787322269611-53yaj5ideu.jpg</v>
+        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
       </c>
       <c r="D104" t="str">
         <v>是</v>
@@ -6499,7 +6499,7 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>山东枣庄</v>
+        <v>广西南宁</v>
       </c>
       <c r="G104" t="str">
         <v/>
@@ -6543,13 +6543,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B105" t="str">
         <v>弟弟</v>
       </c>
       <c r="C105" t="str">
-        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
+        <v>assets/1787322760950-gn3qgego4s.jpg</v>
       </c>
       <c r="D105" t="str">
         <v>是</v>
@@ -6558,7 +6558,7 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>陕西西安</v>
+        <v>广西南宁</v>
       </c>
       <c r="G105" t="str">
         <v/>
@@ -6602,13 +6602,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B106" t="str">
         <v>弟弟</v>
       </c>
       <c r="C106" t="str">
-        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
+        <v>assets/1787322605982-04n50xegt2.jpg</v>
       </c>
       <c r="D106" t="str">
         <v>是</v>
@@ -6617,7 +6617,7 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>山东东营</v>
+        <v>上海</v>
       </c>
       <c r="G106" t="str">
         <v/>
@@ -6661,13 +6661,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>凯米尔色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B107" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C107" t="str">
-        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
+        <v>assets/1787322490045-kog3ru43dy.jpg</v>
       </c>
       <c r="D107" t="str">
         <v>是</v>
@@ -6676,7 +6676,7 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>中国台湾</v>
+        <v>上海</v>
       </c>
       <c r="G107" t="str">
         <v/>
@@ -6720,13 +6720,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>烟灰色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B108" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C108" t="str">
-        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
+        <v>assets/1787322419996-0m33yx89nm.jpg</v>
       </c>
       <c r="D108" t="str">
         <v>是</v>
@@ -6735,7 +6735,7 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>中国台湾</v>
+        <v>广东广州</v>
       </c>
       <c r="G108" t="str">
         <v/>
@@ -6779,13 +6779,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B109" t="str">
         <v>弟弟</v>
       </c>
       <c r="C109" t="str">
-        <v>assets/1787321834306-efgnyhujon.jpg</v>
+        <v>assets/1787322377730-vj5csj2mll.jpg</v>
       </c>
       <c r="D109" t="str">
         <v>是</v>
@@ -6794,7 +6794,7 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>北京</v>
+        <v>柬埔寨</v>
       </c>
       <c r="G109" t="str">
         <v/>
@@ -6838,13 +6838,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B110" t="str">
         <v>弟弟</v>
       </c>
       <c r="C110" t="str">
-        <v>assets/1787321439916-uttgpbkogb.jpg</v>
+        <v>assets/1787322269611-53yaj5ideu.jpg</v>
       </c>
       <c r="D110" t="str">
         <v>是</v>
@@ -6853,7 +6853,7 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>安徽合肥</v>
+        <v>山东枣庄</v>
       </c>
       <c r="G110" t="str">
         <v/>
@@ -6903,7 +6903,7 @@
         <v>弟弟</v>
       </c>
       <c r="C111" t="str">
-        <v>assets/1787321419210-51hhgurygq.jpg</v>
+        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
       </c>
       <c r="D111" t="str">
         <v>是</v>
@@ -6912,7 +6912,7 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>上海</v>
+        <v>陕西西安</v>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -6956,13 +6956,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B112" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C112" t="str">
-        <v>assets/1787321363369-bzjn51j5il.jpg</v>
+        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
       </c>
       <c r="D112" t="str">
         <v>是</v>
@@ -6971,7 +6971,7 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>中国台湾</v>
+        <v>山东东营</v>
       </c>
       <c r="G112" t="str">
         <v/>
@@ -7015,13 +7015,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B113" t="str">
         <v>弟弟</v>
       </c>
       <c r="C113" t="str">
-        <v>assets/1787321332559-87p6spuch3.jpg</v>
+        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
       </c>
       <c r="D113" t="str">
         <v>是</v>
@@ -7074,13 +7074,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B114" t="str">
         <v>妹妹</v>
       </c>
       <c r="C114" t="str">
-        <v>assets/1787321232531-59lnzv8y98.jpg</v>
+        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
       </c>
       <c r="D114" t="str">
         <v>是</v>
@@ -7089,7 +7089,7 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G114" t="str">
         <v/>
@@ -7136,10 +7136,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B115" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C115" t="str">
-        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
+        <v>assets/1787321834306-efgnyhujon.jpg</v>
       </c>
       <c r="D115" t="str">
         <v>是</v>
@@ -7148,7 +7148,7 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>浙江宁波</v>
+        <v>北京</v>
       </c>
       <c r="G115" t="str">
         <v/>
@@ -7195,10 +7195,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B116" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C116" t="str">
-        <v>assets/1787319800704-v3qeu062ak.jpg</v>
+        <v>assets/1787321439916-uttgpbkogb.jpg</v>
       </c>
       <c r="D116" t="str">
         <v>是</v>
@@ -7207,7 +7207,7 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>河北唐山</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G116" t="str">
         <v/>
@@ -7254,10 +7254,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B117" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C117" t="str">
-        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
+        <v>assets/1787321419210-51hhgurygq.jpg</v>
       </c>
       <c r="D117" t="str">
         <v>是</v>
@@ -7266,7 +7266,7 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>河北石家庄</v>
+        <v>上海</v>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -7310,13 +7310,13 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>棕虎补丁</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B118" t="str">
         <v>妹妹</v>
       </c>
       <c r="C118" t="str">
-        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
+        <v>assets/1787321363369-bzjn51j5il.jpg</v>
       </c>
       <c r="D118" t="str">
         <v>是</v>
@@ -7325,7 +7325,7 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>韩国</v>
+        <v>中国台湾</v>
       </c>
       <c r="G118" t="str">
         <v/>
@@ -7369,13 +7369,13 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>蓝银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B119" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C119" t="str">
-        <v>assets/1787319501376-xscwljnu1j.jpg</v>
+        <v>assets/1787321332559-87p6spuch3.jpg</v>
       </c>
       <c r="D119" t="str">
         <v>是</v>
@@ -7384,7 +7384,7 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>美国</v>
+        <v>中国台湾</v>
       </c>
       <c r="G119" t="str">
         <v/>
@@ -7434,7 +7434,7 @@
         <v>妹妹</v>
       </c>
       <c r="C120" t="str">
-        <v>assets/1787319443529-4a0zqikufx.jpg</v>
+        <v>assets/1787321232531-59lnzv8y98.jpg</v>
       </c>
       <c r="D120" t="str">
         <v>是</v>
@@ -7443,7 +7443,7 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>中国台湾</v>
+        <v>北京</v>
       </c>
       <c r="G120" t="str">
         <v/>
@@ -7487,13 +7487,13 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B121" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C121" t="str">
-        <v>assets/1787319356194-lr2d5680i9.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D121" t="str">
         <v>是</v>
@@ -7502,7 +7502,7 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>中国台湾</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G121" t="str">
         <v/>
@@ -7546,13 +7546,13 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B122" t="str">
         <v>妹妹</v>
       </c>
       <c r="C122" t="str">
-        <v>assets/1787319208828-aizqo4blcv.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D122" t="str">
         <v>是</v>
@@ -7561,7 +7561,7 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>山东淄博</v>
+        <v>河北唐山</v>
       </c>
       <c r="G122" t="str">
         <v/>
@@ -7611,7 +7611,7 @@
         <v>妹妹</v>
       </c>
       <c r="C123" t="str">
-        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D123" t="str">
         <v>是</v>
@@ -7620,7 +7620,7 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>韩国</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G123" t="str">
         <v/>
@@ -7670,7 +7670,7 @@
         <v>妹妹</v>
       </c>
       <c r="C124" t="str">
-        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D124" t="str">
         <v>是</v>
@@ -7679,7 +7679,7 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>四川成都</v>
+        <v>韩国</v>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -7723,13 +7723,13 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>银虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B125" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C125" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D125" t="str">
         <v>是</v>
@@ -7738,7 +7738,7 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>广东广州</v>
+        <v>美国</v>
       </c>
       <c r="G125" t="str">
         <v/>
@@ -7782,13 +7782,13 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B126" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C126" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D126" t="str">
         <v>是</v>
@@ -7797,7 +7797,7 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>中国台湾</v>
       </c>
       <c r="G126" t="str">
         <v/>
@@ -7847,7 +7847,7 @@
         <v>弟弟</v>
       </c>
       <c r="C127" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D127" t="str">
         <v>是</v>
@@ -7856,7 +7856,7 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>天津</v>
+        <v>中国台湾</v>
       </c>
       <c r="G127" t="str">
         <v/>
@@ -7900,13 +7900,13 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B128" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C128" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D128" t="str">
         <v>是</v>
@@ -7915,7 +7915,7 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>山西朔州</v>
+        <v>山东淄博</v>
       </c>
       <c r="G128" t="str">
         <v/>
@@ -7945,7 +7945,7 @@
         <v/>
       </c>
       <c r="P128" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q128" t="str">
         <v/>
@@ -7965,7 +7965,7 @@
         <v>妹妹</v>
       </c>
       <c r="C129" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D129" t="str">
         <v>是</v>
@@ -7974,7 +7974,7 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>贵州</v>
+        <v>韩国</v>
       </c>
       <c r="G129" t="str">
         <v/>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>棕虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B130" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C130" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D130" t="str">
         <v>是</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F130" t="str">
-        <v>北京</v>
+        <v>四川成都</v>
       </c>
       <c r="G130" t="str">
         <v/>
@@ -8072,27 +8072,27 @@
         <v/>
       </c>
       <c r="S130" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B131" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C131" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D131" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-04-10</v>
+        <v/>
       </c>
       <c r="F131" t="str">
-        <v/>
+        <v>广东广州</v>
       </c>
       <c r="G131" t="str">
         <v/>
@@ -8131,27 +8131,27 @@
         <v/>
       </c>
       <c r="S131" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>阴影色NS12</v>
+        <v>银虎斑</v>
       </c>
       <c r="B132" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C132" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D132" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-05-28</v>
+        <v/>
       </c>
       <c r="F132" t="str">
-        <v/>
+        <v>黑龙江鹤岗</v>
       </c>
       <c r="G132" t="str">
         <v/>
@@ -8190,27 +8190,27 @@
         <v/>
       </c>
       <c r="S132" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>阴影色NS11</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B133" t="str">
         <v>弟弟</v>
       </c>
       <c r="C133" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D133" t="str">
         <v>是</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-06-15</v>
+        <v/>
       </c>
       <c r="F133" t="str">
-        <v>重庆</v>
+        <v>天津</v>
       </c>
       <c r="G133" t="str">
         <v/>
@@ -8249,27 +8249,27 @@
         <v/>
       </c>
       <c r="S133" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>浅烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B134" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C134" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D134" t="str">
         <v>是</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-03-21</v>
+        <v/>
       </c>
       <c r="F134" t="str">
-        <v>中国澳门</v>
+        <v>山西朔州</v>
       </c>
       <c r="G134" t="str">
         <v/>
@@ -8299,7 +8299,7 @@
         <v/>
       </c>
       <c r="P134" t="str">
-        <v/>
+        <v>已接猫</v>
       </c>
       <c r="Q134" t="str">
         <v/>
@@ -8308,27 +8308,27 @@
         <v/>
       </c>
       <c r="S134" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B135" t="str">
         <v>妹妹</v>
       </c>
       <c r="C135" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D135" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F135" t="str">
-        <v/>
+        <v>贵州</v>
       </c>
       <c r="G135" t="str">
         <v/>
@@ -8367,7 +8367,7 @@
         <v/>
       </c>
       <c r="S135" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="136">
@@ -8375,10 +8375,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B136" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C136" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D136" t="str">
         <v>是</v>
@@ -8387,7 +8387,7 @@
         <v>2026-06-06</v>
       </c>
       <c r="F136" t="str">
-        <v>浙江温州</v>
+        <v>北京</v>
       </c>
       <c r="G136" t="str">
         <v/>
@@ -8431,19 +8431,19 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B137" t="str">
         <v>妹妹</v>
       </c>
       <c r="C137" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D137" t="str">
         <v>否</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-06-15</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F137" t="str">
         <v/>
@@ -8490,22 +8490,22 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B138" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C138" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D138" t="str">
         <v>是</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F138" t="str">
-        <v>北京</v>
+        <v>西安</v>
       </c>
       <c r="G138" t="str">
         <v/>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B139" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C139" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D139" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F139" t="str">
-        <v/>
+        <v>重庆</v>
       </c>
       <c r="G139" t="str">
         <v/>
@@ -8608,22 +8608,22 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>烟灰色</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B140" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C140" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D140" t="str">
         <v>是</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F140" t="str">
-        <v>河北石家庄</v>
+        <v>中国澳门</v>
       </c>
       <c r="G140" t="str">
         <v/>
@@ -8667,13 +8667,13 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B141" t="str">
         <v>妹妹</v>
       </c>
       <c r="C141" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D141" t="str">
         <v>是</v>
@@ -8682,7 +8682,7 @@
         <v>2026-06-06</v>
       </c>
       <c r="F141" t="str">
-        <v>浙江宁波</v>
+        <v>深圳</v>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -8726,13 +8726,13 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B142" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C142" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D142" t="str">
         <v>是</v>
@@ -8741,7 +8741,7 @@
         <v>2026-06-06</v>
       </c>
       <c r="F142" t="str">
-        <v>上海</v>
+        <v>浙江温州</v>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -8785,22 +8785,22 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B143" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C143" t="str">
-        <v>assets/1790733778469-jt9fswxe9w.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D143" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-04-17</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F143" t="str">
-        <v/>
+        <v>安徽合肥</v>
       </c>
       <c r="G143" t="str">
         <v/>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B144" t="str">
         <v>弟弟</v>
       </c>
       <c r="C144" t="str">
-        <v>assets/1790734215453-0zvw0v9uja.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D144" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F144" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G144" t="str">
         <v/>
@@ -8903,19 +8903,19 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>阴影色NS11</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B145" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C145" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D145" t="str">
         <v>否</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F145" t="str">
         <v/>
@@ -8962,22 +8962,22 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>浅色银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B146" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C146" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D146" t="str">
         <v>是</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F146" t="str">
-        <v>香港</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -9021,22 +9021,22 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>浅烟灰色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B147" t="str">
         <v>妹妹</v>
       </c>
       <c r="C147" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D147" t="str">
         <v>是</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F147" t="str">
-        <v>四川成都</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -9080,22 +9080,22 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>凯米尔色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B148" t="str">
         <v>弟弟</v>
       </c>
       <c r="C148" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D148" t="str">
         <v>是</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F148" t="str">
-        <v>上海浦东</v>
+        <v>上海</v>
       </c>
       <c r="G148" t="str">
         <v/>
@@ -9139,19 +9139,19 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>银虎斑补丁</v>
+        <v>纯黑色</v>
       </c>
       <c r="B149" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C149" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1790733778469-jt9fswxe9w.jpg</v>
       </c>
       <c r="D149" t="str">
         <v>否</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-17</v>
       </c>
       <c r="F149" t="str">
         <v/>
@@ -9198,19 +9198,19 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B150" t="str">
         <v>弟弟</v>
       </c>
       <c r="C150" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1790734215453-0zvw0v9uja.jpg</v>
       </c>
       <c r="D150" t="str">
         <v>是</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F150" t="str">
         <v>北京</v>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B151" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C151" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D151" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-02-14</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F151" t="str">
-        <v/>
+        <v>安徽芜湖</v>
       </c>
       <c r="G151" t="str">
         <v/>
@@ -9316,22 +9316,22 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B152" t="str">
         <v>妹妹</v>
       </c>
       <c r="C152" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D152" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-05-24</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F152" t="str">
-        <v/>
+        <v>香港</v>
       </c>
       <c r="G152" t="str">
         <v/>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>银虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B153" t="str">
         <v>妹妹</v>
       </c>
       <c r="C153" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D153" t="str">
         <v>是</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F153" t="str">
-        <v>湖北恩施</v>
+        <v>四川成都</v>
       </c>
       <c r="G153" t="str">
         <v/>
@@ -9434,22 +9434,22 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B154" t="str">
         <v>弟弟</v>
       </c>
       <c r="C154" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D154" t="str">
         <v>是</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F154" t="str">
-        <v>湖北恩施</v>
+        <v>上海浦东</v>
       </c>
       <c r="G154" t="str">
         <v/>
@@ -9493,22 +9493,22 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B155" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C155" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D155" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E155" t="str">
-        <v>2025-11-05</v>
+        <v>2026-04-09</v>
       </c>
       <c r="F155" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G155" t="str">
         <v/>
@@ -9552,22 +9552,22 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B156" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C156" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D156" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E156" t="str">
         <v>2026-05-18</v>
       </c>
       <c r="F156" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G156" t="str">
         <v/>
@@ -9611,22 +9611,22 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>棕虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B157" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C157" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D157" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-05-28</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F157" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G157" t="str">
         <v/>
@@ -9670,19 +9670,19 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B158" t="str">
         <v>妹妹</v>
       </c>
       <c r="C158" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D158" t="str">
         <v>否</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F158" t="str">
         <v/>
@@ -9729,22 +9729,22 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B159" t="str">
         <v>妹妹</v>
       </c>
       <c r="C159" t="str">
-        <v>assets/1790733648123-636cut584p.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D159" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-04-10</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F159" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G159" t="str">
         <v/>
@@ -9791,19 +9791,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B160" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C160" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D160" t="str">
         <v>是</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F160" t="str">
-        <v>韩国</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G160" t="str">
         <v/>
@@ -9847,22 +9847,22 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B161" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C161" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D161" t="str">
         <v>是</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-06-05</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F161" t="str">
-        <v>河北邢台</v>
+        <v>韩国</v>
       </c>
       <c r="G161" t="str">
         <v/>
@@ -9906,22 +9906,22 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B162" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C162" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D162" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F162" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G162" t="str">
         <v/>
@@ -9965,22 +9965,22 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>棕虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B163" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C163" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D163" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-03-05</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F163" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G163" t="str">
         <v/>
@@ -10024,22 +10024,22 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B164" t="str">
         <v>妹妹</v>
       </c>
       <c r="C164" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D164" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-04-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F164" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="G164" t="str">
         <v/>
@@ -10083,19 +10083,19 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B165" t="str">
         <v>妹妹</v>
       </c>
       <c r="C165" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1790733648123-636cut584p.jpg</v>
       </c>
       <c r="D165" t="str">
         <v>否</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F165" t="str">
         <v/>
@@ -10148,16 +10148,16 @@
         <v>妹妹</v>
       </c>
       <c r="C166" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D166" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-04-30</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F166" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G166" t="str">
         <v/>
@@ -10201,52 +10201,52 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>蓝虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B167" t="str">
         <v>妹妹</v>
       </c>
       <c r="C167" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D167" t="str">
         <v>是</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-02-20</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F167" t="str">
-        <v>荷兰</v>
+        <v>河北邢台</v>
       </c>
       <c r="G167" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H167" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I167" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J167" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K167" t="str">
         <v/>
       </c>
       <c r="L167" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M167" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N167" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O167" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P167" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q167" t="str">
         <v/>
@@ -10255,27 +10255,27 @@
         <v/>
       </c>
       <c r="S167" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B168" t="str">
         <v>弟弟</v>
       </c>
       <c r="C168" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D168" t="str">
         <v>是</v>
       </c>
       <c r="E168" t="str">
-        <v/>
+        <v>2026-06-05</v>
       </c>
       <c r="F168" t="str">
-        <v>广东广州</v>
+        <v>四川自贡</v>
       </c>
       <c r="G168" t="str">
         <v/>
@@ -10319,22 +10319,22 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B169" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C169" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D169" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E169" t="str">
-        <v/>
+        <v>2026-03-05</v>
       </c>
       <c r="F169" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G169" t="str">
         <v/>
@@ -10378,22 +10378,22 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B170" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C170" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D170" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E170" t="str">
-        <v/>
+        <v>2026-04-05</v>
       </c>
       <c r="F170" t="str">
-        <v>山西朔州</v>
+        <v/>
       </c>
       <c r="G170" t="str">
         <v/>
@@ -10443,16 +10443,16 @@
         <v>妹妹</v>
       </c>
       <c r="C171" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D171" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E171" t="str">
-        <v/>
+        <v>2026-04-17</v>
       </c>
       <c r="F171" t="str">
-        <v>浙江宁波</v>
+        <v/>
       </c>
       <c r="G171" t="str">
         <v/>
@@ -10499,19 +10499,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B172" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C172" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D172" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E172" t="str">
-        <v/>
+        <v>2026-04-30</v>
       </c>
       <c r="F172" t="str">
-        <v>陕西西安</v>
+        <v/>
       </c>
       <c r="G172" t="str">
         <v/>
@@ -10555,52 +10555,52 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B173" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C173" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D173" t="str">
         <v>是</v>
       </c>
       <c r="E173" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F173" t="str">
-        <v>黑龙江漠河</v>
+        <v>荷兰</v>
       </c>
       <c r="G173" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H173" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I173" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J173" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K173" t="str">
         <v/>
       </c>
       <c r="L173" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M173" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N173" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O173" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P173" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q173" t="str">
         <v/>
@@ -10609,18 +10609,18 @@
         <v/>
       </c>
       <c r="S173" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B174" t="str">
         <v>弟弟</v>
       </c>
       <c r="C174" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D174" t="str">
         <v>是</v>
@@ -10629,7 +10629,7 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>日本</v>
+        <v>广东广州</v>
       </c>
       <c r="G174" t="str">
         <v/>
@@ -10673,13 +10673,13 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B175" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C175" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D175" t="str">
         <v>是</v>
@@ -10688,7 +10688,7 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>浙江杭州</v>
+        <v>广东广州</v>
       </c>
       <c r="G175" t="str">
         <v/>
@@ -10735,10 +10735,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B176" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C176" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D176" t="str">
         <v>是</v>
@@ -10747,7 +10747,7 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>贵州安顺</v>
+        <v>山西朔州</v>
       </c>
       <c r="G176" t="str">
         <v/>
@@ -10797,7 +10797,7 @@
         <v>妹妹</v>
       </c>
       <c r="C177" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D177" t="str">
         <v>是</v>
@@ -10806,7 +10806,7 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>山东青岛</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G177" t="str">
         <v/>
@@ -10856,7 +10856,7 @@
         <v>弟弟</v>
       </c>
       <c r="C178" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D178" t="str">
         <v>是</v>
@@ -10865,7 +10865,7 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>黑龙江漠河</v>
+        <v>陕西西安</v>
       </c>
       <c r="G178" t="str">
         <v/>
@@ -10909,13 +10909,13 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B179" t="str">
         <v>弟弟</v>
       </c>
       <c r="C179" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D179" t="str">
         <v>是</v>
@@ -10924,7 +10924,7 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>河南鹤壁</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G179" t="str">
         <v/>
@@ -10968,13 +10968,13 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B180" t="str">
         <v>弟弟</v>
       </c>
       <c r="C180" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D180" t="str">
         <v>是</v>
@@ -10983,7 +10983,7 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>陕西西安</v>
+        <v>日本</v>
       </c>
       <c r="G180" t="str">
         <v/>
@@ -11027,13 +11027,13 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B181" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C181" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D181" t="str">
         <v>是</v>
@@ -11042,7 +11042,7 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G181" t="str">
         <v/>
@@ -11086,22 +11086,22 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B182" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C182" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D182" t="str">
         <v>是</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F182" t="str">
-        <v>四川成都</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G182" t="str">
         <v/>
@@ -11148,10 +11148,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B183" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C183" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D183" t="str">
         <v>是</v>
@@ -11160,7 +11160,7 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>新加坡</v>
+        <v>山东青岛</v>
       </c>
       <c r="G183" t="str">
         <v/>
@@ -11204,13 +11204,13 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B184" t="str">
         <v>弟弟</v>
       </c>
       <c r="C184" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D184" t="str">
         <v>是</v>
@@ -11219,7 +11219,7 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>上海浦东</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G184" t="str">
         <v/>
@@ -11263,22 +11263,22 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>棕虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B185" t="str">
         <v>弟弟</v>
       </c>
       <c r="C185" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D185" t="str">
         <v>是</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F185" t="str">
-        <v>浙江温州</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G185" t="str">
         <v/>
@@ -11322,66 +11322,420 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B186" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C186" t="str">
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+      </c>
+      <c r="D186" t="str">
+        <v>是</v>
+      </c>
+      <c r="E186" t="str">
+        <v/>
+      </c>
+      <c r="F186" t="str">
+        <v>陕西西安</v>
+      </c>
+      <c r="G186" t="str">
+        <v/>
+      </c>
+      <c r="H186" t="str">
+        <v/>
+      </c>
+      <c r="I186" t="str">
+        <v/>
+      </c>
+      <c r="J186" t="str">
+        <v/>
+      </c>
+      <c r="K186" t="str">
+        <v/>
+      </c>
+      <c r="L186" t="str">
+        <v/>
+      </c>
+      <c r="M186" t="str">
+        <v/>
+      </c>
+      <c r="N186" t="str">
+        <v/>
+      </c>
+      <c r="O186" t="str">
+        <v/>
+      </c>
+      <c r="P186" t="str">
+        <v/>
+      </c>
+      <c r="Q186" t="str">
+        <v/>
+      </c>
+      <c r="R186" t="str">
+        <v/>
+      </c>
+      <c r="S186" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
         <v>棕虎斑</v>
       </c>
-      <c r="B186" t="str">
+      <c r="B187" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C187" t="str">
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+      </c>
+      <c r="D187" t="str">
+        <v>是</v>
+      </c>
+      <c r="E187" t="str">
+        <v/>
+      </c>
+      <c r="F187" t="str">
+        <v>四川成都</v>
+      </c>
+      <c r="G187" t="str">
+        <v/>
+      </c>
+      <c r="H187" t="str">
+        <v/>
+      </c>
+      <c r="I187" t="str">
+        <v/>
+      </c>
+      <c r="J187" t="str">
+        <v/>
+      </c>
+      <c r="K187" t="str">
+        <v/>
+      </c>
+      <c r="L187" t="str">
+        <v/>
+      </c>
+      <c r="M187" t="str">
+        <v/>
+      </c>
+      <c r="N187" t="str">
+        <v/>
+      </c>
+      <c r="O187" t="str">
+        <v/>
+      </c>
+      <c r="P187" t="str">
+        <v/>
+      </c>
+      <c r="Q187" t="str">
+        <v/>
+      </c>
+      <c r="R187" t="str">
+        <v/>
+      </c>
+      <c r="S187" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>烟灰色</v>
+      </c>
+      <c r="B188" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C188" t="str">
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+      </c>
+      <c r="D188" t="str">
+        <v>是</v>
+      </c>
+      <c r="E188" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="F188" t="str">
+        <v>四川成都</v>
+      </c>
+      <c r="G188" t="str">
+        <v/>
+      </c>
+      <c r="H188" t="str">
+        <v/>
+      </c>
+      <c r="I188" t="str">
+        <v/>
+      </c>
+      <c r="J188" t="str">
+        <v/>
+      </c>
+      <c r="K188" t="str">
+        <v/>
+      </c>
+      <c r="L188" t="str">
+        <v/>
+      </c>
+      <c r="M188" t="str">
+        <v/>
+      </c>
+      <c r="N188" t="str">
+        <v/>
+      </c>
+      <c r="O188" t="str">
+        <v/>
+      </c>
+      <c r="P188" t="str">
+        <v/>
+      </c>
+      <c r="Q188" t="str">
+        <v/>
+      </c>
+      <c r="R188" t="str">
+        <v/>
+      </c>
+      <c r="S188" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>银虎斑</v>
+      </c>
+      <c r="B189" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C189" t="str">
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+      </c>
+      <c r="D189" t="str">
+        <v>是</v>
+      </c>
+      <c r="E189" t="str">
+        <v/>
+      </c>
+      <c r="F189" t="str">
+        <v>新加坡</v>
+      </c>
+      <c r="G189" t="str">
+        <v/>
+      </c>
+      <c r="H189" t="str">
+        <v/>
+      </c>
+      <c r="I189" t="str">
+        <v/>
+      </c>
+      <c r="J189" t="str">
+        <v/>
+      </c>
+      <c r="K189" t="str">
+        <v/>
+      </c>
+      <c r="L189" t="str">
+        <v/>
+      </c>
+      <c r="M189" t="str">
+        <v/>
+      </c>
+      <c r="N189" t="str">
+        <v/>
+      </c>
+      <c r="O189" t="str">
+        <v/>
+      </c>
+      <c r="P189" t="str">
+        <v/>
+      </c>
+      <c r="Q189" t="str">
+        <v/>
+      </c>
+      <c r="R189" t="str">
+        <v/>
+      </c>
+      <c r="S189" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B190" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C190" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D190" t="str">
+        <v>是</v>
+      </c>
+      <c r="E190" t="str">
+        <v/>
+      </c>
+      <c r="F190" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G190" t="str">
+        <v/>
+      </c>
+      <c r="H190" t="str">
+        <v/>
+      </c>
+      <c r="I190" t="str">
+        <v/>
+      </c>
+      <c r="J190" t="str">
+        <v/>
+      </c>
+      <c r="K190" t="str">
+        <v/>
+      </c>
+      <c r="L190" t="str">
+        <v/>
+      </c>
+      <c r="M190" t="str">
+        <v/>
+      </c>
+      <c r="N190" t="str">
+        <v/>
+      </c>
+      <c r="O190" t="str">
+        <v/>
+      </c>
+      <c r="P190" t="str">
+        <v/>
+      </c>
+      <c r="Q190" t="str">
+        <v/>
+      </c>
+      <c r="R190" t="str">
+        <v/>
+      </c>
+      <c r="S190" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B191" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C191" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D191" t="str">
+        <v>是</v>
+      </c>
+      <c r="E191" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F191" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G191" t="str">
+        <v/>
+      </c>
+      <c r="H191" t="str">
+        <v/>
+      </c>
+      <c r="I191" t="str">
+        <v/>
+      </c>
+      <c r="J191" t="str">
+        <v/>
+      </c>
+      <c r="K191" t="str">
+        <v/>
+      </c>
+      <c r="L191" t="str">
+        <v/>
+      </c>
+      <c r="M191" t="str">
+        <v/>
+      </c>
+      <c r="N191" t="str">
+        <v/>
+      </c>
+      <c r="O191" t="str">
+        <v/>
+      </c>
+      <c r="P191" t="str">
+        <v/>
+      </c>
+      <c r="Q191" t="str">
+        <v/>
+      </c>
+      <c r="R191" t="str">
+        <v/>
+      </c>
+      <c r="S191" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B192" t="str">
         <v>妹妹</v>
       </c>
-      <c r="C186" t="str">
+      <c r="C192" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D186" t="str">
-        <v>否</v>
-      </c>
-      <c r="E186" t="str">
+      <c r="D192" t="str">
+        <v>是</v>
+      </c>
+      <c r="E192" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F186" t="str">
-        <v/>
-      </c>
-      <c r="G186" t="str">
-        <v/>
-      </c>
-      <c r="H186" t="str">
-        <v/>
-      </c>
-      <c r="I186" t="str">
-        <v/>
-      </c>
-      <c r="J186" t="str">
-        <v/>
-      </c>
-      <c r="K186" t="str">
-        <v/>
-      </c>
-      <c r="L186" t="str">
-        <v/>
-      </c>
-      <c r="M186" t="str">
-        <v/>
-      </c>
-      <c r="N186" t="str">
-        <v/>
-      </c>
-      <c r="O186" t="str">
-        <v/>
-      </c>
-      <c r="P186" t="str">
-        <v/>
-      </c>
-      <c r="Q186" t="str">
-        <v/>
-      </c>
-      <c r="R186" t="str">
-        <v/>
-      </c>
-      <c r="S186" t="str">
+      <c r="F192" t="str">
+        <v>深圳</v>
+      </c>
+      <c r="G192" t="str">
+        <v/>
+      </c>
+      <c r="H192" t="str">
+        <v/>
+      </c>
+      <c r="I192" t="str">
+        <v/>
+      </c>
+      <c r="J192" t="str">
+        <v/>
+      </c>
+      <c r="K192" t="str">
+        <v/>
+      </c>
+      <c r="L192" t="str">
+        <v/>
+      </c>
+      <c r="M192" t="str">
+        <v/>
+      </c>
+      <c r="N192" t="str">
+        <v/>
+      </c>
+      <c r="O192" t="str">
+        <v/>
+      </c>
+      <c r="P192" t="str">
+        <v/>
+      </c>
+      <c r="Q192" t="str">
+        <v/>
+      </c>
+      <c r="R192" t="str">
+        <v/>
+      </c>
+      <c r="S192" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S186"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S192"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S192"/>
+  <dimension ref="A1:S193"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -466,19 +466,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B2" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1791885799211-r54amxe2jp.jpg</v>
+        <v>assets/1792313878597-k9d5tg2u3t.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>否</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-26</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -525,22 +525,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>阴影色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B3" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1791885766213-djh49zfdy8.jpg</v>
+        <v>assets/1791885799211-r54amxe2jp.jpg</v>
       </c>
       <c r="D3" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -590,16 +590,16 @@
         <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1791885692087-flz5al0ukw.jpg</v>
+        <v>assets/1791885766213-djh49zfdy8.jpg</v>
       </c>
       <c r="D4" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>上海</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -643,19 +643,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>银虎斑</v>
+        <v>阴影色</v>
       </c>
       <c r="B5" t="str">
         <v>弟弟</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1791885628374-op5p4tcc5c.jpg</v>
+        <v>assets/1791885692087-flz5al0ukw.jpg</v>
       </c>
       <c r="D5" t="str">
         <v>否</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-06-10</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -702,13 +702,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B6" t="str">
         <v>弟弟</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1791885580674-a6onl6jgc.jpg</v>
+        <v>assets/1791885628374-op5p4tcc5c.jpg</v>
       </c>
       <c r="D6" t="str">
         <v>否</v>
@@ -764,16 +764,16 @@
         <v>棕虎斑</v>
       </c>
       <c r="B7" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1791885502285-o86pddnxqc.jpg</v>
+        <v>assets/1791885580674-a6onl6jgc.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>否</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -820,19 +820,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B8" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1791288567764-tti55g9g1q.jpg</v>
+        <v>assets/1791885502285-o86pddnxqc.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>否</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -879,19 +879,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B9" t="str">
         <v>弟弟</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1791288502036-4v43o0otqq.jpg</v>
+        <v>assets/1791288567764-tti55g9g1q.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>否</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -938,22 +938,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>浅烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B10" t="str">
         <v>弟弟</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1790734752606-rusbv65ug8.jpg</v>
+        <v>assets/1791288502036-4v43o0otqq.jpg</v>
       </c>
       <c r="D10" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-04-28</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>浙江宁波</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -997,19 +997,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B11" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1790734688874-ldibzixi2g.jpg</v>
+        <v>assets/1790734752606-rusbv65ug8.jpg</v>
       </c>
       <c r="D11" t="str">
         <v>否</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-06-06</v>
+        <v>2026-04-28</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1056,22 +1056,22 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B12" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1790734651251-a58tdtmhnx.jpg</v>
+        <v>assets/1790734688874-ldibzixi2g.jpg</v>
       </c>
       <c r="D12" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F12" t="str">
-        <v>成都</v>
+        <v/>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1115,22 +1115,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>浅银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B13" t="str">
         <v>弟弟</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1790734595573-u465hv1hyg.jpg</v>
+        <v>assets/1790734651251-a58tdtmhnx.jpg</v>
       </c>
       <c r="D13" t="str">
         <v>是</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F13" t="str">
-        <v>浙江嘉兴</v>
+        <v>成都</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1177,10 +1177,10 @@
         <v>浅银虎斑</v>
       </c>
       <c r="B14" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1790734548586-cztim8ip4y.jpg</v>
+        <v>assets/1790734595573-u465hv1hyg.jpg</v>
       </c>
       <c r="D14" t="str">
         <v>是</v>
@@ -1189,7 +1189,7 @@
         <v>2026-06-15</v>
       </c>
       <c r="F14" t="str">
-        <v>西安</v>
+        <v>浙江嘉兴</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1233,22 +1233,22 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>蓝虎斑</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B15" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1790734499008-43htmo2xuw.jpg</v>
+        <v>assets/1790734548586-cztim8ip4y.jpg</v>
       </c>
       <c r="D15" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-03-20</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>西安</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1292,22 +1292,22 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>阴影色NS11</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B16" t="str">
         <v>弟弟</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1789655131156-6ywyod2pgz.jpg</v>
+        <v>assets/1790734499008-43htmo2xuw.jpg</v>
       </c>
       <c r="D16" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-06-15</v>
+        <v>2026-03-20</v>
       </c>
       <c r="F16" t="str">
-        <v>广州</v>
+        <v/>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1351,13 +1351,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>浅银虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B17" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1789654858942-ws3mqfv0zf.jpg</v>
+        <v>assets/1789655131156-6ywyod2pgz.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>是</v>
@@ -1366,7 +1366,7 @@
         <v>2026-06-15</v>
       </c>
       <c r="F17" t="str">
-        <v>浙江杭州</v>
+        <v>广州</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1410,22 +1410,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>红虎斑</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B18" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1789654723483-fyl8c7wdqg.jpg</v>
+        <v>assets/1789654858942-ws3mqfv0zf.jpg</v>
       </c>
       <c r="D18" t="str">
         <v>是</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F18" t="str">
-        <v>天津</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1469,22 +1469,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>银虎班补丁</v>
+        <v>红虎斑</v>
       </c>
       <c r="B19" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1789654675792-6d4kyyncmf.jpg</v>
+        <v>assets/1789654723483-fyl8c7wdqg.jpg</v>
       </c>
       <c r="D19" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E19" t="str">
         <v>2026-06-26</v>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>天津</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1528,22 +1528,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>烟灰色</v>
+        <v>银虎班补丁</v>
       </c>
       <c r="B20" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1789654628929-2wok5d7b71.jpg</v>
+        <v>assets/1789654675792-6d4kyyncmf.jpg</v>
       </c>
       <c r="D20" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F20" t="str">
-        <v>新加坡</v>
+        <v/>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>阴影色NS11</v>
+        <v>烟灰色</v>
       </c>
       <c r="B21" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1789654549268-68uab4pdoy.jpg</v>
+        <v>assets/1789654628929-2wok5d7b71.jpg</v>
       </c>
       <c r="D21" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>新加坡</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1646,19 +1646,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>阴影色NS12</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B22" t="str">
         <v>妹妹</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1788534744815-pzs6jqs2pm.jpg</v>
+        <v>assets/1789654549268-68uab4pdoy.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>否</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -1705,22 +1705,22 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B23" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1788534522775-my4ggv0pwo.jpg</v>
+        <v>assets/1788534744815-pzs6jqs2pm.jpg</v>
       </c>
       <c r="D23" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F23" t="str">
-        <v>西藏</v>
+        <v/>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1764,22 +1764,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B24" t="str">
         <v>弟弟</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1788442386268-ilpasqz91m.jpg</v>
+        <v>assets/1788534522775-my4ggv0pwo.jpg</v>
       </c>
       <c r="D24" t="str">
         <v>是</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F24" t="str">
-        <v>成都</v>
+        <v>西藏</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1823,22 +1823,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>浅银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B25" t="str">
         <v>弟弟</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1788442356842-bbleakpy85.jpg</v>
+        <v>assets/1788442386268-ilpasqz91m.jpg</v>
       </c>
       <c r="D25" t="str">
         <v>是</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F25" t="str">
-        <v>浙江嘉兴</v>
+        <v>成都</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1882,22 +1882,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>浅烟灰色</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B26" t="str">
         <v>弟弟</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1788442221802-et3crh0tww.jpg</v>
+        <v>assets/1788442356842-bbleakpy85.jpg</v>
       </c>
       <c r="D26" t="str">
         <v>是</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F26" t="str">
-        <v>成都</v>
+        <v>浙江嘉兴</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1941,22 +1941,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>凯米尔</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B27" t="str">
         <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1788014088852-oqkg79cki9.jpg</v>
+        <v>assets/1788442221802-et3crh0tww.jpg</v>
       </c>
       <c r="D27" t="str">
         <v>是</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-06-26</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F27" t="str">
-        <v>湖北襄阳</v>
+        <v>成都</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -2000,22 +2000,22 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B28" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1788014050978-9a2sguuo1u.jpg</v>
+        <v>assets/1788014088852-oqkg79cki9.jpg</v>
       </c>
       <c r="D28" t="str">
         <v>是</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F28" t="str">
-        <v>深圳</v>
+        <v>湖北襄阳</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2062,19 +2062,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B29" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1788013924404-gmlh0hfjae.jpg</v>
+        <v>assets/1788014050978-9a2sguuo1u.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>是</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F29" t="str">
-        <v>浙江嘉兴</v>
+        <v>深圳</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2118,22 +2118,22 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B30" t="str">
         <v>弟弟</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1788013889955-wpykaycfde.jpg</v>
+        <v>assets/1788013924404-gmlh0hfjae.jpg</v>
       </c>
       <c r="D30" t="str">
         <v>是</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F30" t="str">
-        <v>湖北襄阳</v>
+        <v>浙江嘉兴</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2177,13 +2177,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>银虎斑补丁</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B31" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1788013810551-b90h1mwfiq.jpg</v>
+        <v>assets/1788013889955-wpykaycfde.jpg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
@@ -2192,7 +2192,7 @@
         <v>2026-06-26</v>
       </c>
       <c r="F31" t="str">
-        <v>新疆</v>
+        <v>湖北襄阳</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2236,22 +2236,22 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B32" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1787837910484-r7urrsuib0.jpg</v>
+        <v>assets/1788013810551-b90h1mwfiq.jpg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F32" t="str">
-        <v>香港</v>
+        <v>新疆</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2295,22 +2295,22 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B33" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1787837846581-6q9nxgad35.jpg</v>
+        <v>assets/1787837910484-r7urrsuib0.jpg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-06-10</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F33" t="str">
-        <v>天津</v>
+        <v>香港</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>凯米尔</v>
+        <v>纯黑色</v>
       </c>
       <c r="B34" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1790734407566-tge3si2tw9.jpg</v>
+        <v>assets/1787837846581-6q9nxgad35.jpg</v>
       </c>
       <c r="D34" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F34" t="str">
-        <v/>
+        <v>天津</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2413,19 +2413,19 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔</v>
       </c>
       <c r="B35" t="str">
         <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
+        <v>assets/1790734407566-tge3si2tw9.jpg</v>
       </c>
       <c r="D35" t="str">
         <v>否</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F35" t="str">
         <v/>
@@ -2472,22 +2472,22 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B36" t="str">
         <v>弟弟</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1787837648423-9riberz3tq.jpg</v>
+        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
       </c>
       <c r="D36" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E36" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F36" t="str">
-        <v>北京</v>
+        <v/>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2537,16 +2537,16 @@
         <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
+        <v>assets/1787837648423-9riberz3tq.jpg</v>
       </c>
       <c r="D37" t="str">
         <v>是</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F37" t="str">
-        <v>成都</v>
+        <v>北京</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2596,7 +2596,7 @@
         <v>弟弟</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1787479268842-7en9nzy302.jpg</v>
+        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
       </c>
       <c r="D38" t="str">
         <v>是</v>
@@ -2605,7 +2605,7 @@
         <v>2026-06-10</v>
       </c>
       <c r="F38" t="str">
-        <v>新疆</v>
+        <v>成都</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="J38" t="str">
-        <v>2026-06-10</v>
+        <v/>
       </c>
       <c r="K38" t="str">
         <v/>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B39" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1787479242639-32zuh5lham.jpg</v>
+        <v>assets/1787479268842-7en9nzy302.jpg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
@@ -2664,7 +2664,7 @@
         <v>2026-06-10</v>
       </c>
       <c r="F39" t="str">
-        <v>天津</v>
+        <v>新疆</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2676,7 +2676,7 @@
         <v/>
       </c>
       <c r="J39" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="K39" t="str">
         <v/>
@@ -2708,22 +2708,22 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B40" t="str">
         <v>妹妹</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1787466121255-21jto2cugv.jpg</v>
+        <v>assets/1787479242639-32zuh5lham.jpg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
       </c>
       <c r="E40" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F40" t="str">
-        <v>四川广安</v>
+        <v>天津</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B41" t="str">
         <v>妹妹</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
+        <v>assets/1787466121255-21jto2cugv.jpg</v>
       </c>
       <c r="D41" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F41" t="str">
-        <v/>
+        <v>四川广安</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2826,13 +2826,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B42" t="str">
         <v>妹妹</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1787388277490-e6u506cx0r.jpg</v>
+        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
       </c>
       <c r="D42" t="str">
         <v>否</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B43" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1787328436957-x30od0gw28.jpg</v>
+        <v>assets/1787388277490-e6u506cx0r.jpg</v>
       </c>
       <c r="D43" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E43" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F43" t="str">
-        <v>江苏苏州</v>
+        <v/>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2944,13 +2944,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B44" t="str">
         <v>弟弟</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
+        <v>assets/1787328436957-x30od0gw28.jpg</v>
       </c>
       <c r="D44" t="str">
         <v>是</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>辽宁东港</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3003,13 +3003,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B45" t="str">
         <v>弟弟</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1787327967245-m62ohievcl.jpg</v>
+        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
       </c>
       <c r="D45" t="str">
         <v>是</v>
@@ -3018,7 +3018,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>福建福州</v>
+        <v>辽宁东港</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B46" t="str">
         <v>弟弟</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
+        <v>assets/1787327967245-m62ohievcl.jpg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>上海</v>
+        <v>福建福州</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3121,13 +3121,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>纯蓝色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B47" t="str">
         <v>弟弟</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1787327793837-znk2knoo6p.jpg</v>
+        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>河南鹤壁</v>
+        <v>上海</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3180,13 +3180,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>银虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B48" t="str">
         <v>弟弟</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1787327752832-kkpmp21os3.jpg</v>
+        <v>assets/1787327793837-znk2knoo6p.jpg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>陕西西安</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3242,10 +3242,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B49" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
+        <v>assets/1787327752832-kkpmp21os3.jpg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -3301,10 +3301,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B50" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1787327573762-h23cux94p2.jpg</v>
+        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
@@ -3313,7 +3313,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>北京</v>
+        <v>陕西西安</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3360,10 +3360,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B51" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1787327496557-9daggljg4g.jpg</v>
+        <v>assets/1787327573762-h23cux94p2.jpg</v>
       </c>
       <c r="D51" t="str">
         <v>是</v>
@@ -3372,7 +3372,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>黑龙江哈尔滨</v>
+        <v>北京</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3416,13 +3416,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B52" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
+        <v>assets/1787327496557-9daggljg4g.jpg</v>
       </c>
       <c r="D52" t="str">
         <v>是</v>
@@ -3431,7 +3431,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>甘肃嘉峪关</v>
+        <v>黑龙江哈尔滨</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3475,13 +3475,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B53" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
+        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
       </c>
       <c r="D53" t="str">
         <v>是</v>
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>安徽合肥</v>
+        <v>甘肃嘉峪关</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3534,13 +3534,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B54" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1787327337811-u5u2pdew3.jpg</v>
+        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
@@ -3593,13 +3593,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B55" t="str">
         <v>弟弟</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1787327309143-6c1dan1sev.jpg</v>
+        <v>assets/1787327337811-u5u2pdew3.jpg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
@@ -3608,7 +3608,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>四川成都</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B56" t="str">
         <v>弟弟</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1787327277453-w89ujg69fm.jpg</v>
+        <v>assets/1787327309143-6c1dan1sev.jpg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
@@ -3711,13 +3711,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>蓝银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B57" t="str">
         <v>弟弟</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1787327232159-lkrcl588a5.jpg</v>
+        <v>assets/1787327277453-w89ujg69fm.jpg</v>
       </c>
       <c r="D57" t="str">
         <v>是</v>
@@ -3770,13 +3770,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>玳瑁色</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B58" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1787327182347-3az0z7sys2.jpg</v>
+        <v>assets/1787327232159-lkrcl588a5.jpg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
@@ -3785,7 +3785,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>四川内江</v>
+        <v>四川成都</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>棕虎补丁</v>
+        <v>玳瑁色</v>
       </c>
       <c r="B59" t="str">
         <v>妹妹</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
+        <v>assets/1787327182347-3az0z7sys2.jpg</v>
       </c>
       <c r="D59" t="str">
         <v>是</v>
@@ -3844,7 +3844,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>贵州贵阳</v>
+        <v>四川内江</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3888,13 +3888,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>黑烟色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B60" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1787327101790-tqjlseog5y.jpg</v>
+        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
       </c>
       <c r="D60" t="str">
         <v>是</v>
@@ -3903,7 +3903,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>浙江杭州</v>
+        <v>贵州贵阳</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3947,13 +3947,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>烟灰色</v>
+        <v>黑烟色</v>
       </c>
       <c r="B61" t="str">
         <v>弟弟</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1787327019632-l1780lu2hj.jpg</v>
+        <v>assets/1787327101790-tqjlseog5y.jpg</v>
       </c>
       <c r="D61" t="str">
         <v>是</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>山东威海</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4006,13 +4006,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>棕虎补丁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B62" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1787326905275-plz3fpgo97.jpg</v>
+        <v>assets/1787327019632-l1780lu2hj.jpg</v>
       </c>
       <c r="D62" t="str">
         <v>是</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>浙江杭州</v>
+        <v>山东威海</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4065,13 +4065,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B63" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
+        <v>assets/1787326905275-plz3fpgo97.jpg</v>
       </c>
       <c r="D63" t="str">
         <v>是</v>
@@ -4080,7 +4080,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -4124,13 +4124,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>凯米尔色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B64" t="str">
         <v>弟弟</v>
       </c>
       <c r="C64" t="str">
-        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
+        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
       </c>
       <c r="D64" t="str">
         <v>是</v>
@@ -4183,13 +4183,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>凯米尔</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B65" t="str">
         <v>弟弟</v>
       </c>
       <c r="C65" t="str">
-        <v>assets/1787326814713-p5oavnlulg.jpg</v>
+        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
       </c>
       <c r="D65" t="str">
         <v>是</v>
@@ -4242,13 +4242,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B66" t="str">
         <v>弟弟</v>
       </c>
       <c r="C66" t="str">
-        <v>assets/1787326773577-13q5out2d0.jpg</v>
+        <v>assets/1787326814713-p5oavnlulg.jpg</v>
       </c>
       <c r="D66" t="str">
         <v>是</v>
@@ -4257,7 +4257,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>四川宜宾</v>
+        <v>四川成都</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -4301,13 +4301,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>金棕虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B67" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C67" t="str">
-        <v>assets/1787326548993-89s929m2hg.jpg</v>
+        <v>assets/1787326773577-13q5out2d0.jpg</v>
       </c>
       <c r="D67" t="str">
         <v>是</v>
@@ -4316,7 +4316,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>上海</v>
+        <v>四川宜宾</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4360,13 +4360,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>凯米尔色</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B68" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C68" t="str">
-        <v>assets/1787326449218-09s9ucram4.jpg</v>
+        <v>assets/1787326548993-89s929m2hg.jpg</v>
       </c>
       <c r="D68" t="str">
         <v>是</v>
@@ -4375,7 +4375,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>德国</v>
+        <v>上海</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -4419,13 +4419,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>棕虎补丁</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B69" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C69" t="str">
-        <v>assets/1787326277374-8ti107m5ki.jpg</v>
+        <v>assets/1787326449218-09s9ucram4.jpg</v>
       </c>
       <c r="D69" t="str">
         <v>是</v>
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>广东深圳</v>
+        <v>德国</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4478,13 +4478,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>烟灰色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B70" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C70" t="str">
-        <v>assets/1787326236952-2pmwche4t3.jpg</v>
+        <v>assets/1787326277374-8ti107m5ki.jpg</v>
       </c>
       <c r="D70" t="str">
         <v>是</v>
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>福建泉州</v>
+        <v>广东深圳</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -4537,13 +4537,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B71" t="str">
         <v>弟弟</v>
       </c>
       <c r="C71" t="str">
-        <v>assets/1787326184557-90v6clkwen.jpg</v>
+        <v>assets/1787326236952-2pmwche4t3.jpg</v>
       </c>
       <c r="D71" t="str">
         <v>是</v>
@@ -4552,7 +4552,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>福建福州</v>
+        <v>福建泉州</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -4596,13 +4596,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B72" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C72" t="str">
-        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
+        <v>assets/1787326184557-90v6clkwen.jpg</v>
       </c>
       <c r="D72" t="str">
         <v>是</v>
@@ -4611,7 +4611,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>广西贵港</v>
+        <v>福建福州</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -4655,13 +4655,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B73" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C73" t="str">
-        <v>assets/1787325862706-wq18k3ej56.jpg</v>
+        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
       </c>
       <c r="D73" t="str">
         <v>是</v>
@@ -4670,7 +4670,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>江苏苏州</v>
+        <v>广西贵港</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4720,7 +4720,7 @@
         <v>弟弟</v>
       </c>
       <c r="C74" t="str">
-        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
+        <v>assets/1787325862706-wq18k3ej56.jpg</v>
       </c>
       <c r="D74" t="str">
         <v>是</v>
@@ -4773,13 +4773,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B75" t="str">
         <v>弟弟</v>
       </c>
       <c r="C75" t="str">
-        <v>assets/1787325706797-kgk81ghccy.jpg</v>
+        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
       </c>
       <c r="D75" t="str">
         <v>是</v>
@@ -4788,7 +4788,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>北京</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -4832,13 +4832,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B76" t="str">
         <v>弟弟</v>
       </c>
       <c r="C76" t="str">
-        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
+        <v>assets/1787325706797-kgk81ghccy.jpg</v>
       </c>
       <c r="D76" t="str">
         <v>是</v>
@@ -4847,7 +4847,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>上海</v>
+        <v>北京</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4891,13 +4891,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B77" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C77" t="str">
-        <v>assets/1787325554341-608thexrne.jpg</v>
+        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
       </c>
       <c r="D77" t="str">
         <v>是</v>
@@ -4906,7 +4906,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>江苏苏州</v>
+        <v>上海</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4950,13 +4950,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B78" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C78" t="str">
-        <v>assets/1787325480828-q90pskoiw3.jpg</v>
+        <v>assets/1787325554341-608thexrne.jpg</v>
       </c>
       <c r="D78" t="str">
         <v>是</v>
@@ -4965,7 +4965,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>四川成都</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -5012,10 +5012,10 @@
         <v>浅色银虎斑</v>
       </c>
       <c r="B79" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C79" t="str">
-        <v>assets/1787325448999-a2pg8176fu.jpg</v>
+        <v>assets/1787325480828-q90pskoiw3.jpg</v>
       </c>
       <c r="D79" t="str">
         <v>是</v>
@@ -5024,7 +5024,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>中国台湾</v>
+        <v>四川成都</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -5068,13 +5068,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>棕虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B80" t="str">
         <v>妹妹</v>
       </c>
       <c r="C80" t="str">
-        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
+        <v>assets/1787325448999-a2pg8176fu.jpg</v>
       </c>
       <c r="D80" t="str">
         <v>是</v>
@@ -5083,7 +5083,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>浙江杭州</v>
+        <v>中国台湾</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -5127,13 +5127,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B81" t="str">
         <v>妹妹</v>
       </c>
       <c r="C81" t="str">
-        <v>assets/1787325237876-t19isaq5gu.jpg</v>
+        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
       </c>
       <c r="D81" t="str">
         <v>是</v>
@@ -5142,7 +5142,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>辽宁沈阳</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -5186,13 +5186,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>金棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B82" t="str">
         <v>妹妹</v>
       </c>
       <c r="C82" t="str">
-        <v>assets/1787325199931-e7wms9qtya.jpg</v>
+        <v>assets/1787325237876-t19isaq5gu.jpg</v>
       </c>
       <c r="D82" t="str">
         <v>是</v>
@@ -5201,7 +5201,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>四川成都</v>
+        <v>辽宁沈阳</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -5245,13 +5245,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>蓝虎斑</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B83" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C83" t="str">
-        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
+        <v>assets/1787325199931-e7wms9qtya.jpg</v>
       </c>
       <c r="D83" t="str">
         <v>是</v>
@@ -5260,7 +5260,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>中国香港</v>
+        <v>四川成都</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -5304,13 +5304,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B84" t="str">
         <v>弟弟</v>
       </c>
       <c r="C84" t="str">
-        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
+        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
       </c>
       <c r="D84" t="str">
         <v>是</v>
@@ -5319,7 +5319,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>中国澳门</v>
+        <v>中国香港</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -5363,13 +5363,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B85" t="str">
         <v>弟弟</v>
       </c>
       <c r="C85" t="str">
-        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
+        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
       </c>
       <c r="D85" t="str">
         <v>是</v>
@@ -5378,7 +5378,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>山东青岛</v>
+        <v>中国澳门</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -5422,13 +5422,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>烟灰色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B86" t="str">
         <v>弟弟</v>
       </c>
       <c r="C86" t="str">
-        <v>assets/1787324954998-w5m5jox439.jpg</v>
+        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
       </c>
       <c r="D86" t="str">
         <v>是</v>
@@ -5437,7 +5437,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>海南海口</v>
+        <v>山东青岛</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -5481,13 +5481,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B87" t="str">
         <v>弟弟</v>
       </c>
       <c r="C87" t="str">
-        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
+        <v>assets/1787324954998-w5m5jox439.jpg</v>
       </c>
       <c r="D87" t="str">
         <v>是</v>
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>内蒙古</v>
+        <v>海南海口</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -5540,13 +5540,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B88" t="str">
         <v>弟弟</v>
       </c>
       <c r="C88" t="str">
-        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
+        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
       </c>
       <c r="D88" t="str">
         <v>是</v>
@@ -5555,7 +5555,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>中国香港</v>
+        <v>内蒙古</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -5605,7 +5605,7 @@
         <v>弟弟</v>
       </c>
       <c r="C89" t="str">
-        <v>assets/1787324806613-31yyz14tsf.jpg</v>
+        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
       </c>
       <c r="D89" t="str">
         <v>是</v>
@@ -5614,7 +5614,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>四川成都</v>
+        <v>中国香港</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -5658,13 +5658,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B90" t="str">
         <v>弟弟</v>
       </c>
       <c r="C90" t="str">
-        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
+        <v>assets/1787324806613-31yyz14tsf.jpg</v>
       </c>
       <c r="D90" t="str">
         <v>是</v>
@@ -5673,7 +5673,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>湖北武汉</v>
+        <v>四川成都</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -5717,13 +5717,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>烟灰色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B91" t="str">
         <v>弟弟</v>
       </c>
       <c r="C91" t="str">
-        <v>assets/1787324522658-smn44crast.jpg</v>
+        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
       </c>
       <c r="D91" t="str">
         <v>是</v>
@@ -5776,13 +5776,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B92" t="str">
         <v>弟弟</v>
       </c>
       <c r="C92" t="str">
-        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
+        <v>assets/1787324522658-smn44crast.jpg</v>
       </c>
       <c r="D92" t="str">
         <v>是</v>
@@ -5791,7 +5791,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>新疆</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -5835,13 +5835,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>浅凯米尔</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B93" t="str">
         <v>弟弟</v>
       </c>
       <c r="C93" t="str">
-        <v>assets/1787324331029-d74lcuycf6.jpg</v>
+        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
       </c>
       <c r="D93" t="str">
         <v>是</v>
@@ -5850,7 +5850,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>四川成都</v>
+        <v>新疆</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -5894,13 +5894,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>红虎斑</v>
+        <v>浅凯米尔</v>
       </c>
       <c r="B94" t="str">
         <v>弟弟</v>
       </c>
       <c r="C94" t="str">
-        <v>assets/1787324297469-ans1lse2l5.jpg</v>
+        <v>assets/1787324331029-d74lcuycf6.jpg</v>
       </c>
       <c r="D94" t="str">
         <v>是</v>
@@ -5909,7 +5909,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>四川乐山</v>
+        <v>四川成都</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -5959,7 +5959,7 @@
         <v>弟弟</v>
       </c>
       <c r="C95" t="str">
-        <v>assets/1787324256827-7w383z4bg1.jpg</v>
+        <v>assets/1787324297469-ans1lse2l5.jpg</v>
       </c>
       <c r="D95" t="str">
         <v>是</v>
@@ -5968,7 +5968,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>中国台湾</v>
+        <v>四川乐山</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -6012,13 +6012,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B96" t="str">
         <v>弟弟</v>
       </c>
       <c r="C96" t="str">
-        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
+        <v>assets/1787324256827-7w383z4bg1.jpg</v>
       </c>
       <c r="D96" t="str">
         <v>是</v>
@@ -6027,7 +6027,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>四川成都</v>
+        <v>中国台湾</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -6071,13 +6071,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B97" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C97" t="str">
-        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
+        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
       </c>
       <c r="D97" t="str">
         <v>是</v>
@@ -6086,7 +6086,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>江苏南京</v>
+        <v>四川成都</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -6130,13 +6130,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B98" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C98" t="str">
-        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
+        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
       </c>
       <c r="D98" t="str">
         <v>是</v>
@@ -6189,13 +6189,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B99" t="str">
         <v>弟弟</v>
       </c>
       <c r="C99" t="str">
-        <v>assets/1787323318612-soge38hpsf.jpg</v>
+        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
       </c>
       <c r="D99" t="str">
         <v>是</v>
@@ -6204,7 +6204,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>上海</v>
+        <v>江苏南京</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -6248,13 +6248,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B100" t="str">
         <v>弟弟</v>
       </c>
       <c r="C100" t="str">
-        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
+        <v>assets/1787323318612-soge38hpsf.jpg</v>
       </c>
       <c r="D100" t="str">
         <v>是</v>
@@ -6263,7 +6263,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>四川成都</v>
+        <v>上海</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -6307,13 +6307,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B101" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C101" t="str">
-        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
+        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
       </c>
       <c r="D101" t="str">
         <v>是</v>
@@ -6322,7 +6322,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>浙江宁波</v>
+        <v>四川成都</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -6366,13 +6366,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>银虎斑补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B102" t="str">
         <v>妹妹</v>
       </c>
       <c r="C102" t="str">
-        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
+        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
       </c>
       <c r="D102" t="str">
         <v>是</v>
@@ -6381,7 +6381,7 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>马来西亚</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -6425,13 +6425,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B103" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C103" t="str">
-        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
+        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
       </c>
       <c r="D103" t="str">
         <v>是</v>
@@ -6440,7 +6440,7 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>陕西西安</v>
+        <v>马来西亚</v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -6484,13 +6484,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B104" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C104" t="str">
-        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
+        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
       </c>
       <c r="D104" t="str">
         <v>是</v>
@@ -6499,7 +6499,7 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>广西南宁</v>
+        <v>陕西西安</v>
       </c>
       <c r="G104" t="str">
         <v/>
@@ -6543,13 +6543,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>棕虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B105" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C105" t="str">
-        <v>assets/1787322760950-gn3qgego4s.jpg</v>
+        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
       </c>
       <c r="D105" t="str">
         <v>是</v>
@@ -6602,13 +6602,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B106" t="str">
         <v>弟弟</v>
       </c>
       <c r="C106" t="str">
-        <v>assets/1787322605982-04n50xegt2.jpg</v>
+        <v>assets/1787322760950-gn3qgego4s.jpg</v>
       </c>
       <c r="D106" t="str">
         <v>是</v>
@@ -6617,7 +6617,7 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>上海</v>
+        <v>广西南宁</v>
       </c>
       <c r="G106" t="str">
         <v/>
@@ -6661,13 +6661,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>蓝虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B107" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C107" t="str">
-        <v>assets/1787322490045-kog3ru43dy.jpg</v>
+        <v>assets/1787322605982-04n50xegt2.jpg</v>
       </c>
       <c r="D107" t="str">
         <v>是</v>
@@ -6720,13 +6720,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B108" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C108" t="str">
-        <v>assets/1787322419996-0m33yx89nm.jpg</v>
+        <v>assets/1787322490045-kog3ru43dy.jpg</v>
       </c>
       <c r="D108" t="str">
         <v>是</v>
@@ -6735,7 +6735,7 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>广东广州</v>
+        <v>上海</v>
       </c>
       <c r="G108" t="str">
         <v/>
@@ -6779,13 +6779,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>浅色银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B109" t="str">
         <v>弟弟</v>
       </c>
       <c r="C109" t="str">
-        <v>assets/1787322377730-vj5csj2mll.jpg</v>
+        <v>assets/1787322419996-0m33yx89nm.jpg</v>
       </c>
       <c r="D109" t="str">
         <v>是</v>
@@ -6794,7 +6794,7 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>柬埔寨</v>
+        <v>广东广州</v>
       </c>
       <c r="G109" t="str">
         <v/>
@@ -6838,13 +6838,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>蓝虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B110" t="str">
         <v>弟弟</v>
       </c>
       <c r="C110" t="str">
-        <v>assets/1787322269611-53yaj5ideu.jpg</v>
+        <v>assets/1787322377730-vj5csj2mll.jpg</v>
       </c>
       <c r="D110" t="str">
         <v>是</v>
@@ -6853,7 +6853,7 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>山东枣庄</v>
+        <v>柬埔寨</v>
       </c>
       <c r="G110" t="str">
         <v/>
@@ -6897,13 +6897,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B111" t="str">
         <v>弟弟</v>
       </c>
       <c r="C111" t="str">
-        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
+        <v>assets/1787322269611-53yaj5ideu.jpg</v>
       </c>
       <c r="D111" t="str">
         <v>是</v>
@@ -6912,7 +6912,7 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>陕西西安</v>
+        <v>山东枣庄</v>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -6962,7 +6962,7 @@
         <v>弟弟</v>
       </c>
       <c r="C112" t="str">
-        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
+        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
       </c>
       <c r="D112" t="str">
         <v>是</v>
@@ -6971,7 +6971,7 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>山东东营</v>
+        <v>陕西西安</v>
       </c>
       <c r="G112" t="str">
         <v/>
@@ -7015,13 +7015,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B113" t="str">
         <v>弟弟</v>
       </c>
       <c r="C113" t="str">
-        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
+        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
       </c>
       <c r="D113" t="str">
         <v>是</v>
@@ -7030,7 +7030,7 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>中国台湾</v>
+        <v>山东东营</v>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -7074,13 +7074,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B114" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C114" t="str">
-        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
+        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
       </c>
       <c r="D114" t="str">
         <v>是</v>
@@ -7133,13 +7133,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B115" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C115" t="str">
-        <v>assets/1787321834306-efgnyhujon.jpg</v>
+        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
       </c>
       <c r="D115" t="str">
         <v>是</v>
@@ -7148,7 +7148,7 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G115" t="str">
         <v/>
@@ -7198,7 +7198,7 @@
         <v>弟弟</v>
       </c>
       <c r="C116" t="str">
-        <v>assets/1787321439916-uttgpbkogb.jpg</v>
+        <v>assets/1787321834306-efgnyhujon.jpg</v>
       </c>
       <c r="D116" t="str">
         <v>是</v>
@@ -7207,7 +7207,7 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>安徽合肥</v>
+        <v>北京</v>
       </c>
       <c r="G116" t="str">
         <v/>
@@ -7257,7 +7257,7 @@
         <v>弟弟</v>
       </c>
       <c r="C117" t="str">
-        <v>assets/1787321419210-51hhgurygq.jpg</v>
+        <v>assets/1787321439916-uttgpbkogb.jpg</v>
       </c>
       <c r="D117" t="str">
         <v>是</v>
@@ -7266,7 +7266,7 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>上海</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -7310,13 +7310,13 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B118" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C118" t="str">
-        <v>assets/1787321363369-bzjn51j5il.jpg</v>
+        <v>assets/1787321419210-51hhgurygq.jpg</v>
       </c>
       <c r="D118" t="str">
         <v>是</v>
@@ -7325,7 +7325,7 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>中国台湾</v>
+        <v>上海</v>
       </c>
       <c r="G118" t="str">
         <v/>
@@ -7369,13 +7369,13 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B119" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C119" t="str">
-        <v>assets/1787321332559-87p6spuch3.jpg</v>
+        <v>assets/1787321363369-bzjn51j5il.jpg</v>
       </c>
       <c r="D119" t="str">
         <v>是</v>
@@ -7431,10 +7431,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B120" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C120" t="str">
-        <v>assets/1787321232531-59lnzv8y98.jpg</v>
+        <v>assets/1787321332559-87p6spuch3.jpg</v>
       </c>
       <c r="D120" t="str">
         <v>是</v>
@@ -7443,7 +7443,7 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G120" t="str">
         <v/>
@@ -7487,13 +7487,13 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B121" t="str">
         <v>妹妹</v>
       </c>
       <c r="C121" t="str">
-        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
+        <v>assets/1787321232531-59lnzv8y98.jpg</v>
       </c>
       <c r="D121" t="str">
         <v>是</v>
@@ -7502,7 +7502,7 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>浙江宁波</v>
+        <v>北京</v>
       </c>
       <c r="G121" t="str">
         <v/>
@@ -7552,7 +7552,7 @@
         <v>妹妹</v>
       </c>
       <c r="C122" t="str">
-        <v>assets/1787319800704-v3qeu062ak.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D122" t="str">
         <v>是</v>
@@ -7561,7 +7561,7 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>河北唐山</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G122" t="str">
         <v/>
@@ -7611,7 +7611,7 @@
         <v>妹妹</v>
       </c>
       <c r="C123" t="str">
-        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D123" t="str">
         <v>是</v>
@@ -7620,7 +7620,7 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>河北石家庄</v>
+        <v>河北唐山</v>
       </c>
       <c r="G123" t="str">
         <v/>
@@ -7664,13 +7664,13 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B124" t="str">
         <v>妹妹</v>
       </c>
       <c r="C124" t="str">
-        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D124" t="str">
         <v>是</v>
@@ -7679,7 +7679,7 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>韩国</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -7723,13 +7723,13 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>蓝银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B125" t="str">
         <v>妹妹</v>
       </c>
       <c r="C125" t="str">
-        <v>assets/1787319501376-xscwljnu1j.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D125" t="str">
         <v>是</v>
@@ -7738,7 +7738,7 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>美国</v>
+        <v>韩国</v>
       </c>
       <c r="G125" t="str">
         <v/>
@@ -7782,13 +7782,13 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>棕虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B126" t="str">
         <v>妹妹</v>
       </c>
       <c r="C126" t="str">
-        <v>assets/1787319443529-4a0zqikufx.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D126" t="str">
         <v>是</v>
@@ -7797,7 +7797,7 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>中国台湾</v>
+        <v>美国</v>
       </c>
       <c r="G126" t="str">
         <v/>
@@ -7841,13 +7841,13 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B127" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C127" t="str">
-        <v>assets/1787319356194-lr2d5680i9.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D127" t="str">
         <v>是</v>
@@ -7900,13 +7900,13 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B128" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C128" t="str">
-        <v>assets/1787319208828-aizqo4blcv.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D128" t="str">
         <v>是</v>
@@ -7915,7 +7915,7 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>山东淄博</v>
+        <v>中国台湾</v>
       </c>
       <c r="G128" t="str">
         <v/>
@@ -7959,13 +7959,13 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B129" t="str">
         <v>妹妹</v>
       </c>
       <c r="C129" t="str">
-        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D129" t="str">
         <v>是</v>
@@ -7974,7 +7974,7 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>韩国</v>
+        <v>山东淄博</v>
       </c>
       <c r="G129" t="str">
         <v/>
@@ -8018,13 +8018,13 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B130" t="str">
         <v>妹妹</v>
       </c>
       <c r="C130" t="str">
-        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D130" t="str">
         <v>是</v>
@@ -8033,7 +8033,7 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>四川成都</v>
+        <v>韩国</v>
       </c>
       <c r="G130" t="str">
         <v/>
@@ -8077,13 +8077,13 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B131" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C131" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D131" t="str">
         <v>是</v>
@@ -8092,7 +8092,7 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>广东广州</v>
+        <v>四川成都</v>
       </c>
       <c r="G131" t="str">
         <v/>
@@ -8142,7 +8142,7 @@
         <v>弟弟</v>
       </c>
       <c r="C132" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D132" t="str">
         <v>是</v>
@@ -8151,7 +8151,7 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>广东广州</v>
       </c>
       <c r="G132" t="str">
         <v/>
@@ -8195,13 +8195,13 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B133" t="str">
         <v>弟弟</v>
       </c>
       <c r="C133" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D133" t="str">
         <v>是</v>
@@ -8210,7 +8210,7 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>天津</v>
+        <v>黑龙江鹤岗</v>
       </c>
       <c r="G133" t="str">
         <v/>
@@ -8254,13 +8254,13 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B134" t="str">
         <v>弟弟</v>
       </c>
       <c r="C134" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D134" t="str">
         <v>是</v>
@@ -8269,7 +8269,7 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>山西朔州</v>
+        <v>天津</v>
       </c>
       <c r="G134" t="str">
         <v/>
@@ -8299,7 +8299,7 @@
         <v/>
       </c>
       <c r="P134" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q134" t="str">
         <v/>
@@ -8316,10 +8316,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B135" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C135" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D135" t="str">
         <v>是</v>
@@ -8328,7 +8328,7 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>贵州</v>
+        <v>山西朔州</v>
       </c>
       <c r="G135" t="str">
         <v/>
@@ -8358,7 +8358,7 @@
         <v/>
       </c>
       <c r="P135" t="str">
-        <v/>
+        <v>已接猫</v>
       </c>
       <c r="Q135" t="str">
         <v/>
@@ -8372,22 +8372,22 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B136" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C136" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D136" t="str">
         <v>是</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F136" t="str">
-        <v>北京</v>
+        <v>贵州</v>
       </c>
       <c r="G136" t="str">
         <v/>
@@ -8426,27 +8426,27 @@
         <v/>
       </c>
       <c r="S136" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B137" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C137" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D137" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-04-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F137" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G137" t="str">
         <v/>
@@ -8490,22 +8490,22 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>阴影色NS12</v>
+        <v>纯黑色</v>
       </c>
       <c r="B138" t="str">
         <v>妹妹</v>
       </c>
       <c r="C138" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D138" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-05-28</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F138" t="str">
-        <v>西安</v>
+        <v/>
       </c>
       <c r="G138" t="str">
         <v/>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>阴影色NS11</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B139" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C139" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D139" t="str">
         <v>是</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F139" t="str">
-        <v>重庆</v>
+        <v>西安</v>
       </c>
       <c r="G139" t="str">
         <v/>
@@ -8608,22 +8608,22 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B140" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C140" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D140" t="str">
         <v>是</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F140" t="str">
-        <v>中国澳门</v>
+        <v>重庆</v>
       </c>
       <c r="G140" t="str">
         <v/>
@@ -8667,22 +8667,22 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B141" t="str">
         <v>妹妹</v>
       </c>
       <c r="C141" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D141" t="str">
         <v>是</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F141" t="str">
-        <v>深圳</v>
+        <v>中国澳门</v>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -8732,7 +8732,7 @@
         <v>妹妹</v>
       </c>
       <c r="C142" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D142" t="str">
         <v>是</v>
@@ -8741,7 +8741,7 @@
         <v>2026-06-06</v>
       </c>
       <c r="F142" t="str">
-        <v>浙江温州</v>
+        <v>深圳</v>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -8791,16 +8791,16 @@
         <v>妹妹</v>
       </c>
       <c r="C143" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D143" t="str">
         <v>是</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F143" t="str">
-        <v>安徽合肥</v>
+        <v>浙江温州</v>
       </c>
       <c r="G143" t="str">
         <v/>
@@ -8847,19 +8847,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B144" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C144" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D144" t="str">
         <v>是</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F144" t="str">
-        <v>北京</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G144" t="str">
         <v/>
@@ -8906,19 +8906,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B145" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C145" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D145" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E145" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F145" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G145" t="str">
         <v/>
@@ -8962,22 +8962,22 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B146" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C146" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D146" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E146" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F146" t="str">
-        <v>河北石家庄</v>
+        <v/>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -9024,10 +9024,10 @@
         <v>烟灰色</v>
       </c>
       <c r="B147" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C147" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D147" t="str">
         <v>是</v>
@@ -9036,7 +9036,7 @@
         <v>2026-06-06</v>
       </c>
       <c r="F147" t="str">
-        <v>浙江宁波</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -9083,10 +9083,10 @@
         <v>烟灰色</v>
       </c>
       <c r="B148" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C148" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D148" t="str">
         <v>是</v>
@@ -9095,7 +9095,7 @@
         <v>2026-06-06</v>
       </c>
       <c r="F148" t="str">
-        <v>上海</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G148" t="str">
         <v/>
@@ -9139,22 +9139,22 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>纯黑色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B149" t="str">
         <v>弟弟</v>
       </c>
       <c r="C149" t="str">
-        <v>assets/1790733778469-jt9fswxe9w.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D149" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-04-17</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F149" t="str">
-        <v/>
+        <v>上海</v>
       </c>
       <c r="G149" t="str">
         <v/>
@@ -9198,22 +9198,22 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B150" t="str">
         <v>弟弟</v>
       </c>
       <c r="C150" t="str">
-        <v>assets/1790734215453-0zvw0v9uja.jpg</v>
+        <v>assets/1790733778469-jt9fswxe9w.jpg</v>
       </c>
       <c r="D150" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-06-10</v>
+        <v>2026-04-17</v>
       </c>
       <c r="F150" t="str">
-        <v>北京</v>
+        <v/>
       </c>
       <c r="G150" t="str">
         <v/>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>阴影色NS11</v>
+        <v>银虎斑</v>
       </c>
       <c r="B151" t="str">
         <v>弟弟</v>
       </c>
       <c r="C151" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1790734215453-0zvw0v9uja.jpg</v>
       </c>
       <c r="D151" t="str">
         <v>是</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F151" t="str">
-        <v>安徽芜湖</v>
+        <v>北京</v>
       </c>
       <c r="G151" t="str">
         <v/>
@@ -9316,22 +9316,22 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>浅色银虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B152" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C152" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D152" t="str">
         <v>是</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F152" t="str">
-        <v>香港</v>
+        <v>安徽芜湖</v>
       </c>
       <c r="G152" t="str">
         <v/>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>浅烟灰色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B153" t="str">
         <v>妹妹</v>
       </c>
       <c r="C153" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D153" t="str">
         <v>是</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F153" t="str">
-        <v>四川成都</v>
+        <v>香港</v>
       </c>
       <c r="G153" t="str">
         <v/>
@@ -9434,22 +9434,22 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>凯米尔色</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B154" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C154" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D154" t="str">
         <v>是</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-02-14</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F154" t="str">
-        <v>上海浦东</v>
+        <v>四川成都</v>
       </c>
       <c r="G154" t="str">
         <v/>
@@ -9493,22 +9493,22 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>银虎斑补丁</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B155" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C155" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D155" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-04-09</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F155" t="str">
-        <v/>
+        <v>上海浦东</v>
       </c>
       <c r="G155" t="str">
         <v/>
@@ -9552,22 +9552,22 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B156" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C156" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D156" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-05-18</v>
+        <v>2026-04-09</v>
       </c>
       <c r="F156" t="str">
-        <v>北京</v>
+        <v/>
       </c>
       <c r="G156" t="str">
         <v/>
@@ -9611,22 +9611,22 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B157" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C157" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D157" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-02-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F157" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G157" t="str">
         <v/>
@@ -9670,19 +9670,19 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B158" t="str">
         <v>妹妹</v>
       </c>
       <c r="C158" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D158" t="str">
         <v>否</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-05-24</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F158" t="str">
         <v/>
@@ -9729,22 +9729,22 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B159" t="str">
         <v>妹妹</v>
       </c>
       <c r="C159" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D159" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F159" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G159" t="str">
         <v/>
@@ -9791,10 +9791,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B160" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C160" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D160" t="str">
         <v>是</v>
@@ -9853,16 +9853,16 @@
         <v>弟弟</v>
       </c>
       <c r="C161" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D161" t="str">
         <v>是</v>
       </c>
       <c r="E161" t="str">
-        <v>2025-11-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F161" t="str">
-        <v>韩国</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G161" t="str">
         <v/>
@@ -9909,19 +9909,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B162" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C162" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D162" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-05-18</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F162" t="str">
-        <v/>
+        <v>韩国</v>
       </c>
       <c r="G162" t="str">
         <v/>
@@ -9965,22 +9965,22 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B163" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C163" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D163" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F163" t="str">
-        <v>四川自贡</v>
+        <v/>
       </c>
       <c r="G163" t="str">
         <v/>
@@ -10027,19 +10027,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B164" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C164" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D164" t="str">
         <v>是</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F164" t="str">
-        <v>深圳</v>
+        <v>四川自贡</v>
       </c>
       <c r="G164" t="str">
         <v/>
@@ -10083,22 +10083,22 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B165" t="str">
         <v>妹妹</v>
       </c>
       <c r="C165" t="str">
-        <v>assets/1790733648123-636cut584p.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D165" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-04-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F165" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="G165" t="str">
         <v/>
@@ -10142,22 +10142,22 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B166" t="str">
         <v>妹妹</v>
       </c>
       <c r="C166" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1790733648123-636cut584p.jpg</v>
       </c>
       <c r="D166" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-03-05</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F166" t="str">
-        <v>韩国</v>
+        <v/>
       </c>
       <c r="G166" t="str">
         <v/>
@@ -10201,22 +10201,22 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B167" t="str">
         <v>妹妹</v>
       </c>
       <c r="C167" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D167" t="str">
         <v>是</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F167" t="str">
-        <v>河北邢台</v>
+        <v>韩国</v>
       </c>
       <c r="G167" t="str">
         <v/>
@@ -10260,13 +10260,13 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>棕虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B168" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C168" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D168" t="str">
         <v>是</v>
@@ -10275,7 +10275,7 @@
         <v>2026-06-05</v>
       </c>
       <c r="F168" t="str">
-        <v>四川自贡</v>
+        <v>河北邢台</v>
       </c>
       <c r="G168" t="str">
         <v/>
@@ -10319,22 +10319,22 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>棕虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B169" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C169" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D169" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F169" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G169" t="str">
         <v/>
@@ -10378,19 +10378,19 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B170" t="str">
         <v>妹妹</v>
       </c>
       <c r="C170" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D170" t="str">
         <v>否</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F170" t="str">
         <v/>
@@ -10437,19 +10437,19 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B171" t="str">
         <v>妹妹</v>
       </c>
       <c r="C171" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D171" t="str">
         <v>否</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F171" t="str">
         <v/>
@@ -10502,13 +10502,13 @@
         <v>妹妹</v>
       </c>
       <c r="C172" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D172" t="str">
         <v>否</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-04-30</v>
+        <v>2026-04-17</v>
       </c>
       <c r="F172" t="str">
         <v/>
@@ -10555,52 +10555,52 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B173" t="str">
         <v>妹妹</v>
       </c>
       <c r="C173" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D173" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-02-20</v>
+        <v>2026-04-30</v>
       </c>
       <c r="F173" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G173" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H173" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I173" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J173" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K173" t="str">
         <v/>
       </c>
       <c r="L173" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M173" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N173" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O173" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P173" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q173" t="str">
         <v/>
@@ -10609,57 +10609,57 @@
         <v/>
       </c>
       <c r="S173" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B174" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C174" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D174" t="str">
         <v>是</v>
       </c>
       <c r="E174" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F174" t="str">
-        <v>广东广州</v>
+        <v>荷兰</v>
       </c>
       <c r="G174" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H174" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I174" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J174" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K174" t="str">
         <v/>
       </c>
       <c r="L174" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M174" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N174" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O174" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P174" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q174" t="str">
         <v/>
@@ -10668,7 +10668,7 @@
         <v/>
       </c>
       <c r="S174" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="175">
@@ -10679,7 +10679,7 @@
         <v>弟弟</v>
       </c>
       <c r="C175" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D175" t="str">
         <v>是</v>
@@ -10732,13 +10732,13 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B176" t="str">
         <v>弟弟</v>
       </c>
       <c r="C176" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D176" t="str">
         <v>是</v>
@@ -10747,7 +10747,7 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>山西朔州</v>
+        <v>广东广州</v>
       </c>
       <c r="G176" t="str">
         <v/>
@@ -10794,10 +10794,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B177" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C177" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D177" t="str">
         <v>是</v>
@@ -10806,7 +10806,7 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>浙江宁波</v>
+        <v>山西朔州</v>
       </c>
       <c r="G177" t="str">
         <v/>
@@ -10853,10 +10853,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B178" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C178" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D178" t="str">
         <v>是</v>
@@ -10865,7 +10865,7 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>陕西西安</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G178" t="str">
         <v/>
@@ -10915,7 +10915,7 @@
         <v>弟弟</v>
       </c>
       <c r="C179" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D179" t="str">
         <v>是</v>
@@ -10924,7 +10924,7 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>黑龙江漠河</v>
+        <v>陕西西安</v>
       </c>
       <c r="G179" t="str">
         <v/>
@@ -10968,13 +10968,13 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B180" t="str">
         <v>弟弟</v>
       </c>
       <c r="C180" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D180" t="str">
         <v>是</v>
@@ -10983,7 +10983,7 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>日本</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G180" t="str">
         <v/>
@@ -11027,13 +11027,13 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B181" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C181" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D181" t="str">
         <v>是</v>
@@ -11042,7 +11042,7 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>浙江杭州</v>
+        <v>日本</v>
       </c>
       <c r="G181" t="str">
         <v/>
@@ -11092,7 +11092,7 @@
         <v>妹妹</v>
       </c>
       <c r="C182" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D182" t="str">
         <v>是</v>
@@ -11101,7 +11101,7 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>贵州安顺</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G182" t="str">
         <v/>
@@ -11151,7 +11151,7 @@
         <v>妹妹</v>
       </c>
       <c r="C183" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D183" t="str">
         <v>是</v>
@@ -11160,7 +11160,7 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>山东青岛</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G183" t="str">
         <v/>
@@ -11207,10 +11207,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B184" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C184" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D184" t="str">
         <v>是</v>
@@ -11219,7 +11219,7 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>黑龙江漠河</v>
+        <v>山东青岛</v>
       </c>
       <c r="G184" t="str">
         <v/>
@@ -11263,13 +11263,13 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B185" t="str">
         <v>弟弟</v>
       </c>
       <c r="C185" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D185" t="str">
         <v>是</v>
@@ -11278,7 +11278,7 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>河南鹤壁</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G185" t="str">
         <v/>
@@ -11322,13 +11322,13 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>银虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B186" t="str">
         <v>弟弟</v>
       </c>
       <c r="C186" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D186" t="str">
         <v>是</v>
@@ -11337,7 +11337,7 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>陕西西安</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G186" t="str">
         <v/>
@@ -11381,13 +11381,13 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B187" t="str">
         <v>弟弟</v>
       </c>
       <c r="C187" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D187" t="str">
         <v>是</v>
@@ -11396,7 +11396,7 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>四川成都</v>
+        <v>陕西西安</v>
       </c>
       <c r="G187" t="str">
         <v/>
@@ -11440,19 +11440,19 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B188" t="str">
         <v>弟弟</v>
       </c>
       <c r="C188" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
       </c>
       <c r="D188" t="str">
         <v>是</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F188" t="str">
         <v>四川成都</v>
@@ -11499,22 +11499,22 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B189" t="str">
         <v>弟弟</v>
       </c>
       <c r="C189" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
       </c>
       <c r="D189" t="str">
         <v>是</v>
       </c>
       <c r="E189" t="str">
-        <v/>
+        <v>2026-05-18</v>
       </c>
       <c r="F189" t="str">
-        <v>新加坡</v>
+        <v>四川成都</v>
       </c>
       <c r="G189" t="str">
         <v/>
@@ -11558,13 +11558,13 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B190" t="str">
         <v>弟弟</v>
       </c>
       <c r="C190" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
       </c>
       <c r="D190" t="str">
         <v>是</v>
@@ -11573,7 +11573,7 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>上海浦东</v>
+        <v>新加坡</v>
       </c>
       <c r="G190" t="str">
         <v/>
@@ -11617,22 +11617,22 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B191" t="str">
         <v>弟弟</v>
       </c>
       <c r="C191" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
       </c>
       <c r="D191" t="str">
         <v>是</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F191" t="str">
-        <v>浙江温州</v>
+        <v>上海浦东</v>
       </c>
       <c r="G191" t="str">
         <v/>
@@ -11679,10 +11679,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B192" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C192" t="str">
-        <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
       </c>
       <c r="D192" t="str">
         <v>是</v>
@@ -11691,51 +11691,110 @@
         <v>2026-06-06</v>
       </c>
       <c r="F192" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G192" t="str">
+        <v/>
+      </c>
+      <c r="H192" t="str">
+        <v/>
+      </c>
+      <c r="I192" t="str">
+        <v/>
+      </c>
+      <c r="J192" t="str">
+        <v/>
+      </c>
+      <c r="K192" t="str">
+        <v/>
+      </c>
+      <c r="L192" t="str">
+        <v/>
+      </c>
+      <c r="M192" t="str">
+        <v/>
+      </c>
+      <c r="N192" t="str">
+        <v/>
+      </c>
+      <c r="O192" t="str">
+        <v/>
+      </c>
+      <c r="P192" t="str">
+        <v/>
+      </c>
+      <c r="Q192" t="str">
+        <v/>
+      </c>
+      <c r="R192" t="str">
+        <v/>
+      </c>
+      <c r="S192" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B193" t="str">
+        <v>妹妹</v>
+      </c>
+      <c r="C193" t="str">
+        <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
+      </c>
+      <c r="D193" t="str">
+        <v>是</v>
+      </c>
+      <c r="E193" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F193" t="str">
         <v>深圳</v>
       </c>
-      <c r="G192" t="str">
-        <v/>
-      </c>
-      <c r="H192" t="str">
-        <v/>
-      </c>
-      <c r="I192" t="str">
-        <v/>
-      </c>
-      <c r="J192" t="str">
-        <v/>
-      </c>
-      <c r="K192" t="str">
-        <v/>
-      </c>
-      <c r="L192" t="str">
-        <v/>
-      </c>
-      <c r="M192" t="str">
-        <v/>
-      </c>
-      <c r="N192" t="str">
-        <v/>
-      </c>
-      <c r="O192" t="str">
-        <v/>
-      </c>
-      <c r="P192" t="str">
-        <v/>
-      </c>
-      <c r="Q192" t="str">
-        <v/>
-      </c>
-      <c r="R192" t="str">
-        <v/>
-      </c>
-      <c r="S192" t="str">
+      <c r="G193" t="str">
+        <v/>
+      </c>
+      <c r="H193" t="str">
+        <v/>
+      </c>
+      <c r="I193" t="str">
+        <v/>
+      </c>
+      <c r="J193" t="str">
+        <v/>
+      </c>
+      <c r="K193" t="str">
+        <v/>
+      </c>
+      <c r="L193" t="str">
+        <v/>
+      </c>
+      <c r="M193" t="str">
+        <v/>
+      </c>
+      <c r="N193" t="str">
+        <v/>
+      </c>
+      <c r="O193" t="str">
+        <v/>
+      </c>
+      <c r="P193" t="str">
+        <v/>
+      </c>
+      <c r="Q193" t="str">
+        <v/>
+      </c>
+      <c r="R193" t="str">
+        <v/>
+      </c>
+      <c r="S193" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S192"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S193"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/kittens.xlsx
+++ b/data/kittens.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S193"/>
+  <dimension ref="A1:S195"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -466,19 +466,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B2" t="str">
         <v>弟弟</v>
       </c>
       <c r="C2" t="str">
-        <v>assets/1792313878597-k9d5tg2u3t.jpg</v>
+        <v>assets/1792923925020-a1jfupgum9.jpg</v>
       </c>
       <c r="D2" t="str">
         <v>否</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-03-26</v>
+        <v>2026-07-30</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -525,22 +525,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色</v>
       </c>
       <c r="B3" t="str">
         <v>妹妹</v>
       </c>
       <c r="C3" t="str">
-        <v>assets/1791885799211-r54amxe2jp.jpg</v>
+        <v>assets/1792923857898-zc66s8n60p.jpg</v>
       </c>
       <c r="D3" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-18</v>
       </c>
       <c r="F3" t="str">
-        <v>深圳</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -584,22 +584,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>阴影色</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B4" t="str">
         <v>弟弟</v>
       </c>
       <c r="C4" t="str">
-        <v>assets/1791885766213-djh49zfdy8.jpg</v>
+        <v>assets/1792313878597-k9d5tg2u3t.jpg</v>
       </c>
       <c r="D4" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-06-15</v>
+        <v>2026-03-26</v>
       </c>
       <c r="F4" t="str">
-        <v>上海</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -643,22 +643,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>阴影色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B5" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C5" t="str">
-        <v>assets/1791885692087-flz5al0ukw.jpg</v>
+        <v>assets/1791885799211-r54amxe2jp.jpg</v>
       </c>
       <c r="D5" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>深圳</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -702,22 +702,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>银虎斑</v>
+        <v>阴影色</v>
       </c>
       <c r="B6" t="str">
         <v>弟弟</v>
       </c>
       <c r="C6" t="str">
-        <v>assets/1791885628374-op5p4tcc5c.jpg</v>
+        <v>assets/1791885766213-djh49zfdy8.jpg</v>
       </c>
       <c r="D6" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>上海</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -761,19 +761,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色</v>
       </c>
       <c r="B7" t="str">
         <v>弟弟</v>
       </c>
       <c r="C7" t="str">
-        <v>assets/1791885580674-a6onl6jgc.jpg</v>
+        <v>assets/1792923823270-avmodk29j1.jpg</v>
       </c>
       <c r="D7" t="str">
         <v>否</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-06-10</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -820,19 +820,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B8" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C8" t="str">
-        <v>assets/1791885502285-o86pddnxqc.jpg</v>
+        <v>assets/1791885628374-op5p4tcc5c.jpg</v>
       </c>
       <c r="D8" t="str">
         <v>否</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -879,19 +879,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B9" t="str">
         <v>弟弟</v>
       </c>
       <c r="C9" t="str">
-        <v>assets/1791288567764-tti55g9g1q.jpg</v>
+        <v>assets/1791885580674-a6onl6jgc.jpg</v>
       </c>
       <c r="D9" t="str">
         <v>否</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -941,19 +941,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B10" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C10" t="str">
-        <v>assets/1791288502036-4v43o0otqq.jpg</v>
+        <v>assets/1791885502285-o86pddnxqc.jpg</v>
       </c>
       <c r="D10" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E10" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="F10" t="str">
-        <v>浙江宁波</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -997,19 +997,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>浅烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B11" t="str">
         <v>弟弟</v>
       </c>
       <c r="C11" t="str">
-        <v>assets/1790734752606-rusbv65ug8.jpg</v>
+        <v>assets/1791288567764-tti55g9g1q.jpg</v>
       </c>
       <c r="D11" t="str">
         <v>否</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-04-28</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1059,19 +1059,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B12" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C12" t="str">
-        <v>assets/1790734688874-ldibzixi2g.jpg</v>
+        <v>assets/1791288502036-4v43o0otqq.jpg</v>
       </c>
       <c r="D12" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>浙江宁波</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1115,22 +1115,22 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>烟灰色</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B13" t="str">
         <v>弟弟</v>
       </c>
       <c r="C13" t="str">
-        <v>assets/1790734651251-a58tdtmhnx.jpg</v>
+        <v>assets/1790734752606-rusbv65ug8.jpg</v>
       </c>
       <c r="D13" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-05-18</v>
+        <v>2026-04-28</v>
       </c>
       <c r="F13" t="str">
-        <v>成都</v>
+        <v/>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1174,22 +1174,22 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>浅银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B14" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C14" t="str">
-        <v>assets/1790734595573-u465hv1hyg.jpg</v>
+        <v>assets/1790734688874-ldibzixi2g.jpg</v>
       </c>
       <c r="D14" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F14" t="str">
-        <v>浙江嘉兴</v>
+        <v/>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1233,22 +1233,22 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>浅银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B15" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C15" t="str">
-        <v>assets/1790734548586-cztim8ip4y.jpg</v>
+        <v>assets/1790734651251-a58tdtmhnx.jpg</v>
       </c>
       <c r="D15" t="str">
         <v>是</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-06-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F15" t="str">
-        <v>西安</v>
+        <v>成都</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1292,22 +1292,22 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>蓝虎斑</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B16" t="str">
         <v>弟弟</v>
       </c>
       <c r="C16" t="str">
-        <v>assets/1790734499008-43htmo2xuw.jpg</v>
+        <v>assets/1790734595573-u465hv1hyg.jpg</v>
       </c>
       <c r="D16" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-03-20</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>浙江嘉兴</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1351,13 +1351,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>阴影色NS11</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B17" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C17" t="str">
-        <v>assets/1789655131156-6ywyod2pgz.jpg</v>
+        <v>assets/1790734548586-cztim8ip4y.jpg</v>
       </c>
       <c r="D17" t="str">
         <v>是</v>
@@ -1366,7 +1366,7 @@
         <v>2026-06-15</v>
       </c>
       <c r="F17" t="str">
-        <v>广州</v>
+        <v>西安</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1410,22 +1410,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>浅银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B18" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C18" t="str">
-        <v>assets/1789654858942-ws3mqfv0zf.jpg</v>
+        <v>assets/1790734499008-43htmo2xuw.jpg</v>
       </c>
       <c r="D18" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-06-15</v>
+        <v>2026-03-20</v>
       </c>
       <c r="F18" t="str">
-        <v>浙江杭州</v>
+        <v/>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1469,22 +1469,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>红虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B19" t="str">
         <v>弟弟</v>
       </c>
       <c r="C19" t="str">
-        <v>assets/1789654723483-fyl8c7wdqg.jpg</v>
+        <v>assets/1789655131156-6ywyod2pgz.jpg</v>
       </c>
       <c r="D19" t="str">
         <v>是</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F19" t="str">
-        <v>天津</v>
+        <v>广州</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1528,22 +1528,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>银虎班补丁</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B20" t="str">
         <v>妹妹</v>
       </c>
       <c r="C20" t="str">
-        <v>assets/1789654675792-6d4kyyncmf.jpg</v>
+        <v>assets/1789654858942-ws3mqfv0zf.jpg</v>
       </c>
       <c r="D20" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>浙江杭州</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>烟灰色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B21" t="str">
         <v>弟弟</v>
       </c>
       <c r="C21" t="str">
-        <v>assets/1789654628929-2wok5d7b71.jpg</v>
+        <v>assets/1789654723483-fyl8c7wdqg.jpg</v>
       </c>
       <c r="D21" t="str">
         <v>是</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F21" t="str">
-        <v>新加坡</v>
+        <v>天津</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1646,19 +1646,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>阴影色NS11</v>
+        <v>银虎班补丁</v>
       </c>
       <c r="B22" t="str">
         <v>妹妹</v>
       </c>
       <c r="C22" t="str">
-        <v>assets/1789654549268-68uab4pdoy.jpg</v>
+        <v>assets/1789654675792-6d4kyyncmf.jpg</v>
       </c>
       <c r="D22" t="str">
         <v>否</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -1705,22 +1705,22 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>阴影色NS12</v>
+        <v>烟灰色</v>
       </c>
       <c r="B23" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C23" t="str">
-        <v>assets/1788534744815-pzs6jqs2pm.jpg</v>
+        <v>assets/1789654628929-2wok5d7b71.jpg</v>
       </c>
       <c r="D23" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F23" t="str">
-        <v/>
+        <v>新加坡</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1764,22 +1764,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B24" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C24" t="str">
-        <v>assets/1788534522775-my4ggv0pwo.jpg</v>
+        <v>assets/1789654549268-68uab4pdoy.jpg</v>
       </c>
       <c r="D24" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E24" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="F24" t="str">
-        <v>西藏</v>
+        <v/>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1823,22 +1823,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>红虎斑</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B25" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C25" t="str">
-        <v>assets/1788442386268-ilpasqz91m.jpg</v>
+        <v>assets/1788534744815-pzs6jqs2pm.jpg</v>
       </c>
       <c r="D25" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-06-26</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F25" t="str">
-        <v>成都</v>
+        <v/>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1882,13 +1882,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>浅银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B26" t="str">
         <v>弟弟</v>
       </c>
       <c r="C26" t="str">
-        <v>assets/1788442356842-bbleakpy85.jpg</v>
+        <v>assets/1788534522775-my4ggv0pwo.jpg</v>
       </c>
       <c r="D26" t="str">
         <v>是</v>
@@ -1897,7 +1897,7 @@
         <v>2026-06-15</v>
       </c>
       <c r="F26" t="str">
-        <v>浙江嘉兴</v>
+        <v>西藏</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1941,19 +1941,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>浅烟灰色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B27" t="str">
         <v>弟弟</v>
       </c>
       <c r="C27" t="str">
-        <v>assets/1788442221802-et3crh0tww.jpg</v>
+        <v>assets/1788442386268-ilpasqz91m.jpg</v>
       </c>
       <c r="D27" t="str">
         <v>是</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-03-21</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F27" t="str">
         <v>成都</v>
@@ -2000,22 +2000,22 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>凯米尔</v>
+        <v>浅银虎斑</v>
       </c>
       <c r="B28" t="str">
         <v>弟弟</v>
       </c>
       <c r="C28" t="str">
-        <v>assets/1788014088852-oqkg79cki9.jpg</v>
+        <v>assets/1788442356842-bbleakpy85.jpg</v>
       </c>
       <c r="D28" t="str">
         <v>是</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F28" t="str">
-        <v>湖北襄阳</v>
+        <v>浙江嘉兴</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B29" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C29" t="str">
-        <v>assets/1788014050978-9a2sguuo1u.jpg</v>
+        <v>assets/1788442221802-et3crh0tww.jpg</v>
       </c>
       <c r="D29" t="str">
         <v>是</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F29" t="str">
-        <v>深圳</v>
+        <v>成都</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -2118,22 +2118,22 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B30" t="str">
         <v>弟弟</v>
       </c>
       <c r="C30" t="str">
-        <v>assets/1788013924404-gmlh0hfjae.jpg</v>
+        <v>assets/1788014088852-oqkg79cki9.jpg</v>
       </c>
       <c r="D30" t="str">
         <v>是</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F30" t="str">
-        <v>浙江嘉兴</v>
+        <v>湖北襄阳</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2177,22 +2177,22 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B31" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C31" t="str">
-        <v>assets/1788013889955-wpykaycfde.jpg</v>
+        <v>assets/1788014050978-9a2sguuo1u.jpg</v>
       </c>
       <c r="D31" t="str">
         <v>是</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F31" t="str">
-        <v>湖北襄阳</v>
+        <v>深圳</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -2236,22 +2236,22 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B32" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C32" t="str">
-        <v>assets/1788013810551-b90h1mwfiq.jpg</v>
+        <v>assets/1788013924404-gmlh0hfjae.jpg</v>
       </c>
       <c r="D32" t="str">
         <v>是</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F32" t="str">
-        <v>新疆</v>
+        <v>浙江嘉兴</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2295,22 +2295,22 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B33" t="str">
         <v>弟弟</v>
       </c>
       <c r="C33" t="str">
-        <v>assets/1787837910484-r7urrsuib0.jpg</v>
+        <v>assets/1788013889955-wpykaycfde.jpg</v>
       </c>
       <c r="D33" t="str">
         <v>是</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F33" t="str">
-        <v>香港</v>
+        <v>湖北襄阳</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B34" t="str">
         <v>妹妹</v>
       </c>
       <c r="C34" t="str">
-        <v>assets/1787837846581-6q9nxgad35.jpg</v>
+        <v>assets/1788013810551-b90h1mwfiq.jpg</v>
       </c>
       <c r="D34" t="str">
         <v>是</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F34" t="str">
-        <v>天津</v>
+        <v>新疆</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2413,22 +2413,22 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>凯米尔</v>
+        <v>银虎斑</v>
       </c>
       <c r="B35" t="str">
         <v>弟弟</v>
       </c>
       <c r="C35" t="str">
-        <v>assets/1790734407566-tge3si2tw9.jpg</v>
+        <v>assets/1787837910484-r7urrsuib0.jpg</v>
       </c>
       <c r="D35" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-06-26</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F35" t="str">
-        <v/>
+        <v>香港</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2472,22 +2472,22 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>烟灰色</v>
+        <v>纯黑色</v>
       </c>
       <c r="B36" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C36" t="str">
-        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
+        <v>assets/1787837846581-6q9nxgad35.jpg</v>
       </c>
       <c r="D36" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F36" t="str">
-        <v/>
+        <v>天津</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2531,22 +2531,22 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B37" t="str">
         <v>弟弟</v>
       </c>
       <c r="C37" t="str">
-        <v>assets/1787837648423-9riberz3tq.jpg</v>
+        <v>assets/1790734407566-tge3si2tw9.jpg</v>
       </c>
       <c r="D37" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-26</v>
       </c>
       <c r="F37" t="str">
-        <v>北京</v>
+        <v/>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2590,22 +2590,22 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B38" t="str">
         <v>弟弟</v>
       </c>
       <c r="C38" t="str">
-        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
+        <v>assets/1787837690599-rd37ukkrgw.jpg</v>
       </c>
       <c r="D38" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F38" t="str">
-        <v>成都</v>
+        <v/>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2655,16 +2655,16 @@
         <v>弟弟</v>
       </c>
       <c r="C39" t="str">
-        <v>assets/1787479268842-7en9nzy302.jpg</v>
+        <v>assets/1787837648423-9riberz3tq.jpg</v>
       </c>
       <c r="D39" t="str">
         <v>是</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F39" t="str">
-        <v>新疆</v>
+        <v>北京</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -2676,7 +2676,7 @@
         <v/>
       </c>
       <c r="J39" t="str">
-        <v>2026-06-10</v>
+        <v/>
       </c>
       <c r="K39" t="str">
         <v/>
@@ -2708,13 +2708,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B40" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C40" t="str">
-        <v>assets/1787479242639-32zuh5lham.jpg</v>
+        <v>assets/1787837594903-wtnbv2fz89.jpg</v>
       </c>
       <c r="D40" t="str">
         <v>是</v>
@@ -2723,7 +2723,7 @@
         <v>2026-06-10</v>
       </c>
       <c r="F40" t="str">
-        <v>天津</v>
+        <v>成都</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2770,19 +2770,19 @@
         <v>棕虎斑</v>
       </c>
       <c r="B41" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C41" t="str">
-        <v>assets/1787466121255-21jto2cugv.jpg</v>
+        <v>assets/1787479268842-7en9nzy302.jpg</v>
       </c>
       <c r="D41" t="str">
         <v>是</v>
       </c>
       <c r="E41" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="F41" t="str">
-        <v>四川广安</v>
+        <v>新疆</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2794,7 +2794,7 @@
         <v/>
       </c>
       <c r="J41" t="str">
-        <v/>
+        <v>2026-06-10</v>
       </c>
       <c r="K41" t="str">
         <v/>
@@ -2826,22 +2826,22 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>烟灰色</v>
+        <v>纯黑色</v>
       </c>
       <c r="B42" t="str">
         <v>妹妹</v>
       </c>
       <c r="C42" t="str">
-        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
+        <v>assets/1787479242639-32zuh5lham.jpg</v>
       </c>
       <c r="D42" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F42" t="str">
-        <v/>
+        <v>天津</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2891,16 +2891,16 @@
         <v>妹妹</v>
       </c>
       <c r="C43" t="str">
-        <v>assets/1787388277490-e6u506cx0r.jpg</v>
+        <v>assets/1787466121255-21jto2cugv.jpg</v>
       </c>
       <c r="D43" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F43" t="str">
-        <v/>
+        <v>四川广安</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2944,22 +2944,22 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B44" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C44" t="str">
-        <v>assets/1787328436957-x30od0gw28.jpg</v>
+        <v>assets/1787388322060-uj8bkwqgnv.jpg</v>
       </c>
       <c r="D44" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E44" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F44" t="str">
-        <v>江苏苏州</v>
+        <v/>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3003,22 +3003,22 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B45" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C45" t="str">
-        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
+        <v>assets/1787388277490-e6u506cx0r.jpg</v>
       </c>
       <c r="D45" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E45" t="str">
-        <v/>
+        <v>2026-06-06</v>
       </c>
       <c r="F45" t="str">
-        <v>辽宁东港</v>
+        <v/>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B46" t="str">
         <v>弟弟</v>
       </c>
       <c r="C46" t="str">
-        <v>assets/1787327967245-m62ohievcl.jpg</v>
+        <v>assets/1787328436957-x30od0gw28.jpg</v>
       </c>
       <c r="D46" t="str">
         <v>是</v>
@@ -3077,7 +3077,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>福建福州</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -3127,7 +3127,7 @@
         <v>弟弟</v>
       </c>
       <c r="C47" t="str">
-        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
+        <v>assets/1787328420967-viv9v8nbjn.jpg</v>
       </c>
       <c r="D47" t="str">
         <v>是</v>
@@ -3136,7 +3136,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>上海</v>
+        <v>辽宁东港</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3180,13 +3180,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>纯蓝色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B48" t="str">
         <v>弟弟</v>
       </c>
       <c r="C48" t="str">
-        <v>assets/1787327793837-znk2knoo6p.jpg</v>
+        <v>assets/1787327967245-m62ohievcl.jpg</v>
       </c>
       <c r="D48" t="str">
         <v>是</v>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>河南鹤壁</v>
+        <v>福建福州</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B49" t="str">
         <v>弟弟</v>
       </c>
       <c r="C49" t="str">
-        <v>assets/1787327752832-kkpmp21os3.jpg</v>
+        <v>assets/1787327853521-js8ljh3ulj.jpg</v>
       </c>
       <c r="D49" t="str">
         <v>是</v>
@@ -3254,7 +3254,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>陕西西安</v>
+        <v>上海</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -3298,13 +3298,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>银虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B50" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C50" t="str">
-        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
+        <v>assets/1787327793837-znk2knoo6p.jpg</v>
       </c>
       <c r="D50" t="str">
         <v>是</v>
@@ -3313,7 +3313,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>陕西西安</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -3363,7 +3363,7 @@
         <v>弟弟</v>
       </c>
       <c r="C51" t="str">
-        <v>assets/1787327573762-h23cux94p2.jpg</v>
+        <v>assets/1787327752832-kkpmp21os3.jpg</v>
       </c>
       <c r="D51" t="str">
         <v>是</v>
@@ -3372,7 +3372,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>北京</v>
+        <v>陕西西安</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3422,7 +3422,7 @@
         <v>妹妹</v>
       </c>
       <c r="C52" t="str">
-        <v>assets/1787327496557-9daggljg4g.jpg</v>
+        <v>assets/1787327605711-4o2f6v6ybp.jpg</v>
       </c>
       <c r="D52" t="str">
         <v>是</v>
@@ -3431,7 +3431,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>黑龙江哈尔滨</v>
+        <v>陕西西安</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3475,13 +3475,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B53" t="str">
         <v>弟弟</v>
       </c>
       <c r="C53" t="str">
-        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
+        <v>assets/1787327573762-h23cux94p2.jpg</v>
       </c>
       <c r="D53" t="str">
         <v>是</v>
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>甘肃嘉峪关</v>
+        <v>北京</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3534,13 +3534,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B54" t="str">
         <v>妹妹</v>
       </c>
       <c r="C54" t="str">
-        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
+        <v>assets/1787327496557-9daggljg4g.jpg</v>
       </c>
       <c r="D54" t="str">
         <v>是</v>
@@ -3549,7 +3549,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>安徽合肥</v>
+        <v>黑龙江哈尔滨</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3593,13 +3593,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B55" t="str">
         <v>弟弟</v>
       </c>
       <c r="C55" t="str">
-        <v>assets/1787327337811-u5u2pdew3.jpg</v>
+        <v>assets/1787327456560-p4yhq4qvrv.jpg</v>
       </c>
       <c r="D55" t="str">
         <v>是</v>
@@ -3608,7 +3608,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>安徽合肥</v>
+        <v>甘肃嘉峪关</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B56" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C56" t="str">
-        <v>assets/1787327309143-6c1dan1sev.jpg</v>
+        <v>assets/1787327421713-zg7np4yzkc.jpg</v>
       </c>
       <c r="D56" t="str">
         <v>是</v>
@@ -3667,7 +3667,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>四川成都</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3717,7 +3717,7 @@
         <v>弟弟</v>
       </c>
       <c r="C57" t="str">
-        <v>assets/1787327277453-w89ujg69fm.jpg</v>
+        <v>assets/1787327337811-u5u2pdew3.jpg</v>
       </c>
       <c r="D57" t="str">
         <v>是</v>
@@ -3726,7 +3726,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>四川成都</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3770,13 +3770,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>蓝银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B58" t="str">
         <v>弟弟</v>
       </c>
       <c r="C58" t="str">
-        <v>assets/1787327232159-lkrcl588a5.jpg</v>
+        <v>assets/1787327309143-6c1dan1sev.jpg</v>
       </c>
       <c r="D58" t="str">
         <v>是</v>
@@ -3829,13 +3829,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>玳瑁色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B59" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C59" t="str">
-        <v>assets/1787327182347-3az0z7sys2.jpg</v>
+        <v>assets/1787327277453-w89ujg69fm.jpg</v>
       </c>
       <c r="D59" t="str">
         <v>是</v>
@@ -3844,7 +3844,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>四川内江</v>
+        <v>四川成都</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3888,13 +3888,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>棕虎补丁</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B60" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C60" t="str">
-        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
+        <v>assets/1787327232159-lkrcl588a5.jpg</v>
       </c>
       <c r="D60" t="str">
         <v>是</v>
@@ -3903,7 +3903,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>贵州贵阳</v>
+        <v>四川成都</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3947,13 +3947,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>黑烟色</v>
+        <v>玳瑁色</v>
       </c>
       <c r="B61" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C61" t="str">
-        <v>assets/1787327101790-tqjlseog5y.jpg</v>
+        <v>assets/1787327182347-3az0z7sys2.jpg</v>
       </c>
       <c r="D61" t="str">
         <v>是</v>
@@ -3962,7 +3962,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>浙江杭州</v>
+        <v>四川内江</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -4006,13 +4006,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>烟灰色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B62" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C62" t="str">
-        <v>assets/1787327019632-l1780lu2hj.jpg</v>
+        <v>assets/1787327143756-4xtgfy5ozu.jpg</v>
       </c>
       <c r="D62" t="str">
         <v>是</v>
@@ -4021,7 +4021,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>山东威海</v>
+        <v>贵州贵阳</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -4065,13 +4065,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>棕虎补丁</v>
+        <v>黑烟色</v>
       </c>
       <c r="B63" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C63" t="str">
-        <v>assets/1787326905275-plz3fpgo97.jpg</v>
+        <v>assets/1787327101790-tqjlseog5y.jpg</v>
       </c>
       <c r="D63" t="str">
         <v>是</v>
@@ -4124,13 +4124,13 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B64" t="str">
         <v>弟弟</v>
       </c>
       <c r="C64" t="str">
-        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
+        <v>assets/1787327019632-l1780lu2hj.jpg</v>
       </c>
       <c r="D64" t="str">
         <v>是</v>
@@ -4139,7 +4139,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>四川成都</v>
+        <v>山东威海</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -4183,13 +4183,13 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B65" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C65" t="str">
-        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
+        <v>assets/1787326905275-plz3fpgo97.jpg</v>
       </c>
       <c r="D65" t="str">
         <v>是</v>
@@ -4198,7 +4198,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -4242,13 +4242,13 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>凯米尔</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B66" t="str">
         <v>弟弟</v>
       </c>
       <c r="C66" t="str">
-        <v>assets/1787326814713-p5oavnlulg.jpg</v>
+        <v>assets/1787326874462-z9rzs7wg17.jpg</v>
       </c>
       <c r="D66" t="str">
         <v>是</v>
@@ -4301,13 +4301,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B67" t="str">
         <v>弟弟</v>
       </c>
       <c r="C67" t="str">
-        <v>assets/1787326773577-13q5out2d0.jpg</v>
+        <v>assets/1787326843271-0uhv7b9p89.jpg</v>
       </c>
       <c r="D67" t="str">
         <v>是</v>
@@ -4316,7 +4316,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>四川宜宾</v>
+        <v>四川成都</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4360,13 +4360,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>金棕虎斑</v>
+        <v>凯米尔</v>
       </c>
       <c r="B68" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C68" t="str">
-        <v>assets/1787326548993-89s929m2hg.jpg</v>
+        <v>assets/1787326814713-p5oavnlulg.jpg</v>
       </c>
       <c r="D68" t="str">
         <v>是</v>
@@ -4375,7 +4375,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>上海</v>
+        <v>四川成都</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -4419,13 +4419,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B69" t="str">
         <v>弟弟</v>
       </c>
       <c r="C69" t="str">
-        <v>assets/1787326449218-09s9ucram4.jpg</v>
+        <v>assets/1787326773577-13q5out2d0.jpg</v>
       </c>
       <c r="D69" t="str">
         <v>是</v>
@@ -4434,7 +4434,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>德国</v>
+        <v>四川宜宾</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4478,13 +4478,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>棕虎补丁</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B70" t="str">
         <v>妹妹</v>
       </c>
       <c r="C70" t="str">
-        <v>assets/1787326277374-8ti107m5ki.jpg</v>
+        <v>assets/1787326548993-89s929m2hg.jpg</v>
       </c>
       <c r="D70" t="str">
         <v>是</v>
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>广东深圳</v>
+        <v>上海</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -4537,13 +4537,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B71" t="str">
         <v>弟弟</v>
       </c>
       <c r="C71" t="str">
-        <v>assets/1787326236952-2pmwche4t3.jpg</v>
+        <v>assets/1787326449218-09s9ucram4.jpg</v>
       </c>
       <c r="D71" t="str">
         <v>是</v>
@@ -4552,7 +4552,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>福建泉州</v>
+        <v>德国</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -4596,13 +4596,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B72" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C72" t="str">
-        <v>assets/1787326184557-90v6clkwen.jpg</v>
+        <v>assets/1787326277374-8ti107m5ki.jpg</v>
       </c>
       <c r="D72" t="str">
         <v>是</v>
@@ -4611,7 +4611,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>福建福州</v>
+        <v>广东深圳</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -4655,13 +4655,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>棕虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B73" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C73" t="str">
-        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
+        <v>assets/1787326236952-2pmwche4t3.jpg</v>
       </c>
       <c r="D73" t="str">
         <v>是</v>
@@ -4670,7 +4670,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>广西贵港</v>
+        <v>福建泉州</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -4714,13 +4714,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B74" t="str">
         <v>弟弟</v>
       </c>
       <c r="C74" t="str">
-        <v>assets/1787325862706-wq18k3ej56.jpg</v>
+        <v>assets/1787326184557-90v6clkwen.jpg</v>
       </c>
       <c r="D74" t="str">
         <v>是</v>
@@ -4729,7 +4729,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>江苏苏州</v>
+        <v>福建福州</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -4773,13 +4773,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>凯米尔色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B75" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C75" t="str">
-        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
+        <v>assets/1787326046155-4tk23nq4dj.jpg</v>
       </c>
       <c r="D75" t="str">
         <v>是</v>
@@ -4788,7 +4788,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>江苏苏州</v>
+        <v>广西贵港</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -4832,13 +4832,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B76" t="str">
         <v>弟弟</v>
       </c>
       <c r="C76" t="str">
-        <v>assets/1787325706797-kgk81ghccy.jpg</v>
+        <v>assets/1787325862706-wq18k3ej56.jpg</v>
       </c>
       <c r="D76" t="str">
         <v>是</v>
@@ -4847,7 +4847,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>北京</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -4891,13 +4891,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>蓝虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B77" t="str">
         <v>弟弟</v>
       </c>
       <c r="C77" t="str">
-        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
+        <v>assets/1787325743258-a7oac7hzlo.jpg</v>
       </c>
       <c r="D77" t="str">
         <v>是</v>
@@ -4906,7 +4906,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>上海</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -4950,13 +4950,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B78" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C78" t="str">
-        <v>assets/1787325554341-608thexrne.jpg</v>
+        <v>assets/1787325706797-kgk81ghccy.jpg</v>
       </c>
       <c r="D78" t="str">
         <v>是</v>
@@ -4965,7 +4965,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>江苏苏州</v>
+        <v>北京</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -5009,13 +5009,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>浅色银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B79" t="str">
         <v>弟弟</v>
       </c>
       <c r="C79" t="str">
-        <v>assets/1787325480828-q90pskoiw3.jpg</v>
+        <v>assets/1787325603704-lahzgrm7fa.jpg,assets/1787325690106-wgu3spujit.jpg</v>
       </c>
       <c r="D79" t="str">
         <v>是</v>
@@ -5024,7 +5024,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>四川成都</v>
+        <v>上海</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -5068,13 +5068,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>浅色银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B80" t="str">
         <v>妹妹</v>
       </c>
       <c r="C80" t="str">
-        <v>assets/1787325448999-a2pg8176fu.jpg</v>
+        <v>assets/1787325554341-608thexrne.jpg</v>
       </c>
       <c r="D80" t="str">
         <v>是</v>
@@ -5083,7 +5083,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>中国台湾</v>
+        <v>江苏苏州</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -5127,13 +5127,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>棕虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B81" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C81" t="str">
-        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
+        <v>assets/1787325480828-q90pskoiw3.jpg</v>
       </c>
       <c r="D81" t="str">
         <v>是</v>
@@ -5142,7 +5142,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>浙江杭州</v>
+        <v>四川成都</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -5186,13 +5186,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>烟灰色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B82" t="str">
         <v>妹妹</v>
       </c>
       <c r="C82" t="str">
-        <v>assets/1787325237876-t19isaq5gu.jpg</v>
+        <v>assets/1787325448999-a2pg8176fu.jpg</v>
       </c>
       <c r="D82" t="str">
         <v>是</v>
@@ -5201,7 +5201,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>辽宁沈阳</v>
+        <v>中国台湾</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -5245,13 +5245,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>金棕虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B83" t="str">
         <v>妹妹</v>
       </c>
       <c r="C83" t="str">
-        <v>assets/1787325199931-e7wms9qtya.jpg</v>
+        <v>assets/1787325357634-k55zlfhmqj.jpg</v>
       </c>
       <c r="D83" t="str">
         <v>是</v>
@@ -5260,7 +5260,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>四川成都</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -5304,13 +5304,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>蓝虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B84" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C84" t="str">
-        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
+        <v>assets/1787325237876-t19isaq5gu.jpg</v>
       </c>
       <c r="D84" t="str">
         <v>是</v>
@@ -5319,7 +5319,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>中国香港</v>
+        <v>辽宁沈阳</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -5363,13 +5363,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>烟灰色</v>
+        <v>金棕虎斑</v>
       </c>
       <c r="B85" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C85" t="str">
-        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
+        <v>assets/1787325199931-e7wms9qtya.jpg</v>
       </c>
       <c r="D85" t="str">
         <v>是</v>
@@ -5378,7 +5378,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>中国澳门</v>
+        <v>四川成都</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -5428,7 +5428,7 @@
         <v>弟弟</v>
       </c>
       <c r="C86" t="str">
-        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
+        <v>assets/1787325172354-4sa8uzaey2.jpg</v>
       </c>
       <c r="D86" t="str">
         <v>是</v>
@@ -5437,7 +5437,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>山东青岛</v>
+        <v>中国香港</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -5487,7 +5487,7 @@
         <v>弟弟</v>
       </c>
       <c r="C87" t="str">
-        <v>assets/1787324954998-w5m5jox439.jpg</v>
+        <v>assets/1787325109283-y7mvkk6qg4.jpg</v>
       </c>
       <c r="D87" t="str">
         <v>是</v>
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>海南海口</v>
+        <v>中国澳门</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -5540,13 +5540,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>棕虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B88" t="str">
         <v>弟弟</v>
       </c>
       <c r="C88" t="str">
-        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
+        <v>assets/1787325033629-y3ygps3zaj.jpg</v>
       </c>
       <c r="D88" t="str">
         <v>是</v>
@@ -5555,7 +5555,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>内蒙古</v>
+        <v>山东青岛</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -5605,7 +5605,7 @@
         <v>弟弟</v>
       </c>
       <c r="C89" t="str">
-        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
+        <v>assets/1787324954998-w5m5jox439.jpg</v>
       </c>
       <c r="D89" t="str">
         <v>是</v>
@@ -5614,7 +5614,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>中国香港</v>
+        <v>海南海口</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -5658,13 +5658,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B90" t="str">
         <v>弟弟</v>
       </c>
       <c r="C90" t="str">
-        <v>assets/1787324806613-31yyz14tsf.jpg</v>
+        <v>assets/1787324905909-zrz8o79kdf.jpg</v>
       </c>
       <c r="D90" t="str">
         <v>是</v>
@@ -5673,7 +5673,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>四川成都</v>
+        <v>内蒙古</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -5717,13 +5717,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>红虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B91" t="str">
         <v>弟弟</v>
       </c>
       <c r="C91" t="str">
-        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
+        <v>assets/1787324880505-gbh0sn7b6j.jpg</v>
       </c>
       <c r="D91" t="str">
         <v>是</v>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>湖北武汉</v>
+        <v>中国香港</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -5782,7 +5782,7 @@
         <v>弟弟</v>
       </c>
       <c r="C92" t="str">
-        <v>assets/1787324522658-smn44crast.jpg</v>
+        <v>assets/1787324806613-31yyz14tsf.jpg</v>
       </c>
       <c r="D92" t="str">
         <v>是</v>
@@ -5791,7 +5791,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>湖北武汉</v>
+        <v>四川成都</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -5835,13 +5835,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>棕虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B93" t="str">
         <v>弟弟</v>
       </c>
       <c r="C93" t="str">
-        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
+        <v>assets/1787324789658-uz6ephkdsh.jpg</v>
       </c>
       <c r="D93" t="str">
         <v>是</v>
@@ -5850,7 +5850,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>新疆</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -5894,13 +5894,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>浅凯米尔</v>
+        <v>烟灰色</v>
       </c>
       <c r="B94" t="str">
         <v>弟弟</v>
       </c>
       <c r="C94" t="str">
-        <v>assets/1787324331029-d74lcuycf6.jpg</v>
+        <v>assets/1787324522658-smn44crast.jpg</v>
       </c>
       <c r="D94" t="str">
         <v>是</v>
@@ -5909,7 +5909,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>四川成都</v>
+        <v>湖北武汉</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -5953,13 +5953,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>红虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B95" t="str">
         <v>弟弟</v>
       </c>
       <c r="C95" t="str">
-        <v>assets/1787324297469-ans1lse2l5.jpg</v>
+        <v>assets/1787324365608-6xtrjp7euz.jpg</v>
       </c>
       <c r="D95" t="str">
         <v>是</v>
@@ -5968,7 +5968,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>四川乐山</v>
+        <v>新疆</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -6012,13 +6012,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>红虎斑</v>
+        <v>浅凯米尔</v>
       </c>
       <c r="B96" t="str">
         <v>弟弟</v>
       </c>
       <c r="C96" t="str">
-        <v>assets/1787324256827-7w383z4bg1.jpg</v>
+        <v>assets/1787324331029-d74lcuycf6.jpg</v>
       </c>
       <c r="D96" t="str">
         <v>是</v>
@@ -6027,7 +6027,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>中国台湾</v>
+        <v>四川成都</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -6071,13 +6071,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B97" t="str">
         <v>弟弟</v>
       </c>
       <c r="C97" t="str">
-        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
+        <v>assets/1787324297469-ans1lse2l5.jpg</v>
       </c>
       <c r="D97" t="str">
         <v>是</v>
@@ -6086,7 +6086,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>四川成都</v>
+        <v>四川乐山</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -6130,13 +6130,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>凯米尔色</v>
+        <v>红虎斑</v>
       </c>
       <c r="B98" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C98" t="str">
-        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
+        <v>assets/1787324256827-7w383z4bg1.jpg</v>
       </c>
       <c r="D98" t="str">
         <v>是</v>
@@ -6145,7 +6145,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>江苏南京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -6189,13 +6189,13 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B99" t="str">
         <v>弟弟</v>
       </c>
       <c r="C99" t="str">
-        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
+        <v>assets/1787324228262-y3vwn6i4zk.jpg</v>
       </c>
       <c r="D99" t="str">
         <v>是</v>
@@ -6204,7 +6204,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>江苏南京</v>
+        <v>四川成都</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -6248,13 +6248,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B100" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C100" t="str">
-        <v>assets/1787323318612-soge38hpsf.jpg</v>
+        <v>assets/1787324201418-9tk4ik75mo.jpg</v>
       </c>
       <c r="D100" t="str">
         <v>是</v>
@@ -6263,7 +6263,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>上海</v>
+        <v>江苏南京</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -6313,7 +6313,7 @@
         <v>弟弟</v>
       </c>
       <c r="C101" t="str">
-        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
+        <v>assets/1787324092513-jpa2rmkci2.jpg</v>
       </c>
       <c r="D101" t="str">
         <v>是</v>
@@ -6322,7 +6322,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>四川成都</v>
+        <v>江苏南京</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -6369,10 +6369,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B102" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C102" t="str">
-        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
+        <v>assets/1787323318612-soge38hpsf.jpg</v>
       </c>
       <c r="D102" t="str">
         <v>是</v>
@@ -6381,7 +6381,7 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>浙江宁波</v>
+        <v>上海</v>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -6425,13 +6425,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>银虎斑补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B103" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C103" t="str">
-        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
+        <v>assets/1787323235892-7yq8ioq01e.jpg</v>
       </c>
       <c r="D103" t="str">
         <v>是</v>
@@ -6440,7 +6440,7 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>马来西亚</v>
+        <v>四川成都</v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -6487,10 +6487,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B104" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C104" t="str">
-        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
+        <v>assets/1787322988096-6e2f54q7vo.jpg</v>
       </c>
       <c r="D104" t="str">
         <v>是</v>
@@ -6499,7 +6499,7 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>陕西西安</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G104" t="str">
         <v/>
@@ -6543,13 +6543,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B105" t="str">
         <v>妹妹</v>
       </c>
       <c r="C105" t="str">
-        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
+        <v>assets/1787322938518-85ev8bs2k5.jpg</v>
       </c>
       <c r="D105" t="str">
         <v>是</v>
@@ -6558,7 +6558,7 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>广西南宁</v>
+        <v>马来西亚</v>
       </c>
       <c r="G105" t="str">
         <v/>
@@ -6602,13 +6602,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B106" t="str">
         <v>弟弟</v>
       </c>
       <c r="C106" t="str">
-        <v>assets/1787322760950-gn3qgego4s.jpg</v>
+        <v>assets/1787322881183-tzu9xtw2sg.jpg</v>
       </c>
       <c r="D106" t="str">
         <v>是</v>
@@ -6617,7 +6617,7 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>广西南宁</v>
+        <v>陕西西安</v>
       </c>
       <c r="G106" t="str">
         <v/>
@@ -6661,13 +6661,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>红虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B107" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C107" t="str">
-        <v>assets/1787322605982-04n50xegt2.jpg</v>
+        <v>assets/1787322840098-nhy4jjyx7k.jpg</v>
       </c>
       <c r="D107" t="str">
         <v>是</v>
@@ -6676,7 +6676,7 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>上海</v>
+        <v>广西南宁</v>
       </c>
       <c r="G107" t="str">
         <v/>
@@ -6720,13 +6720,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B108" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C108" t="str">
-        <v>assets/1787322490045-kog3ru43dy.jpg</v>
+        <v>assets/1787322760950-gn3qgego4s.jpg</v>
       </c>
       <c r="D108" t="str">
         <v>是</v>
@@ -6735,7 +6735,7 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>上海</v>
+        <v>广西南宁</v>
       </c>
       <c r="G108" t="str">
         <v/>
@@ -6785,7 +6785,7 @@
         <v>弟弟</v>
       </c>
       <c r="C109" t="str">
-        <v>assets/1787322419996-0m33yx89nm.jpg</v>
+        <v>assets/1787322605982-04n50xegt2.jpg</v>
       </c>
       <c r="D109" t="str">
         <v>是</v>
@@ -6794,7 +6794,7 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>广东广州</v>
+        <v>上海</v>
       </c>
       <c r="G109" t="str">
         <v/>
@@ -6838,13 +6838,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>浅色银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B110" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C110" t="str">
-        <v>assets/1787322377730-vj5csj2mll.jpg</v>
+        <v>assets/1787322490045-kog3ru43dy.jpg</v>
       </c>
       <c r="D110" t="str">
         <v>是</v>
@@ -6853,7 +6853,7 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>柬埔寨</v>
+        <v>上海</v>
       </c>
       <c r="G110" t="str">
         <v/>
@@ -6897,13 +6897,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>蓝虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B111" t="str">
         <v>弟弟</v>
       </c>
       <c r="C111" t="str">
-        <v>assets/1787322269611-53yaj5ideu.jpg</v>
+        <v>assets/1787322419996-0m33yx89nm.jpg</v>
       </c>
       <c r="D111" t="str">
         <v>是</v>
@@ -6912,7 +6912,7 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>山东枣庄</v>
+        <v>广东广州</v>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -6956,13 +6956,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>银虎斑</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B112" t="str">
         <v>弟弟</v>
       </c>
       <c r="C112" t="str">
-        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
+        <v>assets/1787322377730-vj5csj2mll.jpg</v>
       </c>
       <c r="D112" t="str">
         <v>是</v>
@@ -6971,7 +6971,7 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>陕西西安</v>
+        <v>柬埔寨</v>
       </c>
       <c r="G112" t="str">
         <v/>
@@ -7015,13 +7015,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B113" t="str">
         <v>弟弟</v>
       </c>
       <c r="C113" t="str">
-        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
+        <v>assets/1787322269611-53yaj5ideu.jpg</v>
       </c>
       <c r="D113" t="str">
         <v>是</v>
@@ -7030,7 +7030,7 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>山东东营</v>
+        <v>山东枣庄</v>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -7074,13 +7074,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B114" t="str">
         <v>弟弟</v>
       </c>
       <c r="C114" t="str">
-        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
+        <v>assets/1787321989528-7d6liuhuk9.jpg</v>
       </c>
       <c r="D114" t="str">
         <v>是</v>
@@ -7089,7 +7089,7 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>中国台湾</v>
+        <v>陕西西安</v>
       </c>
       <c r="G114" t="str">
         <v/>
@@ -7133,13 +7133,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B115" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C115" t="str">
-        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
+        <v>assets/1787321941642-xlrc1no2ua.jpg</v>
       </c>
       <c r="D115" t="str">
         <v>是</v>
@@ -7148,7 +7148,7 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>中国台湾</v>
+        <v>山东东营</v>
       </c>
       <c r="G115" t="str">
         <v/>
@@ -7192,13 +7192,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>银虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B116" t="str">
         <v>弟弟</v>
       </c>
       <c r="C116" t="str">
-        <v>assets/1787321834306-efgnyhujon.jpg</v>
+        <v>assets/1787321903535-6orj7qcgzn.jpg</v>
       </c>
       <c r="D116" t="str">
         <v>是</v>
@@ -7207,7 +7207,7 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G116" t="str">
         <v/>
@@ -7251,13 +7251,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B117" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C117" t="str">
-        <v>assets/1787321439916-uttgpbkogb.jpg</v>
+        <v>assets/1787321858985-v4qej7cq7g.jpg</v>
       </c>
       <c r="D117" t="str">
         <v>是</v>
@@ -7266,7 +7266,7 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>安徽合肥</v>
+        <v>中国台湾</v>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -7316,7 +7316,7 @@
         <v>弟弟</v>
       </c>
       <c r="C118" t="str">
-        <v>assets/1787321419210-51hhgurygq.jpg</v>
+        <v>assets/1787321834306-efgnyhujon.jpg</v>
       </c>
       <c r="D118" t="str">
         <v>是</v>
@@ -7325,7 +7325,7 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>上海</v>
+        <v>北京</v>
       </c>
       <c r="G118" t="str">
         <v/>
@@ -7369,13 +7369,13 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>凯米尔色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B119" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C119" t="str">
-        <v>assets/1787321363369-bzjn51j5il.jpg</v>
+        <v>assets/1787321439916-uttgpbkogb.jpg</v>
       </c>
       <c r="D119" t="str">
         <v>是</v>
@@ -7384,7 +7384,7 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>中国台湾</v>
+        <v>安徽合肥</v>
       </c>
       <c r="G119" t="str">
         <v/>
@@ -7428,13 +7428,13 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B120" t="str">
         <v>弟弟</v>
       </c>
       <c r="C120" t="str">
-        <v>assets/1787321332559-87p6spuch3.jpg</v>
+        <v>assets/1787321419210-51hhgurygq.jpg</v>
       </c>
       <c r="D120" t="str">
         <v>是</v>
@@ -7443,7 +7443,7 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>中国台湾</v>
+        <v>上海</v>
       </c>
       <c r="G120" t="str">
         <v/>
@@ -7487,13 +7487,13 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>棕虎斑</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B121" t="str">
         <v>妹妹</v>
       </c>
       <c r="C121" t="str">
-        <v>assets/1787321232531-59lnzv8y98.jpg</v>
+        <v>assets/1787321363369-bzjn51j5il.jpg</v>
       </c>
       <c r="D121" t="str">
         <v>是</v>
@@ -7502,7 +7502,7 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>北京</v>
+        <v>中国台湾</v>
       </c>
       <c r="G121" t="str">
         <v/>
@@ -7546,13 +7546,13 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B122" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C122" t="str">
-        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
+        <v>assets/1787321332559-87p6spuch3.jpg</v>
       </c>
       <c r="D122" t="str">
         <v>是</v>
@@ -7561,7 +7561,7 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>浙江宁波</v>
+        <v>中国台湾</v>
       </c>
       <c r="G122" t="str">
         <v/>
@@ -7605,13 +7605,13 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B123" t="str">
         <v>妹妹</v>
       </c>
       <c r="C123" t="str">
-        <v>assets/1787319800704-v3qeu062ak.jpg</v>
+        <v>assets/1787321232531-59lnzv8y98.jpg</v>
       </c>
       <c r="D123" t="str">
         <v>是</v>
@@ -7620,7 +7620,7 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>河北唐山</v>
+        <v>北京</v>
       </c>
       <c r="G123" t="str">
         <v/>
@@ -7670,7 +7670,7 @@
         <v>妹妹</v>
       </c>
       <c r="C124" t="str">
-        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
+        <v>assets/1787319975814-g1pfa56vfp.jpg</v>
       </c>
       <c r="D124" t="str">
         <v>是</v>
@@ -7679,7 +7679,7 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>河北石家庄</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -7723,13 +7723,13 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>棕虎补丁</v>
+        <v>银虎斑</v>
       </c>
       <c r="B125" t="str">
         <v>妹妹</v>
       </c>
       <c r="C125" t="str">
-        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
+        <v>assets/1787319800704-v3qeu062ak.jpg</v>
       </c>
       <c r="D125" t="str">
         <v>是</v>
@@ -7738,7 +7738,7 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>韩国</v>
+        <v>河北唐山</v>
       </c>
       <c r="G125" t="str">
         <v/>
@@ -7782,13 +7782,13 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>蓝银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B126" t="str">
         <v>妹妹</v>
       </c>
       <c r="C126" t="str">
-        <v>assets/1787319501376-xscwljnu1j.jpg</v>
+        <v>assets/1787319745369-zn66xr3bvb.jpg</v>
       </c>
       <c r="D126" t="str">
         <v>是</v>
@@ -7797,7 +7797,7 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>美国</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G126" t="str">
         <v/>
@@ -7841,13 +7841,13 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>棕虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B127" t="str">
         <v>妹妹</v>
       </c>
       <c r="C127" t="str">
-        <v>assets/1787319443529-4a0zqikufx.jpg</v>
+        <v>assets/1787319547969-zqlq35fxxt.jpg</v>
       </c>
       <c r="D127" t="str">
         <v>是</v>
@@ -7856,7 +7856,7 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>中国台湾</v>
+        <v>韩国</v>
       </c>
       <c r="G127" t="str">
         <v/>
@@ -7900,13 +7900,13 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>蓝虎斑</v>
+        <v>蓝银虎斑</v>
       </c>
       <c r="B128" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C128" t="str">
-        <v>assets/1787319356194-lr2d5680i9.jpg</v>
+        <v>assets/1787319501376-xscwljnu1j.jpg</v>
       </c>
       <c r="D128" t="str">
         <v>是</v>
@@ -7915,7 +7915,7 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>中国台湾</v>
+        <v>美国</v>
       </c>
       <c r="G128" t="str">
         <v/>
@@ -7965,7 +7965,7 @@
         <v>妹妹</v>
       </c>
       <c r="C129" t="str">
-        <v>assets/1787319208828-aizqo4blcv.jpg</v>
+        <v>assets/1787319443529-4a0zqikufx.jpg</v>
       </c>
       <c r="D129" t="str">
         <v>是</v>
@@ -7974,7 +7974,7 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>山东淄博</v>
+        <v>中国台湾</v>
       </c>
       <c r="G129" t="str">
         <v/>
@@ -8018,13 +8018,13 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B130" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C130" t="str">
-        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
+        <v>assets/1787319356194-lr2d5680i9.jpg</v>
       </c>
       <c r="D130" t="str">
         <v>是</v>
@@ -8033,7 +8033,7 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>韩国</v>
+        <v>中国台湾</v>
       </c>
       <c r="G130" t="str">
         <v/>
@@ -8077,13 +8077,13 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>棕虎补丁</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B131" t="str">
         <v>妹妹</v>
       </c>
       <c r="C131" t="str">
-        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
+        <v>assets/1787319208828-aizqo4blcv.jpg</v>
       </c>
       <c r="D131" t="str">
         <v>是</v>
@@ -8092,7 +8092,7 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>四川成都</v>
+        <v>山东淄博</v>
       </c>
       <c r="G131" t="str">
         <v/>
@@ -8139,10 +8139,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B132" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C132" t="str">
-        <v>assets/1787318867999-3gxdddp72x.jpg</v>
+        <v>assets/1787319162970-cc2v8ovnni.jpg</v>
       </c>
       <c r="D132" t="str">
         <v>是</v>
@@ -8151,7 +8151,7 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>广东广州</v>
+        <v>韩国</v>
       </c>
       <c r="G132" t="str">
         <v/>
@@ -8195,13 +8195,13 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>银虎斑</v>
+        <v>棕虎补丁</v>
       </c>
       <c r="B133" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C133" t="str">
-        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
+        <v>assets/1787319098214-8pwa9yx2wc.jpg</v>
       </c>
       <c r="D133" t="str">
         <v>是</v>
@@ -8210,7 +8210,7 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>黑龙江鹤岗</v>
+        <v>四川成都</v>
       </c>
       <c r="G133" t="str">
         <v/>
@@ -8254,13 +8254,13 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B134" t="str">
         <v>弟弟</v>
       </c>
       <c r="C134" t="str">
-        <v>assets/1787318530612-779fbkfcoi.jpg</v>
+        <v>assets/1787318867999-3gxdddp72x.jpg</v>
       </c>
       <c r="D134" t="str">
         <v>是</v>
@@ -8269,7 +8269,7 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>天津</v>
+        <v>广东广州</v>
       </c>
       <c r="G134" t="str">
         <v/>
@@ -8319,7 +8319,7 @@
         <v>弟弟</v>
       </c>
       <c r="C135" t="str">
-        <v>assets/1787318365475-sj87wtsai3.jpg</v>
+        <v>assets/1787318609722-0ojb3aikwi.jpg</v>
       </c>
       <c r="D135" t="str">
         <v>是</v>
@@ -8328,7 +8328,7 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>山西朔州</v>
+        <v>黑龙江鹤岗</v>
       </c>
       <c r="G135" t="str">
         <v/>
@@ -8358,7 +8358,7 @@
         <v/>
       </c>
       <c r="P135" t="str">
-        <v>已接猫</v>
+        <v/>
       </c>
       <c r="Q135" t="str">
         <v/>
@@ -8372,13 +8372,13 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B136" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C136" t="str">
-        <v>assets/1787318326155-ia4noopjhq.jpg</v>
+        <v>assets/1787318530612-779fbkfcoi.jpg</v>
       </c>
       <c r="D136" t="str">
         <v>是</v>
@@ -8387,7 +8387,7 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>贵州</v>
+        <v>天津</v>
       </c>
       <c r="G136" t="str">
         <v/>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B137" t="str">
         <v>弟弟</v>
       </c>
       <c r="C137" t="str">
-        <v>assets/1787304479674-w0trechn4p.jpg</v>
+        <v>assets/1787318365475-sj87wtsai3.jpg</v>
       </c>
       <c r="D137" t="str">
         <v>是</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F137" t="str">
-        <v>北京</v>
+        <v>山西朔州</v>
       </c>
       <c r="G137" t="str">
         <v/>
@@ -8476,7 +8476,7 @@
         <v/>
       </c>
       <c r="P137" t="str">
-        <v/>
+        <v>已接猫</v>
       </c>
       <c r="Q137" t="str">
         <v/>
@@ -8485,27 +8485,27 @@
         <v/>
       </c>
       <c r="S137" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>纯黑色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B138" t="str">
         <v>妹妹</v>
       </c>
       <c r="C138" t="str">
-        <v>assets/1787283819124-4v7d1w01la.jpg</v>
+        <v>assets/1787318326155-ia4noopjhq.jpg</v>
       </c>
       <c r="D138" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-04-10</v>
+        <v/>
       </c>
       <c r="F138" t="str">
-        <v/>
+        <v>贵州</v>
       </c>
       <c r="G138" t="str">
         <v/>
@@ -8544,27 +8544,27 @@
         <v/>
       </c>
       <c r="S138" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>阴影色NS12</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B139" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C139" t="str">
-        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
+        <v>assets/1787304479674-w0trechn4p.jpg</v>
       </c>
       <c r="D139" t="str">
         <v>是</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F139" t="str">
-        <v>西安</v>
+        <v>北京</v>
       </c>
       <c r="G139" t="str">
         <v/>
@@ -8608,22 +8608,22 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>阴影色NS11</v>
+        <v>纯黑色</v>
       </c>
       <c r="B140" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C140" t="str">
-        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
+        <v>assets/1787283819124-4v7d1w01la.jpg</v>
       </c>
       <c r="D140" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-06-15</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F140" t="str">
-        <v>重庆</v>
+        <v/>
       </c>
       <c r="G140" t="str">
         <v/>
@@ -8667,22 +8667,22 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色NS12</v>
       </c>
       <c r="B141" t="str">
         <v>妹妹</v>
       </c>
       <c r="C141" t="str">
-        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
+        <v>assets/1787283212708-jdnyi6ecci.jpg</v>
       </c>
       <c r="D141" t="str">
         <v>是</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-03-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F141" t="str">
-        <v>中国澳门</v>
+        <v>西安</v>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -8726,22 +8726,22 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>棕虎斑</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B142" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C142" t="str">
-        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
+        <v>assets/1787283153501-s2tjg9spwu.jpg</v>
       </c>
       <c r="D142" t="str">
         <v>是</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F142" t="str">
-        <v>深圳</v>
+        <v>重庆</v>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -8785,22 +8785,22 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>棕虎斑</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B143" t="str">
         <v>妹妹</v>
       </c>
       <c r="C143" t="str">
-        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
+        <v>assets/1787283092677-i4d8tyrjtf.jpg</v>
       </c>
       <c r="D143" t="str">
         <v>是</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-06-06</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F143" t="str">
-        <v>浙江温州</v>
+        <v>中国澳门</v>
       </c>
       <c r="G143" t="str">
         <v/>
@@ -8850,16 +8850,16 @@
         <v>妹妹</v>
       </c>
       <c r="C144" t="str">
-        <v>assets/1787282942262-syr48fym6c.jpg</v>
+        <v>assets/1787283031104-bpyq9wy2tl.jpg</v>
       </c>
       <c r="D144" t="str">
         <v>是</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F144" t="str">
-        <v>安徽合肥</v>
+        <v>深圳</v>
       </c>
       <c r="G144" t="str">
         <v/>
@@ -8906,10 +8906,10 @@
         <v>棕虎斑</v>
       </c>
       <c r="B145" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C145" t="str">
-        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
+        <v>assets/1787282991501-2fjfws0rqw.jpg</v>
       </c>
       <c r="D145" t="str">
         <v>是</v>
@@ -8918,7 +8918,7 @@
         <v>2026-06-06</v>
       </c>
       <c r="F145" t="str">
-        <v>北京</v>
+        <v>浙江温州</v>
       </c>
       <c r="G145" t="str">
         <v/>
@@ -8968,16 +8968,16 @@
         <v>妹妹</v>
       </c>
       <c r="C146" t="str">
-        <v>assets/1787282703381-2uakw592b4.jpg</v>
+        <v>assets/1787282942262-syr48fym6c.jpg</v>
       </c>
       <c r="D146" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F146" t="str">
-        <v/>
+        <v>安徽合肥</v>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -9021,13 +9021,13 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B147" t="str">
         <v>弟弟</v>
       </c>
       <c r="C147" t="str">
-        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
+        <v>assets/1787282819855-7vhx3m0v40.jpg</v>
       </c>
       <c r="D147" t="str">
         <v>是</v>
@@ -9036,7 +9036,7 @@
         <v>2026-06-06</v>
       </c>
       <c r="F147" t="str">
-        <v>河北石家庄</v>
+        <v>北京</v>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -9080,22 +9080,22 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>烟灰色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B148" t="str">
         <v>妹妹</v>
       </c>
       <c r="C148" t="str">
-        <v>assets/1787282617957-svcoyyznpg.jpg</v>
+        <v>assets/1787282703381-2uakw592b4.jpg</v>
       </c>
       <c r="D148" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E148" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="F148" t="str">
-        <v>浙江宁波</v>
+        <v/>
       </c>
       <c r="G148" t="str">
         <v/>
@@ -9145,7 +9145,7 @@
         <v>弟弟</v>
       </c>
       <c r="C149" t="str">
-        <v>assets/1787282419632-78nixqjzua.jpg</v>
+        <v>assets/1787282649397-9hc31ncrpc.jpg</v>
       </c>
       <c r="D149" t="str">
         <v>是</v>
@@ -9154,7 +9154,7 @@
         <v>2026-06-06</v>
       </c>
       <c r="F149" t="str">
-        <v>上海</v>
+        <v>河北石家庄</v>
       </c>
       <c r="G149" t="str">
         <v/>
@@ -9198,22 +9198,22 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>纯黑色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B150" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C150" t="str">
-        <v>assets/1790733778469-jt9fswxe9w.jpg</v>
+        <v>assets/1787282617957-svcoyyznpg.jpg</v>
       </c>
       <c r="D150" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-04-17</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F150" t="str">
-        <v/>
+        <v>浙江宁波</v>
       </c>
       <c r="G150" t="str">
         <v/>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>银虎斑</v>
+        <v>烟灰色</v>
       </c>
       <c r="B151" t="str">
         <v>弟弟</v>
       </c>
       <c r="C151" t="str">
-        <v>assets/1790734215453-0zvw0v9uja.jpg</v>
+        <v>assets/1787282419632-78nixqjzua.jpg</v>
       </c>
       <c r="D151" t="str">
         <v>是</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F151" t="str">
-        <v>北京</v>
+        <v>上海</v>
       </c>
       <c r="G151" t="str">
         <v/>
@@ -9316,22 +9316,22 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>阴影色NS11</v>
+        <v>纯黑色</v>
       </c>
       <c r="B152" t="str">
         <v>弟弟</v>
       </c>
       <c r="C152" t="str">
-        <v>assets/1787280590041-vzcwebdok1.jpg</v>
+        <v>assets/1790733778469-jt9fswxe9w.jpg</v>
       </c>
       <c r="D152" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-05-28</v>
+        <v>2026-04-17</v>
       </c>
       <c r="F152" t="str">
-        <v>安徽芜湖</v>
+        <v/>
       </c>
       <c r="G152" t="str">
         <v/>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>浅色银虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B153" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C153" t="str">
-        <v>assets/1787281786169-9ia0h837ct.jpg</v>
+        <v>assets/1790734215453-0zvw0v9uja.jpg</v>
       </c>
       <c r="D153" t="str">
         <v>是</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-06-15</v>
+        <v>2026-06-10</v>
       </c>
       <c r="F153" t="str">
-        <v>香港</v>
+        <v>北京</v>
       </c>
       <c r="G153" t="str">
         <v/>
@@ -9434,22 +9434,22 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>浅烟灰色</v>
+        <v>阴影色NS11</v>
       </c>
       <c r="B154" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C154" t="str">
-        <v>assets/1785843720843-63qz159daui.jpg</v>
+        <v>assets/1787280590041-vzcwebdok1.jpg</v>
       </c>
       <c r="D154" t="str">
         <v>是</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-03-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F154" t="str">
-        <v>四川成都</v>
+        <v>安徽芜湖</v>
       </c>
       <c r="G154" t="str">
         <v/>
@@ -9493,22 +9493,22 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>凯米尔色</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B155" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C155" t="str">
-        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
+        <v>assets/1787281786169-9ia0h837ct.jpg</v>
       </c>
       <c r="D155" t="str">
         <v>是</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-02-14</v>
+        <v>2026-06-15</v>
       </c>
       <c r="F155" t="str">
-        <v>上海浦东</v>
+        <v>香港</v>
       </c>
       <c r="G155" t="str">
         <v/>
@@ -9552,22 +9552,22 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>银虎斑补丁</v>
+        <v>浅烟灰色</v>
       </c>
       <c r="B156" t="str">
         <v>妹妹</v>
       </c>
       <c r="C156" t="str">
-        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
+        <v>assets/1785843720843-63qz159daui.jpg</v>
       </c>
       <c r="D156" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-04-09</v>
+        <v>2026-03-21</v>
       </c>
       <c r="F156" t="str">
-        <v/>
+        <v>四川成都</v>
       </c>
       <c r="G156" t="str">
         <v/>
@@ -9611,22 +9611,22 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>烟灰色</v>
+        <v>凯米尔色</v>
       </c>
       <c r="B157" t="str">
         <v>弟弟</v>
       </c>
       <c r="C157" t="str">
-        <v>assets/1785843953805-mxl3x1982io.jpg</v>
+        <v>assets/1787301984056-iu6afro5z5.jpg, assets/1785843763310-elg05ur61ri.jpg</v>
       </c>
       <c r="D157" t="str">
         <v>是</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-05-18</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F157" t="str">
-        <v>北京</v>
+        <v>上海浦东</v>
       </c>
       <c r="G157" t="str">
         <v/>
@@ -9670,19 +9670,19 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>棕虎斑玳瑁</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B158" t="str">
         <v>妹妹</v>
       </c>
       <c r="C158" t="str">
-        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
+        <v>assets/1785843820715-9kz7gy4mbr7.jpg</v>
       </c>
       <c r="D158" t="str">
         <v>否</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-02-14</v>
+        <v>2026-04-09</v>
       </c>
       <c r="F158" t="str">
         <v/>
@@ -9729,22 +9729,22 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>银虎斑补丁</v>
+        <v>烟灰色</v>
       </c>
       <c r="B159" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C159" t="str">
-        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
+        <v>assets/1785843953805-mxl3x1982io.jpg</v>
       </c>
       <c r="D159" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F159" t="str">
-        <v/>
+        <v>北京</v>
       </c>
       <c r="G159" t="str">
         <v/>
@@ -9788,22 +9788,22 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑玳瑁</v>
       </c>
       <c r="B160" t="str">
         <v>妹妹</v>
       </c>
       <c r="C160" t="str">
-        <v>assets/1785838787730-s5f333sc3u.jpg</v>
+        <v>assets/1785844013835-ek4xpcje7kh.jpg</v>
       </c>
       <c r="D160" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-06-05</v>
+        <v>2026-02-14</v>
       </c>
       <c r="F160" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G160" t="str">
         <v/>
@@ -9847,22 +9847,22 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>银虎斑</v>
+        <v>银虎斑补丁</v>
       </c>
       <c r="B161" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C161" t="str">
-        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
+        <v>assets/1785844434338-ek5zbdgdcne.jpg</v>
       </c>
       <c r="D161" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-24</v>
       </c>
       <c r="F161" t="str">
-        <v>湖北恩施</v>
+        <v/>
       </c>
       <c r="G161" t="str">
         <v/>
@@ -9909,19 +9909,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B162" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C162" t="str">
-        <v>assets/1785842429109-porc98rel5.jpg</v>
+        <v>assets/1785838787730-s5f333sc3u.jpg</v>
       </c>
       <c r="D162" t="str">
         <v>是</v>
       </c>
       <c r="E162" t="str">
-        <v>2025-11-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F162" t="str">
-        <v>韩国</v>
+        <v>湖北恩施</v>
       </c>
       <c r="G162" t="str">
         <v/>
@@ -9968,19 +9968,19 @@
         <v>银虎斑</v>
       </c>
       <c r="B163" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C163" t="str">
-        <v>assets/1785842594141-fcglbzjp509.jpg</v>
+        <v>assets/1785842296661-6qw3zs3as8h.jpg</v>
       </c>
       <c r="D163" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-05-18</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F163" t="str">
-        <v/>
+        <v>湖北恩施</v>
       </c>
       <c r="G163" t="str">
         <v/>
@@ -10024,22 +10024,22 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B164" t="str">
         <v>弟弟</v>
       </c>
       <c r="C164" t="str">
-        <v>assets/1785842639100-82k775dhwiv.jpg</v>
+        <v>assets/1785842429109-porc98rel5.jpg</v>
       </c>
       <c r="D164" t="str">
         <v>是</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-05-28</v>
+        <v>2025-11-05</v>
       </c>
       <c r="F164" t="str">
-        <v>四川自贡</v>
+        <v>韩国</v>
       </c>
       <c r="G164" t="str">
         <v/>
@@ -10083,22 +10083,22 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B165" t="str">
         <v>妹妹</v>
       </c>
       <c r="C165" t="str">
-        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
+        <v>assets/1785842594141-fcglbzjp509.jpg</v>
       </c>
       <c r="D165" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-18</v>
       </c>
       <c r="F165" t="str">
-        <v>深圳</v>
+        <v/>
       </c>
       <c r="G165" t="str">
         <v/>
@@ -10142,22 +10142,22 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>纯黑色</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B166" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C166" t="str">
-        <v>assets/1790733648123-636cut584p.jpg</v>
+        <v>assets/1785842639100-82k775dhwiv.jpg</v>
       </c>
       <c r="D166" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-04-10</v>
+        <v>2026-05-28</v>
       </c>
       <c r="F166" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G166" t="str">
         <v/>
@@ -10201,22 +10201,22 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B167" t="str">
         <v>妹妹</v>
       </c>
       <c r="C167" t="str">
-        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
+        <v>assets/1785842684502-mnhr0r96eee.jpg</v>
       </c>
       <c r="D167" t="str">
         <v>是</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="F167" t="str">
-        <v>韩国</v>
+        <v>深圳</v>
       </c>
       <c r="G167" t="str">
         <v/>
@@ -10260,22 +10260,22 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>浅色银虎斑</v>
+        <v>纯黑色</v>
       </c>
       <c r="B168" t="str">
         <v>妹妹</v>
       </c>
       <c r="C168" t="str">
-        <v>assets/1785842950972-a88lbrskpc.jpg</v>
+        <v>assets/1790733648123-636cut584p.jpg</v>
       </c>
       <c r="D168" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-06-05</v>
+        <v>2026-04-10</v>
       </c>
       <c r="F168" t="str">
-        <v>河北邢台</v>
+        <v/>
       </c>
       <c r="G168" t="str">
         <v/>
@@ -10319,22 +10319,22 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B169" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C169" t="str">
-        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
+        <v>assets/1785842817046-6keqv4rw4yf.jpg</v>
       </c>
       <c r="D169" t="str">
         <v>是</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-06-05</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F169" t="str">
-        <v>四川自贡</v>
+        <v>韩国</v>
       </c>
       <c r="G169" t="str">
         <v/>
@@ -10378,22 +10378,22 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>棕虎斑补丁</v>
+        <v>浅色银虎斑</v>
       </c>
       <c r="B170" t="str">
         <v>妹妹</v>
       </c>
       <c r="C170" t="str">
-        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
+        <v>assets/1785842950972-a88lbrskpc.jpg</v>
       </c>
       <c r="D170" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-03-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F170" t="str">
-        <v/>
+        <v>河北邢台</v>
       </c>
       <c r="G170" t="str">
         <v/>
@@ -10437,22 +10437,22 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>蓝虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B171" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C171" t="str">
-        <v>assets/1785843497557-st27fk8drqi.jpg</v>
+        <v>assets/1785843011477-n3l1wi6ech.jpg</v>
       </c>
       <c r="D171" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-04-05</v>
+        <v>2026-06-05</v>
       </c>
       <c r="F171" t="str">
-        <v/>
+        <v>四川自贡</v>
       </c>
       <c r="G171" t="str">
         <v/>
@@ -10496,19 +10496,19 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑补丁</v>
       </c>
       <c r="B172" t="str">
         <v>妹妹</v>
       </c>
       <c r="C172" t="str">
-        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
+        <v>assets/1785842523893-7nwnnhwi4ns.jpg</v>
       </c>
       <c r="D172" t="str">
         <v>否</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-04-17</v>
+        <v>2026-03-05</v>
       </c>
       <c r="F172" t="str">
         <v/>
@@ -10555,19 +10555,19 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>银虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B173" t="str">
         <v>妹妹</v>
       </c>
       <c r="C173" t="str">
-        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
+        <v>assets/1785843497557-st27fk8drqi.jpg</v>
       </c>
       <c r="D173" t="str">
         <v>否</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-04-30</v>
+        <v>2026-04-05</v>
       </c>
       <c r="F173" t="str">
         <v/>
@@ -10614,52 +10614,52 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>蓝虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B174" t="str">
         <v>妹妹</v>
       </c>
       <c r="C174" t="str">
-        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
+        <v>assets/1785843621923-ylhakbtw13i.jpg</v>
       </c>
       <c r="D174" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-02-20</v>
+        <v>2026-04-17</v>
       </c>
       <c r="F174" t="str">
-        <v>荷兰</v>
+        <v/>
       </c>
       <c r="G174" t="str">
-        <v>阿泽</v>
+        <v/>
       </c>
       <c r="H174" t="str">
-        <v>小辫子</v>
+        <v/>
       </c>
       <c r="I174" t="str">
-        <v>驺驺</v>
+        <v/>
       </c>
       <c r="J174" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="K174" t="str">
         <v/>
       </c>
       <c r="L174" t="str">
-        <v>2026-07-02</v>
+        <v/>
       </c>
       <c r="M174" t="str">
-        <v>2026-08-03</v>
+        <v/>
       </c>
       <c r="N174" t="str">
-        <v>2026-11-04</v>
+        <v/>
       </c>
       <c r="O174" t="str">
-        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
+        <v/>
       </c>
       <c r="P174" t="str">
-        <v>已付定金</v>
+        <v/>
       </c>
       <c r="Q174" t="str">
         <v/>
@@ -10668,27 +10668,27 @@
         <v/>
       </c>
       <c r="S174" t="str">
-        <v>否</v>
+        <v/>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>红虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B175" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C175" t="str">
-        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
+        <v>assets/1785843663884-sfxvpmiet7.jpg</v>
       </c>
       <c r="D175" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="E175" t="str">
-        <v/>
+        <v>2026-04-30</v>
       </c>
       <c r="F175" t="str">
-        <v>广东广州</v>
+        <v/>
       </c>
       <c r="G175" t="str">
         <v/>
@@ -10732,52 +10732,52 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>红虎斑</v>
+        <v>蓝虎斑</v>
       </c>
       <c r="B176" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C176" t="str">
-        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
+        <v>assets/1785852601940-o236xtv7yx.jpeg</v>
       </c>
       <c r="D176" t="str">
         <v>是</v>
       </c>
       <c r="E176" t="str">
-        <v/>
+        <v>2026-02-20</v>
       </c>
       <c r="F176" t="str">
-        <v>广东广州</v>
+        <v>荷兰</v>
       </c>
       <c r="G176" t="str">
-        <v/>
+        <v>阿泽</v>
       </c>
       <c r="H176" t="str">
-        <v/>
+        <v>小辫子</v>
       </c>
       <c r="I176" t="str">
-        <v/>
+        <v>驺驺</v>
       </c>
       <c r="J176" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="K176" t="str">
         <v/>
       </c>
       <c r="L176" t="str">
-        <v/>
+        <v>2026-07-02</v>
       </c>
       <c r="M176" t="str">
-        <v/>
+        <v>2026-08-03</v>
       </c>
       <c r="N176" t="str">
-        <v/>
+        <v>2026-11-04</v>
       </c>
       <c r="O176" t="str">
-        <v/>
+        <v>2026-08-03 · 血清检测,2026-07-02 · 打疫苗 · assets/diary/zouzou-depart.jpg,2026-07-30 · 6.2斤 · 五个月10天了 · assets/feedback/zouzou-1.jpg</v>
       </c>
       <c r="P176" t="str">
-        <v/>
+        <v>已付定金</v>
       </c>
       <c r="Q176" t="str">
         <v/>
@@ -10786,18 +10786,18 @@
         <v/>
       </c>
       <c r="S176" t="str">
-        <v/>
+        <v>否</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B177" t="str">
         <v>弟弟</v>
       </c>
       <c r="C177" t="str">
-        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
+        <v>assets/1785853950207-cedor66ou2q.jpeg</v>
       </c>
       <c r="D177" t="str">
         <v>是</v>
@@ -10806,7 +10806,7 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>山西朔州</v>
+        <v>广东广州</v>
       </c>
       <c r="G177" t="str">
         <v/>
@@ -10850,13 +10850,13 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>银虎斑</v>
+        <v>红虎斑</v>
       </c>
       <c r="B178" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C178" t="str">
-        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
+        <v>assets/1785854129383-c8qkvl537x.jpeg</v>
       </c>
       <c r="D178" t="str">
         <v>是</v>
@@ -10865,7 +10865,7 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>浙江宁波</v>
+        <v>广东广州</v>
       </c>
       <c r="G178" t="str">
         <v/>
@@ -10915,7 +10915,7 @@
         <v>弟弟</v>
       </c>
       <c r="C179" t="str">
-        <v>assets/1785854260793-steez4s972l.jpeg</v>
+        <v>assets/1785854166720-48r17hry9cd.jpeg</v>
       </c>
       <c r="D179" t="str">
         <v>是</v>
@@ -10924,7 +10924,7 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>陕西西安</v>
+        <v>山西朔州</v>
       </c>
       <c r="G179" t="str">
         <v/>
@@ -10971,10 +10971,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B180" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C180" t="str">
-        <v>assets/1785854319988-cohio08aod5.jpeg</v>
+        <v>assets/1785854224521-2cpg6xipfn6.jpeg</v>
       </c>
       <c r="D180" t="str">
         <v>是</v>
@@ -10983,7 +10983,7 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>黑龙江漠河</v>
+        <v>浙江宁波</v>
       </c>
       <c r="G180" t="str">
         <v/>
@@ -11027,13 +11027,13 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B181" t="str">
         <v>弟弟</v>
       </c>
       <c r="C181" t="str">
-        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
+        <v>assets/1785854260793-steez4s972l.jpeg</v>
       </c>
       <c r="D181" t="str">
         <v>是</v>
@@ -11042,7 +11042,7 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>日本</v>
+        <v>陕西西安</v>
       </c>
       <c r="G181" t="str">
         <v/>
@@ -11089,10 +11089,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B182" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C182" t="str">
-        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
+        <v>assets/1785854319988-cohio08aod5.jpeg</v>
       </c>
       <c r="D182" t="str">
         <v>是</v>
@@ -11101,7 +11101,7 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>浙江杭州</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G182" t="str">
         <v/>
@@ -11145,13 +11145,13 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B183" t="str">
-        <v>妹妹</v>
+        <v>弟弟</v>
       </c>
       <c r="C183" t="str">
-        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
+        <v>assets/1785854520974-96b8b1ekqd9.jpeg</v>
       </c>
       <c r="D183" t="str">
         <v>是</v>
@@ -11160,7 +11160,7 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>贵州安顺</v>
+        <v>日本</v>
       </c>
       <c r="G183" t="str">
         <v/>
@@ -11210,7 +11210,7 @@
         <v>妹妹</v>
       </c>
       <c r="C184" t="str">
-        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
+        <v>assets/1785854664100-haqoiu1h7hj.jpeg</v>
       </c>
       <c r="D184" t="str">
         <v>是</v>
@@ -11219,7 +11219,7 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>山东青岛</v>
+        <v>浙江杭州</v>
       </c>
       <c r="G184" t="str">
         <v/>
@@ -11266,10 +11266,10 @@
         <v>银虎斑</v>
       </c>
       <c r="B185" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C185" t="str">
-        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
+        <v>assets/1785854690732-orrs40sx9rs.jpeg</v>
       </c>
       <c r="D185" t="str">
         <v>是</v>
@@ -11278,7 +11278,7 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>黑龙江漠河</v>
+        <v>贵州安顺</v>
       </c>
       <c r="G185" t="str">
         <v/>
@@ -11322,13 +11322,13 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>纯蓝色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B186" t="str">
-        <v>弟弟</v>
+        <v>妹妹</v>
       </c>
       <c r="C186" t="str">
-        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
+        <v>assets/1785854734122-wcpmib4m7.jpeg</v>
       </c>
       <c r="D186" t="str">
         <v>是</v>
@@ -11337,7 +11337,7 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>河南鹤壁</v>
+        <v>山东青岛</v>
       </c>
       <c r="G186" t="str">
         <v/>
@@ -11387,7 +11387,7 @@
         <v>弟弟</v>
       </c>
       <c r="C187" t="str">
-        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
+        <v>assets/1785854758707-1kxdkfvs6jc.jpeg</v>
       </c>
       <c r="D187" t="str">
         <v>是</v>
@@ -11396,7 +11396,7 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>陕西西安</v>
+        <v>黑龙江漠河</v>
       </c>
       <c r="G187" t="str">
         <v/>
@@ -11440,13 +11440,13 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>棕虎斑</v>
+        <v>纯蓝色</v>
       </c>
       <c r="B188" t="str">
         <v>弟弟</v>
       </c>
       <c r="C188" t="str">
-        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
+        <v>assets/1785854784780-3g0u60pdo93.jpeg</v>
       </c>
       <c r="D188" t="str">
         <v>是</v>
@@ -11455,7 +11455,7 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>四川成都</v>
+        <v>河南鹤壁</v>
       </c>
       <c r="G188" t="str">
         <v/>
@@ -11499,22 +11499,22 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>烟灰色</v>
+        <v>银虎斑</v>
       </c>
       <c r="B189" t="str">
         <v>弟弟</v>
       </c>
       <c r="C189" t="str">
-        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
+        <v>assets/1785854813179-8oyxr0h2bbu.jpeg</v>
       </c>
       <c r="D189" t="str">
         <v>是</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-05-18</v>
+        <v/>
       </c>
       <c r="F189" t="str">
-        <v>四川成都</v>
+        <v>陕西西安</v>
       </c>
       <c r="G189" t="str">
         <v/>
@@ -11558,13 +11558,13 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>银虎斑</v>
+        <v>棕虎斑</v>
       </c>
       <c r="B190" t="str">
         <v>弟弟</v>
       </c>
       <c r="C190" t="str">
-        <v>assets/1785854997023-mawkallt2a.jpeg</v>
+        <v>assets/1785854838933-uq6amircyzd.jpeg</v>
       </c>
       <c r="D190" t="str">
         <v>是</v>
@@ -11573,7 +11573,7 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>新加坡</v>
+        <v>四川成都</v>
       </c>
       <c r="G190" t="str">
         <v/>
@@ -11617,22 +11617,22 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>凯米尔色</v>
+        <v>烟灰色</v>
       </c>
       <c r="B191" t="str">
         <v>弟弟</v>
       </c>
       <c r="C191" t="str">
-        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+        <v>assets/1785854869973-za3p6wikqpo.jpeg</v>
       </c>
       <c r="D191" t="str">
         <v>是</v>
       </c>
       <c r="E191" t="str">
-        <v/>
+        <v>2026-05-18</v>
       </c>
       <c r="F191" t="str">
-        <v>上海浦东</v>
+        <v>四川成都</v>
       </c>
       <c r="G191" t="str">
         <v/>
@@ -11676,22 +11676,22 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>棕虎斑</v>
+        <v>银虎斑</v>
       </c>
       <c r="B192" t="str">
         <v>弟弟</v>
       </c>
       <c r="C192" t="str">
-        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+        <v>assets/1785854997023-mawkallt2a.jpeg</v>
       </c>
       <c r="D192" t="str">
         <v>是</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-06-06</v>
+        <v/>
       </c>
       <c r="F192" t="str">
-        <v>浙江温州</v>
+        <v>新加坡</v>
       </c>
       <c r="G192" t="str">
         <v/>
@@ -11735,66 +11735,184 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
+        <v>凯米尔色</v>
+      </c>
+      <c r="B193" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C193" t="str">
+        <v>assets/1785855043327-wdc5pxwm34k.jpeg</v>
+      </c>
+      <c r="D193" t="str">
+        <v>是</v>
+      </c>
+      <c r="E193" t="str">
+        <v/>
+      </c>
+      <c r="F193" t="str">
+        <v>上海浦东</v>
+      </c>
+      <c r="G193" t="str">
+        <v/>
+      </c>
+      <c r="H193" t="str">
+        <v/>
+      </c>
+      <c r="I193" t="str">
+        <v/>
+      </c>
+      <c r="J193" t="str">
+        <v/>
+      </c>
+      <c r="K193" t="str">
+        <v/>
+      </c>
+      <c r="L193" t="str">
+        <v/>
+      </c>
+      <c r="M193" t="str">
+        <v/>
+      </c>
+      <c r="N193" t="str">
+        <v/>
+      </c>
+      <c r="O193" t="str">
+        <v/>
+      </c>
+      <c r="P193" t="str">
+        <v/>
+      </c>
+      <c r="Q193" t="str">
+        <v/>
+      </c>
+      <c r="R193" t="str">
+        <v/>
+      </c>
+      <c r="S193" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
         <v>棕虎斑</v>
       </c>
-      <c r="B193" t="str">
+      <c r="B194" t="str">
+        <v>弟弟</v>
+      </c>
+      <c r="C194" t="str">
+        <v>assets/1785912551260-jplefm937nk.jpeg, assets/videos/02.mp4</v>
+      </c>
+      <c r="D194" t="str">
+        <v>是</v>
+      </c>
+      <c r="E194" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F194" t="str">
+        <v>浙江温州</v>
+      </c>
+      <c r="G194" t="str">
+        <v/>
+      </c>
+      <c r="H194" t="str">
+        <v/>
+      </c>
+      <c r="I194" t="str">
+        <v/>
+      </c>
+      <c r="J194" t="str">
+        <v/>
+      </c>
+      <c r="K194" t="str">
+        <v/>
+      </c>
+      <c r="L194" t="str">
+        <v/>
+      </c>
+      <c r="M194" t="str">
+        <v/>
+      </c>
+      <c r="N194" t="str">
+        <v/>
+      </c>
+      <c r="O194" t="str">
+        <v/>
+      </c>
+      <c r="P194" t="str">
+        <v/>
+      </c>
+      <c r="Q194" t="str">
+        <v/>
+      </c>
+      <c r="R194" t="str">
+        <v/>
+      </c>
+      <c r="S194" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>棕虎斑</v>
+      </c>
+      <c r="B195" t="str">
         <v>妹妹</v>
       </c>
-      <c r="C193" t="str">
+      <c r="C195" t="str">
         <v>assets/1785912694000-m20f5kvvrr.jpeg</v>
       </c>
-      <c r="D193" t="str">
-        <v>是</v>
-      </c>
-      <c r="E193" t="str">
+      <c r="D195" t="str">
+        <v>是</v>
+      </c>
+      <c r="E195" t="str">
         <v>2026-06-06</v>
       </c>
-      <c r="F193" t="str">
+      <c r="F195" t="str">
         <v>深圳</v>
       </c>
-      <c r="G193" t="str">
-        <v/>
-      </c>
-      <c r="H193" t="str">
-        <v/>
-      </c>
-      <c r="I193" t="str">
-        <v/>
-      </c>
-      <c r="J193" t="str">
-        <v/>
-      </c>
-      <c r="K193" t="str">
-        <v/>
-      </c>
-      <c r="L193" t="str">
-        <v/>
-      </c>
-      <c r="M193" t="str">
-        <v/>
-      </c>
-      <c r="N193" t="str">
-        <v/>
-      </c>
-      <c r="O193" t="str">
-        <v/>
-      </c>
-      <c r="P193" t="str">
-        <v/>
-      </c>
-      <c r="Q193" t="str">
-        <v/>
-      </c>
-      <c r="R193" t="str">
-        <v/>
-      </c>
-      <c r="S193" t="str">
+      <c r="G195" t="str">
+        <v/>
+      </c>
+      <c r="H195" t="str">
+        <v/>
+      </c>
+      <c r="I195" t="str">
+        <v/>
+      </c>
+      <c r="J195" t="str">
+        <v/>
+      </c>
+      <c r="K195" t="str">
+        <v/>
+      </c>
+      <c r="L195" t="str">
+        <v/>
+      </c>
+      <c r="M195" t="str">
+        <v/>
+      </c>
+      <c r="N195" t="str">
+        <v/>
+      </c>
+      <c r="O195" t="str">
+        <v/>
+      </c>
+      <c r="P195" t="str">
+        <v/>
+      </c>
+      <c r="Q195" t="str">
+        <v/>
+      </c>
+      <c r="R195" t="str">
+        <v/>
+      </c>
+      <c r="S195" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S193"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S195"/>
   </ignoredErrors>
 </worksheet>
 </file>
